--- a/workspaces/nasdaq_hourly_24hrs/treasury/tnx_ma_ratio_20.xlsx
+++ b/workspaces/nasdaq_hourly_24hrs/treasury/tnx_ma_ratio_20.xlsx
@@ -625,486 +625,486 @@
         <v>16</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>-3.648970421738184</v>
+        <v>-3.615960962337972</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>-3.983358279213867</v>
+        <v>-3.949943212867538</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>0.795548020583368</v>
+        <v>0.8306814201895136</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>-6.126483228134397</v>
+        <v>-6.090554643001397</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>-12.70632542363794</v>
+        <v>-12.64112056627233</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>-18.74085468389723</v>
+        <v>-18.67586029428402</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>-19.51535749124432</v>
+        <v>-19.44942855103064</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>-7.358037702713119</v>
+        <v>-7.291670576513198</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>-13.54056738972794</v>
+        <v>-13.47423996419435</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>-14.31493717284889</v>
+        <v>-14.24767324933735</v>
       </c>
       <c r="M6" s="4" t="n">
-        <v>-1.594505209472544</v>
+        <v>-1.527454587259349</v>
       </c>
       <c r="N6" s="4" t="n">
-        <v>-14.32815231643328</v>
+        <v>-14.26079219099792</v>
       </c>
       <c r="O6" s="4" t="n">
-        <v>-15.45308203537201</v>
+        <v>-15.38437616111161</v>
       </c>
       <c r="P6" s="4" t="n">
-        <v>-9.447149725915104</v>
+        <v>-9.378118390504696</v>
       </c>
       <c r="Q6" s="4" t="n">
-        <v>-10.10696880541808</v>
+        <v>-10.03712956851162</v>
       </c>
       <c r="R6" s="4" t="n">
-        <v>-9.51631950452083</v>
+        <v>-9.447124969330019</v>
       </c>
       <c r="S6" s="4" t="n">
-        <v>-22.12644273400235</v>
+        <v>-22.05707975961501</v>
       </c>
       <c r="T6" s="4" t="n">
-        <v>-9.76041937891452</v>
+        <v>-9.690857748665536</v>
       </c>
       <c r="U6" s="4" t="n">
-        <v>2.933551609506914</v>
+        <v>3.002930018205753</v>
       </c>
       <c r="V6" s="4" t="n">
-        <v>3.121099505936797</v>
+        <v>3.19030117313811</v>
       </c>
       <c r="W6" s="4" t="n">
-        <v>2.579323049819784</v>
+        <v>2.649198020584485</v>
       </c>
       <c r="X6" s="4" t="n">
-        <v>2.504221894247472</v>
+        <v>2.574226415431404</v>
       </c>
       <c r="Y6" s="4" t="n">
-        <v>2.779723094244865</v>
+        <v>2.84944795053498</v>
       </c>
       <c r="Z6" s="4" t="n">
-        <v>2.704678362571677</v>
+        <v>2.774532710278955</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>X ≈ -0.02059</t>
+          <t>X ≈ -0.02058</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>-3.648651574369218</v>
+        <v>-1.776630970591576</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>7.478787821167401</v>
+        <v>8.927324149752934</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>-5.414880578929505</v>
+        <v>-3.539670391358591</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>-2.303108283254787</v>
+        <v>-0.5680692023262921</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>-6.491301890099123</v>
+        <v>-4.584821464740095</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>-10.13282700071991</v>
+        <v>-8.084306995080681</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>0.5743991755642099</v>
+        <v>-1.485333105525633</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>-15.01268155994653</v>
+        <v>-16.50571789459047</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>-14.97556361169556</v>
+        <v>-16.46907581909801</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>-15.75037450858154</v>
+        <v>-13.55539715889715</v>
       </c>
       <c r="M7" s="4" t="n">
-        <v>-23.14389734138044</v>
+        <v>-20.66479600397564</v>
       </c>
       <c r="N7" s="4" t="n">
-        <v>-19.59674325901184</v>
+        <v>-17.25846290808551</v>
       </c>
       <c r="O7" s="4" t="n">
-        <v>-20.72327461623323</v>
+        <v>-18.38295965439533</v>
       </c>
       <c r="P7" s="4" t="n">
-        <v>-20.95028898844203</v>
+        <v>-18.60898257033779</v>
       </c>
       <c r="Q7" s="4" t="n">
-        <v>-17.77794507150168</v>
+        <v>-15.57719177582113</v>
       </c>
       <c r="R7" s="4" t="n">
-        <v>-17.18967788937569</v>
+        <v>-14.98892256049297</v>
       </c>
       <c r="S7" s="4" t="n">
-        <v>-17.32836241666342</v>
+        <v>-15.12675959826029</v>
       </c>
       <c r="T7" s="4" t="n">
-        <v>-17.43849793150923</v>
+        <v>-15.23607986772546</v>
       </c>
       <c r="U7" s="4" t="n">
-        <v>-13.38785389787984</v>
+        <v>-11.3272221740006</v>
       </c>
       <c r="V7" s="4" t="n">
-        <v>-17.04673781295888</v>
+        <v>-18.54261115099277</v>
       </c>
       <c r="W7" s="4" t="n">
-        <v>-21.43727047470605</v>
+        <v>-22.79062181536202</v>
       </c>
       <c r="X7" s="4" t="n">
-        <v>-25.36347335676273</v>
+        <v>-26.57475837311694</v>
       </c>
       <c r="Y7" s="4" t="n">
-        <v>-25.09643074133976</v>
+        <v>-22.60579687902953</v>
       </c>
       <c r="Z7" s="4" t="n">
-        <v>-21.33378317588757</v>
+        <v>-18.9847265489772</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>X ≈ -0.01899</t>
+          <t>X ≈ -0.01898</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>7.809475256408362</v>
+        <v>6.314767112448735</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>11.29839419986623</v>
+        <v>9.956478028830702</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>17.51505884176063</v>
+        <v>16.48018318889687</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>1.51983618672314</v>
+        <v>-0.1262811852932515</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>-6.490719664448299</v>
+        <v>-8.414001482012637</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>-10.1319678961532</v>
+        <v>-12.2090525549478</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>-18.5567944812511</v>
+        <v>-16.96028547341049</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>-18.83893312376054</v>
+        <v>-17.24159680969895</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>-22.63161118266886</v>
+        <v>-21.18697965788824</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>-23.40877313899437</v>
+        <v>-25.94585166638187</v>
       </c>
       <c r="M8" s="4" t="n">
-        <v>-19.31155743236465</v>
+        <v>-21.69643847343924</v>
       </c>
       <c r="N8" s="4" t="n">
-        <v>-19.5956148636342</v>
+        <v>-21.98086868510991</v>
       </c>
       <c r="O8" s="4" t="n">
-        <v>-9.222471868879104</v>
+        <v>-11.14708297003283</v>
       </c>
       <c r="P8" s="4" t="n">
-        <v>-1.777250774606486</v>
+        <v>-3.395382034041724</v>
       </c>
       <c r="Q8" s="4" t="n">
-        <v>-6.270440912470399</v>
+        <v>-8.041713339915319</v>
       </c>
       <c r="R8" s="4" t="n">
-        <v>-1.842014675055879</v>
+        <v>-3.46100903371368</v>
       </c>
       <c r="S8" s="4" t="n">
-        <v>-1.976080143986451</v>
+        <v>-3.595388337532469</v>
       </c>
       <c r="T8" s="4" t="n">
-        <v>-5.920699383817784</v>
+        <v>-7.693927167219762</v>
       </c>
       <c r="U8" s="4" t="n">
-        <v>-9.547259211878085</v>
+        <v>-11.47487084694864</v>
       </c>
       <c r="V8" s="4" t="n">
-        <v>-17.04641050765671</v>
+        <v>-15.28698087070352</v>
       </c>
       <c r="W8" s="4" t="n">
-        <v>-17.59433980117309</v>
+        <v>-15.83371737647918</v>
       </c>
       <c r="X8" s="4" t="n">
-        <v>-13.83183406369539</v>
+        <v>-11.91680742361215</v>
       </c>
       <c r="Y8" s="4" t="n">
-        <v>-17.40635855615092</v>
+        <v>-19.64363211266975</v>
       </c>
       <c r="Z8" s="4" t="n">
-        <v>-21.33378317588843</v>
+        <v>-23.72546728972053</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>X ≈ -0.01739</t>
+          <t>X ≈ -0.01738</t>
         </is>
       </c>
       <c r="B9" t="n">
         <v>52</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>-11.28589112058766</v>
+        <v>-11.25296343496465</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>-0.1634297191682847</v>
+        <v>-0.1299942940045256</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>-7.325276331252638</v>
+        <v>-7.290218655739316</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>-0.3915741412308478</v>
+        <v>-0.3556166395393419</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>-0.7545135936980856</v>
+        <v>-0.689249743650187</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>5.168242938929779</v>
+        <v>5.233372521890153</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>-1.337918309400699</v>
+        <v>-1.271899559835575</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>0.2987356135590957</v>
+        <v>0.3651260713496214</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>-7.315998728826955</v>
+        <v>-7.249660617105022</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>3.399894058628576</v>
+        <v>3.467229290544218</v>
       </c>
       <c r="M9" s="4" t="n">
-        <v>7.504859058120587</v>
+        <v>7.571937024705413</v>
       </c>
       <c r="N9" s="4" t="n">
-        <v>11.06083742560166</v>
+        <v>11.12829421157882</v>
       </c>
       <c r="O9" s="4" t="n">
-        <v>15.6929635696447</v>
+        <v>15.76178252843881</v>
       </c>
       <c r="P9" s="4" t="n">
-        <v>9.725536300660018</v>
+        <v>9.794626290592774</v>
       </c>
       <c r="Q9" s="4" t="n">
-        <v>12.90701952531182</v>
+        <v>12.97692453539225</v>
       </c>
       <c r="R9" s="4" t="n">
-        <v>7.749596271567846</v>
+        <v>7.818831981362791</v>
       </c>
       <c r="S9" s="4" t="n">
-        <v>5.699616150755261</v>
+        <v>5.769041219137677</v>
       </c>
       <c r="T9" s="4" t="n">
-        <v>9.435505428554819</v>
+        <v>9.505102154535223</v>
       </c>
       <c r="U9" s="4" t="n">
-        <v>7.733891204607637</v>
+        <v>7.803272832156786</v>
       </c>
       <c r="V9" s="4" t="n">
-        <v>4.081631726968624</v>
+        <v>4.15082981935182</v>
       </c>
       <c r="W9" s="4" t="n">
-        <v>1.618876962943894</v>
+        <v>1.688746861281963</v>
       </c>
       <c r="X9" s="4" t="n">
-        <v>-0.3784667308591807</v>
+        <v>-0.3084670873393875</v>
       </c>
       <c r="Y9" s="4" t="n">
-        <v>-0.1039236391921321</v>
+        <v>-0.03420123041784962</v>
       </c>
       <c r="Z9" s="4" t="n">
-        <v>-2.103013945119216</v>
+        <v>-2.033159597411938</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>X ≈ -0.01579</t>
+          <t>X ≈ -0.01578</t>
         </is>
       </c>
       <c r="B10" t="n">
         <v>59</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>-7.85307739961182</v>
+        <v>-7.820133880655717</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>-8.190870470674007</v>
+        <v>-8.157513805085252</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>-7.938838266062859</v>
+        <v>-7.903798172403889</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>-5.282254977881976</v>
+        <v>-5.246344875992911</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>-5.646654712167837</v>
+        <v>-5.581442482731127</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>-8.833688864505575</v>
+        <v>-8.768670748535087</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>-4.547239724543772</v>
+        <v>-4.481256130103468</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>-14.94338827141708</v>
+        <v>-14.87710732574375</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>-13.21889465130354</v>
+        <v>-13.15260638397154</v>
       </c>
       <c r="L10" s="4" t="n">
-        <v>-7.244337620405645</v>
+        <v>-7.1770715703516</v>
       </c>
       <c r="M10" s="4" t="n">
-        <v>-5.285685113845346</v>
+        <v>-5.21868108358634</v>
       </c>
       <c r="N10" s="4" t="n">
-        <v>-2.188729837271524</v>
+        <v>-2.121342401151537</v>
       </c>
       <c r="O10" s="4" t="n">
-        <v>-3.310407192213908</v>
+        <v>-3.241675927052434</v>
       </c>
       <c r="P10" s="4" t="n">
-        <v>4.915744742792263</v>
+        <v>4.984810208455499</v>
       </c>
       <c r="Q10" s="4" t="n">
-        <v>4.260298827680067</v>
+        <v>4.330168600410339</v>
       </c>
       <c r="R10" s="4" t="n">
-        <v>6.545983659987392</v>
+        <v>6.615210843760266</v>
       </c>
       <c r="S10" s="4" t="n">
-        <v>1.341210083833715</v>
+        <v>1.41061838058345</v>
       </c>
       <c r="T10" s="4" t="n">
-        <v>4.620077488358334</v>
+        <v>4.6896593365759</v>
       </c>
       <c r="U10" s="4" t="n">
-        <v>3.14492653307331</v>
+        <v>3.214296012333342</v>
       </c>
       <c r="V10" s="4" t="n">
-        <v>-3.4383360046211</v>
+        <v>-3.369152725695187</v>
       </c>
       <c r="W10" s="4" t="n">
-        <v>-3.98210072562236</v>
+        <v>-3.912239855167286</v>
       </c>
       <c r="X10" s="4" t="n">
-        <v>-7.446984081176332</v>
+        <v>-7.376991747418543</v>
       </c>
       <c r="Y10" s="4" t="n">
-        <v>-5.480312416600164</v>
+        <v>-5.41059297409452</v>
       </c>
       <c r="Z10" s="4" t="n">
-        <v>-5.558033501834068</v>
+        <v>-5.488179154126406</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>X ≈ -0.01419</t>
+          <t>X ≈ -0.01418</t>
         </is>
       </c>
       <c r="B11" t="n">
         <v>87</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>1.489319041332628</v>
+        <v>1.522333989012111</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>-3.410517906328259</v>
+        <v>-3.377135235959976</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>-1.415654694690332</v>
+        <v>-1.380574866615071</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>-6.693643392896362</v>
+        <v>-6.657760648706557</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>-1.346728607192929</v>
+        <v>-1.281505745389879</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>-3.447016119610282</v>
+        <v>-3.381981680350194</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>-1.930557516560619</v>
+        <v>-1.864575930498944</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>4.654047453269058</v>
+        <v>4.720434771279855</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>9.272989657055248</v>
+        <v>9.339396854752536</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>7.360322033186044</v>
+        <v>7.427655504960271</v>
       </c>
       <c r="M11" s="4" t="n">
-        <v>8.780027351385172</v>
+        <v>8.847092117233693</v>
       </c>
       <c r="N11" s="4" t="n">
-        <v>5.069451603407238</v>
+        <v>5.136861955390771</v>
       </c>
       <c r="O11" s="4" t="n">
-        <v>5.095582807630088</v>
+        <v>5.16433979058052</v>
       </c>
       <c r="P11" s="4" t="n">
-        <v>7.167534204905657</v>
+        <v>7.236600109106845</v>
       </c>
       <c r="Q11" s="4" t="n">
-        <v>5.366924945313166</v>
+        <v>5.436790395957537</v>
       </c>
       <c r="R11" s="4" t="n">
-        <v>4.815827772656881</v>
+        <v>4.885042258836862</v>
       </c>
       <c r="S11" s="4" t="n">
-        <v>4.684322654417372</v>
+        <v>4.753733385739636</v>
       </c>
       <c r="T11" s="4" t="n">
-        <v>1.139243426800142</v>
+        <v>1.208810760954115</v>
       </c>
       <c r="U11" s="4" t="n">
-        <v>3.650395566062279</v>
+        <v>3.719761155887213</v>
       </c>
       <c r="V11" s="4" t="n">
-        <v>3.838570139380124</v>
+        <v>3.907760788596761</v>
       </c>
       <c r="W11" s="4" t="n">
-        <v>3.297149672726711</v>
+        <v>3.367015973844275</v>
       </c>
       <c r="X11" s="4" t="n">
-        <v>3.222302598734039</v>
+        <v>3.292301160100386</v>
       </c>
       <c r="Y11" s="4" t="n">
-        <v>3.497946672437308</v>
+        <v>3.567668591244647</v>
       </c>
       <c r="Z11" s="4" t="n">
-        <v>5.721919741883703</v>
+        <v>5.791774089590724</v>
       </c>
     </row>
     <row r="12">
@@ -1117,76 +1117,76 @@
         <v>99</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>-2.140368658012889</v>
+        <v>-2.107406661709021</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>1.535162008169102</v>
+        <v>1.568573629114461</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>4.118793465581867</v>
+        <v>4.153907724451074</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>6.421673505772951</v>
+        <v>6.457651466434811</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>13.08596266209678</v>
+        <v>13.1512804159641</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>11.26818873898216</v>
+        <v>11.33331355226224</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>9.498884623046884</v>
+        <v>9.564927419426247</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>13.2444109245116</v>
+        <v>13.31084050940109</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>13.29039534866715</v>
+        <v>13.35681471902659</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>12.52376346618983</v>
+        <v>12.59111406428654</v>
       </c>
       <c r="M12" s="4" t="n">
-        <v>10.78914679847064</v>
+        <v>10.85621010712135</v>
       </c>
       <c r="N12" s="4" t="n">
-        <v>13.53277594487946</v>
+        <v>13.60021759077324</v>
       </c>
       <c r="O12" s="4" t="n">
-        <v>15.43575411177547</v>
+        <v>15.50454889620516</v>
       </c>
       <c r="P12" s="4" t="n">
-        <v>13.20628805592533</v>
+        <v>13.27537004431227</v>
       </c>
       <c r="Q12" s="4" t="n">
-        <v>12.55414135448436</v>
+        <v>12.624024911306</v>
       </c>
       <c r="R12" s="4" t="n">
-        <v>8.115074910988831</v>
+        <v>8.184291289345467</v>
       </c>
       <c r="S12" s="4" t="n">
-        <v>7.984841051074042</v>
+        <v>8.054253197346767</v>
       </c>
       <c r="T12" s="4" t="n">
-        <v>7.882700434474515</v>
+        <v>7.952277223238283</v>
       </c>
       <c r="U12" s="4" t="n">
-        <v>9.109300986087653</v>
+        <v>9.178672268612097</v>
       </c>
       <c r="V12" s="4" t="n">
-        <v>9.299383748591964</v>
+        <v>9.368578967586913</v>
       </c>
       <c r="W12" s="4" t="n">
-        <v>8.759913410855553</v>
+        <v>8.829782999464094</v>
       </c>
       <c r="X12" s="4" t="n">
-        <v>11.71523741777734</v>
+        <v>11.78524089460847</v>
       </c>
       <c r="Y12" s="4" t="n">
-        <v>15.02307948422729</v>
+        <v>15.09280525995</v>
       </c>
       <c r="Z12" s="4" t="n">
-        <v>10.91174906964404</v>
+        <v>10.98160341735109</v>
       </c>
     </row>
     <row r="13">
@@ -1199,978 +1199,978 @@
         <v>111</v>
       </c>
       <c r="C13" s="4" t="n">
-        <v>3.954422520118271</v>
+        <v>3.987427970357693</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>6.302428245436197</v>
+        <v>6.335872920808434</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>7.558533495268158</v>
+        <v>7.593668239783433</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>9.536292176715726</v>
+        <v>9.572288966875078</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>8.279733035505757</v>
+        <v>8.344988924563026</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>5.783175936612217</v>
+        <v>5.848234097116396</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>12.18164644348774</v>
+        <v>12.24769147136745</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>10.11725457881761</v>
+        <v>10.18364467231268</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>10.16247662020488</v>
+        <v>10.22885890975796</v>
       </c>
       <c r="L13" s="4" t="n">
-        <v>10.29178822037129</v>
+        <v>10.35910946421774</v>
       </c>
       <c r="M13" s="4" t="n">
-        <v>12.36190087238795</v>
+        <v>12.42895976904861</v>
       </c>
       <c r="N13" s="4" t="n">
-        <v>12.08789944126663</v>
+        <v>12.15532149814652</v>
       </c>
       <c r="O13" s="4" t="n">
-        <v>12.76637832300847</v>
+        <v>12.83514969045103</v>
       </c>
       <c r="P13" s="4" t="n">
-        <v>13.44777760201844</v>
+        <v>13.5168511119203</v>
       </c>
       <c r="Q13" s="4" t="n">
-        <v>10.1019999489279</v>
+        <v>10.17186337378924</v>
       </c>
       <c r="R13" s="4" t="n">
-        <v>13.39482900082628</v>
+        <v>13.46405540002367</v>
       </c>
       <c r="S13" s="4" t="n">
-        <v>16.86151522864068</v>
+        <v>16.93094813113717</v>
       </c>
       <c r="T13" s="4" t="n">
-        <v>14.96466032697094</v>
+        <v>15.0342495942304</v>
       </c>
       <c r="U13" s="4" t="n">
-        <v>13.38677523321444</v>
+        <v>13.45615056900728</v>
       </c>
       <c r="V13" s="4" t="n">
-        <v>11.77929495772828</v>
+        <v>11.8484899187647</v>
       </c>
       <c r="W13" s="4" t="n">
-        <v>10.34101043783117</v>
+        <v>10.41087832938575</v>
       </c>
       <c r="X13" s="4" t="n">
-        <v>7.56796554703984</v>
+        <v>7.637962664937028</v>
       </c>
       <c r="Y13" s="4" t="n">
-        <v>7.845316779122747</v>
+        <v>7.915038126342495</v>
       </c>
       <c r="Z13" s="4" t="n">
-        <v>5.069543227437755</v>
+        <v>5.139397575145033</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>X ≈ -0.009392</t>
+          <t>X ≈ -0.009389</t>
         </is>
       </c>
       <c r="B14" t="n">
         <v>150</v>
       </c>
       <c r="C14" s="4" t="n">
-        <v>6.935287193765326</v>
+        <v>6.968308161588872</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>8.585482160059399</v>
+        <v>8.618939066249176</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>7.821407514889579</v>
+        <v>7.856532097830645</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>9.762423359103387</v>
+        <v>9.798413194754687</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>10.72552388108278</v>
+        <v>10.79077311449065</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>10.25426536624083</v>
+        <v>10.31933267953607</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>6.176204903012319</v>
+        <v>6.242171841029744</v>
       </c>
       <c r="J14" s="4" t="n">
-        <v>5.902348302930037</v>
+        <v>5.968676988435398</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>4.620393701008254</v>
+        <v>4.68670754165165</v>
       </c>
       <c r="L14" s="4" t="n">
-        <v>6.504560563660341</v>
+        <v>6.571831196287789</v>
       </c>
       <c r="M14" s="4" t="n">
-        <v>7.442991884252493</v>
+        <v>7.509998650660684</v>
       </c>
       <c r="N14" s="4" t="n">
-        <v>7.167669712253996</v>
+        <v>7.235043349809047</v>
       </c>
       <c r="O14" s="4" t="n">
-        <v>4.058040025900191</v>
+        <v>4.126744760172251</v>
       </c>
       <c r="P14" s="4" t="n">
-        <v>4.503039462580837</v>
+        <v>4.572051822419375</v>
       </c>
       <c r="Q14" s="4" t="n">
-        <v>6.507061907726857</v>
+        <v>6.576893138398084</v>
       </c>
       <c r="R14" s="4" t="n">
-        <v>6.438654354109964</v>
+        <v>6.507840045275202</v>
       </c>
       <c r="S14" s="4" t="n">
-        <v>10.29787854473182</v>
+        <v>10.36727928132449</v>
       </c>
       <c r="T14" s="4" t="n">
-        <v>8.201799399524177</v>
+        <v>8.271359312116047</v>
       </c>
       <c r="U14" s="4" t="n">
-        <v>8.420648695300905</v>
+        <v>8.490003847433677</v>
       </c>
       <c r="V14" s="4" t="n">
-        <v>9.276861791345098</v>
+        <v>9.346045292615329</v>
       </c>
       <c r="W14" s="4" t="n">
-        <v>12.06775910491471</v>
+        <v>12.13762477964405</v>
       </c>
       <c r="X14" s="4" t="n">
-        <v>10.66425085393666</v>
+        <v>10.73424744497159</v>
       </c>
       <c r="Y14" s="4" t="n">
-        <v>12.27583505182232</v>
+        <v>12.34555692097858</v>
       </c>
       <c r="Z14" s="4" t="n">
-        <v>10.20467836257325</v>
+        <v>10.27453271028038</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>X ≈ -0.007794</t>
+          <t>X ≈ -0.00779</t>
         </is>
       </c>
       <c r="B15" t="n">
         <v>186</v>
       </c>
       <c r="C15" s="4" t="n">
-        <v>4.349106279332879</v>
+        <v>4.38206874871814</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>-3.44808020000734</v>
+        <v>-3.414801805210971</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>-1.677716053024547</v>
+        <v>-1.642733042619518</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>-2.921078931785736</v>
+        <v>-2.885258620231966</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>-5.421430917819848</v>
+        <v>-5.35641244905576</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>-3.634557437675312</v>
+        <v>-3.569685064040208</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>-4.403368440154175</v>
+        <v>-4.337560962900739</v>
       </c>
       <c r="J15" s="4" t="n">
-        <v>0.1274071983358098</v>
+        <v>0.1936324789802129</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>0.1699255411092437</v>
+        <v>0.236151752787741</v>
       </c>
       <c r="L15" s="4" t="n">
-        <v>0.4685816362256787</v>
+        <v>0.5357602329850764</v>
       </c>
       <c r="M15" s="4" t="n">
-        <v>-1.398459845262202</v>
+        <v>-1.33155891176493</v>
       </c>
       <c r="N15" s="4" t="n">
-        <v>-3.282032522389578</v>
+        <v>-3.214769134156796</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>-1.190723437258704</v>
+        <v>-1.122089499046474</v>
       </c>
       <c r="P15" s="4" t="n">
-        <v>1.26567540027375</v>
+        <v>1.334636825644822</v>
       </c>
       <c r="Q15" s="4" t="n">
-        <v>3.289353291133502</v>
+        <v>3.35914059130814</v>
       </c>
       <c r="R15" s="4" t="n">
-        <v>4.420588097633065</v>
+        <v>4.489740861680382</v>
       </c>
       <c r="S15" s="4" t="n">
-        <v>4.289205538363746</v>
+        <v>4.358563599173301</v>
       </c>
       <c r="T15" s="4" t="n">
-        <v>3.650824117753814</v>
+        <v>3.720350904208239</v>
       </c>
       <c r="U15" s="4" t="n">
-        <v>3.331664025679828</v>
+        <v>3.40099022171465</v>
       </c>
       <c r="V15" s="4" t="n">
-        <v>2.447019150614317</v>
+        <v>2.516175479600925</v>
       </c>
       <c r="W15" s="4" t="n">
-        <v>2.442936560030184</v>
+        <v>2.512777627588854</v>
       </c>
       <c r="X15" s="4" t="n">
-        <v>3.443074115228171</v>
+        <v>3.513056840576226</v>
       </c>
       <c r="Y15" s="4" t="n">
-        <v>4.794294995846109</v>
+        <v>4.864010059644372</v>
       </c>
       <c r="Z15" s="4" t="n">
-        <v>4.18317298622889</v>
+        <v>4.253027333936409</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>X ≈ -0.006195</t>
+          <t>X ≈ -0.006191</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>-0.7678695743609936</v>
+        <v>-0.7331267348505506</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>0.6457033442089113</v>
+        <v>0.671775548818303</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>-0.7983106355920029</v>
+        <v>-0.7622603155831129</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>3.739222246256176</v>
+        <v>3.747099895347262</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>1.62301872138088</v>
+        <v>1.672401811192223</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>2.396198363696023</v>
+        <v>2.440901099572713</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>1.035890520602656</v>
+        <v>1.090292433503194</v>
       </c>
       <c r="J16" s="4" t="n">
-        <v>-0.9964701855709635</v>
+        <v>-0.9303241146533026</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>1.384452365254141</v>
+        <v>1.436592956500597</v>
       </c>
       <c r="L16" s="4" t="n">
-        <v>4.705305747861146</v>
+        <v>4.73562008618778</v>
       </c>
       <c r="M16" s="4" t="n">
-        <v>4.399321400914708</v>
+        <v>4.430671982080149</v>
       </c>
       <c r="N16" s="4" t="n">
-        <v>4.120432095157042</v>
+        <v>4.154031348701892</v>
       </c>
       <c r="O16" s="4" t="n">
-        <v>5.334857758224238</v>
+        <v>5.361004731001891</v>
       </c>
       <c r="P16" s="4" t="n">
-        <v>5.117868653978043</v>
+        <v>5.143204320503472</v>
       </c>
       <c r="Q16" s="4" t="n">
-        <v>5.629161059707592</v>
+        <v>5.652095406086922</v>
       </c>
       <c r="R16" s="4" t="n">
-        <v>2.125872283199371</v>
+        <v>2.170023107712076</v>
       </c>
       <c r="S16" s="4" t="n">
-        <v>4.089451347974837</v>
+        <v>3.787318269342862</v>
       </c>
       <c r="T16" s="4" t="n">
-        <v>6.920686509034283</v>
+        <v>6.601431364710848</v>
       </c>
       <c r="U16" s="4" t="n">
-        <v>3.031213990850901</v>
+        <v>2.735613609767562</v>
       </c>
       <c r="V16" s="4" t="n">
-        <v>6.744943673357369</v>
+        <v>6.428421326437913</v>
       </c>
       <c r="W16" s="4" t="n">
-        <v>7.965778390607433</v>
+        <v>7.975788046659723</v>
       </c>
       <c r="X16" s="4" t="n">
-        <v>6.71692003069213</v>
+        <v>6.735563828407017</v>
       </c>
       <c r="Y16" s="4" t="n">
-        <v>6.159566223042752</v>
+        <v>5.844163630138567</v>
       </c>
       <c r="Z16" s="4" t="n">
-        <v>4.322325421396634</v>
+        <v>4.017222768759908</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>X ≈ -0.004595</t>
+          <t>X ≈ -0.004593</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="C17" s="4" t="n">
-        <v>-6.599510675664291</v>
+        <v>-6.487467972602943</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>1.229722012179913</v>
+        <v>1.238768167204505</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>2.703716623705553</v>
+        <v>2.695008683500099</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>0.238391101289281</v>
+        <v>0.2568467555059044</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>-5.96997307319343</v>
+        <v>-5.84242405554982</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>-8.121938612097559</v>
+        <v>-7.966629873846919</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>-5.394753293922193</v>
+        <v>-5.272079596473183</v>
       </c>
       <c r="J17" s="4" t="n">
-        <v>-2.166422147035874</v>
+        <v>-2.086361970767868</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>-1.539709064204729</v>
+        <v>-1.468016372984358</v>
       </c>
       <c r="L17" s="4" t="n">
-        <v>-0.5584734812383942</v>
+        <v>-0.5060892386049787</v>
       </c>
       <c r="M17" s="4" t="n">
-        <v>-1.452513983343643</v>
+        <v>-1.389857290572365</v>
       </c>
       <c r="N17" s="4" t="n">
-        <v>0.02420794022231831</v>
+        <v>0.06861842528399364</v>
       </c>
       <c r="O17" s="4" t="n">
-        <v>1.825210706295877</v>
+        <v>1.84377795387045</v>
       </c>
       <c r="P17" s="4" t="n">
-        <v>-4.258904000732009</v>
+        <v>-4.166352138317365</v>
       </c>
       <c r="Q17" s="4" t="n">
-        <v>-3.750732802716072</v>
+        <v>-3.664477377156281</v>
       </c>
       <c r="R17" s="4" t="n">
-        <v>-1.391238831186925</v>
+        <v>-1.33315706557952</v>
       </c>
       <c r="S17" s="4" t="n">
-        <v>-2.69964840553412</v>
+        <v>-2.626181595130006</v>
       </c>
       <c r="T17" s="4" t="n">
-        <v>0.1307789528956746</v>
+        <v>0.1695374233275615</v>
       </c>
       <c r="U17" s="4" t="n">
-        <v>2.111772647841413</v>
+        <v>2.127454702128432</v>
       </c>
       <c r="V17" s="4" t="n">
-        <v>1.714939968373855</v>
+        <v>1.735415187456198</v>
       </c>
       <c r="W17" s="4" t="n">
-        <v>2.344704753066821</v>
+        <v>2.354645510460919</v>
       </c>
       <c r="X17" s="4" t="n">
-        <v>1.429769273268292</v>
+        <v>1.119459032640357</v>
       </c>
       <c r="Y17" s="4" t="n">
-        <v>2.884768124290034</v>
+        <v>2.557381518180804</v>
       </c>
       <c r="Z17" s="4" t="n">
-        <v>1.96938424492604</v>
+        <v>1.321044338187349</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>X ≈ -0.002997</t>
+          <t>X ≈ -0.002994</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>218</v>
+        <v>221</v>
       </c>
       <c r="C18" s="4" t="n">
-        <v>0.4498333357348514</v>
+        <v>1.09760340781343</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>2.838250436706488</v>
+        <v>3.444992774782506</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>3.68540956440372</v>
+        <v>4.261800510766122</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>3.887470739150842</v>
+        <v>4.451928379294081</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>2.165134494159602</v>
+        <v>2.780739662558794</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>2.809104683897566</v>
+        <v>3.417941743757147</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>2.498329405320462</v>
+        <v>2.653777005194868</v>
       </c>
       <c r="J18" s="4" t="n">
-        <v>0.8531961874704734</v>
+        <v>0.5805574836546512</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>1.351192527385528</v>
+        <v>1.071358425476511</v>
       </c>
       <c r="L18" s="4" t="n">
-        <v>-0.3338295428921256</v>
+        <v>-0.5989966622721994</v>
       </c>
       <c r="M18" s="4" t="n">
-        <v>1.309782599373186</v>
+        <v>1.472832969649161</v>
       </c>
       <c r="N18" s="4" t="n">
-        <v>-0.7942988488233169</v>
+        <v>-0.6029322670626627</v>
       </c>
       <c r="O18" s="4" t="n">
-        <v>-1.915877549393379</v>
+        <v>-1.722060780483048</v>
       </c>
       <c r="P18" s="4" t="n">
-        <v>-1.221614793942194</v>
+        <v>-1.04081187433281</v>
       </c>
       <c r="Q18" s="4" t="n">
-        <v>-1.420989152960153</v>
+        <v>-1.245317217960171</v>
       </c>
       <c r="R18" s="4" t="n">
-        <v>-1.742071674891072</v>
+        <v>-1.103073476394364</v>
       </c>
       <c r="S18" s="4" t="n">
-        <v>-2.79154364962681</v>
+        <v>-2.138218182024801</v>
       </c>
       <c r="T18" s="4" t="n">
-        <v>-3.354868255527791</v>
+        <v>-3.597126048535877</v>
       </c>
       <c r="U18" s="4" t="n">
-        <v>-2.222881122312849</v>
+        <v>-2.479058360844633</v>
       </c>
       <c r="V18" s="4" t="n">
-        <v>-3.869701729823902</v>
+        <v>-4.09962385720317</v>
       </c>
       <c r="W18" s="4" t="n">
-        <v>-3.496182060373997</v>
+        <v>-3.738015895160288</v>
       </c>
       <c r="X18" s="4" t="n">
-        <v>-2.654705923356161</v>
+        <v>-2.909956356986008</v>
       </c>
       <c r="Y18" s="4" t="n">
-        <v>-3.756077545864862</v>
+        <v>-3.992928535580695</v>
       </c>
       <c r="Z18" s="4" t="n">
-        <v>1.213852674499705</v>
+        <v>0.9080168731762015</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>X ≈ -0.001398</t>
+          <t>X ≈ -0.001395</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="C19" s="4" t="n">
-        <v>-1.838420286333942</v>
+        <v>-2.473337660517785</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>-0.3394925581958788</v>
+        <v>-0.9528423601530207</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>-4.074600286502744</v>
+        <v>-4.713082447380756</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>-0.197561433342635</v>
+        <v>-0.7781244817122825</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>-1.482894015070812</v>
+        <v>-2.043974999406352</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>-0.3761735822192307</v>
+        <v>-0.9264532308274198</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>-1.610929450095746</v>
+        <v>-1.699382891062605</v>
       </c>
       <c r="J19" s="4" t="n">
-        <v>0.4115299030684838</v>
+        <v>0.8178954033028063</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>0.4546826532128918</v>
+        <v>0.8609797469944951</v>
       </c>
       <c r="L19" s="4" t="n">
-        <v>-0.7798188147733853</v>
+        <v>-0.3777747247265069</v>
       </c>
       <c r="M19" s="4" t="n">
-        <v>-1.424523440160776</v>
+        <v>-1.501325623790088</v>
       </c>
       <c r="N19" s="4" t="n">
-        <v>-2.628483077121928</v>
+        <v>-2.71565925387555</v>
       </c>
       <c r="O19" s="4" t="n">
-        <v>-2.373133845759412</v>
+        <v>-2.440709587745381</v>
       </c>
       <c r="P19" s="4" t="n">
-        <v>-2.332220910025384</v>
+        <v>-2.662763907111255</v>
       </c>
       <c r="Q19" s="4" t="n">
-        <v>-5.495892010384445</v>
+        <v>-6.131764087495824</v>
       </c>
       <c r="R19" s="4" t="n">
-        <v>-5.365554025026562</v>
+        <v>-6.472262883277985</v>
       </c>
       <c r="S19" s="4" t="n">
-        <v>-4.575373146681244</v>
+        <v>-5.673284836137142</v>
       </c>
       <c r="T19" s="4" t="n">
-        <v>-7.454709133870232</v>
+        <v>-7.383923972554726</v>
       </c>
       <c r="U19" s="4" t="n">
-        <v>-5.854538292288943</v>
+        <v>-5.495134255124036</v>
       </c>
       <c r="V19" s="4" t="n">
-        <v>-4.281283804281109</v>
+        <v>-3.903904260248595</v>
       </c>
       <c r="W19" s="4" t="n">
-        <v>-5.751533742331233</v>
+        <v>-5.383283927085323</v>
       </c>
       <c r="X19" s="4" t="n">
-        <v>-3.512673983159132</v>
+        <v>-3.115640037959217</v>
       </c>
       <c r="Y19" s="4" t="n">
-        <v>-2.774935853713991</v>
+        <v>-2.372820658669546</v>
       </c>
       <c r="Z19" s="4" t="n">
-        <v>-0.9990253411306114</v>
+        <v>-0.5705377122546693</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>X ≈ 0.0002014</t>
+          <t>X ≈ 0.0002037</t>
         </is>
       </c>
       <c r="B20" t="n">
         <v>186</v>
       </c>
       <c r="C20" s="4" t="n">
-        <v>2.996575611081042</v>
+        <v>3.024034024505994</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>-2.134059720197278</v>
+        <v>-2.099161031999841</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>-1.969965590768552</v>
+        <v>-1.933334177900626</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>-0.01876243854343329</v>
+        <v>0.01343249460005325</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>3.888389489039533</v>
+        <v>3.944173539618134</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>1.942886769135285</v>
+        <v>2.002225645337973</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>1.17283682587378</v>
+        <v>1.234839880688078</v>
       </c>
       <c r="J20" s="4" t="n">
-        <v>-3.380852380351698</v>
+        <v>-3.310662724088651</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>-3.340543046638551</v>
+        <v>-3.270668872814653</v>
       </c>
       <c r="L20" s="4" t="n">
-        <v>-5.186205525297957</v>
+        <v>-5.112789619476494</v>
       </c>
       <c r="M20" s="4" t="n">
-        <v>-3.842033028848974</v>
+        <v>-3.77168173227998</v>
       </c>
       <c r="N20" s="4" t="n">
-        <v>-6.267127063971358</v>
+        <v>-6.191097931175165</v>
       </c>
       <c r="O20" s="4" t="n">
-        <v>-10.07755466054011</v>
+        <v>-9.993709381299212</v>
       </c>
       <c r="P20" s="4" t="n">
-        <v>-9.226873293430835</v>
+        <v>-9.148772287200813</v>
       </c>
       <c r="Q20" s="4" t="n">
-        <v>-8.279749727479818</v>
+        <v>-8.205610702558353</v>
       </c>
       <c r="R20" s="4" t="n">
-        <v>-6.838501730873212</v>
+        <v>-7.077511896461736</v>
       </c>
       <c r="S20" s="4" t="n">
-        <v>-8.044821903271142</v>
+        <v>-8.288393578179246</v>
       </c>
       <c r="T20" s="4" t="n">
-        <v>-8.153050521513407</v>
+        <v>-8.394218825929052</v>
       </c>
       <c r="U20" s="4" t="n">
-        <v>-9.015575281346564</v>
+        <v>-9.249564638257453</v>
       </c>
       <c r="V20" s="4" t="n">
-        <v>-7.221164679559919</v>
+        <v>-7.145494315695466</v>
       </c>
       <c r="W20" s="4" t="n">
-        <v>-7.230028365987259</v>
+        <v>-7.15056047061826</v>
       </c>
       <c r="X20" s="4" t="n">
-        <v>-5.155445787221211</v>
+        <v>-5.081678287189384</v>
       </c>
       <c r="Y20" s="4" t="n">
-        <v>-3.805401803534785</v>
+        <v>-3.73501107561038</v>
       </c>
       <c r="Z20" s="4" t="n">
-        <v>-3.343708734201087</v>
+        <v>-3.27385438649388</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>X ≈ 0.001801</t>
+          <t>X ≈ 0.001803</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="C21" s="4" t="n">
-        <v>1.623019071045341</v>
+        <v>2.115328903206148</v>
       </c>
       <c r="D21" s="4" t="n">
-        <v>1.297366054872498</v>
+        <v>1.287354294425434</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>0.3473292875760663</v>
+        <v>0.3301036295005773</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>-1.377850878991083</v>
+        <v>-1.385919372113541</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>-5.324829875699372</v>
+        <v>-5.508436894595846</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>-1.05926061851919</v>
+        <v>-0.995568724913511</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>2.747420732508424</v>
+        <v>2.783452340201137</v>
       </c>
       <c r="J21" s="4" t="n">
-        <v>-0.08788265471703482</v>
+        <v>-0.0286306287671465</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>-0.5530486107444332</v>
+        <v>-0.4914275462380076</v>
       </c>
       <c r="L21" s="4" t="n">
-        <v>-4.4041230002547</v>
+        <v>-4.313491248950896</v>
       </c>
       <c r="M21" s="4" t="n">
-        <v>-4.856561595157018</v>
+        <v>-5.050687179431314</v>
       </c>
       <c r="N21" s="4" t="n">
-        <v>-5.369248812581596</v>
+        <v>-5.850684751154034</v>
       </c>
       <c r="O21" s="4" t="n">
-        <v>-8.764974454609167</v>
+        <v>-9.533653796272567</v>
       </c>
       <c r="P21" s="4" t="n">
-        <v>-9.498214127102266</v>
+        <v>-10.27098310621095</v>
       </c>
       <c r="Q21" s="4" t="n">
-        <v>-5.042803672177449</v>
+        <v>-5.551695401256914</v>
       </c>
       <c r="R21" s="4" t="n">
-        <v>-3.934178165862384</v>
+        <v>-4.147725907857186</v>
       </c>
       <c r="S21" s="4" t="n">
-        <v>-4.580715586548408</v>
+        <v>-4.494393645034421</v>
       </c>
       <c r="T21" s="4" t="n">
-        <v>-3.153196970894136</v>
+        <v>-3.071277628409938</v>
       </c>
       <c r="U21" s="4" t="n">
-        <v>-1.911642519335039</v>
+        <v>-1.838337551577105</v>
       </c>
       <c r="V21" s="4" t="n">
-        <v>-3.261726128878664</v>
+        <v>-3.179588678324166</v>
       </c>
       <c r="W21" s="4" t="n">
-        <v>-4.020764511562056</v>
+        <v>-4.230238545435917</v>
       </c>
       <c r="X21" s="4" t="n">
-        <v>-4.096719567204609</v>
+        <v>-4.308234762927377</v>
       </c>
       <c r="Y21" s="4" t="n">
-        <v>-3.821944400722536</v>
+        <v>-4.036343280101448</v>
       </c>
       <c r="Z21" s="4" t="n">
-        <v>0.2046783625730981</v>
+        <v>-0.03158973869921056</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>X ≈ 0.003399</t>
+          <t>X ≈ 0.003402</t>
         </is>
       </c>
       <c r="B22" t="n">
         <v>203</v>
       </c>
       <c r="C22" s="4" t="n">
-        <v>1.652380681995545</v>
+        <v>0.6789197442905959</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>-1.839422841082104</v>
+        <v>-2.317827876377969</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>-4.506697479141913</v>
+        <v>-5.001212404815362</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>-10.12033030736346</v>
+        <v>-10.34010546563325</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>-8.056157998412949</v>
+        <v>-8.248343979433365</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>-9.341589425468747</v>
+        <v>-9.522454951655355</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>-9.635691606153088</v>
+        <v>-9.540924712992201</v>
       </c>
       <c r="J22" s="4" t="n">
-        <v>-9.438343825563152</v>
+        <v>-9.342292651493253</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>-9.893505712375664</v>
+        <v>-9.796230983802957</v>
       </c>
       <c r="L22" s="4" t="n">
-        <v>-8.225102676962315</v>
+        <v>-8.131939607025153</v>
       </c>
       <c r="M22" s="4" t="n">
-        <v>-10.89776613908387</v>
+        <v>-10.80509536693331</v>
       </c>
       <c r="N22" s="4" t="n">
-        <v>-12.67089685873714</v>
+        <v>-12.58177199474877</v>
       </c>
       <c r="O22" s="4" t="n">
-        <v>-11.35501991544052</v>
+        <v>-11.27601003321506</v>
       </c>
       <c r="P22" s="4" t="n">
-        <v>-15.02681316239222</v>
+        <v>-14.9575350975595</v>
       </c>
       <c r="Q22" s="4" t="n">
-        <v>-14.70484387424955</v>
+        <v>-14.63477786796009</v>
       </c>
       <c r="R22" s="4" t="n">
-        <v>-14.09790066846185</v>
+        <v>-14.02850778985077</v>
       </c>
       <c r="S22" s="4" t="n">
-        <v>-15.71522830954711</v>
+        <v>-15.64565887376459</v>
       </c>
       <c r="T22" s="4" t="n">
-        <v>-13.56175692759746</v>
+        <v>-13.78221680168045</v>
       </c>
       <c r="U22" s="4" t="n">
-        <v>-17.48492820156635</v>
+        <v>-17.98902008845986</v>
       </c>
       <c r="V22" s="4" t="n">
-        <v>-15.04002463054182</v>
+        <v>-15.82849006796562</v>
       </c>
       <c r="W22" s="4" t="n">
-        <v>-15.58322503953983</v>
+        <v>-16.37967853132524</v>
       </c>
       <c r="X22" s="4" t="n">
-        <v>-14.67395842030559</v>
+        <v>-15.17976648535045</v>
       </c>
       <c r="Y22" s="4" t="n">
-        <v>-14.39918325382346</v>
+        <v>-14.61144507479451</v>
       </c>
       <c r="Z22" s="4" t="n">
-        <v>-13.98251375565351</v>
+        <v>-13.91265940794623</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>X ≈ 0.004998</t>
+          <t>X ≈ 0.005</t>
         </is>
       </c>
       <c r="B23" t="n">
         <v>184</v>
       </c>
       <c r="C23" s="4" t="n">
-        <v>2.282019721837315</v>
+        <v>2.315294014156144</v>
       </c>
       <c r="D23" s="4" t="n">
-        <v>3.023644479964595</v>
+        <v>3.057317488577937</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>2.139973867453193</v>
+        <v>2.17532829112168</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>-2.889959344807686</v>
+        <v>-2.852121873968443</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>-2.168570440305409</v>
+        <v>-2.098953649475824</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>-2.526542452624724</v>
+        <v>-2.45464304825817</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>-4.384074654215716</v>
+        <v>-4.302784083706591</v>
       </c>
       <c r="J23" s="4" t="n">
-        <v>-3.038110150680865</v>
+        <v>-2.959892069530611</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>-4.085752460197924</v>
+        <v>-4.003416769386291</v>
       </c>
       <c r="L23" s="4" t="n">
-        <v>-3.776809906054474</v>
+        <v>-3.695103828565799</v>
       </c>
       <c r="M23" s="4" t="n">
-        <v>0.3018971871477589</v>
+        <v>0.3677870587636036</v>
       </c>
       <c r="N23" s="4" t="n">
-        <v>1.653238066281489</v>
+        <v>1.719879946568511</v>
       </c>
       <c r="O23" s="4" t="n">
-        <v>-0.5582096739446669</v>
+        <v>-0.487157019784668</v>
       </c>
       <c r="P23" s="4" t="n">
-        <v>0.3073900367599904</v>
+        <v>0.3766681015927134</v>
       </c>
       <c r="Q23" s="4" t="n">
-        <v>-0.3515412022772537</v>
+        <v>-0.2814751959877881</v>
       </c>
       <c r="R23" s="4" t="n">
-        <v>0.2435188473441272</v>
+        <v>0.3129117259552032</v>
       </c>
       <c r="S23" s="4" t="n">
-        <v>1.739859935803842</v>
+        <v>1.809429371586369</v>
       </c>
       <c r="T23" s="4" t="n">
-        <v>0.5479199979694229</v>
+        <v>0.6176321460260468</v>
       </c>
       <c r="U23" s="4" t="n">
-        <v>0.7640431609013092</v>
+        <v>0.8335235269504437</v>
       </c>
       <c r="V23" s="4" t="n">
-        <v>-0.6793478260869534</v>
+        <v>-0.6100654456902248</v>
       </c>
       <c r="W23" s="4" t="n">
-        <v>-1.222548235084972</v>
+        <v>-1.152611613656319</v>
       </c>
       <c r="X23" s="4" t="n">
-        <v>-1.29850329072746</v>
+        <v>-1.228457575065299</v>
       </c>
       <c r="Y23" s="4" t="n">
-        <v>-3.197641167723653</v>
+        <v>-3.127895906061568</v>
       </c>
       <c r="Z23" s="4" t="n">
-        <v>-2.730104246122487</v>
+        <v>-2.660249898415209</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>X ≈ 0.006598</t>
+          <t>X ≈ 0.006599</t>
         </is>
       </c>
       <c r="B24" t="n">
         <v>162</v>
       </c>
       <c r="C24" s="4" t="n">
-        <v>4.913778593723819</v>
+        <v>4.947052886042648</v>
       </c>
       <c r="D24" s="4" t="n">
-        <v>-1.54691453504914</v>
+        <v>-1.513241526435799</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>-0.5160293707329444</v>
+        <v>-0.4806749470644576</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>3.069681493227556</v>
+        <v>3.100968657681996</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>-1.576805189082165</v>
+        <v>-1.506968458057564</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>-0.1653825191746208</v>
+        <v>-0.09938894533383547</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>2.754047917032629</v>
+        <v>2.806908836767988</v>
       </c>
       <c r="J24" s="4" t="n">
-        <v>0.0166893349166628</v>
+        <v>0.08487561676384558</v>
       </c>
       <c r="K24" s="4" t="n">
-        <v>-0.5590487194571452</v>
+        <v>-0.4873087284622386</v>
       </c>
       <c r="L24" s="4" t="n">
-        <v>-4.42093228930743</v>
+        <v>-4.33014308923444</v>
       </c>
       <c r="M24" s="4" t="n">
-        <v>-7.850276725895725</v>
+        <v>-7.755132329582537</v>
       </c>
       <c r="N24" s="4" t="n">
-        <v>-1.956531123197713</v>
+        <v>-1.881498692351059</v>
       </c>
       <c r="O24" s="4" t="n">
-        <v>0.6226813620187031</v>
+        <v>0.6931578622482277</v>
       </c>
       <c r="P24" s="4" t="n">
-        <v>-2.067811251484649</v>
+        <v>-1.998533186651926</v>
       </c>
       <c r="Q24" s="4" t="n">
-        <v>-3.344026441139306</v>
+        <v>-3.27396043484984</v>
       </c>
       <c r="R24" s="4" t="n">
-        <v>-2.748966391517925</v>
+        <v>-2.679573512906849</v>
       </c>
       <c r="S24" s="4" t="n">
-        <v>-1.648492184432207</v>
+        <v>-1.578922748649681</v>
       </c>
       <c r="T24" s="4" t="n">
-        <v>-0.5189076992929174</v>
+        <v>-0.4491955512362935</v>
       </c>
       <c r="U24" s="4" t="n">
-        <v>-1.537352437595771</v>
+        <v>-1.467872071546637</v>
       </c>
       <c r="V24" s="4" t="n">
-        <v>-1.350308641975303</v>
+        <v>-1.281026261578575</v>
       </c>
       <c r="W24" s="4" t="n">
-        <v>-0.6589411497386237</v>
+        <v>-0.589004528309971</v>
       </c>
       <c r="X24" s="4" t="n">
-        <v>-1.35218015599866</v>
+        <v>-1.282134440336499</v>
       </c>
       <c r="Y24" s="4" t="n">
-        <v>-1.077404989516452</v>
+        <v>-1.007659727854367</v>
       </c>
       <c r="Z24" s="4" t="n">
-        <v>-4.239766081871423</v>
+        <v>-4.169911734164145</v>
       </c>
     </row>
     <row r="25">
@@ -2183,158 +2183,158 @@
         <v>135</v>
       </c>
       <c r="C25" s="4" t="n">
-        <v>0.3690095420327282</v>
+        <v>0.4022838343515573</v>
       </c>
       <c r="D25" s="4" t="n">
-        <v>5.904412141742789</v>
+        <v>5.93808515035613</v>
       </c>
       <c r="E25" s="4" t="n">
-        <v>5.225113528828238</v>
+        <v>5.260467952496725</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>7.463729393321536</v>
+        <v>7.486511769795484</v>
       </c>
       <c r="G25" s="4" t="n">
-        <v>4.188993115609939</v>
+        <v>4.243866216730488</v>
       </c>
       <c r="H25" s="4" t="n">
-        <v>8.059080392844649</v>
+        <v>8.089435515533907</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>2.873171143082111</v>
+        <v>2.919498285296676</v>
       </c>
       <c r="J25" s="4" t="n">
-        <v>1.125241960647926</v>
+        <v>1.187601088764026</v>
       </c>
       <c r="K25" s="4" t="n">
-        <v>1.167521183207754</v>
+        <v>1.231372990789886</v>
       </c>
       <c r="L25" s="4" t="n">
-        <v>2.616104747729722</v>
+        <v>2.675844738345717</v>
       </c>
       <c r="M25" s="4" t="n">
-        <v>1.408982533363528</v>
+        <v>1.47559497614882</v>
       </c>
       <c r="N25" s="4" t="n">
-        <v>0.3891478891478855</v>
+        <v>0.4605126674155144</v>
       </c>
       <c r="O25" s="4" t="n">
-        <v>1.48687889288297</v>
+        <v>1.556731176623551</v>
       </c>
       <c r="P25" s="4" t="n">
-        <v>4.228485044811585</v>
+        <v>4.297763109644308</v>
       </c>
       <c r="Q25" s="4" t="n">
-        <v>-0.8748906386701734</v>
+        <v>-0.8048246323807078</v>
       </c>
       <c r="R25" s="4" t="n">
-        <v>-1.761312070530273</v>
+        <v>-1.691919191919197</v>
       </c>
       <c r="S25" s="4" t="n">
-        <v>-1.154665023938456</v>
+        <v>-1.08509558815593</v>
       </c>
       <c r="T25" s="4" t="n">
-        <v>-1.259648440033736</v>
+        <v>-1.189936291977112</v>
       </c>
       <c r="U25" s="4" t="n">
-        <v>-1.043525277101871</v>
+        <v>-0.9740449110527365</v>
       </c>
       <c r="V25" s="4" t="n">
-        <v>-0.1157407407407476</v>
+        <v>-0.04645836034401896</v>
       </c>
       <c r="W25" s="4" t="n">
-        <v>0.0817995910020457</v>
+        <v>0.1517362124306985</v>
       </c>
       <c r="X25" s="4" t="n">
-        <v>-7.401562872047926</v>
+        <v>-7.331517156385765</v>
       </c>
       <c r="Y25" s="4" t="n">
-        <v>-9.349009927788067</v>
+        <v>-9.279264666125982</v>
       </c>
       <c r="Z25" s="4" t="n">
-        <v>-8.684210526315795</v>
+        <v>-8.614356178608517</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>X ≈ 0.009793</t>
+          <t>X ≈ 0.009798</t>
         </is>
       </c>
       <c r="B26" t="n">
         <v>137</v>
       </c>
       <c r="C26" s="4" t="n">
-        <v>3.917974019984285</v>
+        <v>3.951248312303115</v>
       </c>
       <c r="D26" s="4" t="n">
-        <v>-1.477040853207349</v>
+        <v>-1.443367844594007</v>
       </c>
       <c r="E26" s="4" t="n">
-        <v>4.299696170783086</v>
+        <v>4.335050594451573</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>1.075868395508245</v>
+        <v>0.7282008976472625</v>
       </c>
       <c r="G26" s="4" t="n">
-        <v>6.915003198952917</v>
+        <v>6.159174288595807</v>
       </c>
       <c r="H26" s="4" t="n">
-        <v>6.378481827575087</v>
+        <v>5.631428010030803</v>
       </c>
       <c r="I26" s="4" t="n">
-        <v>4.899260051512577</v>
+        <v>4.130748533993291</v>
       </c>
       <c r="J26" s="4" t="n">
-        <v>6.09163432640046</v>
+        <v>5.708043575527235</v>
       </c>
       <c r="K26" s="4" t="n">
-        <v>5.414819382437301</v>
+        <v>5.446311201950053</v>
       </c>
       <c r="L26" s="4" t="n">
-        <v>3.189232620127584</v>
+        <v>3.240874920588503</v>
       </c>
       <c r="M26" s="4" t="n">
-        <v>2.733664879943696</v>
+        <v>2.792657094615976</v>
       </c>
       <c r="N26" s="4" t="n">
-        <v>-0.465137052728295</v>
+        <v>-0.3888028909633121</v>
       </c>
       <c r="O26" s="4" t="n">
-        <v>-2.319555278514706</v>
+        <v>-2.24229341693529</v>
       </c>
       <c r="P26" s="4" t="n">
-        <v>-0.3511310676512451</v>
+        <v>-0.2818530028185222</v>
       </c>
       <c r="Q26" s="4" t="n">
-        <v>-1.010062306688546</v>
+        <v>-0.9399963003990806</v>
       </c>
       <c r="R26" s="4" t="n">
-        <v>-4.064637293563521</v>
+        <v>-3.995244414952445</v>
       </c>
       <c r="S26" s="4" t="n">
-        <v>-7.848366024208786</v>
+        <v>-7.77879658842626</v>
       </c>
       <c r="T26" s="4" t="n">
-        <v>-6.493495425705532</v>
+        <v>-6.423783277648909</v>
       </c>
       <c r="U26" s="4" t="n">
-        <v>-4.817518248175176</v>
+        <v>-4.748037882126042</v>
       </c>
       <c r="V26" s="4" t="n">
-        <v>-5.360401459854018</v>
+        <v>-5.291119079457289</v>
       </c>
       <c r="W26" s="4" t="n">
-        <v>-4.443747854253473</v>
+        <v>-4.373811232824821</v>
       </c>
       <c r="X26" s="4" t="n">
-        <v>-1.599994880698993</v>
+        <v>-1.529949165036832</v>
       </c>
       <c r="Y26" s="4" t="n">
-        <v>-4.974854750713178</v>
+        <v>-4.905109489051092</v>
       </c>
       <c r="Z26" s="4" t="n">
-        <v>-8.700431126477994</v>
+        <v>-8.630576778770717</v>
       </c>
     </row>
     <row r="27">
@@ -2347,76 +2347,76 @@
         <v>120</v>
       </c>
       <c r="C27" s="4" t="n">
-        <v>-9.037778759710619</v>
+        <v>-9.00450446739179</v>
       </c>
       <c r="D27" s="4" t="n">
-        <v>-4.407460033866435</v>
+        <v>-4.373787025253094</v>
       </c>
       <c r="E27" s="4" t="n">
-        <v>-8.375872539479261</v>
+        <v>-8.340518115810774</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>-7.449209880653314</v>
+        <v>-7.41301616323441</v>
       </c>
       <c r="G27" s="4" t="n">
-        <v>-2.071045166759113</v>
+        <v>-2.005372136863436</v>
       </c>
       <c r="H27" s="4" t="n">
-        <v>-1.405606925972592</v>
+        <v>-1.781634013740124</v>
       </c>
       <c r="I27" s="4" t="n">
-        <v>-1.740621268252731</v>
+        <v>-2.583000247251249</v>
       </c>
       <c r="J27" s="4" t="n">
-        <v>-0.3660435739323873</v>
+        <v>-1.235464494795536</v>
       </c>
       <c r="K27" s="4" t="n">
-        <v>-2.827864802425118</v>
+        <v>-3.689594611084132</v>
       </c>
       <c r="L27" s="4" t="n">
-        <v>-3.124635993011033</v>
+        <v>-4.011912051836504</v>
       </c>
       <c r="M27" s="4" t="n">
-        <v>-1.183610059229061</v>
+        <v>-1.593548960448821</v>
       </c>
       <c r="N27" s="4" t="n">
-        <v>-0.6293706293706336</v>
+        <v>-1.058352670939144</v>
       </c>
       <c r="O27" s="4" t="n">
-        <v>-0.08719518119110603</v>
+        <v>-0.5396017787748875</v>
       </c>
       <c r="P27" s="4" t="n">
-        <v>0.5247813411078752</v>
+        <v>0.5940594059405981</v>
       </c>
       <c r="Q27" s="4" t="n">
-        <v>2.365850102070574</v>
+        <v>2.43591610836004</v>
       </c>
       <c r="R27" s="4" t="n">
-        <v>0.4609101516919054</v>
+        <v>0.5303030303029814</v>
       </c>
       <c r="S27" s="4" t="n">
-        <v>0.3268164575430319</v>
+        <v>0.396385893325558</v>
       </c>
       <c r="T27" s="4" t="n">
-        <v>-0.6115002918855836</v>
+        <v>-0.5417881438289598</v>
       </c>
       <c r="U27" s="4" t="n">
-        <v>-3.728710462287097</v>
+        <v>-3.659230096237962</v>
       </c>
       <c r="V27" s="4" t="n">
-        <v>-6.875</v>
+        <v>-6.805717619603271</v>
       </c>
       <c r="W27" s="4" t="n">
-        <v>-4.918200408997905</v>
+        <v>-4.848263787569252</v>
       </c>
       <c r="X27" s="4" t="n">
-        <v>-3.327488797973899</v>
+        <v>-3.257443082311738</v>
       </c>
       <c r="Y27" s="4" t="n">
-        <v>-4.719380298158427</v>
+        <v>-4.649635036496342</v>
       </c>
       <c r="Z27" s="4" t="n">
-        <v>-3.961988304093524</v>
+        <v>-3.892133956386246</v>
       </c>
     </row>
     <row r="28">
@@ -2429,76 +2429,76 @@
         <v>94</v>
       </c>
       <c r="C28" s="4" t="n">
-        <v>0.03981441288495091</v>
+        <v>0.07308870520378008</v>
       </c>
       <c r="D28" s="4" t="n">
-        <v>-11.95679334502291</v>
+        <v>-11.92312033640957</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>-10.23957367201515</v>
+        <v>-10.20421924834666</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>-7.776861141636218</v>
+        <v>-7.740667424217314</v>
       </c>
       <c r="G28" s="4" t="n">
-        <v>-9.220551914329128</v>
+        <v>-9.154878884433451</v>
       </c>
       <c r="H28" s="4" t="n">
-        <v>-9.015582113614883</v>
+        <v>-8.950107510628612</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>-8.742076595873414</v>
+        <v>-8.675684544723467</v>
       </c>
       <c r="J28" s="4" t="n">
-        <v>-9.493288783885141</v>
+        <v>-10.02697542083316</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>-8.414630369475645</v>
+        <v>-8.933775032810786</v>
       </c>
       <c r="L28" s="4" t="n">
-        <v>-3.869316844074916</v>
+        <v>-4.419636377976751</v>
       </c>
       <c r="M28" s="4" t="n">
-        <v>-2.53112778972551</v>
+        <v>-3.081399898311915</v>
       </c>
       <c r="N28" s="4" t="n">
-        <v>0.3812676685016783</v>
+        <v>0.4584142378276113</v>
       </c>
       <c r="O28" s="4" t="n">
-        <v>2.448265811716666</v>
+        <v>2.517265941961625</v>
       </c>
       <c r="P28" s="4" t="n">
-        <v>4.354568575150431</v>
+        <v>4.423846639983154</v>
       </c>
       <c r="Q28" s="4" t="n">
-        <v>4.759467123347171</v>
+        <v>4.829533129636637</v>
       </c>
       <c r="R28" s="4" t="n">
-        <v>6.418356960202651</v>
+        <v>6.487749838813727</v>
       </c>
       <c r="S28" s="4" t="n">
-        <v>8.411922840521754</v>
+        <v>8.48149227630428</v>
       </c>
       <c r="T28" s="4" t="n">
-        <v>7.243109637192404</v>
+        <v>7.312821785249028</v>
       </c>
       <c r="U28" s="4" t="n">
-        <v>2.140083863954068</v>
+        <v>2.209564230003203</v>
       </c>
       <c r="V28" s="4" t="n">
-        <v>0.1994680851063819</v>
+        <v>0.2687504655031105</v>
       </c>
       <c r="W28" s="4" t="n">
-        <v>1.783927250576546</v>
+        <v>1.853863872005199</v>
       </c>
       <c r="X28" s="4" t="n">
-        <v>2.771801982167943</v>
+        <v>2.841847697830104</v>
       </c>
       <c r="Y28" s="4" t="n">
-        <v>1.982747361416003</v>
+        <v>2.052492623078088</v>
       </c>
       <c r="Z28" s="4" t="n">
-        <v>-2.348513126788632</v>
+        <v>-2.278658779081354</v>
       </c>
     </row>
     <row r="29">
@@ -2511,76 +2511,76 @@
         <v>67</v>
       </c>
       <c r="C29" s="4" t="n">
-        <v>-11.11651668013418</v>
+        <v>-11.08324238781535</v>
       </c>
       <c r="D29" s="4" t="n">
-        <v>-12.98030291759946</v>
+        <v>-12.94662990898612</v>
       </c>
       <c r="E29" s="4" t="n">
-        <v>-18.94721625989274</v>
+        <v>-18.91186183622425</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>-22.64608419995153</v>
+        <v>-22.60989048253263</v>
       </c>
       <c r="G29" s="4" t="n">
-        <v>-15.59826835572004</v>
+        <v>-15.53259532582437</v>
       </c>
       <c r="H29" s="4" t="n">
-        <v>-15.36601198097812</v>
+        <v>-15.30053737799185</v>
       </c>
       <c r="I29" s="4" t="n">
-        <v>-14.67790503281387</v>
+        <v>-14.61151298166392</v>
       </c>
       <c r="J29" s="4" t="n">
-        <v>-9.022383833989323</v>
+        <v>-8.955648582073891</v>
       </c>
       <c r="K29" s="4" t="n">
-        <v>-0.6343826717939152</v>
+        <v>-1.469511537689016</v>
       </c>
       <c r="L29" s="4" t="n">
-        <v>-7.378367336294644</v>
+        <v>-8.230613172150896</v>
       </c>
       <c r="M29" s="4" t="n">
-        <v>-5.611470755746474</v>
+        <v>-6.450488688035563</v>
       </c>
       <c r="N29" s="4" t="n">
-        <v>-10.36817659951983</v>
+        <v>-11.23390508882319</v>
       </c>
       <c r="O29" s="4" t="n">
-        <v>-5.522518564275636</v>
+        <v>-5.453518434030677</v>
       </c>
       <c r="P29" s="4" t="n">
-        <v>-5.74387537530999</v>
+        <v>-5.674597310477267</v>
       </c>
       <c r="Q29" s="4" t="n">
-        <v>-1.925194674048875</v>
+        <v>-1.855128667759409</v>
       </c>
       <c r="R29" s="4" t="n">
-        <v>-1.330134624427401</v>
+        <v>-1.260741745816325</v>
       </c>
       <c r="S29" s="4" t="n">
-        <v>1.520846308289343</v>
+        <v>1.590415744071869</v>
       </c>
       <c r="T29" s="4" t="n">
-        <v>-0.0766744212388204</v>
+        <v>-0.006962273182196554</v>
       </c>
       <c r="U29" s="4" t="n">
-        <v>3.124523368558634</v>
+        <v>3.194003734607769</v>
       </c>
       <c r="V29" s="4" t="n">
-        <v>1.819029850746269</v>
+        <v>1.888312231142997</v>
       </c>
       <c r="W29" s="4" t="n">
-        <v>-3.201782498550237</v>
+        <v>-3.131845877121584</v>
       </c>
       <c r="X29" s="4" t="n">
-        <v>1.199874386105705</v>
+        <v>1.269920101767866</v>
       </c>
       <c r="Y29" s="4" t="n">
-        <v>-1.510425074277791</v>
+        <v>-1.440679812615706</v>
       </c>
       <c r="Z29" s="4" t="n">
-        <v>-0.09382910011350987</v>
+        <v>-0.02397475240623237</v>
       </c>
     </row>
     <row r="30">
@@ -2593,76 +2593,76 @@
         <v>65</v>
       </c>
       <c r="C30" s="4" t="n">
-        <v>-4.443352174981563</v>
+        <v>-4.410077882662733</v>
       </c>
       <c r="D30" s="4" t="n">
-        <v>-3.240066151164335</v>
+        <v>-3.206393142550994</v>
       </c>
       <c r="E30" s="4" t="n">
-        <v>1.474079538595703</v>
+        <v>1.50943396226419</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>0.7602862254025027</v>
+        <v>0.7964799428214064</v>
       </c>
       <c r="G30" s="4" t="n">
-        <v>3.471939517301536</v>
+        <v>3.537612547197213</v>
       </c>
       <c r="H30" s="4" t="n">
-        <v>-4.033203561999414</v>
+        <v>-3.967728959013144</v>
       </c>
       <c r="I30" s="4" t="n">
-        <v>-1.729146617130361</v>
+        <v>-1.662754565980414</v>
       </c>
       <c r="J30" s="4" t="n">
-        <v>-2.007701262648879</v>
+        <v>-1.940966010733447</v>
       </c>
       <c r="K30" s="4" t="n">
-        <v>-0.4277236591646698</v>
+        <v>-0.361017290357168</v>
       </c>
       <c r="L30" s="4" t="n">
-        <v>-1.201559069934184</v>
+        <v>-1.133932966393743</v>
       </c>
       <c r="M30" s="4" t="n">
-        <v>3.688184812565815</v>
+        <v>3.755511291152843</v>
       </c>
       <c r="N30" s="4" t="n">
-        <v>6.486013986013944</v>
+        <v>6.553684964627877</v>
       </c>
       <c r="O30" s="4" t="n">
-        <v>5.3615227675268</v>
+        <v>5.430522897771759</v>
       </c>
       <c r="P30" s="4" t="n">
-        <v>3.601704418030948</v>
+        <v>3.670982482863671</v>
       </c>
       <c r="Q30" s="4" t="n">
-        <v>6.01969625591682</v>
+        <v>6.089762262206285</v>
       </c>
       <c r="R30" s="4" t="n">
-        <v>5.076294767076568</v>
+        <v>5.145687645687644</v>
       </c>
       <c r="S30" s="4" t="n">
-        <v>3.403739534466105</v>
+        <v>3.473308970248631</v>
       </c>
       <c r="T30" s="4" t="n">
-        <v>3.298756118370825</v>
+        <v>3.368468266427449</v>
       </c>
       <c r="U30" s="4" t="n">
-        <v>8.130263896687218</v>
+        <v>8.199744262736353</v>
       </c>
       <c r="V30" s="4" t="n">
-        <v>6.778846153846104</v>
+        <v>6.848128534242832</v>
       </c>
       <c r="W30" s="4" t="n">
-        <v>7.774107283309696</v>
+        <v>7.844043904738349</v>
       </c>
       <c r="X30" s="4" t="n">
-        <v>3.082767612282467</v>
+        <v>3.152813327944628</v>
       </c>
       <c r="Y30" s="4" t="n">
-        <v>7.972927394149217</v>
+        <v>8.042672655811302</v>
       </c>
       <c r="Z30" s="4" t="n">
-        <v>10.97390913180383</v>
+        <v>11.04376347951111</v>
       </c>
     </row>
     <row r="31">
@@ -2675,76 +2675,76 @@
         <v>43</v>
       </c>
       <c r="C31" s="4" t="n">
-        <v>-9.488074894122889</v>
+        <v>-9.45480060180406</v>
       </c>
       <c r="D31" s="4" t="n">
-        <v>6.45581935867461</v>
+        <v>6.489492367287951</v>
       </c>
       <c r="E31" s="4" t="n">
-        <v>0.3649561038908331</v>
+        <v>0.40031052755932</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>-2.674418604651166</v>
+        <v>-2.638224887232262</v>
       </c>
       <c r="G31" s="4" t="n">
-        <v>6.262637191720138</v>
+        <v>6.328310221615816</v>
       </c>
       <c r="H31" s="4" t="n">
-        <v>4.124220409378083</v>
+        <v>4.189695012364353</v>
       </c>
       <c r="I31" s="4" t="n">
-        <v>10.32809846337057</v>
+        <v>10.39449051452052</v>
       </c>
       <c r="J31" s="4" t="n">
-        <v>7.723962422503178</v>
+        <v>7.79069767441861</v>
       </c>
       <c r="K31" s="4" t="n">
-        <v>10.09105988287465</v>
+        <v>10.15776625168215</v>
       </c>
       <c r="L31" s="4" t="n">
-        <v>11.64280586745412</v>
+        <v>11.71043197099456</v>
       </c>
       <c r="M31" s="4" t="n">
-        <v>14.24274652991822</v>
+        <v>14.31007300850525</v>
       </c>
       <c r="N31" s="4" t="n">
-        <v>13.96365262644339</v>
+        <v>14.03132360505732</v>
       </c>
       <c r="O31" s="4" t="n">
-        <v>12.83916140795625</v>
+        <v>12.90816153820121</v>
       </c>
       <c r="P31" s="4" t="n">
-        <v>10.29222320157293</v>
+        <v>10.36150126640565</v>
       </c>
       <c r="Q31" s="4" t="n">
-        <v>11.95887335788449</v>
+        <v>12.02893936417396</v>
       </c>
       <c r="R31" s="4" t="n">
-        <v>12.55393340750582</v>
+        <v>12.62332628611689</v>
       </c>
       <c r="S31" s="4" t="n">
-        <v>12.41983971335692</v>
+        <v>12.48940914913945</v>
       </c>
       <c r="T31" s="4" t="n">
-        <v>7.663693506564101</v>
+        <v>7.733405654620725</v>
       </c>
       <c r="U31" s="4" t="n">
-        <v>12.53097946019358</v>
+        <v>12.60045982624272</v>
       </c>
       <c r="V31" s="4" t="n">
-        <v>15.04360465116285</v>
+        <v>15.11288703155958</v>
       </c>
       <c r="W31" s="4" t="n">
-        <v>7.523660056118395</v>
+        <v>7.593596677547048</v>
       </c>
       <c r="X31" s="4" t="n">
-        <v>5.122123605126951</v>
+        <v>5.192169320789112</v>
       </c>
       <c r="Y31" s="4" t="n">
-        <v>5.396898771609081</v>
+        <v>5.466644033271166</v>
       </c>
       <c r="Z31" s="4" t="n">
-        <v>9.972120223038253</v>
+        <v>10.04197457074553</v>
       </c>
     </row>
     <row r="32">
@@ -2757,76 +2757,76 @@
         <v>34</v>
       </c>
       <c r="C32" s="4" t="n">
-        <v>2.208231535425696</v>
+        <v>2.241505827744525</v>
       </c>
       <c r="D32" s="4" t="n">
-        <v>1.873056020781327</v>
+        <v>1.906729029394668</v>
       </c>
       <c r="E32" s="4" t="n">
-        <v>12.19806143904812</v>
+        <v>12.2334158627166</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>17.36662106703147</v>
+        <v>17.40281478445037</v>
       </c>
       <c r="G32" s="4" t="n">
-        <v>5.236645399654478</v>
+        <v>5.302318429550155</v>
       </c>
       <c r="H32" s="4" t="n">
-        <v>8.364986483249453</v>
+        <v>8.430461086235724</v>
       </c>
       <c r="I32" s="4" t="n">
-        <v>-1.231409060569277</v>
+        <v>-1.16501700941933</v>
       </c>
       <c r="J32" s="4" t="n">
-        <v>4.372389235088676</v>
+        <v>4.439124487004108</v>
       </c>
       <c r="K32" s="4" t="n">
-        <v>7.355081770699584</v>
+        <v>7.421788139507086</v>
       </c>
       <c r="L32" s="4" t="n">
-        <v>6.581246359930113</v>
+        <v>6.648872463470553</v>
       </c>
       <c r="M32" s="4" t="n">
-        <v>-1.967923784719254</v>
+        <v>-1.900597306132227</v>
       </c>
       <c r="N32" s="4" t="n">
-        <v>9.517688194158751</v>
+        <v>9.585359172772684</v>
       </c>
       <c r="O32" s="4" t="n">
-        <v>5.452020505083404</v>
+        <v>5.521020635328362</v>
       </c>
       <c r="P32" s="4" t="n">
-        <v>8.171840164637253</v>
+        <v>8.241118229469976</v>
       </c>
       <c r="Q32" s="4" t="n">
-        <v>4.571732455011663</v>
+        <v>4.641798461301128</v>
       </c>
       <c r="R32" s="4" t="n">
-        <v>8.107968975221404</v>
+        <v>8.17736185383248</v>
       </c>
       <c r="S32" s="4" t="n">
-        <v>13.85622822224887</v>
+        <v>13.9257976580314</v>
       </c>
       <c r="T32" s="4" t="n">
-        <v>13.75124480615364</v>
+        <v>13.82095695421026</v>
       </c>
       <c r="U32" s="4" t="n">
-        <v>11.02619149849722</v>
+        <v>11.09567186454635</v>
       </c>
       <c r="V32" s="4" t="n">
-        <v>14.15441176470588</v>
+        <v>14.22369414510261</v>
       </c>
       <c r="W32" s="4" t="n">
-        <v>16.55238782629616</v>
+        <v>16.62232444772481</v>
       </c>
       <c r="X32" s="4" t="n">
-        <v>13.53525630006528</v>
+        <v>13.60530201572744</v>
       </c>
       <c r="Y32" s="4" t="n">
-        <v>7.927678525370986</v>
+        <v>7.997423787033071</v>
       </c>
       <c r="Z32" s="4" t="n">
-        <v>13.73409012727902</v>
+        <v>13.8039444749863</v>
       </c>
     </row>
     <row r="33">
@@ -2839,76 +2839,76 @@
         <v>32</v>
       </c>
       <c r="C33" s="4" t="n">
-        <v>-3.674121405750817</v>
+        <v>-3.640847113431988</v>
       </c>
       <c r="D33" s="4" t="n">
-        <v>-0.8842969203951014</v>
+        <v>-0.85062391178176</v>
       </c>
       <c r="E33" s="4" t="n">
-        <v>3.926002615518783</v>
+        <v>3.96135703918727</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>0.08720930232558288</v>
+        <v>0.1234030197444866</v>
       </c>
       <c r="G33" s="4" t="n">
-        <v>-0.2780604826984643</v>
+        <v>-0.2123874528027869</v>
       </c>
       <c r="H33" s="4" t="n">
-        <v>-6.340895869691636</v>
+        <v>-6.275421266705365</v>
       </c>
       <c r="I33" s="4" t="n">
-        <v>-7.113762001745663</v>
+        <v>-7.047369950595716</v>
       </c>
       <c r="J33" s="4" t="n">
-        <v>-10.51731664726427</v>
+        <v>-10.45058139534883</v>
       </c>
       <c r="K33" s="4" t="n">
-        <v>-16.72580058224167</v>
+        <v>-16.65909421343417</v>
       </c>
       <c r="L33" s="4" t="n">
-        <v>-14.37463599301106</v>
+        <v>-14.30700988947062</v>
       </c>
       <c r="M33" s="4" t="n">
-        <v>-14.10027672589572</v>
+        <v>-14.0329502473087</v>
       </c>
       <c r="N33" s="4" t="n">
-        <v>-17.50437062937063</v>
+        <v>-17.43669965075669</v>
       </c>
       <c r="O33" s="4" t="n">
-        <v>-12.37886184785781</v>
+        <v>-12.30986171761285</v>
       </c>
       <c r="P33" s="4" t="n">
-        <v>-9.475218658892082</v>
+        <v>-9.405940594059359</v>
       </c>
       <c r="Q33" s="4" t="n">
-        <v>-13.25914989792934</v>
+        <v>-13.18908389163987</v>
       </c>
       <c r="R33" s="4" t="n">
-        <v>-15.78908984830804</v>
+        <v>-15.71969696969697</v>
       </c>
       <c r="S33" s="4" t="n">
-        <v>-6.548183542456968</v>
+        <v>-6.478614106674442</v>
       </c>
       <c r="T33" s="4" t="n">
-        <v>-6.653166958552248</v>
+        <v>-6.583454810495624</v>
       </c>
       <c r="U33" s="4" t="n">
-        <v>-0.1870437956204327</v>
+        <v>-0.1175634295712982</v>
       </c>
       <c r="V33" s="4" t="n">
-        <v>3.125000000000043</v>
+        <v>3.194282380396771</v>
       </c>
       <c r="W33" s="4" t="n">
-        <v>8.831799591002088</v>
+        <v>8.901736212430741</v>
       </c>
       <c r="X33" s="4" t="n">
-        <v>5.630844535359437</v>
+        <v>5.700890251021598</v>
       </c>
       <c r="Y33" s="4" t="n">
-        <v>5.905619701841566</v>
+        <v>5.975364963503651</v>
       </c>
       <c r="Z33" s="4" t="n">
-        <v>-3.545321637426859</v>
+        <v>-3.475467289719582</v>
       </c>
     </row>
     <row r="34">
@@ -2921,76 +2921,76 @@
         <v>20</v>
       </c>
       <c r="C34" s="4" t="n">
-        <v>6.325878594249168</v>
+        <v>6.359152886567998</v>
       </c>
       <c r="D34" s="4" t="n">
-        <v>5.990703079604842</v>
+        <v>6.024376088218183</v>
       </c>
       <c r="E34" s="4" t="n">
-        <v>4.55100261551874</v>
+        <v>4.586357039187227</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>8.837209302325583</v>
+        <v>8.873403019744487</v>
       </c>
       <c r="G34" s="4" t="n">
-        <v>8.471939517301536</v>
+        <v>8.537612547197213</v>
       </c>
       <c r="H34" s="4" t="n">
-        <v>3.659104130308322</v>
+        <v>3.724578733294592</v>
       </c>
       <c r="I34" s="4" t="n">
-        <v>12.88623799825429</v>
+        <v>12.95263004940424</v>
       </c>
       <c r="J34" s="4" t="n">
-        <v>17.60768335273573</v>
+        <v>17.67441860465117</v>
       </c>
       <c r="K34" s="4" t="n">
-        <v>7.649199417758368</v>
+        <v>7.71590578656587</v>
       </c>
       <c r="L34" s="4" t="n">
-        <v>11.87536400698894</v>
+        <v>11.94299011052938</v>
       </c>
       <c r="M34" s="4" t="n">
-        <v>12.14972327410428</v>
+        <v>12.2170497526913</v>
       </c>
       <c r="N34" s="4" t="n">
-        <v>11.87062937062942</v>
+        <v>11.93830034924335</v>
       </c>
       <c r="O34" s="4" t="n">
-        <v>5.746138152142301</v>
+        <v>5.815138282387259</v>
       </c>
       <c r="P34" s="4" t="n">
-        <v>-4.475218658892118</v>
+        <v>-4.405940594059395</v>
       </c>
       <c r="Q34" s="4" t="n">
-        <v>-5.134149897929497</v>
+        <v>-5.064083891640031</v>
       </c>
       <c r="R34" s="4" t="n">
-        <v>-4.539089848308038</v>
+        <v>-4.469696969696962</v>
       </c>
       <c r="S34" s="4" t="n">
-        <v>-4.673183542456897</v>
+        <v>-4.603614106674371</v>
       </c>
       <c r="T34" s="4" t="n">
-        <v>-4.778166958552241</v>
+        <v>-4.708454810495617</v>
       </c>
       <c r="U34" s="4" t="n">
-        <v>-4.562043795620426</v>
+        <v>-4.492563429571291</v>
       </c>
       <c r="V34" s="4" t="n">
-        <v>-4.375000000000071</v>
+        <v>-4.305717619603342</v>
       </c>
       <c r="W34" s="4" t="n">
-        <v>-4.918200408998025</v>
+        <v>-4.848263787569373</v>
       </c>
       <c r="X34" s="4" t="n">
-        <v>-4.994155464640492</v>
+        <v>-4.924109748978331</v>
       </c>
       <c r="Y34" s="4" t="n">
-        <v>-4.719380298158427</v>
+        <v>-4.649635036496342</v>
       </c>
       <c r="Z34" s="4" t="n">
-        <v>-4.795321637426973</v>
+        <v>-4.725467289719695</v>
       </c>
     </row>
   </sheetData>
@@ -3184,489 +3184,489 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3332</v>
+        <v>3336</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>-0.02285463972992829</v>
+        <v>-0.02369915272937106</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>-0.07369763595862366</v>
+        <v>-0.07449228581394607</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>-0.06575849393547628</v>
+        <v>-0.06660691672578878</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>-0.1067047788200028</v>
+        <v>-0.107526658443831</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>-0.1866698530356743</v>
+        <v>-0.1881698671097922</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>-0.311045123423014</v>
+        <v>-0.3123920478622324</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>-0.3206894427728813</v>
+        <v>-0.3220493421853803</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>-0.2537264441579339</v>
+        <v>-0.2551756674252132</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>-0.2250162978078123</v>
+        <v>-0.2264994655976622</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>-0.1748451980319814</v>
+        <v>-0.1764128745452496</v>
       </c>
       <c r="M6" s="4" t="n">
-        <v>-0.1223245584816723</v>
+        <v>-0.1239475599393316</v>
       </c>
       <c r="N6" s="4" t="n">
-        <v>-0.1748251748251661</v>
+        <v>-0.1763949912584906</v>
       </c>
       <c r="O6" s="4" t="n">
-        <v>-0.1452767446570533</v>
+        <v>-0.146917289766975</v>
       </c>
       <c r="P6" s="4" t="n">
-        <v>-0.1394915493768707</v>
+        <v>-0.1411468104371636</v>
       </c>
       <c r="Q6" s="4" t="n">
-        <v>-0.09224627625926729</v>
+        <v>-0.09397925785820149</v>
       </c>
       <c r="R6" s="4" t="n">
-        <v>-0.07801200399667607</v>
+        <v>-0.07974481658692412</v>
       </c>
       <c r="S6" s="4" t="n">
-        <v>0.01534595739328637</v>
+        <v>0.01349627322385771</v>
       </c>
       <c r="T6" s="4" t="n">
-        <v>0.04807630088453863</v>
+        <v>0.04618313085686054</v>
       </c>
       <c r="U6" s="4" t="n">
-        <v>0.0124242894859492</v>
+        <v>0.01057934205396549</v>
       </c>
       <c r="V6" s="4" t="n">
-        <v>-0.112410071942449</v>
+        <v>-0.1141008531362004</v>
       </c>
       <c r="W6" s="4" t="n">
-        <v>-0.1580804689679667</v>
+        <v>-0.1597342877190471</v>
       </c>
       <c r="X6" s="4" t="n">
-        <v>-0.1861170723190284</v>
+        <v>-0.1877406656950029</v>
       </c>
       <c r="Y6" s="4" t="n">
-        <v>-0.1934277028989086</v>
+        <v>-0.1950350964304306</v>
       </c>
       <c r="Z6" s="4" t="n">
-        <v>-0.1914801008122566</v>
+        <v>-0.1930931890002014</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>X &gt; -0.02139</t>
+          <t>X &gt; -0.02138</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>3316</v>
+        <v>3320</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>-0.005358303025424505</v>
+        <v>-0.006387047622816056</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>-0.05483316964617302</v>
+        <v>-0.05581541387633848</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>-0.06991437579081605</v>
+        <v>-0.07093119786754443</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>-0.07765880319001184</v>
+        <v>-0.0786927886387403</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>-0.1262613822486855</v>
+        <v>-0.1281556468728624</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>-0.2221196249406319</v>
+        <v>-0.2238934057107969</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>-0.2280734328888201</v>
+        <v>-0.2298692014198522</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>-0.2194474996052023</v>
+        <v>-0.2212648485862445</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>-0.1607675591254463</v>
+        <v>-0.1626549330743075</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>-0.1066179749930498</v>
+        <v>-0.1085995715342065</v>
       </c>
       <c r="M7" s="4" t="n">
-        <v>-0.1152211536518024</v>
+        <v>-0.1171836706510376</v>
       </c>
       <c r="N7" s="4" t="n">
-        <v>-0.1065340909090864</v>
+        <v>-0.1085183782476946</v>
       </c>
       <c r="O7" s="4" t="n">
-        <v>-0.07141519922537043</v>
+        <v>-0.0734837530376069</v>
       </c>
       <c r="P7" s="4" t="n">
-        <v>-0.09458125660709271</v>
+        <v>-0.09663128475008875</v>
       </c>
       <c r="Q7" s="4" t="n">
-        <v>-0.0439243340196569</v>
+        <v>-0.04606046118036033</v>
       </c>
       <c r="R7" s="4" t="n">
-        <v>-0.03247131641875711</v>
+        <v>-0.03460081585081554</v>
       </c>
       <c r="S7" s="4" t="n">
-        <v>0.1221820910067706</v>
+        <v>0.1198604950688704</v>
       </c>
       <c r="T7" s="4" t="n">
-        <v>0.09540317991854863</v>
+        <v>0.09310862907143047</v>
       </c>
       <c r="U7" s="4" t="n">
-        <v>-0.001670414108843943</v>
+        <v>-0.003841625060019283</v>
       </c>
       <c r="V7" s="4" t="n">
-        <v>-0.1280120481927725</v>
+        <v>-0.1300256821784842</v>
       </c>
       <c r="W7" s="4" t="n">
-        <v>-0.1712886886002423</v>
+        <v>-0.1732713108916002</v>
       </c>
       <c r="X7" s="4" t="n">
-        <v>-0.1990982012288782</v>
+        <v>-0.2010513504233202</v>
       </c>
       <c r="Y7" s="4" t="n">
-        <v>-0.2077734244774021</v>
+        <v>-0.2097073038856863</v>
       </c>
       <c r="Z7" s="4" t="n">
-        <v>-0.2054543274148344</v>
+        <v>-0.2073950005629897</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>X &gt; -0.01979</t>
+          <t>X &gt; -0.01978</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3290</v>
+        <v>3293</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>0.02343368027395343</v>
+        <v>0.008127554843063933</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>-0.1143693841632398</v>
+        <v>-0.1294700656279346</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>-0.02767452129792503</v>
+        <v>-0.04249027523643178</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>-0.0600716644417858</v>
+        <v>-0.07468028843540964</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>-0.0759601502717544</v>
+        <v>-0.09161450594288567</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>-0.1437979253144093</v>
+        <v>-0.1594442204958</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>-0.2344151617094212</v>
+        <v>-0.2195753886622285</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>-0.1025404827149643</v>
+        <v>-0.08774519105750755</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>-0.04369014351242839</v>
+        <v>-0.02895515660220127</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>0.01701049609305727</v>
+        <v>0.001653551714746015</v>
       </c>
       <c r="M8" s="4" t="n">
-        <v>0.06676838460987966</v>
+        <v>0.05129052704096893</v>
       </c>
       <c r="N8" s="4" t="n">
-        <v>0.04749187820054601</v>
+        <v>0.03209762609655797</v>
       </c>
       <c r="O8" s="4" t="n">
-        <v>0.09179098461723356</v>
+        <v>0.07663949304094331</v>
       </c>
       <c r="P8" s="4" t="n">
-        <v>0.07023588656242197</v>
+        <v>0.0551553792981565</v>
       </c>
       <c r="Q8" s="4" t="n">
-        <v>0.09622294232519124</v>
+        <v>0.08128255293907927</v>
       </c>
       <c r="R8" s="4" t="n">
-        <v>0.1031175501152433</v>
+        <v>0.08801281521669324</v>
       </c>
       <c r="S8" s="4" t="n">
-        <v>0.2600891296692041</v>
+        <v>0.2448707418104092</v>
       </c>
       <c r="T8" s="4" t="n">
-        <v>0.2339689637778548</v>
+        <v>0.2187958715292311</v>
       </c>
       <c r="U8" s="4" t="n">
-        <v>0.1041170541519563</v>
+        <v>0.0890011550254286</v>
       </c>
       <c r="V8" s="4" t="n">
-        <v>0.005692167577407758</v>
+        <v>0.0209429809426851</v>
       </c>
       <c r="W8" s="4" t="n">
-        <v>-0.003229258071741015</v>
+        <v>0.01217310563458085</v>
       </c>
       <c r="X8" s="4" t="n">
-        <v>-0.0002307987839387238</v>
+        <v>0.01519222370748707</v>
       </c>
       <c r="Y8" s="4" t="n">
-        <v>-0.01108494720128306</v>
+        <v>-0.02607705228262347</v>
       </c>
       <c r="Z8" s="4" t="n">
-        <v>-0.03848273165182547</v>
+        <v>-0.05343570757568727</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>X &gt; -0.01819</t>
+          <t>X &gt; -0.01818</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3264</v>
+        <v>3268</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>-0.03858748424182323</v>
+        <v>-0.040117851809363</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>-0.2052798783987768</v>
+        <v>-0.2066269512954548</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>-0.1674144316654278</v>
+        <v>-0.1688877160575331</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>-0.07265671472679713</v>
+        <v>-0.07428554473239757</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>-0.02486218845539412</v>
+        <v>-0.02794875490196347</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>-0.06423529687022977</v>
+        <v>-0.0672654541673694</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>-0.08846483624738255</v>
+        <v>-0.0915099810371629</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>0.04670774297963476</v>
+        <v>0.04348072401778325</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>0.136238149078892</v>
+        <v>0.1329024359719</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>0.2036129392647084</v>
+        <v>0.2001503786585701</v>
       </c>
       <c r="M9" s="4" t="n">
-        <v>0.2211300485931389</v>
+        <v>0.2176593229442716</v>
       </c>
       <c r="N9" s="4" t="n">
-        <v>0.2039627039627092</v>
+        <v>0.2004954711945288</v>
       </c>
       <c r="O9" s="4" t="n">
-        <v>0.1659854803865102</v>
+        <v>0.1625002829971294</v>
       </c>
       <c r="P9" s="4" t="n">
-        <v>0.08495238570164076</v>
+        <v>0.08155177933900859</v>
       </c>
       <c r="Q9" s="4" t="n">
-        <v>0.1469377892077546</v>
+        <v>0.1434229743960458</v>
       </c>
       <c r="R9" s="4" t="n">
-        <v>0.1186118631833963</v>
+        <v>0.1151626151626175</v>
       </c>
       <c r="S9" s="4" t="n">
-        <v>0.2779017525598491</v>
+        <v>0.2742484887454069</v>
       </c>
       <c r="T9" s="4" t="n">
-        <v>0.2829951209584536</v>
+        <v>0.2793277185208751</v>
       </c>
       <c r="U9" s="4" t="n">
-        <v>0.1809968896044012</v>
+        <v>0.1774640681372261</v>
       </c>
       <c r="V9" s="4" t="n">
-        <v>0.141523867809056</v>
+        <v>0.1380476615703259</v>
       </c>
       <c r="W9" s="4" t="n">
-        <v>0.1368960097348264</v>
+        <v>0.1333931980620022</v>
       </c>
       <c r="X9" s="4" t="n">
-        <v>0.1099474134978351</v>
+        <v>0.1064712907769447</v>
       </c>
       <c r="Y9" s="4" t="n">
-        <v>0.1274803450268607</v>
+        <v>0.1239960433445759</v>
       </c>
       <c r="Z9" s="4" t="n">
-        <v>0.1311489508083881</v>
+        <v>0.127653885310977</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>X &gt; -0.01659</t>
+          <t>X &gt; -0.01658</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>3212</v>
+        <v>3216</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>0.1434983778658889</v>
+        <v>0.1411843777690223</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>-0.2059574027698829</v>
+        <v>-0.2078660365501577</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>-0.05153372843424364</v>
+        <v>-0.05374181777909826</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>-0.06749366797144063</v>
+        <v>-0.06973665887108638</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>-0.01304965013888904</v>
+        <v>-0.01725607722319467</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>-0.148945405295386</v>
+        <v>-0.1529722871135775</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>-0.0682370714267222</v>
+        <v>-0.07242407988744048</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>0.04262759065395016</v>
+        <v>0.03827999078978195</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>0.2568845742504635</v>
+        <v>0.2522722365813479</v>
       </c>
       <c r="L10" s="4" t="n">
-        <v>0.1518674167843486</v>
+        <v>0.1473244758544539</v>
       </c>
       <c r="M10" s="4" t="n">
-        <v>0.1032116461972947</v>
+        <v>0.09874687254265524</v>
       </c>
       <c r="N10" s="4" t="n">
-        <v>0.028197608842774</v>
+        <v>0.02380220797935806</v>
       </c>
       <c r="O10" s="4" t="n">
-        <v>-0.08538527323784706</v>
+        <v>-0.08972691748886064</v>
       </c>
       <c r="P10" s="4" t="n">
-        <v>-0.07112182462769567</v>
+        <v>-0.07550042046982242</v>
       </c>
       <c r="Q10" s="4" t="n">
-        <v>-0.05963887650750621</v>
+        <v>-0.0640838916399602</v>
       </c>
       <c r="R10" s="4" t="n">
-        <v>-0.004928357624812918</v>
+        <v>-0.009399202947584229</v>
       </c>
       <c r="S10" s="4" t="n">
-        <v>0.190128044992548</v>
+        <v>0.1854023376320981</v>
       </c>
       <c r="T10" s="4" t="n">
-        <v>0.1348224758790693</v>
+        <v>0.130154748784328</v>
       </c>
       <c r="U10" s="4" t="n">
-        <v>0.05872089197670505</v>
+        <v>0.05416119011203335</v>
       </c>
       <c r="V10" s="4" t="n">
-        <v>0.07773631840796469</v>
+        <v>0.0731643679743641</v>
       </c>
       <c r="W10" s="4" t="n">
-        <v>0.1129037900689198</v>
+        <v>0.1082444448009952</v>
       </c>
       <c r="X10" s="4" t="n">
-        <v>0.11785449180001</v>
+        <v>0.1131804934081728</v>
       </c>
       <c r="Y10" s="4" t="n">
-        <v>0.1312266112720053</v>
+        <v>0.126553959462619</v>
       </c>
       <c r="Z10" s="4" t="n">
-        <v>0.1673184621994963</v>
+        <v>0.1625924117729127</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>X &gt; -0.01499</t>
+          <t>X &gt; -0.01498</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>3153</v>
+        <v>3157</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>0.2931330023096521</v>
+        <v>0.2899704966309287</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>-0.0565410148833152</v>
+        <v>-0.05929802313755772</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>0.09605617569518188</v>
+        <v>0.09296496870264548</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>0.03008670541414205</v>
+        <v>0.02700704870262172</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>0.09236826887782712</v>
+        <v>0.08673093510653729</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>0.01356644503553639</v>
+        <v>0.00804330022372568</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>0.01557553768647324</v>
+        <v>0.009970944174241936</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>0.323050976591837</v>
+        <v>0.3170281224576499</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>0.5090479026068522</v>
+        <v>0.5027910324675133</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>0.2902677013369015</v>
+        <v>0.2842073921440118</v>
       </c>
       <c r="M11" s="4" t="n">
-        <v>0.2040505008888616</v>
+        <v>0.1981223078963481</v>
       </c>
       <c r="N11" s="4" t="n">
-        <v>0.06968150333079848</v>
+        <v>0.06389201853961168</v>
       </c>
       <c r="O11" s="4" t="n">
-        <v>-0.02503757478571345</v>
+        <v>-0.03082131357240314</v>
       </c>
       <c r="P11" s="4" t="n">
-        <v>-0.1644377546872491</v>
+        <v>-0.1700706856287084</v>
       </c>
       <c r="Q11" s="4" t="n">
-        <v>-0.1404750086188571</v>
+        <v>-0.1462064437561992</v>
       </c>
       <c r="R11" s="4" t="n">
-        <v>-0.1275112339454978</v>
+        <v>-0.1332040787017092</v>
       </c>
       <c r="S11" s="4" t="n">
-        <v>0.1685886094417626</v>
+        <v>0.1625047302408547</v>
       </c>
       <c r="T11" s="4" t="n">
-        <v>0.05089287050758173</v>
+        <v>0.04494386165107045</v>
       </c>
       <c r="U11" s="4" t="n">
-        <v>0.0009707705606913919</v>
+        <v>-0.004897395415703443</v>
       </c>
       <c r="V11" s="4" t="n">
-        <v>0.1435302502375677</v>
+        <v>0.1374965531268799</v>
       </c>
       <c r="W11" s="4" t="n">
-        <v>0.1895308964519842</v>
+        <v>0.1833817820509509</v>
       </c>
       <c r="X11" s="4" t="n">
-        <v>0.2594103039806654</v>
+        <v>0.2531615394039903</v>
       </c>
       <c r="Y11" s="4" t="n">
-        <v>0.2362316232112533</v>
+        <v>0.2300356411477296</v>
       </c>
       <c r="Z11" s="4" t="n">
-        <v>0.2744531802071037</v>
+        <v>0.2681975819940234</v>
       </c>
     </row>
     <row r="12">
@@ -3676,79 +3676,79 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>3066</v>
+        <v>3070</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>0.2591903456250506</v>
+        <v>0.2550468406579114</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>0.03863054074477645</v>
+        <v>0.03472537670463538</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>0.1389520810192266</v>
+        <v>0.1347232637100291</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>0.2208774811979097</v>
+        <v>0.2164450909419031</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>0.1332036988250351</v>
+        <v>0.1255050690489483</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>0.1117630148738229</v>
+        <v>0.1041124120510659</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>0.07079849128056281</v>
+        <v>0.06309328231645139</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>0.200155773241903</v>
+        <v>0.1922410285008027</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>0.2603646238602764</v>
+        <v>0.2523725612822361</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>0.08964972127465387</v>
+        <v>0.08177091467983644</v>
       </c>
       <c r="M12" s="4" t="n">
-        <v>-0.03929913576905619</v>
+        <v>-0.04697879093503587</v>
       </c>
       <c r="N12" s="4" t="n">
-        <v>-0.07219064236608119</v>
+        <v>-0.07986967022457492</v>
       </c>
       <c r="O12" s="4" t="n">
-        <v>-0.1703389359305731</v>
+        <v>-0.1780457487715239</v>
       </c>
       <c r="P12" s="4" t="n">
-        <v>-0.3724878396463467</v>
+        <v>-0.3799665680853792</v>
       </c>
       <c r="Q12" s="4" t="n">
-        <v>-0.2967515239456873</v>
+        <v>-0.3044216636438577</v>
       </c>
       <c r="R12" s="4" t="n">
-        <v>-0.2677821059528043</v>
+        <v>-0.2754149683974205</v>
       </c>
       <c r="S12" s="4" t="n">
-        <v>0.04045134202073797</v>
+        <v>0.03239499309805893</v>
       </c>
       <c r="T12" s="4" t="n">
-        <v>0.02001012478108777</v>
+        <v>0.0119613143418249</v>
       </c>
       <c r="U12" s="4" t="n">
-        <v>-0.1025843361609731</v>
+        <v>-0.110449608433079</v>
       </c>
       <c r="V12" s="4" t="n">
-        <v>0.03868078175896272</v>
+        <v>0.03065193147024559</v>
       </c>
       <c r="W12" s="4" t="n">
-        <v>0.1013499331330365</v>
+        <v>0.09316152971022973</v>
       </c>
       <c r="X12" s="4" t="n">
-        <v>0.1753360607831596</v>
+        <v>0.1670360843549332</v>
       </c>
       <c r="Y12" s="4" t="n">
-        <v>0.1436780650629572</v>
+        <v>0.1354512546140398</v>
       </c>
       <c r="Z12" s="4" t="n">
-        <v>0.1198773188679425</v>
+        <v>0.1116662607689705</v>
       </c>
     </row>
     <row r="13">
@@ -3758,79 +3758,79 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>2967</v>
+        <v>2971</v>
       </c>
       <c r="C13" s="4" t="n">
-        <v>0.3392565206706024</v>
+        <v>0.33376878503163</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>-0.01130428071629552</v>
+        <v>-0.01638568926257022</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>0.006156564648591711</v>
+        <v>0.0007955418610308129</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>0.01397528826465333</v>
+        <v>0.008474902058090095</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>-0.2989914940849374</v>
+        <v>-0.3085412989566336</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>-0.2604938596414215</v>
+        <v>-0.2700683058489375</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>-0.2437888113971809</v>
+        <v>-0.2535279157898742</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>-0.2350923763960111</v>
+        <v>-0.2448984358577064</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>-0.1744088988076982</v>
+        <v>-0.1842951511434379</v>
       </c>
       <c r="L13" s="4" t="n">
-        <v>-0.3252398172311217</v>
+        <v>-0.3350668408943989</v>
       </c>
       <c r="M13" s="4" t="n">
-        <v>-0.400612296365523</v>
+        <v>-0.410296091812711</v>
       </c>
       <c r="N13" s="4" t="n">
-        <v>-0.5261480714652862</v>
+        <v>-0.5357190942699361</v>
       </c>
       <c r="O13" s="4" t="n">
-        <v>-0.6910680265011493</v>
+        <v>-0.7006229516839042</v>
       </c>
       <c r="P13" s="4" t="n">
-        <v>-0.825571362956623</v>
+        <v>-0.8349912482023072</v>
       </c>
       <c r="Q13" s="4" t="n">
-        <v>-0.7255477473917864</v>
+        <v>-0.7352248312372751</v>
       </c>
       <c r="R13" s="4" t="n">
-        <v>-0.5474932096525791</v>
+        <v>-0.5573102627483308</v>
       </c>
       <c r="S13" s="4" t="n">
-        <v>-0.2246294066129906</v>
+        <v>-0.2349102786019088</v>
       </c>
       <c r="T13" s="4" t="n">
-        <v>-0.2423445569377094</v>
+        <v>-0.2526267957156492</v>
       </c>
       <c r="U13" s="4" t="n">
-        <v>-0.4099576583391453</v>
+        <v>-0.4199827844100099</v>
       </c>
       <c r="V13" s="4" t="n">
-        <v>-0.2703214405923902</v>
+        <v>-0.2805075355696616</v>
       </c>
       <c r="W13" s="4" t="n">
-        <v>-0.1875606783582171</v>
+        <v>-0.197961164838965</v>
       </c>
       <c r="X13" s="4" t="n">
-        <v>-0.2097162595209952</v>
+        <v>-0.2201070580937738</v>
       </c>
       <c r="Y13" s="4" t="n">
-        <v>-0.3528034787514187</v>
+        <v>-0.3629593971962137</v>
       </c>
       <c r="Z13" s="4" t="n">
-        <v>-0.2402154695805976</v>
+        <v>-0.2505430217963678</v>
       </c>
     </row>
     <row r="14">
@@ -3840,1145 +3840,1145 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>2856</v>
+        <v>2860</v>
       </c>
       <c r="C14" s="4" t="n">
-        <v>0.198751119431563</v>
+        <v>0.1919659285382096</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>-0.2566909440226439</v>
+        <v>-0.262924397555544</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>-0.2873706900078474</v>
+        <v>-0.2938928740373541</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>-0.3561147588705182</v>
+        <v>-0.3627080913666205</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>-0.6324083087854149</v>
+        <v>-0.6443950943449863</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>-0.4953843874369852</v>
+        <v>-0.5075268956143759</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>-0.7267101395807245</v>
+        <v>-0.7387151017949236</v>
       </c>
       <c r="J14" s="4" t="n">
-        <v>-0.6374419954536847</v>
+        <v>-0.649642591454537</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>-0.5761576007020963</v>
+        <v>-0.5884420395210839</v>
       </c>
       <c r="L14" s="4" t="n">
-        <v>-0.7378764111295339</v>
+        <v>-0.7501205366522541</v>
       </c>
       <c r="M14" s="4" t="n">
-        <v>-0.8966343417897633</v>
+        <v>-0.9086028752237638</v>
       </c>
       <c r="N14" s="4" t="n">
-        <v>-1.016399918073553</v>
+        <v>-1.02827346691268</v>
       </c>
       <c r="O14" s="4" t="n">
-        <v>-1.214099029580829</v>
+        <v>-1.225962379403136</v>
       </c>
       <c r="P14" s="4" t="n">
-        <v>-1.380312866847468</v>
+        <v>-1.392003311829434</v>
       </c>
       <c r="Q14" s="4" t="n">
-        <v>-1.146366302815984</v>
+        <v>-1.15854189094285</v>
       </c>
       <c r="R14" s="4" t="n">
-        <v>-1.089369177916986</v>
+        <v>-1.101496132876889</v>
       </c>
       <c r="S14" s="4" t="n">
-        <v>-0.8886917506302154</v>
+        <v>-0.9011376504484261</v>
       </c>
       <c r="T14" s="4" t="n">
-        <v>-0.8333731080980229</v>
+        <v>-0.8459286416191389</v>
       </c>
       <c r="U14" s="4" t="n">
-        <v>-0.9461752181999472</v>
+        <v>-0.9585320159587312</v>
       </c>
       <c r="V14" s="4" t="n">
-        <v>-0.7386363636363669</v>
+        <v>-0.7512483458602546</v>
       </c>
       <c r="W14" s="4" t="n">
-        <v>-0.596759345689108</v>
+        <v>-0.6097028375169131</v>
       </c>
       <c r="X14" s="4" t="n">
-        <v>-0.5120001112465786</v>
+        <v>-0.5250880858057982</v>
       </c>
       <c r="Y14" s="4" t="n">
-        <v>-0.6714279005385464</v>
+        <v>-0.6842383220608355</v>
       </c>
       <c r="Z14" s="4" t="n">
-        <v>-0.446582141628582</v>
+        <v>-0.4597330239853505</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>X &gt; -0.008593</t>
+          <t>X &gt; -0.008589</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>2706</v>
+        <v>2710</v>
       </c>
       <c r="C15" s="4" t="n">
-        <v>-0.17467105763793</v>
+        <v>-0.1831083648040845</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>-0.7468335772866226</v>
+        <v>-0.7545404564377165</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>-0.7368595040265475</v>
+        <v>-0.7450234075355837</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>-0.9170093330375906</v>
+        <v>-0.9251317787903091</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>-1.262005436826897</v>
+        <v>-1.277337984132942</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>-1.091262976886981</v>
+        <v>-1.106799565825646</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>-1.109355097595866</v>
+        <v>-1.125111058039835</v>
       </c>
       <c r="J15" s="4" t="n">
-        <v>-0.9999580873818275</v>
+        <v>-1.015970243477959</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>-0.8642147682026717</v>
+        <v>-0.8804244886634862</v>
       </c>
       <c r="L15" s="4" t="n">
-        <v>-1.139341875364003</v>
+        <v>-1.155394617811297</v>
       </c>
       <c r="M15" s="4" t="n">
-        <v>-1.358919609308742</v>
+        <v>-1.374577129424004</v>
       </c>
       <c r="N15" s="4" t="n">
-        <v>-1.470062314433179</v>
+        <v>-1.485652626509818</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>-1.506346205605283</v>
+        <v>-1.522237682331657</v>
       </c>
       <c r="P15" s="4" t="n">
-        <v>-1.706441044753689</v>
+        <v>-1.722117064647641</v>
       </c>
       <c r="Q15" s="4" t="n">
-        <v>-1.570613986327224</v>
+        <v>-1.58670250142297</v>
       </c>
       <c r="R15" s="4" t="n">
-        <v>-1.506665382574809</v>
+        <v>-1.522677102147306</v>
       </c>
       <c r="S15" s="4" t="n">
-        <v>-1.508789882302153</v>
+        <v>-1.524850764753204</v>
       </c>
       <c r="T15" s="4" t="n">
-        <v>-1.334214156192374</v>
+        <v>-1.350575576327728</v>
       </c>
       <c r="U15" s="4" t="n">
-        <v>-1.46540049056695</v>
+        <v>-1.481513705814393</v>
       </c>
       <c r="V15" s="4" t="n">
-        <v>-1.293819188191883</v>
+        <v>-1.310139137657806</v>
       </c>
       <c r="W15" s="4" t="n">
-        <v>-1.298783650046303</v>
+        <v>-1.315274476843165</v>
       </c>
       <c r="X15" s="4" t="n">
-        <v>-1.131526217964051</v>
+        <v>-1.148298539538871</v>
       </c>
       <c r="Y15" s="4" t="n">
-        <v>-1.389125403441028</v>
+        <v>-1.405444700826848</v>
       </c>
       <c r="Z15" s="4" t="n">
-        <v>-1.037006781551078</v>
+        <v>-1.05388057385246</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>X &gt; -0.006994</t>
+          <t>X &gt; -0.006991</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>2520</v>
+        <v>2524</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>-0.5085689087000702</v>
+        <v>-0.5195279143742511</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>-0.547455850371513</v>
+        <v>-0.5584990099750229</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>-0.6674153301719272</v>
+        <v>-0.6788688940151317</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>-0.7690899102728395</v>
+        <v>-0.7806850305699768</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>-0.9550002227536041</v>
+        <v>-0.9767405790316559</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>-0.9035436238287957</v>
+        <v>-0.9253032493962081</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>-0.8662255413594195</v>
+        <v>-0.8883774279668799</v>
       </c>
       <c r="J16" s="4" t="n">
-        <v>-1.083168382280036</v>
+        <v>-1.105108954403953</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>-0.9405441719852234</v>
+        <v>-0.9627078408464982</v>
       </c>
       <c r="L16" s="4" t="n">
-        <v>-1.258021944076567</v>
+        <v>-1.280020133757461</v>
       </c>
       <c r="M16" s="4" t="n">
-        <v>-1.3560011633217</v>
+        <v>-1.377747251644529</v>
       </c>
       <c r="N16" s="4" t="n">
-        <v>-1.336321656226872</v>
+        <v>-1.358229619210952</v>
       </c>
       <c r="O16" s="4" t="n">
-        <v>-1.529642171840386</v>
+        <v>-1.551725622938257</v>
       </c>
       <c r="P16" s="4" t="n">
-        <v>-1.925811544267617</v>
+        <v>-1.947377058147801</v>
       </c>
       <c r="Q16" s="4" t="n">
-        <v>-1.929325856806457</v>
+        <v>-1.951174298272413</v>
       </c>
       <c r="R16" s="4" t="n">
-        <v>-1.944153139447288</v>
+        <v>-1.965747522619559</v>
       </c>
       <c r="S16" s="4" t="n">
-        <v>-1.93673716335131</v>
+        <v>-1.958414580795342</v>
       </c>
       <c r="T16" s="4" t="n">
-        <v>-1.702157457364592</v>
+        <v>-1.724265087175468</v>
       </c>
       <c r="U16" s="4" t="n">
-        <v>-1.819469538194696</v>
+        <v>-1.841317877969871</v>
       </c>
       <c r="V16" s="4" t="n">
-        <v>-1.569928684627577</v>
+        <v>-1.59211002466656</v>
       </c>
       <c r="W16" s="4" t="n">
-        <v>-1.574958236980514</v>
+        <v>-1.597373403714933</v>
       </c>
       <c r="X16" s="4" t="n">
-        <v>-1.469175290175848</v>
+        <v>-1.491805710973658</v>
       </c>
       <c r="Y16" s="4" t="n">
-        <v>-1.84552071862651</v>
+        <v>-1.867456818674569</v>
       </c>
       <c r="Z16" s="4" t="n">
-        <v>-1.422305764411028</v>
+        <v>-1.444960158182383</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>X &gt; -0.005395</t>
+          <t>X &gt; -0.005392</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>2350</v>
+        <v>2353</v>
       </c>
       <c r="C17" s="4" t="n">
-        <v>-0.4898109882054484</v>
+        <v>-0.5040050081688037</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>-0.6337694942347838</v>
+        <v>-0.647906978336124</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>-0.6579463080777188</v>
+        <v>-0.6728085739606868</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>-1.095223130106852</v>
+        <v>-1.109733573847421</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>-1.141495210201626</v>
+        <v>-1.169262189200929</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>-1.142248363351861</v>
+        <v>-1.1699360346379</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>-1.003825426692849</v>
+        <v>-1.032173665243292</v>
       </c>
       <c r="J17" s="4" t="n">
-        <v>-1.089440166722817</v>
+        <v>-1.117811125078561</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>-1.108735410849334</v>
+        <v>-1.137072667173044</v>
       </c>
       <c r="L17" s="4" t="n">
-        <v>-1.6894116068976</v>
+        <v>-1.717195857348891</v>
       </c>
       <c r="M17" s="4" t="n">
-        <v>-1.772343646692001</v>
+        <v>-1.7998635665476</v>
       </c>
       <c r="N17" s="4" t="n">
-        <v>-1.731065544624869</v>
+        <v>-1.758823170215244</v>
       </c>
       <c r="O17" s="4" t="n">
-        <v>-2.026223017845055</v>
+        <v>-2.054095742157877</v>
       </c>
       <c r="P17" s="4" t="n">
-        <v>-2.435354367119437</v>
+        <v>-2.462672177463297</v>
       </c>
       <c r="Q17" s="4" t="n">
-        <v>-2.476110016724498</v>
+        <v>-2.503728110191425</v>
       </c>
       <c r="R17" s="4" t="n">
-        <v>-2.238580510447264</v>
+        <v>-2.266307139188491</v>
       </c>
       <c r="S17" s="4" t="n">
-        <v>-2.372674204596187</v>
+        <v>-2.375975276661727</v>
       </c>
       <c r="T17" s="4" t="n">
-        <v>-2.325937659189194</v>
+        <v>-2.329319950444727</v>
       </c>
       <c r="U17" s="4" t="n">
-        <v>-2.170370048806504</v>
+        <v>-2.173938058336674</v>
       </c>
       <c r="V17" s="4" t="n">
-        <v>-2.171430089247771</v>
+        <v>-2.174987568669486</v>
       </c>
       <c r="W17" s="4" t="n">
-        <v>-2.265139184508158</v>
+        <v>-2.293085519318026</v>
       </c>
       <c r="X17" s="4" t="n">
-        <v>-2.061360909132269</v>
+        <v>-2.089714844519804</v>
       </c>
       <c r="Y17" s="4" t="n">
-        <v>-2.424612114406834</v>
+        <v>-2.427884824091926</v>
       </c>
       <c r="Z17" s="4" t="n">
-        <v>-1.837874828916263</v>
+        <v>-1.841914378542405</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>X &gt; -0.003796</t>
+          <t>X &gt; -0.003793</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>2180</v>
+        <v>2181</v>
       </c>
       <c r="C18" s="4" t="n">
-        <v>-0.01336651716508186</v>
+        <v>-0.0321317253248381</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>-0.7790876392304256</v>
+        <v>-0.7966956647336403</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>-0.9200943348681534</v>
+        <v>-0.9384044328709251</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>-1.199220570169857</v>
+        <v>-1.217506071164607</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>-0.7649625328123548</v>
+        <v>-0.8007230598969244</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>-0.5979605916606872</v>
+        <v>-0.6339290010093137</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>-0.6614136205327554</v>
+        <v>-0.6978023584246102</v>
       </c>
       <c r="J18" s="4" t="n">
-        <v>-1.005455333395659</v>
+        <v>-1.041428389884359</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>-1.075127373661076</v>
+        <v>-1.110973484504747</v>
       </c>
       <c r="L18" s="4" t="n">
-        <v>-1.777604029540747</v>
+        <v>-1.812707245897236</v>
       </c>
       <c r="M18" s="4" t="n">
-        <v>-1.797284491998965</v>
+        <v>-1.832197853327848</v>
       </c>
       <c r="N18" s="4" t="n">
-        <v>-1.86794466959001</v>
+        <v>-1.902940526669106</v>
       </c>
       <c r="O18" s="4" t="n">
-        <v>-2.326564179819357</v>
+        <v>-2.361493392647041</v>
       </c>
       <c r="P18" s="4" t="n">
-        <v>-2.293150955323959</v>
+        <v>-2.328315023283146</v>
       </c>
       <c r="Q18" s="4" t="n">
-        <v>-2.376712826991216</v>
+        <v>-2.412188048789339</v>
       </c>
       <c r="R18" s="4" t="n">
-        <v>-2.304657613875811</v>
+        <v>-2.339898066589107</v>
       </c>
       <c r="S18" s="4" t="n">
-        <v>-2.347176216449647</v>
+        <v>-2.356243279056706</v>
       </c>
       <c r="T18" s="4" t="n">
-        <v>-2.517516477562786</v>
+        <v>-2.526387106927459</v>
       </c>
       <c r="U18" s="4" t="n">
-        <v>-2.50429860771942</v>
+        <v>-2.51315839524635</v>
       </c>
       <c r="V18" s="4" t="n">
-        <v>-2.474495644199905</v>
+        <v>-2.48337329725895</v>
       </c>
       <c r="W18" s="4" t="n">
-        <v>-2.624622427346573</v>
+        <v>-2.659619098924615</v>
       </c>
       <c r="X18" s="4" t="n">
-        <v>-2.333605005924966</v>
+        <v>-2.342799625295399</v>
       </c>
       <c r="Y18" s="4" t="n">
-        <v>-2.838646353204304</v>
+        <v>-2.821037419631089</v>
       </c>
       <c r="Z18" s="4" t="n">
-        <v>-2.134771178711304</v>
+        <v>-2.091354497422515</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>X &gt; -0.002197</t>
+          <t>X &gt; -0.002194</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>1962</v>
+        <v>1960</v>
       </c>
       <c r="C19" s="4" t="n">
-        <v>-0.0648331674872864</v>
+        <v>-0.1595151255409419</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>-1.181014092112299</v>
+        <v>-1.274967677556639</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>-1.43181699034281</v>
+        <v>-1.524754071923887</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>-1.764408493427709</v>
+        <v>-1.856763731139793</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>-1.090528869142574</v>
+        <v>-1.204551254622807</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>-0.9765234000560525</v>
+        <v>-1.09079810029165</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>-1.012496178960895</v>
+        <v>-1.075710031567418</v>
       </c>
       <c r="J19" s="4" t="n">
-        <v>-1.211972169047449</v>
+        <v>-1.224315572564024</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>-1.344718473777363</v>
+        <v>-1.35704254170161</v>
       </c>
       <c r="L19" s="4" t="n">
-        <v>-1.938023416946152</v>
+        <v>-1.949559306601898</v>
       </c>
       <c r="M19" s="4" t="n">
-        <v>-2.142514168818103</v>
+        <v>-2.204856941020665</v>
       </c>
       <c r="N19" s="4" t="n">
-        <v>-1.987238649675199</v>
+        <v>-2.049523090634935</v>
       </c>
       <c r="O19" s="4" t="n">
-        <v>-2.37219602764447</v>
+        <v>-2.433592682079819</v>
       </c>
       <c r="P19" s="4" t="n">
-        <v>-2.412210528810817</v>
+        <v>-2.473487572220911</v>
       </c>
       <c r="Q19" s="4" t="n">
-        <v>-2.482904346327999</v>
+        <v>-2.543758688387932</v>
       </c>
       <c r="R19" s="4" t="n">
-        <v>-2.367167162651896</v>
+        <v>-2.47935634946311</v>
       </c>
       <c r="S19" s="4" t="n">
-        <v>-2.297802057207733</v>
+        <v>-2.380826721120009</v>
       </c>
       <c r="T19" s="4" t="n">
-        <v>-2.424477391122224</v>
+        <v>-2.405655828307324</v>
       </c>
       <c r="U19" s="4" t="n">
-        <v>-2.535567217209035</v>
+        <v>-2.517003348104907</v>
       </c>
       <c r="V19" s="4" t="n">
-        <v>-2.319472745797249</v>
+        <v>-2.301132800448912</v>
       </c>
       <c r="W19" s="4" t="n">
-        <v>-2.527782468121295</v>
+        <v>-2.538024358124567</v>
       </c>
       <c r="X19" s="4" t="n">
-        <v>-2.297927126210389</v>
+        <v>-2.278849810140478</v>
       </c>
       <c r="Y19" s="4" t="n">
-        <v>-2.736709554019804</v>
+        <v>-2.688900717271466</v>
       </c>
       <c r="Z19" s="4" t="n">
-        <v>-2.50684049573475</v>
+        <v>-2.429548922372682</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>X &gt; -0.0005982</t>
+          <t>X &gt; -0.0005956</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>1746</v>
+        <v>1747</v>
       </c>
       <c r="C20" s="4" t="n">
-        <v>0.1545796719576558</v>
+        <v>0.1225937467830818</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>-1.285119848885472</v>
+        <v>-1.314242258327653</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>-1.104874726900341</v>
+        <v>-1.136022564212205</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>-1.958245243128964</v>
+        <v>-1.988274984790657</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>-1.041988851089599</v>
+        <v>-1.102205944010962</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>-1.05079348061318</v>
+        <v>-1.110835568635032</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>-0.9384631969648325</v>
+        <v>-0.9996697802380083</v>
       </c>
       <c r="J20" s="4" t="n">
-        <v>-1.412817786216429</v>
+        <v>-1.473308668076115</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>-1.567324798765846</v>
+        <v>-1.627471132137941</v>
       </c>
       <c r="L20" s="4" t="n">
-        <v>-2.081306460513908</v>
+        <v>-2.141196465124771</v>
       </c>
       <c r="M20" s="4" t="n">
-        <v>-2.231337764115921</v>
+        <v>-2.290633798816948</v>
       </c>
       <c r="N20" s="4" t="n">
-        <v>-1.907909442156011</v>
+        <v>-1.968305573307951</v>
       </c>
       <c r="O20" s="4" t="n">
-        <v>-2.372080008908597</v>
+        <v>-2.432724965476062</v>
       </c>
       <c r="P20" s="4" t="n">
-        <v>-2.422106151753347</v>
+        <v>-2.450410377411735</v>
       </c>
       <c r="Q20" s="4" t="n">
-        <v>-2.110163604382876</v>
+        <v>-2.106297240185313</v>
       </c>
       <c r="R20" s="4" t="n">
-        <v>-1.996232705450907</v>
+        <v>-1.992528019925288</v>
       </c>
       <c r="S20" s="4" t="n">
-        <v>-2.016040685314103</v>
+        <v>-1.979399372236983</v>
       </c>
       <c r="T20" s="4" t="n">
-        <v>-1.802180680679179</v>
+        <v>-1.798688962408818</v>
       </c>
       <c r="U20" s="4" t="n">
-        <v>-2.124972857405325</v>
+        <v>-2.153899808783173</v>
       </c>
       <c r="V20" s="4" t="n">
-        <v>-2.076774470520895</v>
+        <v>-2.105717619603276</v>
       </c>
       <c r="W20" s="4" t="n">
-        <v>-2.128967877497388</v>
+        <v>-2.191120930426436</v>
       </c>
       <c r="X20" s="4" t="n">
-        <v>-2.147649164526008</v>
+        <v>-2.176825586599904</v>
       </c>
       <c r="Y20" s="4" t="n">
-        <v>-2.731980527253512</v>
+        <v>-2.727438240157674</v>
       </c>
       <c r="Z20" s="4" t="n">
-        <v>-2.693374329294031</v>
+        <v>-2.656205698420258</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>X &gt; 0.001001</t>
+          <t>X &gt; 0.001003</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>1560</v>
+        <v>1561</v>
       </c>
       <c r="C21" s="4" t="n">
-        <v>-0.1842736900147557</v>
+        <v>-0.2231255944446318</v>
       </c>
       <c r="D21" s="4" t="n">
-        <v>-1.183900094998293</v>
+        <v>-1.220715742054104</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>-1.001729277746826</v>
+        <v>-1.041019386668289</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>-2.189491269829539</v>
+        <v>-2.226787214878222</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>-1.62984165318192</v>
+        <v>-1.703504204071827</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>-1.407732279621655</v>
+        <v>-1.48177047305461</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>-1.190195122764813</v>
+        <v>-1.265921411840992</v>
       </c>
       <c r="J21" s="4" t="n">
-        <v>-1.178167507684918</v>
+        <v>-1.254379869601848</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>-1.355902623057958</v>
+        <v>-1.431676910635147</v>
       </c>
       <c r="L21" s="4" t="n">
-        <v>-1.711106956635817</v>
+        <v>-1.787118100800988</v>
       </c>
       <c r="M21" s="4" t="n">
-        <v>-2.039293328705433</v>
+        <v>-2.114160438391501</v>
       </c>
       <c r="N21" s="4" t="n">
-        <v>-1.388156571862645</v>
+        <v>-1.465141333357082</v>
       </c>
       <c r="O21" s="4" t="n">
-        <v>-1.453350338906368</v>
+        <v>-1.531800493123015</v>
       </c>
       <c r="P21" s="4" t="n">
-        <v>-1.610768531014884</v>
+        <v>-1.652271162023666</v>
       </c>
       <c r="Q21" s="4" t="n">
-        <v>-1.374559105090547</v>
+        <v>-1.379537276058862</v>
       </c>
       <c r="R21" s="4" t="n">
-        <v>-1.418885244727484</v>
+        <v>-1.386629877045216</v>
       </c>
       <c r="S21" s="4" t="n">
-        <v>-1.29722446317308</v>
+        <v>-1.227655027390554</v>
       </c>
       <c r="T21" s="4" t="n">
-        <v>-1.044961584272016</v>
+        <v>-1.012802636582578</v>
       </c>
       <c r="U21" s="4" t="n">
-        <v>-1.303401029935415</v>
+        <v>-1.308420207064906</v>
       </c>
       <c r="V21" s="4" t="n">
-        <v>-1.463404868673926</v>
+        <v>-1.505206110651869</v>
       </c>
       <c r="W21" s="4" t="n">
-        <v>-1.520764511562056</v>
+        <v>-1.600181946137084</v>
       </c>
       <c r="X21" s="4" t="n">
-        <v>-1.789027259512352</v>
+        <v>-1.830699640213204</v>
       </c>
       <c r="Y21" s="4" t="n">
-        <v>-2.603995682773821</v>
+        <v>-2.607381515369589</v>
       </c>
       <c r="Z21" s="4" t="n">
-        <v>-2.615834457939727</v>
+        <v>-2.582610146862486</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>X &gt; 0.0026</t>
+          <t>X &gt; 0.002602</t>
         </is>
       </c>
       <c r="B22" t="n">
         <v>1365</v>
       </c>
       <c r="C22" s="4" t="n">
-        <v>-0.4424583701661859</v>
+        <v>-0.5589036761585859</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>-1.538366687836977</v>
+        <v>-1.58084887549731</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>-1.194451929935802</v>
+        <v>-1.237898588989971</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>-2.305439897092178</v>
+        <v>-2.34752721281366</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>-1.101986192822281</v>
+        <v>-1.15715489466325</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>-1.457513945493432</v>
+        <v>-1.551584057403076</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>-1.752711673518135</v>
+        <v>-1.847369950595755</v>
       </c>
       <c r="J22" s="4" t="n">
-        <v>-1.333922486680322</v>
+        <v>-1.430384888798621</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>-1.470596053388462</v>
+        <v>-1.566687075779356</v>
       </c>
       <c r="L22" s="4" t="n">
-        <v>-1.326390378975972</v>
+        <v>-1.424356828246133</v>
       </c>
       <c r="M22" s="4" t="n">
-        <v>-1.636826433498065</v>
+        <v>-1.692505316601178</v>
       </c>
       <c r="N22" s="4" t="n">
-        <v>-0.8194291089027956</v>
+        <v>-0.8354222784939225</v>
       </c>
       <c r="O22" s="4" t="n">
-        <v>-0.4088326080916929</v>
+        <v>-0.3828164290810321</v>
       </c>
       <c r="P22" s="4" t="n">
-        <v>-0.4839905887166864</v>
+        <v>-0.4147125238839635</v>
       </c>
       <c r="Q22" s="4" t="n">
-        <v>-0.8505241669352799</v>
+        <v>-0.7804581606458143</v>
       </c>
       <c r="R22" s="4" t="n">
-        <v>-1.059557684565355</v>
+        <v>-0.9901648059542794</v>
       </c>
       <c r="S22" s="4" t="n">
-        <v>-0.8281543026908906</v>
+        <v>-0.7585848669083646</v>
       </c>
       <c r="T22" s="4" t="n">
-        <v>-0.7437851004688554</v>
+        <v>-0.7172267403201857</v>
       </c>
       <c r="U22" s="4" t="n">
-        <v>-1.216509388592613</v>
+        <v>-1.232329511442643</v>
       </c>
       <c r="V22" s="4" t="n">
-        <v>-1.206501831501825</v>
+        <v>-1.264781947088657</v>
       </c>
       <c r="W22" s="4" t="n">
-        <v>-1.163621654419195</v>
+        <v>-1.222532793417251</v>
       </c>
       <c r="X22" s="4" t="n">
-        <v>-1.459356929842023</v>
+        <v>-1.474951007208098</v>
       </c>
       <c r="Y22" s="4" t="n">
-        <v>-2.430003008781149</v>
+        <v>-2.402197261972191</v>
       </c>
       <c r="Z22" s="4" t="n">
-        <v>-3.018764860870128</v>
+        <v>-2.948910513162851</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>X &gt; 0.004199</t>
+          <t>X &gt; 0.004201</t>
         </is>
       </c>
       <c r="B23" t="n">
         <v>1162</v>
       </c>
       <c r="C23" s="4" t="n">
-        <v>-0.8084242286763725</v>
+        <v>-0.7751499363575434</v>
       </c>
       <c r="D23" s="4" t="n">
-        <v>-1.485772540583319</v>
+        <v>-1.452099531969978</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>-0.6158066231467885</v>
+        <v>-0.5804521994783016</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>-0.940187957948396</v>
+        <v>-0.9512334216584222</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>0.1128992430941622</v>
+        <v>0.08166729484477742</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>-0.08017545802786685</v>
+        <v>-0.1590825156361149</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>-0.3755645768530016</v>
+        <v>-0.503315202948194</v>
       </c>
       <c r="J23" s="4" t="n">
-        <v>0.08191015685944336</v>
+        <v>-0.04818413507485531</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>0.0008761159526855522</v>
+        <v>-0.1289956701607764</v>
       </c>
       <c r="L23" s="4" t="n">
-        <v>-0.1211936522193255</v>
+        <v>-0.2525501982184792</v>
       </c>
       <c r="M23" s="4" t="n">
-        <v>-0.01895142469091127</v>
+        <v>-0.1005468138323025</v>
       </c>
       <c r="N23" s="4" t="n">
-        <v>1.251008028116459</v>
+        <v>1.216650864707226</v>
       </c>
       <c r="O23" s="4" t="n">
-        <v>1.503453126324672</v>
+        <v>1.520211369231554</v>
       </c>
       <c r="P23" s="4" t="n">
-        <v>2.056622993431461</v>
+        <v>2.125901058264184</v>
       </c>
       <c r="Q23" s="4" t="n">
-        <v>1.569808793981075</v>
+        <v>1.63987480027054</v>
       </c>
       <c r="R23" s="4" t="n">
-        <v>1.218225125874397</v>
+        <v>1.287618004485473</v>
       </c>
       <c r="S23" s="4" t="n">
-        <v>1.772599590073149</v>
+        <v>1.842169025855675</v>
       </c>
       <c r="T23" s="4" t="n">
-        <v>1.495499134390954</v>
+        <v>1.565211282447578</v>
       </c>
       <c r="U23" s="4" t="n">
-        <v>1.625563777529308</v>
+        <v>1.695044143578443</v>
       </c>
       <c r="V23" s="4" t="n">
-        <v>1.210197934595527</v>
+        <v>1.279480314992256</v>
       </c>
       <c r="W23" s="4" t="n">
-        <v>1.355465683945248</v>
+        <v>1.4254023053739</v>
       </c>
       <c r="X23" s="4" t="n">
-        <v>0.84921802933534</v>
+        <v>0.919263744997501</v>
       </c>
       <c r="Y23" s="4" t="n">
-        <v>-0.3390016406713485</v>
+        <v>-0.2692563790092635</v>
       </c>
       <c r="Z23" s="4" t="n">
-        <v>-1.103411138287491</v>
+        <v>-1.033556790580214</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>X &gt; 0.005798</t>
+          <t>X &gt; 0.005799</t>
         </is>
       </c>
       <c r="B24" t="n">
         <v>978</v>
       </c>
       <c r="C24" s="4" t="n">
-        <v>-1.389857446359933</v>
+        <v>-1.356583154041104</v>
       </c>
       <c r="D24" s="4" t="n">
-        <v>-2.334170016841817</v>
+        <v>-2.300497008228476</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>-1.134276572298525</v>
+        <v>-1.098922148630038</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>-0.5733598033654701</v>
+        <v>-0.5936020563976427</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>0.5421328031611523</v>
+        <v>0.4919272680093982</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>0.3800817270496637</v>
+        <v>0.272802083548406</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>0.3785927383154544</v>
+        <v>0.2115132981352019</v>
       </c>
       <c r="J24" s="4" t="n">
-        <v>0.6689078425316524</v>
+        <v>0.4996218566836887</v>
       </c>
       <c r="K24" s="4" t="n">
-        <v>0.7697305719973855</v>
+        <v>0.5999342707978101</v>
       </c>
       <c r="L24" s="4" t="n">
-        <v>0.5665705509562144</v>
+        <v>0.3951286034010622</v>
       </c>
       <c r="M24" s="4" t="n">
-        <v>-0.07931558070144717</v>
+        <v>-0.1886587080630306</v>
       </c>
       <c r="N24" s="4" t="n">
-        <v>1.175332847111996</v>
+        <v>1.121973818631062</v>
       </c>
       <c r="O24" s="4" t="n">
-        <v>1.891332426170855</v>
+        <v>1.897875769619056</v>
       </c>
       <c r="P24" s="4" t="n">
-        <v>2.385722036404403</v>
+        <v>2.455000101237125</v>
       </c>
       <c r="Q24" s="4" t="n">
-        <v>1.931289774872212</v>
+        <v>2.001355781161678</v>
       </c>
       <c r="R24" s="4" t="n">
-        <v>1.40160544821547</v>
+        <v>1.470998326826546</v>
       </c>
       <c r="S24" s="4" t="n">
-        <v>1.778759197829338</v>
+        <v>1.848328633611864</v>
       </c>
       <c r="T24" s="4" t="n">
-        <v>1.673775781734058</v>
+        <v>1.743487929790682</v>
       </c>
       <c r="U24" s="4" t="n">
-        <v>1.787649455913311</v>
+        <v>1.857129821962445</v>
       </c>
       <c r="V24" s="4" t="n">
-        <v>1.565695296523515</v>
+        <v>1.634977676920244</v>
       </c>
       <c r="W24" s="4" t="n">
-        <v>1.840490797546018</v>
+        <v>1.91042741897467</v>
       </c>
       <c r="X24" s="4" t="n">
-        <v>1.253288298140617</v>
+        <v>1.323334013802778</v>
       </c>
       <c r="Y24" s="4" t="n">
-        <v>0.1988201108395202</v>
+        <v>0.2685653725016053</v>
       </c>
       <c r="Z24" s="4" t="n">
-        <v>-0.7973666272019599</v>
+        <v>-0.7275122794946824</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>X &gt; 0.007397</t>
+          <t>X &gt; 0.007398</t>
         </is>
       </c>
       <c r="B25" t="n">
         <v>816</v>
       </c>
       <c r="C25" s="4" t="n">
-        <v>-2.641314601376557</v>
+        <v>-2.608040309057728</v>
       </c>
       <c r="D25" s="4" t="n">
-        <v>-2.490463384550658</v>
+        <v>-2.456790375937317</v>
       </c>
       <c r="E25" s="4" t="n">
-        <v>-1.257016825550515</v>
+        <v>-1.221662401882028</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>-1.296610649012614</v>
+        <v>-1.327083006986982</v>
       </c>
       <c r="G25" s="4" t="n">
-        <v>0.9628043163271087</v>
+        <v>0.8887668606844557</v>
       </c>
       <c r="H25" s="4" t="n">
-        <v>0.4883724229912403</v>
+        <v>0.3466929495764859</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>-0.09300498098868815</v>
+        <v>-0.3037490514463101</v>
       </c>
       <c r="J25" s="4" t="n">
-        <v>0.7983923991905044</v>
+        <v>0.581961183726591</v>
       </c>
       <c r="K25" s="4" t="n">
-        <v>1.033532343094969</v>
+        <v>0.8157839838862131</v>
       </c>
       <c r="L25" s="4" t="n">
-        <v>1.556736556008545</v>
+        <v>1.333234012968404</v>
       </c>
       <c r="M25" s="4" t="n">
-        <v>1.463448764300352</v>
+        <v>1.313508849150402</v>
       </c>
       <c r="N25" s="4" t="n">
-        <v>1.797099958864663</v>
+        <v>1.718251449487809</v>
       </c>
       <c r="O25" s="4" t="n">
-        <v>2.143196975671643</v>
+        <v>2.137047707111797</v>
       </c>
       <c r="P25" s="4" t="n">
-        <v>3.269879380323559</v>
+        <v>3.339157445156282</v>
       </c>
       <c r="Q25" s="4" t="n">
-        <v>2.978595200109787</v>
+        <v>3.048661206399252</v>
       </c>
       <c r="R25" s="4" t="n">
-        <v>2.225616034044897</v>
+        <v>2.295008912655973</v>
       </c>
       <c r="S25" s="4" t="n">
-        <v>2.459169398719503</v>
+        <v>2.528738834502029</v>
       </c>
       <c r="T25" s="4" t="n">
-        <v>2.109087943408539</v>
+        <v>2.178800091465163</v>
       </c>
       <c r="U25" s="4" t="n">
-        <v>2.4477601259482</v>
+        <v>2.517240491997335</v>
       </c>
       <c r="V25" s="4" t="n">
-        <v>2.144607843137258</v>
+        <v>2.213890223533987</v>
       </c>
       <c r="W25" s="4" t="n">
-        <v>2.336701551786362</v>
+        <v>2.406638173215015</v>
       </c>
       <c r="X25" s="4" t="n">
-        <v>1.770550417712379</v>
+        <v>1.84059613337454</v>
       </c>
       <c r="Y25" s="4" t="n">
-        <v>0.4521883292925466</v>
+        <v>0.5219335909546317</v>
       </c>
       <c r="Z25" s="4" t="n">
-        <v>-0.1139490884072956</v>
+        <v>-0.04409474070001806</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>X &gt; 0.008996</t>
+          <t>X &gt; 0.008997</t>
         </is>
       </c>
       <c r="B26" t="n">
         <v>681</v>
       </c>
       <c r="C26" s="4" t="n">
-        <v>-3.238074894122889</v>
+        <v>-3.20480060180406</v>
       </c>
       <c r="D26" s="4" t="n">
-        <v>-4.154645757604428</v>
+        <v>-4.120972748991086</v>
       </c>
       <c r="E26" s="4" t="n">
-        <v>-2.542020640295206</v>
+        <v>-2.506666216626719</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>-3.033241934937884</v>
+        <v>-3.074271398860162</v>
       </c>
       <c r="G26" s="4" t="n">
-        <v>0.3232514706543057</v>
+        <v>0.2236590588251204</v>
       </c>
       <c r="H26" s="4" t="n">
-        <v>-1.012428716407015</v>
+        <v>-1.188211964379832</v>
       </c>
       <c r="I26" s="4" t="n">
-        <v>-0.6810134637340042</v>
+        <v>-0.9427187878050631</v>
       </c>
       <c r="J26" s="4" t="n">
-        <v>0.7335984332628271</v>
+        <v>0.4619004096002257</v>
       </c>
       <c r="K26" s="4" t="n">
-        <v>1.006970678755437</v>
+        <v>0.7333984979361361</v>
       </c>
       <c r="L26" s="4" t="n">
-        <v>1.346729645755453</v>
+        <v>1.067077701770259</v>
       </c>
       <c r="M26" s="4" t="n">
-        <v>1.474246034750379</v>
+        <v>1.281377238071421</v>
       </c>
       <c r="N26" s="4" t="n">
-        <v>2.07620939999795</v>
+        <v>1.967582926110069</v>
       </c>
       <c r="O26" s="4" t="n">
-        <v>2.273304084594507</v>
+        <v>2.252088429014755</v>
       </c>
       <c r="P26" s="4" t="n">
-        <v>3.079847420403027</v>
+        <v>3.14912548523575</v>
       </c>
       <c r="Q26" s="4" t="n">
-        <v>3.742502084449427</v>
+        <v>3.812568090738893</v>
       </c>
       <c r="R26" s="4" t="n">
-        <v>3.015976230987107</v>
+        <v>3.085369109598183</v>
       </c>
       <c r="S26" s="4" t="n">
-        <v>3.17556829307901</v>
+        <v>3.245137728861536</v>
       </c>
       <c r="T26" s="4" t="n">
-        <v>2.776899120742904</v>
+        <v>2.846611268799528</v>
       </c>
       <c r="U26" s="4" t="n">
-        <v>3.139865161795129</v>
+        <v>3.209345527844263</v>
       </c>
       <c r="V26" s="4" t="n">
-        <v>2.592694566813513</v>
+        <v>2.661976947210242</v>
       </c>
       <c r="W26" s="4" t="n">
-        <v>2.783708548417607</v>
+        <v>2.85364516984626</v>
       </c>
       <c r="X26" s="4" t="n">
-        <v>3.588810761497463</v>
+        <v>3.658856477159624</v>
       </c>
       <c r="Y26" s="4" t="n">
-        <v>2.395157146775489</v>
+        <v>2.464902408437574</v>
       </c>
       <c r="Z26" s="4" t="n">
-        <v>1.585001416904966</v>
+        <v>1.654855764612243</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>X &gt; 0.01059</t>
+          <t>X &gt; 0.0106</t>
         </is>
       </c>
       <c r="B27" t="n">
         <v>544</v>
       </c>
       <c r="C27" s="4" t="n">
-        <v>-5.040241624330029</v>
+        <v>-5.0069673320112</v>
       </c>
       <c r="D27" s="4" t="n">
-        <v>-4.828969051542664</v>
+        <v>-4.795296042929323</v>
       </c>
       <c r="E27" s="4" t="n">
-        <v>-4.265026528379259</v>
+        <v>-4.229672104710772</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>-4.068073029186259</v>
+        <v>-4.031879311767355</v>
       </c>
       <c r="G27" s="4" t="n">
-        <v>-1.336803652097373</v>
+        <v>-1.271130622201696</v>
       </c>
       <c r="H27" s="4" t="n">
-        <v>-2.873742585020146</v>
+        <v>-2.905658060876625</v>
       </c>
       <c r="I27" s="4" t="n">
-        <v>-2.086339698272212</v>
+        <v>-2.220411844949133</v>
       </c>
       <c r="J27" s="4" t="n">
-        <v>-0.6157598707074925</v>
+        <v>-0.8592790274071191</v>
       </c>
       <c r="K27" s="4" t="n">
-        <v>-0.1030941602232787</v>
+        <v>-0.4534931205379564</v>
       </c>
       <c r="L27" s="4" t="n">
-        <v>0.8827169481654096</v>
+        <v>0.5196324462958088</v>
       </c>
       <c r="M27" s="4" t="n">
-        <v>1.157076215280746</v>
+        <v>0.9007791859636924</v>
       </c>
       <c r="N27" s="4" t="n">
-        <v>2.716217605923489</v>
+        <v>2.561010971953927</v>
       </c>
       <c r="O27" s="4" t="n">
-        <v>3.429961681553991</v>
+        <v>3.38394562183673</v>
       </c>
       <c r="P27" s="4" t="n">
-        <v>3.943898988166694</v>
+        <v>4.013177052999417</v>
       </c>
       <c r="Q27" s="4" t="n">
-        <v>4.939379513835284</v>
+        <v>5.00944552012475</v>
       </c>
       <c r="R27" s="4" t="n">
-        <v>4.799145445809607</v>
+        <v>4.868538324420683</v>
       </c>
       <c r="S27" s="4" t="n">
-        <v>5.951816457543032</v>
+        <v>6.021385893325558</v>
       </c>
       <c r="T27" s="4" t="n">
-        <v>5.111538923800694</v>
+        <v>5.181251071857318</v>
       </c>
       <c r="U27" s="4" t="n">
-        <v>5.143838557320741</v>
+        <v>5.213318923369876</v>
       </c>
       <c r="V27" s="4" t="n">
-        <v>4.595588235294116</v>
+        <v>4.664870615690845</v>
       </c>
       <c r="W27" s="4" t="n">
-        <v>4.603858414531466</v>
+        <v>4.673795035960119</v>
       </c>
       <c r="X27" s="4" t="n">
-        <v>4.895550417712379</v>
+        <v>4.96559613337454</v>
       </c>
       <c r="Y27" s="4" t="n">
-        <v>4.251207937135682</v>
+        <v>4.320953198797767</v>
       </c>
       <c r="Z27" s="4" t="n">
-        <v>4.175266597867214</v>
+        <v>4.245120945574492</v>
       </c>
     </row>
     <row r="28">
@@ -4991,76 +4991,76 @@
         <v>424</v>
       </c>
       <c r="C28" s="4" t="n">
-        <v>-3.908863189788356</v>
+        <v>-3.875588897469527</v>
       </c>
       <c r="D28" s="4" t="n">
-        <v>-4.948264056545362</v>
+        <v>-4.914591047932021</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>-3.101579544105675</v>
+        <v>-3.066225120437188</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>-3.111147505186153</v>
+        <v>-3.074953787767249</v>
       </c>
       <c r="G28" s="4" t="n">
-        <v>-1.128999449834616</v>
+        <v>-1.063326419938939</v>
       </c>
       <c r="H28" s="4" t="n">
-        <v>-3.289252677203415</v>
+        <v>-3.223778074217144</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>-2.18418453695697</v>
+        <v>-2.117792485807023</v>
       </c>
       <c r="J28" s="4" t="n">
-        <v>-0.6864342943230923</v>
+        <v>-0.7528114422971939</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>0.6680673422866761</v>
+        <v>0.4623846598053092</v>
       </c>
       <c r="L28" s="4" t="n">
-        <v>2.016873440951194</v>
+        <v>1.802145040106844</v>
       </c>
       <c r="M28" s="4" t="n">
-        <v>1.819534594858993</v>
+        <v>1.606721114193654</v>
       </c>
       <c r="N28" s="4" t="n">
-        <v>3.663082200818053</v>
+        <v>3.585359172772719</v>
       </c>
       <c r="O28" s="4" t="n">
-        <v>4.425383435161102</v>
+        <v>4.494383565406061</v>
       </c>
       <c r="P28" s="4" t="n">
-        <v>4.911573793938068</v>
+        <v>4.980851858770791</v>
       </c>
       <c r="Q28" s="4" t="n">
-        <v>5.667736894523408</v>
+        <v>5.737802900812873</v>
       </c>
       <c r="R28" s="4" t="n">
-        <v>6.02694788754102</v>
+        <v>6.096340766152096</v>
       </c>
       <c r="S28" s="4" t="n">
-        <v>7.543797589618507</v>
+        <v>7.613367025401033</v>
       </c>
       <c r="T28" s="4" t="n">
-        <v>6.731267003711906</v>
+        <v>6.80097915176853</v>
       </c>
       <c r="U28" s="4" t="n">
-        <v>7.654937336455042</v>
+        <v>7.724417702504176</v>
       </c>
       <c r="V28" s="4" t="n">
-        <v>7.841981132075475</v>
+        <v>7.911263512472203</v>
       </c>
       <c r="W28" s="4" t="n">
-        <v>7.29878072307752</v>
+        <v>7.368717344506173</v>
       </c>
       <c r="X28" s="4" t="n">
-        <v>7.222825667434911</v>
+        <v>7.292871383097072</v>
       </c>
       <c r="Y28" s="4" t="n">
-        <v>6.79005366410572</v>
+        <v>6.859798925767805</v>
       </c>
       <c r="Z28" s="4" t="n">
-        <v>6.478263268233469</v>
+        <v>6.548117615940747</v>
       </c>
     </row>
     <row r="29">
@@ -5073,76 +5073,76 @@
         <v>330</v>
       </c>
       <c r="C29" s="4" t="n">
-        <v>-5.033638022064999</v>
+        <v>-5.000363729746169</v>
       </c>
       <c r="D29" s="4" t="n">
-        <v>-2.951895107706306</v>
+        <v>-2.918222099092965</v>
       </c>
       <c r="E29" s="4" t="n">
-        <v>-1.06833273191328</v>
+        <v>-1.032978308244793</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>-1.782126045106438</v>
+        <v>-1.745932327687534</v>
       </c>
       <c r="G29" s="4" t="n">
-        <v>1.175867009748664</v>
+        <v>1.241540039644342</v>
       </c>
       <c r="H29" s="4" t="n">
-        <v>-1.658116413498327</v>
+        <v>-1.592641810512056</v>
       </c>
       <c r="I29" s="4" t="n">
-        <v>-0.3161789201747069</v>
+        <v>-0.24978686902476</v>
       </c>
       <c r="J29" s="4" t="n">
-        <v>1.822184863309744</v>
+        <v>1.888920115225176</v>
       </c>
       <c r="K29" s="4" t="n">
-        <v>3.255260023818977</v>
+        <v>3.138866511641396</v>
       </c>
       <c r="L29" s="4" t="n">
-        <v>3.693545825170752</v>
+        <v>3.574410050106415</v>
       </c>
       <c r="M29" s="4" t="n">
-        <v>3.058814183195189</v>
+        <v>2.942125281392215</v>
       </c>
       <c r="N29" s="4" t="n">
-        <v>4.597902097902107</v>
+        <v>4.476064699696479</v>
       </c>
       <c r="O29" s="4" t="n">
-        <v>4.988562394566479</v>
+        <v>5.057562524811438</v>
       </c>
       <c r="P29" s="4" t="n">
-        <v>5.070235886562422</v>
+        <v>5.139513951395145</v>
       </c>
       <c r="Q29" s="4" t="n">
-        <v>5.926456162676637</v>
+        <v>5.996522168966102</v>
       </c>
       <c r="R29" s="4" t="n">
-        <v>5.915455606237408</v>
+        <v>5.984848484848484</v>
       </c>
       <c r="S29" s="4" t="n">
-        <v>7.296513427240001</v>
+        <v>7.366082863022527</v>
       </c>
       <c r="T29" s="4" t="n">
-        <v>6.585469405084126</v>
+        <v>6.65518155314075</v>
       </c>
       <c r="U29" s="4" t="n">
-        <v>9.225834992258349</v>
+        <v>9.295315358307484</v>
       </c>
       <c r="V29" s="4" t="n">
-        <v>10.01893939393939</v>
+        <v>10.08822177433612</v>
       </c>
       <c r="W29" s="4" t="n">
-        <v>8.869678378880828</v>
+        <v>8.93961500030948</v>
       </c>
       <c r="X29" s="4" t="n">
-        <v>8.490693020207921</v>
+        <v>8.560738735870082</v>
       </c>
       <c r="Y29" s="4" t="n">
-        <v>8.159407580629455</v>
+        <v>8.229152842291541</v>
       </c>
       <c r="Z29" s="4" t="n">
-        <v>8.99255715045188</v>
+        <v>9.062411498159157</v>
       </c>
     </row>
     <row r="30">
@@ -5155,76 +5155,76 @@
         <v>263</v>
       </c>
       <c r="C30" s="4" t="n">
-        <v>-3.484007337309734</v>
+        <v>-3.450733044990905</v>
       </c>
       <c r="D30" s="4" t="n">
-        <v>-0.3971296200148942</v>
+        <v>-0.3634566114015527</v>
       </c>
       <c r="E30" s="4" t="n">
-        <v>3.486363832248784</v>
+        <v>3.521718255917271</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>3.533026792819882</v>
+        <v>3.569220510238786</v>
       </c>
       <c r="G30" s="4" t="n">
-        <v>5.449125829088608</v>
+        <v>5.514798858984285</v>
       </c>
       <c r="H30" s="4" t="n">
-        <v>1.834009073274096</v>
+        <v>1.899483676260367</v>
       </c>
       <c r="I30" s="4" t="n">
-        <v>3.342511762512842</v>
+        <v>3.408903813662789</v>
       </c>
       <c r="J30" s="4" t="n">
-        <v>4.584869664522806</v>
+        <v>4.651604916438238</v>
       </c>
       <c r="K30" s="4" t="n">
-        <v>4.246157592663316</v>
+        <v>4.312863961470818</v>
       </c>
       <c r="L30" s="4" t="n">
-        <v>6.514147276950915</v>
+        <v>6.581773380491356</v>
       </c>
       <c r="M30" s="4" t="n">
-        <v>5.267593996537734</v>
+        <v>5.334920475124761</v>
       </c>
       <c r="N30" s="4" t="n">
-        <v>8.410553325001999</v>
+        <v>8.478224303615931</v>
       </c>
       <c r="O30" s="4" t="n">
-        <v>7.666290243396979</v>
+        <v>7.735290373641938</v>
       </c>
       <c r="P30" s="4" t="n">
-        <v>7.825161569244749</v>
+        <v>7.894439634077472</v>
       </c>
       <c r="Q30" s="4" t="n">
-        <v>7.926686603971724</v>
+        <v>7.99675261026119</v>
       </c>
       <c r="R30" s="4" t="n">
-        <v>7.761290379828829</v>
+        <v>7.830683258439905</v>
       </c>
       <c r="S30" s="4" t="n">
-        <v>8.767881096326292</v>
+        <v>8.837450532108818</v>
       </c>
       <c r="T30" s="4" t="n">
-        <v>8.282669543348902</v>
+        <v>8.352381691405526</v>
       </c>
       <c r="U30" s="4" t="n">
-        <v>10.78016152757349</v>
+        <v>10.84964189362262</v>
       </c>
       <c r="V30" s="4" t="n">
-        <v>12.10788973384031</v>
+        <v>12.17717211423704</v>
       </c>
       <c r="W30" s="4" t="n">
-        <v>11.94491746172448</v>
+        <v>12.01485408315313</v>
       </c>
       <c r="X30" s="4" t="n">
-        <v>10.34804985855336</v>
+        <v>10.41809557421552</v>
       </c>
       <c r="Y30" s="4" t="n">
-        <v>10.62282502503549</v>
+        <v>10.69257028669757</v>
       </c>
       <c r="Z30" s="4" t="n">
-        <v>11.30733995953127</v>
+        <v>11.37719430723855</v>
       </c>
     </row>
     <row r="31">
@@ -5237,76 +5237,76 @@
         <v>198</v>
       </c>
       <c r="C31" s="4" t="n">
-        <v>-3.169070900700291</v>
+        <v>-3.135796608381462</v>
       </c>
       <c r="D31" s="4" t="n">
-        <v>0.5361576250594169</v>
+        <v>0.5698306336727583</v>
       </c>
       <c r="E31" s="4" t="n">
-        <v>4.146962211478332</v>
+        <v>4.182316635146819</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>4.443269908386192</v>
+        <v>4.479463625805096</v>
       </c>
       <c r="G31" s="4" t="n">
-        <v>6.098202143564166</v>
+        <v>6.163875173459843</v>
       </c>
       <c r="H31" s="4" t="n">
-        <v>3.760114231318418</v>
+        <v>3.825588834304689</v>
       </c>
       <c r="I31" s="4" t="n">
-        <v>5.007450119466419</v>
+        <v>5.073842170616366</v>
       </c>
       <c r="J31" s="4" t="n">
-        <v>6.749097494149879</v>
+        <v>6.815832746065311</v>
       </c>
       <c r="K31" s="4" t="n">
-        <v>5.780512549071496</v>
+        <v>5.847218917878998</v>
       </c>
       <c r="L31" s="4" t="n">
-        <v>9.047081178706115</v>
+        <v>9.114707282246556</v>
       </c>
       <c r="M31" s="4" t="n">
-        <v>5.786086910467908</v>
+        <v>5.853413389054936</v>
       </c>
       <c r="N31" s="4" t="n">
-        <v>9.04234654234655</v>
+        <v>9.110017520960483</v>
       </c>
       <c r="O31" s="4" t="n">
-        <v>8.422905828909911</v>
+        <v>8.49190595915487</v>
       </c>
       <c r="P31" s="4" t="n">
-        <v>9.211650027976553</v>
+        <v>9.280928092809276</v>
       </c>
       <c r="Q31" s="4" t="n">
-        <v>8.552718788939252</v>
+        <v>8.622784795228718</v>
       </c>
       <c r="R31" s="4" t="n">
-        <v>8.642728333510128</v>
+        <v>8.712121212121204</v>
       </c>
       <c r="S31" s="4" t="n">
-        <v>10.52883665956323</v>
+        <v>10.59840609534575</v>
       </c>
       <c r="T31" s="4" t="n">
-        <v>9.918802738417455</v>
+        <v>9.988514886474078</v>
       </c>
       <c r="U31" s="4" t="n">
-        <v>11.65007741650079</v>
+        <v>11.71955778254992</v>
       </c>
       <c r="V31" s="4" t="n">
-        <v>13.85732323232324</v>
+        <v>13.92660561271997</v>
       </c>
       <c r="W31" s="4" t="n">
-        <v>13.31412282332528</v>
+        <v>13.38405944475394</v>
       </c>
       <c r="X31" s="4" t="n">
-        <v>12.73311726263217</v>
+        <v>12.80316297829433</v>
       </c>
       <c r="Y31" s="4" t="n">
-        <v>11.49274091396278</v>
+        <v>11.56248617562487</v>
       </c>
       <c r="Z31" s="4" t="n">
-        <v>11.41679957469432</v>
+        <v>11.48665392240159</v>
       </c>
     </row>
     <row r="32">
@@ -5319,76 +5319,76 @@
         <v>155</v>
       </c>
       <c r="C32" s="4" t="n">
-        <v>-1.416056889621764</v>
+        <v>-1.382782597302935</v>
       </c>
       <c r="D32" s="4" t="n">
-        <v>-1.106071113943507</v>
+        <v>-1.072398105330166</v>
       </c>
       <c r="E32" s="4" t="n">
-        <v>5.196163905841317</v>
+        <v>5.231518329509804</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>6.41785446361591</v>
+        <v>6.454048181034814</v>
       </c>
       <c r="G32" s="4" t="n">
-        <v>6.052584678591863</v>
+        <v>6.11825770848754</v>
       </c>
       <c r="H32" s="4" t="n">
-        <v>3.659104130308322</v>
+        <v>3.724578733294592</v>
       </c>
       <c r="I32" s="4" t="n">
-        <v>3.531399288576871</v>
+        <v>3.597791339726818</v>
       </c>
       <c r="J32" s="4" t="n">
-        <v>6.478651094671214</v>
+        <v>6.545386346586646</v>
       </c>
       <c r="K32" s="4" t="n">
-        <v>4.584683288726112</v>
+        <v>4.651389657533613</v>
       </c>
       <c r="L32" s="4" t="n">
-        <v>8.326976910214746</v>
+        <v>8.394603013755187</v>
       </c>
       <c r="M32" s="4" t="n">
-        <v>3.440045854749435</v>
+        <v>3.507372333336463</v>
       </c>
       <c r="N32" s="4" t="n">
-        <v>7.677080983532605</v>
+        <v>7.744751962146537</v>
       </c>
       <c r="O32" s="4" t="n">
-        <v>7.197751055368037</v>
+        <v>7.266751185612996</v>
       </c>
       <c r="P32" s="4" t="n">
-        <v>8.911878115301427</v>
+        <v>8.98115618013415</v>
       </c>
       <c r="Q32" s="4" t="n">
-        <v>7.607785585941535</v>
+        <v>7.677851592231001</v>
       </c>
       <c r="R32" s="4" t="n">
-        <v>7.557684345240354</v>
+        <v>7.62707722385143</v>
       </c>
       <c r="S32" s="4" t="n">
-        <v>10.00423581238174</v>
+        <v>10.07380524816426</v>
       </c>
       <c r="T32" s="4" t="n">
-        <v>10.54441368660905</v>
+        <v>10.61412583466567</v>
       </c>
       <c r="U32" s="4" t="n">
-        <v>11.40569813986344</v>
+        <v>11.47517850591257</v>
       </c>
       <c r="V32" s="4" t="n">
-        <v>13.52822580645162</v>
+        <v>13.59750818684834</v>
       </c>
       <c r="W32" s="4" t="n">
-        <v>14.92050926842141</v>
+        <v>14.99044588985006</v>
       </c>
       <c r="X32" s="4" t="n">
-        <v>14.8445542127788</v>
+        <v>14.91459992844096</v>
       </c>
       <c r="Y32" s="4" t="n">
-        <v>13.18384550829318</v>
+        <v>13.25359076995527</v>
       </c>
       <c r="Z32" s="4" t="n">
-        <v>11.81758158837956</v>
+        <v>11.88743593608684</v>
       </c>
     </row>
     <row r="33">
@@ -5401,76 +5401,76 @@
         <v>121</v>
       </c>
       <c r="C33" s="4" t="n">
-        <v>-2.434451984263198</v>
+        <v>-2.401177691944369</v>
       </c>
       <c r="D33" s="4" t="n">
-        <v>-1.943181217915779</v>
+        <v>-1.909508209302437</v>
       </c>
       <c r="E33" s="4" t="n">
-        <v>3.228688565931968</v>
+        <v>3.264042989600455</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>3.341341533730542</v>
+        <v>3.377535251149446</v>
       </c>
       <c r="G33" s="4" t="n">
-        <v>6.281856872673437</v>
+        <v>6.347529902569114</v>
       </c>
       <c r="H33" s="4" t="n">
-        <v>2.336790080721549</v>
+        <v>2.40226468370782</v>
       </c>
       <c r="I33" s="4" t="n">
-        <v>4.869709072634464</v>
+        <v>4.936101123784411</v>
       </c>
       <c r="J33" s="4" t="n">
-        <v>7.070493270091106</v>
+        <v>7.137228522006538</v>
       </c>
       <c r="K33" s="4" t="n">
-        <v>3.806224211146791</v>
+        <v>3.872930579954293</v>
       </c>
       <c r="L33" s="4" t="n">
-        <v>8.817512767319521</v>
+        <v>8.885138870859961</v>
       </c>
       <c r="M33" s="4" t="n">
-        <v>4.959640629476176</v>
+        <v>5.026967108063204</v>
       </c>
       <c r="N33" s="4" t="n">
-        <v>7.159885568976492</v>
+        <v>7.227556547590424</v>
       </c>
       <c r="O33" s="4" t="n">
-        <v>7.688286912472812</v>
+        <v>7.75728704271777</v>
       </c>
       <c r="P33" s="4" t="n">
-        <v>9.119822663421935</v>
+        <v>9.189100728254658</v>
       </c>
       <c r="Q33" s="4" t="n">
-        <v>8.460891424384634</v>
+        <v>8.5309574306741</v>
       </c>
       <c r="R33" s="4" t="n">
-        <v>7.403058912022537</v>
+        <v>7.472451790633613</v>
       </c>
       <c r="S33" s="4" t="n">
-        <v>8.921857779857092</v>
+        <v>8.991427215639618</v>
       </c>
       <c r="T33" s="4" t="n">
-        <v>9.643320644753544</v>
+        <v>9.713032792810168</v>
       </c>
       <c r="U33" s="4" t="n">
-        <v>11.51233636966882</v>
+        <v>11.58181673571796</v>
       </c>
       <c r="V33" s="4" t="n">
-        <v>13.35227272727273</v>
+        <v>13.42155510766946</v>
       </c>
       <c r="W33" s="4" t="n">
-        <v>14.46196488025824</v>
+        <v>14.5319015016869</v>
       </c>
       <c r="X33" s="4" t="n">
-        <v>15.21245610560738</v>
+        <v>15.28250182126954</v>
       </c>
       <c r="Y33" s="4" t="n">
-        <v>14.66078499109776</v>
+        <v>14.73053025275985</v>
       </c>
       <c r="Z33" s="4" t="n">
-        <v>11.27905852786235</v>
+        <v>11.34891287556963</v>
       </c>
     </row>
     <row r="34">
@@ -5483,76 +5483,76 @@
         <v>89</v>
       </c>
       <c r="C34" s="4" t="n">
-        <v>-1.988728147323826</v>
+        <v>-1.955453855004997</v>
       </c>
       <c r="D34" s="4" t="n">
-        <v>-2.323903661968153</v>
+        <v>-2.290230653354811</v>
       </c>
       <c r="E34" s="4" t="n">
-        <v>2.977968907653569</v>
+        <v>3.013323331322056</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>4.511366605696374</v>
+        <v>4.547560323115277</v>
       </c>
       <c r="G34" s="4" t="n">
-        <v>8.640478843144237</v>
+        <v>8.706151873039914</v>
       </c>
       <c r="H34" s="4" t="n">
-        <v>5.456856939297083</v>
+        <v>5.522331542283354</v>
       </c>
       <c r="I34" s="4" t="n">
-        <v>9.178372829714966</v>
+        <v>9.244764880864913</v>
       </c>
       <c r="J34" s="4" t="n">
-        <v>13.39420020666832</v>
+        <v>13.46093545858375</v>
       </c>
       <c r="K34" s="4" t="n">
-        <v>11.18852526045499</v>
+        <v>11.2552316292625</v>
       </c>
       <c r="L34" s="4" t="n">
-        <v>17.15626288339343</v>
+        <v>17.22388898693387</v>
       </c>
       <c r="M34" s="4" t="n">
-        <v>11.81264462241889</v>
+        <v>11.87997110100591</v>
       </c>
       <c r="N34" s="4" t="n">
-        <v>16.0279327414159</v>
+        <v>16.09560372002983</v>
       </c>
       <c r="O34" s="4" t="n">
-        <v>14.90344152292875</v>
+        <v>14.97244165317371</v>
       </c>
       <c r="P34" s="4" t="n">
-        <v>15.80568021751237</v>
+        <v>15.87495828234509</v>
       </c>
       <c r="Q34" s="4" t="n">
-        <v>16.27034448409304</v>
+        <v>16.3404104903825</v>
       </c>
       <c r="R34" s="4" t="n">
-        <v>15.74180902809645</v>
+        <v>15.81120190670752</v>
       </c>
       <c r="S34" s="4" t="n">
-        <v>14.48411982832955</v>
+        <v>14.55368926411208</v>
       </c>
       <c r="T34" s="4" t="n">
-        <v>15.50273191785224</v>
+        <v>15.57244406590887</v>
       </c>
       <c r="U34" s="4" t="n">
-        <v>15.71885508078406</v>
+        <v>15.78833544683319</v>
       </c>
       <c r="V34" s="4" t="n">
-        <v>17.02949438202246</v>
+        <v>17.09877676241919</v>
       </c>
       <c r="W34" s="4" t="n">
-        <v>16.48629397302451</v>
+        <v>16.55623059445316</v>
       </c>
       <c r="X34" s="4" t="n">
-        <v>18.65752992861787</v>
+        <v>18.72757564428003</v>
       </c>
       <c r="Y34" s="4" t="n">
-        <v>17.80870958948201</v>
+        <v>17.8784548511441</v>
       </c>
       <c r="Z34" s="4" t="n">
-        <v>16.60917274459556</v>
+        <v>16.67902709230284</v>
       </c>
     </row>
     <row r="35">
@@ -5565,76 +5565,76 @@
         <v>69</v>
       </c>
       <c r="C35" s="4" t="n">
-        <v>-4.398759086910211</v>
+        <v>-4.365484794591382</v>
       </c>
       <c r="D35" s="4" t="n">
-        <v>-4.733934601554537</v>
+        <v>-4.700261592941196</v>
       </c>
       <c r="E35" s="4" t="n">
-        <v>2.522017108272365</v>
+        <v>2.557371531940852</v>
       </c>
       <c r="F35" s="4" t="n">
-        <v>3.257499157398044</v>
+        <v>3.293692874816948</v>
       </c>
       <c r="G35" s="4" t="n">
-        <v>8.689330821649364</v>
+        <v>8.755003851545041</v>
       </c>
       <c r="H35" s="4" t="n">
-        <v>5.977944710018463</v>
+        <v>6.043419313004733</v>
       </c>
       <c r="I35" s="4" t="n">
-        <v>8.103629302602123</v>
+        <v>8.17002135375207</v>
       </c>
       <c r="J35" s="4" t="n">
-        <v>12.17290074404008</v>
+        <v>12.23963599595551</v>
       </c>
       <c r="K35" s="4" t="n">
-        <v>12.21441680906271</v>
+        <v>12.28112317787021</v>
       </c>
       <c r="L35" s="4" t="n">
-        <v>18.68695820988749</v>
+        <v>18.75458431342793</v>
       </c>
       <c r="M35" s="4" t="n">
-        <v>11.71494066540862</v>
+        <v>11.78226714399565</v>
       </c>
       <c r="N35" s="4" t="n">
-        <v>17.23294821120909</v>
+        <v>17.30061918982302</v>
       </c>
       <c r="O35" s="4" t="n">
-        <v>17.55773235504078</v>
+        <v>17.62673248528574</v>
       </c>
       <c r="P35" s="4" t="n">
-        <v>21.68420163096295</v>
+        <v>21.75347969579568</v>
       </c>
       <c r="Q35" s="4" t="n">
-        <v>22.47454575424448</v>
+        <v>22.54461176053395</v>
       </c>
       <c r="R35" s="4" t="n">
-        <v>21.62033044154703</v>
+        <v>21.68972332015811</v>
       </c>
       <c r="S35" s="4" t="n">
-        <v>20.03696138507927</v>
+        <v>20.10653082086179</v>
       </c>
       <c r="T35" s="4" t="n">
-        <v>21.38125333130283</v>
+        <v>21.45096547935945</v>
       </c>
       <c r="U35" s="4" t="n">
-        <v>21.59737649423464</v>
+        <v>21.66685686028378</v>
       </c>
       <c r="V35" s="4" t="n">
-        <v>23.23369565217391</v>
+        <v>23.30297803257064</v>
       </c>
       <c r="W35" s="4" t="n">
-        <v>22.69049524317595</v>
+        <v>22.76043186460461</v>
       </c>
       <c r="X35" s="4" t="n">
-        <v>25.51309091217103</v>
+        <v>25.58313662783319</v>
       </c>
       <c r="Y35" s="4" t="n">
-        <v>24.33859071633432</v>
+        <v>24.4083359779964</v>
       </c>
       <c r="Z35" s="4" t="n">
-        <v>22.813374014747</v>
+        <v>22.88322836245428</v>
       </c>
     </row>
   </sheetData>
@@ -5831,486 +5831,486 @@
         <v>69</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>-5.848034449229054</v>
+        <v>-5.814760156910225</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>-6.183209963873381</v>
+        <v>-6.149536955260039</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>-7.622910427959518</v>
+        <v>-7.587556004291031</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>-6.887428378833832</v>
+        <v>-6.851234661414928</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>-2.904872076901356</v>
+        <v>-2.839199047005678</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>3.079393985380783</v>
+        <v>3.144868588367054</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>3.755803215645606</v>
+        <v>3.822195266795553</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>0.5786978454893585</v>
+        <v>0.6454330974047906</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>-0.8290614518068509</v>
+        <v>-0.7623550829993491</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>-3.052172224895116</v>
+        <v>-2.984546121354676</v>
       </c>
       <c r="M6" s="4" t="n">
-        <v>-5.676363682417467</v>
+        <v>-5.609037203830439</v>
       </c>
       <c r="N6" s="4" t="n">
-        <v>-3.056906861254681</v>
+        <v>-2.989235882640749</v>
       </c>
       <c r="O6" s="4" t="n">
-        <v>-4.181398079741825</v>
+        <v>-4.112397949496867</v>
       </c>
       <c r="P6" s="4" t="n">
-        <v>-4.40275489077618</v>
+        <v>-4.333476825943457</v>
       </c>
       <c r="Q6" s="4" t="n">
-        <v>-6.510961492132317</v>
+        <v>-6.440895485842852</v>
       </c>
       <c r="R6" s="4" t="n">
-        <v>-7.365176804829787</v>
+        <v>-7.295783926218711</v>
       </c>
       <c r="S6" s="4" t="n">
-        <v>-11.84709658593523</v>
+        <v>-11.7775271501527</v>
       </c>
       <c r="T6" s="4" t="n">
-        <v>-13.40135536434935</v>
+        <v>-13.33164321629273</v>
       </c>
       <c r="U6" s="4" t="n">
-        <v>-11.73595683909869</v>
+        <v>-11.66647647304956</v>
       </c>
       <c r="V6" s="4" t="n">
-        <v>-5.751811594202891</v>
+        <v>-5.682529213806163</v>
       </c>
       <c r="W6" s="4" t="n">
-        <v>-3.396461278563173</v>
+        <v>-3.32652465713452</v>
       </c>
       <c r="X6" s="4" t="n">
-        <v>-2.023140971886939</v>
+        <v>-1.953095256224778</v>
       </c>
       <c r="Y6" s="4" t="n">
-        <v>-1.748365805404809</v>
+        <v>-1.678620543742724</v>
       </c>
       <c r="Z6" s="4" t="n">
-        <v>-1.824307144673277</v>
+        <v>-1.754452796966</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>X &lt; -0.02139</t>
+          <t>X &lt; -0.02138</t>
         </is>
       </c>
       <c r="B7" t="n">
         <v>85</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>-5.438827288103738</v>
+        <v>-5.405552995784909</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>-5.774002802748065</v>
+        <v>-5.740329794134723</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>-6.037232678598905</v>
+        <v>-6.001878254930418</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>-6.751025991792062</v>
+        <v>-6.714832274373158</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>-4.763354600345515</v>
+        <v>-4.697681570449838</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>-1.046778222632852</v>
+        <v>-0.9813036196465816</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>-0.6431737664515893</v>
+        <v>-0.5767817153016424</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>-0.9217284119701503</v>
+        <v>-0.8549931600547183</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>-3.233153523418103</v>
+        <v>-3.166447154610601</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>-5.183459522422822</v>
+        <v>-5.115833418882382</v>
       </c>
       <c r="M7" s="4" t="n">
-        <v>-4.909100255307486</v>
+        <v>-4.841773776720458</v>
       </c>
       <c r="N7" s="4" t="n">
-        <v>-5.188194158782387</v>
+        <v>-5.120523180168455</v>
       </c>
       <c r="O7" s="4" t="n">
-        <v>-6.312685377269531</v>
+        <v>-6.243685247024573</v>
       </c>
       <c r="P7" s="4" t="n">
-        <v>-5.357571600068596</v>
+        <v>-5.288293535235873</v>
       </c>
       <c r="Q7" s="4" t="n">
-        <v>-7.192973427341187</v>
+        <v>-7.122907421051721</v>
       </c>
       <c r="R7" s="4" t="n">
-        <v>-7.774383965955096</v>
+        <v>-7.70499108734402</v>
       </c>
       <c r="S7" s="4" t="n">
-        <v>-13.7908306012805</v>
+        <v>-13.72126116549797</v>
       </c>
       <c r="T7" s="4" t="n">
-        <v>-12.71934342914049</v>
+        <v>-12.64963128108386</v>
       </c>
       <c r="U7" s="4" t="n">
-        <v>-8.973808501502788</v>
+        <v>-8.904328135453653</v>
       </c>
       <c r="V7" s="4" t="n">
-        <v>-4.080882352941174</v>
+        <v>-4.011599972544445</v>
       </c>
       <c r="W7" s="4" t="n">
-        <v>-2.271141585468548</v>
+        <v>-2.201204964039896</v>
       </c>
       <c r="X7" s="4" t="n">
-        <v>-1.170626052875853</v>
+        <v>-1.100580337213692</v>
       </c>
       <c r="Y7" s="4" t="n">
-        <v>-0.895850886393724</v>
+        <v>-0.826105624731639</v>
       </c>
       <c r="Z7" s="4" t="n">
-        <v>-0.9717922256621918</v>
+        <v>-0.9019378779549143</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>X &lt; -0.01979</t>
+          <t>X &lt; -0.01978</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>-5.025472757102143</v>
+        <v>-4.533704256289113</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>-2.657945569043775</v>
+        <v>-2.18990962606749</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>-5.899447834931713</v>
+        <v>-5.413642960812773</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>-5.71234024722397</v>
+        <v>-5.233739837398375</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>-5.176709131347117</v>
+        <v>-4.676673167088495</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>-3.187742716538523</v>
+        <v>-2.703992695276838</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>-0.3570052449889474</v>
+        <v>-0.7973699505957583</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>-4.239163494111111</v>
+        <v>-4.647009966777404</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>-5.999449230890285</v>
+        <v>-6.391237070576992</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>-7.674185542560615</v>
+        <v>-7.164152746613482</v>
       </c>
       <c r="M8" s="4" t="n">
-        <v>-9.201628077247072</v>
+        <v>-8.675807390165843</v>
       </c>
       <c r="N8" s="4" t="n">
-        <v>-8.57982107982108</v>
+        <v>-8.061699650756694</v>
       </c>
       <c r="O8" s="4" t="n">
-        <v>-9.704312298308224</v>
+        <v>-9.184861717612812</v>
       </c>
       <c r="P8" s="4" t="n">
-        <v>-9.024768208441678</v>
+        <v>-8.513083451202263</v>
       </c>
       <c r="Q8" s="4" t="n">
-        <v>-9.683699447478979</v>
+        <v>-9.171226748782821</v>
       </c>
       <c r="R8" s="4" t="n">
-        <v>-9.989540298758499</v>
+        <v>-9.469696969696969</v>
       </c>
       <c r="S8" s="4" t="n">
-        <v>-14.62813849741192</v>
+        <v>-14.06789982096016</v>
       </c>
       <c r="T8" s="4" t="n">
-        <v>-13.8322210126063</v>
+        <v>-13.27988338192419</v>
       </c>
       <c r="U8" s="4" t="n">
-        <v>-10.01249424607089</v>
+        <v>-9.492563429571298</v>
       </c>
       <c r="V8" s="4" t="n">
-        <v>-7.122747747747752</v>
+        <v>-7.52000333388898</v>
       </c>
       <c r="W8" s="4" t="n">
-        <v>-6.765047255844799</v>
+        <v>-7.169692358997871</v>
       </c>
       <c r="X8" s="4" t="n">
-        <v>-6.841002311487408</v>
+        <v>-7.245538320406972</v>
       </c>
       <c r="Y8" s="4" t="n">
-        <v>-6.566227145005278</v>
+        <v>-6.07820646506778</v>
       </c>
       <c r="Z8" s="4" t="n">
-        <v>-5.741267583372846</v>
+        <v>-5.261181575433916</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>X &lt; -0.01819</t>
+          <t>X &lt; -0.01818</t>
         </is>
       </c>
       <c r="B9" t="n">
         <v>137</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>-2.579230894801888</v>
+        <v>-2.545956602483059</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>0.005301619750859743</v>
+        <v>0.03897462836420118</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>-1.434398844335277</v>
+        <v>-1.39904442066679</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>-4.337973179426236</v>
+        <v>-4.301779462007332</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>-5.433169971749557</v>
+        <v>-5.367496941853879</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>-4.516078351443497</v>
+        <v>-4.450603748457226</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>-3.82909046889899</v>
+        <v>-3.762698417749043</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>-7.027353143614626</v>
+        <v>-6.960617891699194</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>-9.175618100489807</v>
+        <v>-9.108911731682305</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>-10.67938051855851</v>
+        <v>-10.61175441501807</v>
       </c>
       <c r="M9" s="4" t="n">
-        <v>-11.13494825874244</v>
+        <v>-11.06762178015541</v>
       </c>
       <c r="N9" s="4" t="n">
-        <v>-10.68411515491808</v>
+        <v>-10.61644417630414</v>
       </c>
       <c r="O9" s="4" t="n">
-        <v>-9.618825351507404</v>
+        <v>-9.549825221262445</v>
       </c>
       <c r="P9" s="4" t="n">
-        <v>-7.650401140643943</v>
+        <v>-7.58112307581122</v>
       </c>
       <c r="Q9" s="4" t="n">
-        <v>-9.039259386980518</v>
+        <v>-8.969193380691053</v>
       </c>
       <c r="R9" s="4" t="n">
-        <v>-8.444199337359137</v>
+        <v>-8.374806458748061</v>
       </c>
       <c r="S9" s="4" t="n">
-        <v>-12.22792806800442</v>
+        <v>-12.15835863222189</v>
       </c>
       <c r="T9" s="4" t="n">
-        <v>-12.3329114840997</v>
+        <v>-12.26319933604307</v>
       </c>
       <c r="U9" s="4" t="n">
-        <v>-9.927007299270066</v>
+        <v>-9.857526933220932</v>
       </c>
       <c r="V9" s="4" t="n">
-        <v>-9.010036496350359</v>
+        <v>-8.940754115953631</v>
       </c>
       <c r="W9" s="4" t="n">
-        <v>-8.823309898049047</v>
+        <v>-8.753373276620394</v>
       </c>
       <c r="X9" s="4" t="n">
-        <v>-8.169337946392382</v>
+        <v>-8.099292230730221</v>
       </c>
       <c r="Y9" s="4" t="n">
-        <v>-8.624489787209527</v>
+        <v>-8.554744525547441</v>
       </c>
       <c r="Z9" s="4" t="n">
-        <v>-8.700431126477994</v>
+        <v>-8.630576778770717</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>X &lt; -0.01659</t>
+          <t>X &lt; -0.01658</t>
         </is>
       </c>
       <c r="B10" t="n">
         <v>189</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>-4.996872728502119</v>
+        <v>-4.96359843618329</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>-0.04104295214115439</v>
+        <v>-0.00736994352781295</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>-3.068045003528873</v>
+        <v>-3.032690579860386</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>-3.252737787621513</v>
+        <v>-3.216544070202609</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>-4.147108101746078</v>
+        <v>-4.0814350718504</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>-1.843541372337178</v>
+        <v>-1.778066769350907</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>-3.145508033491737</v>
+        <v>-3.07911598234179</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>-5.01136426631188</v>
+        <v>-4.944629014396448</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>-8.673551904992955</v>
+        <v>-8.606845536185453</v>
       </c>
       <c r="L10" s="4" t="n">
-        <v>-6.801884670259739</v>
+        <v>-6.734258566719298</v>
       </c>
       <c r="M10" s="4" t="n">
-        <v>-5.998424874043877</v>
+        <v>-5.93109839545685</v>
       </c>
       <c r="N10" s="4" t="n">
-        <v>-4.690217190217183</v>
+        <v>-4.62254621160325</v>
       </c>
       <c r="O10" s="4" t="n">
-        <v>-2.640105234101156</v>
+        <v>-2.571105103856198</v>
       </c>
       <c r="P10" s="4" t="n">
-        <v>-2.861462045135511</v>
+        <v>-2.792183980302788</v>
       </c>
       <c r="Q10" s="4" t="n">
-        <v>-2.991292755072287</v>
+        <v>-2.921226748782821</v>
       </c>
       <c r="R10" s="4" t="n">
-        <v>-3.983534292752488</v>
+        <v>-3.914141414141412</v>
       </c>
       <c r="S10" s="4" t="n">
-        <v>-7.292231161504581</v>
+        <v>-7.222661725722055</v>
       </c>
       <c r="T10" s="4" t="n">
-        <v>-6.339013519398804</v>
+        <v>-6.269301371342181</v>
       </c>
       <c r="U10" s="4" t="n">
-        <v>-5.064689298265932</v>
+        <v>-4.995208932216798</v>
       </c>
       <c r="V10" s="4" t="n">
-        <v>-5.406746031746032</v>
+        <v>-5.337463651349303</v>
       </c>
       <c r="W10" s="4" t="n">
-        <v>-5.949946440743986</v>
+        <v>-5.880009819315333</v>
       </c>
       <c r="X10" s="4" t="n">
-        <v>-6.025901496386595</v>
+        <v>-5.955855780724434</v>
       </c>
       <c r="Y10" s="4" t="n">
-        <v>-6.280226859004991</v>
+        <v>-6.210481597342906</v>
       </c>
       <c r="Z10" s="4" t="n">
-        <v>-6.885268727373997</v>
+        <v>-6.81541437966672</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>X &lt; -0.01499</t>
+          <t>X &lt; -0.01498</t>
         </is>
       </c>
       <c r="B11" t="n">
         <v>248</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>-5.69025043800886</v>
+        <v>-5.656976145690031</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>-1.993167888137059</v>
+        <v>-1.959494879523717</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>-4.23931996512642</v>
+        <v>-4.203965541457933</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>-3.743435858964745</v>
+        <v>-3.707242141545841</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>-4.5119314504404</v>
+        <v>-4.446258420544723</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>-3.51831522453039</v>
+        <v>-3.452840621544119</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>-3.484729743681193</v>
+        <v>-3.418337692531246</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>-7.392316647264266</v>
+        <v>-7.325581395348834</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>-9.770155420951305</v>
+        <v>-9.703449052143803</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>-6.914958573656222</v>
+        <v>-6.847332470115781</v>
       </c>
       <c r="M11" s="4" t="n">
-        <v>-5.834147693637661</v>
+        <v>-5.766821215050633</v>
       </c>
       <c r="N11" s="4" t="n">
-        <v>-4.097112564854498</v>
+        <v>-4.029441586240566</v>
       </c>
       <c r="O11" s="4" t="n">
-        <v>-2.802248944631955</v>
+        <v>-2.733248814386997</v>
       </c>
       <c r="P11" s="4" t="n">
-        <v>-1.007476723408253</v>
+        <v>-0.93819865857553</v>
       </c>
       <c r="Q11" s="4" t="n">
-        <v>-1.263182155993938</v>
+        <v>-1.193116149704473</v>
       </c>
       <c r="R11" s="4" t="n">
-        <v>-1.474573719275782</v>
+        <v>-1.405180840664705</v>
       </c>
       <c r="S11" s="4" t="n">
-        <v>-5.237699671489231</v>
+        <v>-5.168130235706705</v>
       </c>
       <c r="T11" s="4" t="n">
-        <v>-3.729779861778063</v>
+        <v>-3.660067713721439</v>
       </c>
       <c r="U11" s="4" t="n">
-        <v>-3.110430892394618</v>
+        <v>-3.040950526345483</v>
       </c>
       <c r="V11" s="4" t="n">
-        <v>-4.939516129032263</v>
+        <v>-4.870233748635535</v>
       </c>
       <c r="W11" s="4" t="n">
-        <v>-5.482716538030218</v>
+        <v>-5.412779916601565</v>
       </c>
       <c r="X11" s="4" t="n">
-        <v>-6.365123206576051</v>
+        <v>-6.29507749091389</v>
       </c>
       <c r="Y11" s="4" t="n">
-        <v>-6.090348040093922</v>
+        <v>-6.020602778431837</v>
       </c>
       <c r="Z11" s="4" t="n">
-        <v>-6.569515185814005</v>
+        <v>-6.499660838106728</v>
       </c>
     </row>
     <row r="12">
@@ -6323,76 +6323,76 @@
         <v>335</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>-3.823375137094082</v>
+        <v>-3.790100844775253</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>-2.367505875619003</v>
+        <v>-2.333832867005661</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>-3.508698877018567</v>
+        <v>-3.47334445335008</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>-4.520999652898297</v>
+        <v>-4.484805935479393</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>-3.692239587176076</v>
+        <v>-3.626566557280398</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>-3.50507497416929</v>
+        <v>-3.439600371183019</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>-3.083911255477048</v>
+        <v>-3.017519204327101</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>-4.257988289055305</v>
+        <v>-4.191253037139873</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>-4.813487149405816</v>
+        <v>-4.746780780598314</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>-3.199262858682701</v>
+        <v>-3.13163675514226</v>
       </c>
       <c r="M12" s="4" t="n">
-        <v>-2.029381203507668</v>
+        <v>-1.962054724920641</v>
       </c>
       <c r="N12" s="4" t="n">
-        <v>-1.711460181609425</v>
+        <v>-1.643789202995492</v>
       </c>
       <c r="O12" s="4" t="n">
-        <v>-0.7463991612906042</v>
+        <v>-0.6773990310456455</v>
       </c>
       <c r="P12" s="4" t="n">
-        <v>1.121796266481013</v>
+        <v>1.191074331313736</v>
       </c>
       <c r="Q12" s="4" t="n">
-        <v>0.4628650274437121</v>
+        <v>0.5329310337331776</v>
       </c>
       <c r="R12" s="4" t="n">
-        <v>0.1624026890053827</v>
+        <v>0.2317955676164587</v>
       </c>
       <c r="S12" s="4" t="n">
-        <v>-2.658258169322636</v>
+        <v>-2.58868873354011</v>
       </c>
       <c r="T12" s="4" t="n">
-        <v>-2.46473412273135</v>
+        <v>-2.395021974674727</v>
       </c>
       <c r="U12" s="4" t="n">
-        <v>-1.353088571739832</v>
+        <v>-1.283608205690697</v>
       </c>
       <c r="V12" s="4" t="n">
-        <v>-2.65858208955224</v>
+        <v>-2.589299709155512</v>
       </c>
       <c r="W12" s="4" t="n">
-        <v>-3.201782498550195</v>
+        <v>-3.131845877121542</v>
       </c>
       <c r="X12" s="4" t="n">
-        <v>-3.874752479565934</v>
+        <v>-3.804706763903773</v>
       </c>
       <c r="Y12" s="4" t="n">
-        <v>-3.599977313083805</v>
+        <v>-3.53023205142172</v>
       </c>
       <c r="Z12" s="4" t="n">
-        <v>-3.3774111896657</v>
+        <v>-3.307556841958423</v>
       </c>
     </row>
     <row r="13">
@@ -6405,76 +6405,76 @@
         <v>434</v>
       </c>
       <c r="C13" s="4" t="n">
-        <v>-3.44370665920701</v>
+        <v>-3.41043236688818</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>-1.474734708413564</v>
+        <v>-1.441061699800223</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>-1.762361439780804</v>
+        <v>-1.727007016112317</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>-2.015325259886396</v>
+        <v>-1.979131542467492</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>0.1539671670711229</v>
+        <v>0.2196401969668003</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>-0.1196977130096499</v>
+        <v>-0.05422311002337921</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>-0.2013196054323387</v>
+        <v>-0.1349275542823918</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>-0.2494595044071275</v>
+        <v>-0.1827242524916954</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>-0.6687729324720451</v>
+        <v>-0.6020665636645433</v>
       </c>
       <c r="L13" s="4" t="n">
-        <v>0.4007096291087535</v>
+        <v>0.4683357326491944</v>
       </c>
       <c r="M13" s="4" t="n">
-        <v>0.9054836427678623</v>
+        <v>0.9728101213548896</v>
       </c>
       <c r="N13" s="4" t="n">
-        <v>1.778463472011858</v>
+        <v>1.84613445062579</v>
       </c>
       <c r="O13" s="4" t="n">
-        <v>2.9581197189625</v>
+        <v>3.027119849207459</v>
       </c>
       <c r="P13" s="4" t="n">
-        <v>3.888836640647042</v>
+        <v>3.958114705479765</v>
       </c>
       <c r="Q13" s="4" t="n">
-        <v>3.229905401609741</v>
+        <v>3.299971407899207</v>
       </c>
       <c r="R13" s="4" t="n">
-        <v>1.981647478880888</v>
+        <v>2.051040357491964</v>
       </c>
       <c r="S13" s="4" t="n">
-        <v>-0.2261789341620357</v>
+        <v>-0.1566094983795097</v>
       </c>
       <c r="T13" s="4" t="n">
-        <v>-0.1007476037135362</v>
+        <v>-0.03103545565691235</v>
       </c>
       <c r="U13" s="4" t="n">
-        <v>1.037034545393389</v>
+        <v>1.106514911442524</v>
       </c>
       <c r="V13" s="4" t="n">
-        <v>0.07200460829493238</v>
+        <v>0.141286988691661</v>
       </c>
       <c r="W13" s="4" t="n">
-        <v>-0.4711958007030219</v>
+        <v>-0.4012591792743692</v>
       </c>
       <c r="X13" s="4" t="n">
-        <v>-0.3167361098018517</v>
+        <v>-0.2466903941396907</v>
       </c>
       <c r="Y13" s="4" t="n">
-        <v>0.6492832963116157</v>
+        <v>0.7190285579737008</v>
       </c>
       <c r="Z13" s="4" t="n">
-        <v>-0.1179022825881901</v>
+        <v>-0.04804793488091263</v>
       </c>
     </row>
     <row r="14">
@@ -6487,1142 +6487,1142 @@
         <v>545</v>
       </c>
       <c r="C14" s="4" t="n">
-        <v>-1.93100213969575</v>
+        <v>-1.89772784737692</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>0.119143446577354</v>
+        <v>0.1528164551906954</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>0.1473328907480962</v>
+        <v>0.182687314416583</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>0.3509707702154969</v>
+        <v>0.3871644876344007</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>1.820563370512545</v>
+        <v>1.886236400408222</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>1.09029679085878</v>
+        <v>1.15577139384505</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>2.335779282657967</v>
+        <v>2.402171333807914</v>
       </c>
       <c r="J14" s="4" t="n">
-        <v>1.873738398607294</v>
+        <v>1.940473650522726</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>1.548281986565705</v>
+        <v>1.614988355373207</v>
       </c>
       <c r="L14" s="4" t="n">
-        <v>2.425822722585274</v>
+        <v>2.493448826125714</v>
       </c>
       <c r="M14" s="4" t="n">
-        <v>3.250640705296931</v>
+        <v>3.317967183883958</v>
       </c>
       <c r="N14" s="4" t="n">
-        <v>3.888977994482588</v>
+        <v>3.95664897309652</v>
       </c>
       <c r="O14" s="4" t="n">
-        <v>4.966321638380769</v>
+        <v>5.035321768625728</v>
       </c>
       <c r="P14" s="4" t="n">
-        <v>5.845882258539071</v>
+        <v>5.915160323371794</v>
       </c>
       <c r="Q14" s="4" t="n">
-        <v>4.636492303905435</v>
+        <v>4.7065583101949</v>
       </c>
       <c r="R14" s="4" t="n">
-        <v>4.314121160866272</v>
+        <v>4.383514039477348</v>
       </c>
       <c r="S14" s="4" t="n">
-        <v>3.26259627405679</v>
+        <v>3.332165709839316</v>
       </c>
       <c r="T14" s="4" t="n">
-        <v>2.974126619429406</v>
+        <v>3.043838767486029</v>
       </c>
       <c r="U14" s="4" t="n">
-        <v>3.557222259425444</v>
+        <v>3.626702625474579</v>
       </c>
       <c r="V14" s="4" t="n">
-        <v>2.459862385321102</v>
+        <v>2.529144765717831</v>
       </c>
       <c r="W14" s="4" t="n">
-        <v>1.733175737791036</v>
+        <v>1.803112359219689</v>
       </c>
       <c r="X14" s="4" t="n">
-        <v>1.290248205084211</v>
+        <v>1.360293920746372</v>
       </c>
       <c r="Y14" s="4" t="n">
-        <v>2.115482087162668</v>
+        <v>2.185227348824753</v>
       </c>
       <c r="Z14" s="4" t="n">
-        <v>0.9386233167015376</v>
+        <v>1.008477664408815</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>X &lt; -0.008593</t>
+          <t>X &lt; -0.008589</t>
         </is>
       </c>
       <c r="B15" t="n">
         <v>695</v>
       </c>
       <c r="C15" s="4" t="n">
-        <v>-0.005056657549360466</v>
+        <v>0.0282176347694687</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>1.961926101187615</v>
+        <v>1.995599109800956</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>1.817189665878445</v>
+        <v>1.852544089546932</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>2.398360381462268</v>
+        <v>2.434554098881172</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>3.759709301474196</v>
+        <v>3.825382331369873</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>3.083564561963001</v>
+        <v>3.149039164949272</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>3.174007782426955</v>
+        <v>3.240399833576902</v>
       </c>
       <c r="J15" s="4" t="n">
-        <v>2.751568244822067</v>
+        <v>2.818303496737499</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>2.217544741499381</v>
+        <v>2.284251110306883</v>
       </c>
       <c r="L15" s="4" t="n">
-        <v>3.314212927852246</v>
+        <v>3.381839031392687</v>
       </c>
       <c r="M15" s="4" t="n">
-        <v>4.164111763312917</v>
+        <v>4.231438241899944</v>
       </c>
       <c r="N15" s="4" t="n">
-        <v>4.604442320269662</v>
+        <v>4.672113298883595</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>4.774915130559499</v>
+        <v>4.843915260804458</v>
       </c>
       <c r="P15" s="4" t="n">
-        <v>5.560752564129452</v>
+        <v>5.630030628962174</v>
       </c>
       <c r="Q15" s="4" t="n">
-        <v>5.045706217178484</v>
+        <v>5.11577222346795</v>
       </c>
       <c r="R15" s="4" t="n">
-        <v>4.777456914281892</v>
+        <v>4.846849792892968</v>
       </c>
       <c r="S15" s="4" t="n">
-        <v>4.787248112219288</v>
+        <v>4.856817548001814</v>
       </c>
       <c r="T15" s="4" t="n">
-        <v>4.106725127778688</v>
+        <v>4.176437275835312</v>
       </c>
       <c r="U15" s="4" t="n">
-        <v>4.61061807488317</v>
+        <v>4.680098440932305</v>
       </c>
       <c r="V15" s="4" t="n">
-        <v>3.934352517985609</v>
+        <v>4.003634898382337</v>
       </c>
       <c r="W15" s="4" t="n">
-        <v>3.966691677332982</v>
+        <v>4.036628298761634</v>
       </c>
       <c r="X15" s="4" t="n">
-        <v>3.315197053345045</v>
+        <v>3.385242769007206</v>
       </c>
       <c r="Y15" s="4" t="n">
-        <v>4.309396680258835</v>
+        <v>4.379141941920921</v>
       </c>
       <c r="Z15" s="4" t="n">
-        <v>2.938491312213387</v>
+        <v>3.008345659920664</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>X &lt; -0.006994</t>
+          <t>X &lt; -0.006991</t>
         </is>
       </c>
       <c r="B16" t="n">
         <v>881</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>0.9229274024217347</v>
+        <v>0.9562016947405638</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>0.8147666437365402</v>
+        <v>0.8484396523498816</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>1.077676849343945</v>
+        <v>1.113031273012432</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>1.271942559987338</v>
+        <v>1.308136277406241</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>1.814731798799841</v>
+        <v>1.880404828695518</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>1.661374277867907</v>
+        <v>1.726848880854178</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>1.569552413691298</v>
+        <v>1.635944464841245</v>
       </c>
       <c r="J16" s="4" t="n">
-        <v>2.199056792009287</v>
+        <v>2.265792043924719</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>1.78654334511365</v>
+        <v>1.853249713921151</v>
       </c>
       <c r="L16" s="4" t="n">
-        <v>2.715318604037748</v>
+        <v>2.782944707578189</v>
       </c>
       <c r="M16" s="4" t="n">
-        <v>2.989677871153084</v>
+        <v>3.057004349740112</v>
       </c>
       <c r="N16" s="4" t="n">
-        <v>2.937598723637322</v>
+        <v>3.005269702251255</v>
       </c>
       <c r="O16" s="4" t="n">
-        <v>3.515718174843705</v>
+        <v>3.584718305088664</v>
       </c>
       <c r="P16" s="4" t="n">
-        <v>4.656449899564173</v>
+        <v>4.725727964396896</v>
       </c>
       <c r="Q16" s="4" t="n">
-        <v>4.678562928404283</v>
+        <v>4.748628934693748</v>
       </c>
       <c r="R16" s="4" t="n">
-        <v>4.706086088127826</v>
+        <v>4.775478966738902</v>
       </c>
       <c r="S16" s="4" t="n">
-        <v>4.685499771958462</v>
+        <v>4.755069207740988</v>
       </c>
       <c r="T16" s="4" t="n">
-        <v>4.012979465965351</v>
+        <v>4.082691614021975</v>
       </c>
       <c r="U16" s="4" t="n">
-        <v>4.342610006876725</v>
+        <v>4.41209037292586</v>
       </c>
       <c r="V16" s="4" t="n">
-        <v>3.621594778660608</v>
+        <v>3.690877159057337</v>
       </c>
       <c r="W16" s="4" t="n">
-        <v>3.645931259560498</v>
+        <v>3.715867880989151</v>
       </c>
       <c r="X16" s="4" t="n">
-        <v>3.342961447958757</v>
+        <v>3.413007163620918</v>
       </c>
       <c r="Y16" s="4" t="n">
-        <v>4.412288260297863</v>
+        <v>4.482033521959949</v>
       </c>
       <c r="Z16" s="4" t="n">
-        <v>3.201273141233706</v>
+        <v>3.271127488940984</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>X &lt; -0.005395</t>
+          <t>X &lt; -0.005392</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>1051</v>
+        <v>1052</v>
       </c>
       <c r="C17" s="4" t="n">
-        <v>0.6468662485701913</v>
+        <v>0.6801405408890204</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>0.7865245420930052</v>
+        <v>0.8201975507063466</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>0.7713255025082901</v>
+        <v>0.806679926176777</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>1.671967137083413</v>
+        <v>1.708160854502317</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>1.781531160226507</v>
+        <v>1.847204190122184</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>1.778762249966448</v>
+        <v>1.844236852952719</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>1.480729926079562</v>
+        <v>1.547121977229509</v>
       </c>
       <c r="J17" s="4" t="n">
-        <v>1.677009088728141</v>
+        <v>1.743744340643573</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>1.718525153750775</v>
+        <v>1.785231522558277</v>
       </c>
       <c r="L17" s="4" t="n">
-        <v>3.033958498916761</v>
+        <v>3.101584602457201</v>
       </c>
       <c r="M17" s="4" t="n">
-        <v>3.213351004398675</v>
+        <v>3.280677482985702</v>
       </c>
       <c r="N17" s="4" t="n">
-        <v>3.124190624190625</v>
+        <v>3.191861602804558</v>
       </c>
       <c r="O17" s="4" t="n">
-        <v>3.804067876738628</v>
+        <v>3.873068006983587</v>
       </c>
       <c r="P17" s="4" t="n">
-        <v>4.722312205305407</v>
+        <v>4.79159027013813</v>
       </c>
       <c r="Q17" s="4" t="n">
-        <v>4.823115059335528</v>
+        <v>4.893181065624994</v>
       </c>
       <c r="R17" s="4" t="n">
-        <v>4.278573969355769</v>
+        <v>4.347966847966845</v>
       </c>
       <c r="S17" s="4" t="n">
-        <v>4.585371590622884</v>
+        <v>4.59391675752309</v>
       </c>
       <c r="T17" s="4" t="n">
-        <v>4.480388174527604</v>
+        <v>4.489076053701908</v>
       </c>
       <c r="U17" s="4" t="n">
-        <v>4.126169132136219</v>
+        <v>4.135166864825656</v>
       </c>
       <c r="V17" s="4" t="n">
-        <v>4.12309885931559</v>
+        <v>4.132079151526838</v>
       </c>
       <c r="W17" s="4" t="n">
-        <v>4.340354724081898</v>
+        <v>4.410291345510551</v>
       </c>
       <c r="X17" s="4" t="n">
-        <v>3.884171531557158</v>
+        <v>3.954217247219319</v>
       </c>
       <c r="Y17" s="4" t="n">
-        <v>4.6954627085019</v>
+        <v>4.703977130804034</v>
       </c>
       <c r="Z17" s="4" t="n">
-        <v>3.382604147539794</v>
+        <v>3.392403432713834</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>X &lt; -0.003796</t>
+          <t>X &lt; -0.003793</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>1221</v>
+        <v>1224</v>
       </c>
       <c r="C18" s="4" t="n">
-        <v>-0.3679989567712099</v>
+        <v>-0.3347246644523807</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>0.8478459367477384</v>
+        <v>0.8815189453610799</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>1.04079853388609</v>
+        <v>1.076152957554577</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>1.469862363550078</v>
+        <v>1.506056080968982</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>0.6964293132199018</v>
+        <v>0.7621023431155791</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>0.3937980078593455</v>
+        <v>0.4592726108456162</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>0.5188910594787899</v>
+        <v>0.5852831106287368</v>
       </c>
       <c r="J18" s="4" t="n">
-        <v>1.138295597633693</v>
+        <v>1.205030849549125</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>1.261444315717554</v>
+        <v>1.328150684525056</v>
       </c>
       <c r="L18" s="4" t="n">
-        <v>2.528425231478728</v>
+        <v>2.596051335019169</v>
       </c>
       <c r="M18" s="4" t="n">
-        <v>2.557886539410397</v>
+        <v>2.625213017997424</v>
       </c>
       <c r="N18" s="4" t="n">
-        <v>2.686955901241618</v>
+        <v>2.75462687985555</v>
       </c>
       <c r="O18" s="4" t="n">
-        <v>3.521648356223857</v>
+        <v>3.590648486468815</v>
       </c>
       <c r="P18" s="4" t="n">
-        <v>3.463556851311957</v>
+        <v>3.532834916144679</v>
       </c>
       <c r="Q18" s="4" t="n">
-        <v>3.6209521428869</v>
+        <v>3.691018149176365</v>
       </c>
       <c r="R18" s="4" t="n">
-        <v>3.481318314957264</v>
+        <v>3.55071119356834</v>
       </c>
       <c r="S18" s="4" t="n">
-        <v>3.56211057519009</v>
+        <v>3.580059362713314</v>
       </c>
       <c r="T18" s="4" t="n">
-        <v>3.865623891120947</v>
+        <v>3.883381924198247</v>
       </c>
       <c r="U18" s="4" t="n">
-        <v>3.836649014837079</v>
+        <v>3.854375345938912</v>
       </c>
       <c r="V18" s="4" t="n">
-        <v>3.778594771241828</v>
+        <v>3.796323196723264</v>
       </c>
       <c r="W18" s="4" t="n">
-        <v>4.052387826296162</v>
+        <v>4.122324447724814</v>
       </c>
       <c r="X18" s="4" t="n">
-        <v>3.538142164141121</v>
+        <v>3.556282407884339</v>
       </c>
       <c r="Y18" s="4" t="n">
-        <v>4.437739178109972</v>
+        <v>4.402652545202997</v>
       </c>
       <c r="Z18" s="4" t="n">
-        <v>3.185841343736087</v>
+        <v>3.101330095901289</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>X &lt; -0.002197</t>
+          <t>X &lt; -0.002194</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>1439</v>
+        <v>1445</v>
       </c>
       <c r="C19" s="4" t="n">
-        <v>-0.2437679753973683</v>
+        <v>-0.1138761590751187</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>1.153558242460036</v>
+        <v>1.280254373142149</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>1.446359510875638</v>
+        <v>1.571142654678233</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>1.841367306483583</v>
+        <v>1.964689326798435</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>0.9216969670589918</v>
+        <v>1.075648508469683</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>0.7623612335654215</v>
+        <v>0.9168332284536476</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>0.8210959331122254</v>
+        <v>0.9056037700128243</v>
       </c>
       <c r="J19" s="4" t="n">
-        <v>1.096941841994223</v>
+        <v>1.11148637781853</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>1.277058045616997</v>
+        <v>1.291286146178599</v>
       </c>
       <c r="L19" s="4" t="n">
-        <v>2.097124228749159</v>
+        <v>2.108965214263819</v>
       </c>
       <c r="M19" s="4" t="n">
-        <v>2.371483495864496</v>
+        <v>2.452181149648425</v>
       </c>
       <c r="N19" s="4" t="n">
-        <v>2.161689661689671</v>
+        <v>2.242588039423111</v>
       </c>
       <c r="O19" s="4" t="n">
-        <v>2.700400106404189</v>
+        <v>2.779177009911393</v>
       </c>
       <c r="P19" s="4" t="n">
-        <v>2.756243572570106</v>
+        <v>2.834723306355535</v>
       </c>
       <c r="Q19" s="4" t="n">
-        <v>2.859613095833566</v>
+        <v>2.93729923422449</v>
       </c>
       <c r="R19" s="4" t="n">
-        <v>2.692372383154186</v>
+        <v>2.840123223940651</v>
       </c>
       <c r="S19" s="4" t="n">
-        <v>2.601435042841224</v>
+        <v>2.706206086963178</v>
       </c>
       <c r="T19" s="4" t="n">
-        <v>2.773844137148174</v>
+        <v>2.739677969587362</v>
       </c>
       <c r="U19" s="4" t="n">
-        <v>2.920619172479427</v>
+        <v>2.886413057289005</v>
       </c>
       <c r="V19" s="4" t="n">
-        <v>2.62222607489597</v>
+        <v>2.58916481469825</v>
       </c>
       <c r="W19" s="4" t="n">
-        <v>2.911203197104683</v>
+        <v>2.919902302396089</v>
       </c>
       <c r="X19" s="4" t="n">
-        <v>2.601264382687688</v>
+        <v>2.567239731990462</v>
       </c>
       <c r="Y19" s="4" t="n">
-        <v>3.19728636850823</v>
+        <v>3.118531053469042</v>
       </c>
       <c r="Z19" s="4" t="n">
-        <v>2.887096708646766</v>
+        <v>2.76588219124924</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>X &lt; -0.0005982</t>
+          <t>X &lt; -0.0005956</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>1655</v>
+        <v>1658</v>
       </c>
       <c r="C20" s="4" t="n">
-        <v>-0.4531701715545253</v>
+        <v>-0.4198958792356962</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>0.9575904968234212</v>
+        <v>0.9912635054367627</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>0.7219839520629847</v>
+        <v>0.7573383757314716</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>1.573512733993248</v>
+        <v>1.609706451412151</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>0.6061959893063573</v>
+        <v>0.6718690192020347</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>0.6127465144142832</v>
+        <v>0.6782211174005539</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>0.5021320379893908</v>
+        <v>0.5685240891393377</v>
       </c>
       <c r="J20" s="4" t="n">
-        <v>1.006238440032547</v>
+        <v>1.072973691947979</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>1.16816389698775</v>
+        <v>1.234870265795251</v>
       </c>
       <c r="L20" s="4" t="n">
-        <v>1.718831797476597</v>
+        <v>1.786457901017037</v>
       </c>
       <c r="M20" s="4" t="n">
-        <v>1.872781672659357</v>
+        <v>1.940108151246385</v>
       </c>
       <c r="N20" s="4" t="n">
-        <v>1.533483073218179</v>
+        <v>1.601154051832111</v>
       </c>
       <c r="O20" s="4" t="n">
-        <v>2.034518645820739</v>
+        <v>2.103518776065698</v>
       </c>
       <c r="P20" s="4" t="n">
-        <v>2.091046401348841</v>
+        <v>2.123258683484245</v>
       </c>
       <c r="Q20" s="4" t="n">
-        <v>1.770612006832479</v>
+        <v>1.766138865735115</v>
       </c>
       <c r="R20" s="4" t="n">
-        <v>1.642344750848068</v>
+        <v>1.638069436082681</v>
       </c>
       <c r="S20" s="4" t="n">
-        <v>1.665779063091883</v>
+        <v>1.624561691037783</v>
       </c>
       <c r="T20" s="4" t="n">
-        <v>1.440168385235452</v>
+        <v>1.436123502757397</v>
       </c>
       <c r="U20" s="4" t="n">
-        <v>1.776918809928418</v>
+        <v>1.809425720519123</v>
       </c>
       <c r="V20" s="4" t="n">
-        <v>1.722708082026536</v>
+        <v>1.755162428618547</v>
       </c>
       <c r="W20" s="4" t="n">
-        <v>1.782643981834376</v>
+        <v>1.852580603263029</v>
       </c>
       <c r="X20" s="4" t="n">
-        <v>1.80427543457489</v>
+        <v>1.837048272734499</v>
       </c>
       <c r="Y20" s="4" t="n">
-        <v>2.418300861261855</v>
+        <v>2.413091139619453</v>
       </c>
       <c r="Z20" s="4" t="n">
-        <v>2.379904948675815</v>
+        <v>2.337258886396178</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>X &lt; 0.001001</t>
+          <t>X &lt; 0.001003</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>1841</v>
+        <v>1844</v>
       </c>
       <c r="C21" s="4" t="n">
-        <v>-0.1026928343222266</v>
+        <v>-0.06941854200339748</v>
       </c>
       <c r="D21" s="4" t="n">
-        <v>0.6443827332845302</v>
+        <v>0.6780557418978717</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>0.4492710137871399</v>
+        <v>0.4846254374556267</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>1.412966878083161</v>
+        <v>1.449160595502065</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>0.9394719848340003</v>
+        <v>1.005145014729678</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>0.7478487190529108</v>
+        <v>0.8133233220391816</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>0.5702206822369789</v>
+        <v>0.6366127333869258</v>
       </c>
       <c r="J21" s="4" t="n">
-        <v>0.5622288072811941</v>
+        <v>0.6289640591966261</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>0.7119699805289272</v>
+        <v>0.778676349336429</v>
       </c>
       <c r="L21" s="4" t="n">
-        <v>1.020385652010582</v>
+        <v>1.088011755551022</v>
       </c>
       <c r="M21" s="4" t="n">
-        <v>1.294744919125918</v>
+        <v>1.362071397712945</v>
       </c>
       <c r="N21" s="4" t="n">
-        <v>0.7450882450882546</v>
+        <v>0.8127592237021872</v>
       </c>
       <c r="O21" s="4" t="n">
-        <v>0.8110732170772934</v>
+        <v>0.8800733473222522</v>
       </c>
       <c r="P21" s="4" t="n">
-        <v>0.9470877839882235</v>
+        <v>0.9836697955509948</v>
       </c>
       <c r="Q21" s="4" t="n">
-        <v>0.754257469351181</v>
+        <v>0.7584269308708613</v>
       </c>
       <c r="R21" s="4" t="n">
-        <v>0.7861134037244781</v>
+        <v>0.7575757575757578</v>
       </c>
       <c r="S21" s="4" t="n">
-        <v>0.6847340280419516</v>
+        <v>0.6236586205982846</v>
       </c>
       <c r="T21" s="4" t="n">
-        <v>0.4712907420985033</v>
+        <v>0.4431423741280938</v>
       </c>
       <c r="U21" s="4" t="n">
-        <v>0.6874139050303185</v>
+        <v>0.6916185855966361</v>
       </c>
       <c r="V21" s="4" t="n">
-        <v>0.8202277657266777</v>
+        <v>0.8568840064129972</v>
       </c>
       <c r="W21" s="4" t="n">
-        <v>0.8735566408935824</v>
+        <v>0.9434932623222352</v>
       </c>
       <c r="X21" s="4" t="n">
-        <v>1.101883602098454</v>
+        <v>1.138796975533531</v>
       </c>
       <c r="Y21" s="4" t="n">
-        <v>1.789848800647214</v>
+        <v>1.792881232484127</v>
       </c>
       <c r="Z21" s="4" t="n">
-        <v>1.801636537478046</v>
+        <v>1.771278914184926</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>X &lt; 0.0026</t>
+          <t>X &lt; 0.002602</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>2036</v>
+        <v>2040</v>
       </c>
       <c r="C22" s="4" t="n">
-        <v>0.0630549498916082</v>
+        <v>0.1414857318584168</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>0.704919005349872</v>
+        <v>0.7339905342894752</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>0.4376660253868394</v>
+        <v>0.4672745599290522</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>1.140580088842434</v>
+        <v>1.169645089046583</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>0.3356424972722252</v>
+        <v>0.3735500471972131</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>0.5716590887841377</v>
+        <v>0.6371336917704085</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>0.7758325268326942</v>
+        <v>0.8422245779826412</v>
       </c>
       <c r="J22" s="4" t="n">
-        <v>0.4972778813141332</v>
+        <v>0.5640131332295653</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>0.5876459248419081</v>
+        <v>0.6543522936494099</v>
       </c>
       <c r="L22" s="4" t="n">
-        <v>0.497738213144288</v>
+        <v>0.5653643166847289</v>
       </c>
       <c r="M22" s="4" t="n">
-        <v>0.7029979564112168</v>
+        <v>0.7417200018363985</v>
       </c>
       <c r="N22" s="4" t="n">
-        <v>0.1591379280865794</v>
+        <v>0.1698587273576209</v>
       </c>
       <c r="O22" s="4" t="n">
-        <v>-0.1051338635133519</v>
+        <v>-0.1228197049113007</v>
       </c>
       <c r="P22" s="4" t="n">
-        <v>-0.05280064616574265</v>
+        <v>-0.09963868883223626</v>
       </c>
       <c r="Q22" s="4" t="n">
-        <v>0.1988569580940833</v>
+        <v>0.1509698718009034</v>
       </c>
       <c r="R22" s="4" t="n">
-        <v>0.3335216166601072</v>
+        <v>0.2858042527969218</v>
       </c>
       <c r="S22" s="4" t="n">
-        <v>0.1797576340136189</v>
+        <v>0.1321980263979654</v>
       </c>
       <c r="T22" s="4" t="n">
-        <v>0.1237938257614744</v>
+        <v>0.1055442105518551</v>
       </c>
       <c r="U22" s="4" t="n">
-        <v>0.4379562043795673</v>
+        <v>0.4486706546598427</v>
       </c>
       <c r="V22" s="4" t="n">
-        <v>0.4289215686274517</v>
+        <v>0.4689026645711607</v>
       </c>
       <c r="W22" s="4" t="n">
-        <v>0.4054876733953776</v>
+        <v>0.4458538594895174</v>
       </c>
       <c r="X22" s="4" t="n">
-        <v>0.6044706393829955</v>
+        <v>0.6151059372961001</v>
       </c>
       <c r="Y22" s="4" t="n">
-        <v>1.25263737489017</v>
+        <v>1.232717904680115</v>
       </c>
       <c r="Z22" s="4" t="n">
-        <v>1.648686221119263</v>
+        <v>1.598062122045086</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>X &lt; 0.004199</t>
+          <t>X &lt; 0.004201</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>2239</v>
+        <v>2243</v>
       </c>
       <c r="C23" s="4" t="n">
-        <v>0.2061446696372329</v>
+        <v>0.1882808192816299</v>
       </c>
       <c r="D23" s="4" t="n">
-        <v>0.4716258835090557</v>
+        <v>0.453074051017154</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>-0.01180253317188829</v>
+        <v>-0.03039085624919124</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>0.1177241713890496</v>
+        <v>0.1234030197444866</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>-0.4250866700042764</v>
+        <v>-0.4091723751974641</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>-0.3266925851821298</v>
+        <v>-0.2860690040612184</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>-0.1674681712974149</v>
+        <v>-0.1010761201474679</v>
       </c>
       <c r="J23" s="4" t="n">
-        <v>-0.4016375527236562</v>
+        <v>-0.3349023008082241</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>-0.3601214877010221</v>
+        <v>-0.2934151188935203</v>
       </c>
       <c r="L23" s="4" t="n">
-        <v>-0.2906368807163418</v>
+        <v>-0.2230107771759009</v>
       </c>
       <c r="M23" s="4" t="n">
-        <v>-0.3458362285600174</v>
+        <v>-0.3040332477525496</v>
       </c>
       <c r="N23" s="4" t="n">
-        <v>-0.9992062579801342</v>
+        <v>-0.9822500280314372</v>
       </c>
       <c r="O23" s="4" t="n">
-        <v>-1.12052851452443</v>
+        <v>-1.128936284856486</v>
       </c>
       <c r="P23" s="4" t="n">
-        <v>-1.404965212916132</v>
+        <v>-1.438785689487716</v>
       </c>
       <c r="Q23" s="4" t="n">
-        <v>-1.148384773374268</v>
+        <v>-1.183089220236759</v>
       </c>
       <c r="R23" s="4" t="n">
-        <v>-0.9721116551616333</v>
+        <v>-1.006791594308254</v>
       </c>
       <c r="S23" s="4" t="n">
-        <v>-1.258223613694724</v>
+        <v>-1.292502995563325</v>
       </c>
       <c r="T23" s="4" t="n">
-        <v>-1.114469853875185</v>
+        <v>-1.149095095066542</v>
       </c>
       <c r="U23" s="4" t="n">
-        <v>-1.184147182429705</v>
+        <v>-1.218542077258135</v>
       </c>
       <c r="V23" s="4" t="n">
-        <v>-0.9710766830138198</v>
+        <v>-1.005762123386091</v>
       </c>
       <c r="W23" s="4" t="n">
-        <v>-1.042196840755317</v>
+        <v>-1.077115078753636</v>
       </c>
       <c r="X23" s="4" t="n">
-        <v>-0.7795191415705034</v>
+        <v>-0.8149783458603608</v>
       </c>
       <c r="Y23" s="4" t="n">
-        <v>-0.1658088695870035</v>
+        <v>-0.20221970672808</v>
       </c>
       <c r="Z23" s="4" t="n">
-        <v>0.2314760401077152</v>
+        <v>0.1942830446539858</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>X &lt; 0.005798</t>
+          <t>X &lt; 0.005799</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>2423</v>
+        <v>2427</v>
       </c>
       <c r="C24" s="4" t="n">
-        <v>0.3644189796530597</v>
+        <v>0.350147565241798</v>
       </c>
       <c r="D24" s="4" t="n">
-        <v>0.6666669844449089</v>
+        <v>0.651730715572846</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>0.1521515691502557</v>
+        <v>0.1373607262007468</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>-0.1102671030909121</v>
+        <v>-0.1020068163210865</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>-0.5576050046516912</v>
+        <v>-0.5378282072103318</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>-0.4935425664499888</v>
+        <v>-0.4509749992730789</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>-0.4867615914051271</v>
+        <v>-0.4203695402551801</v>
       </c>
       <c r="J24" s="4" t="n">
-        <v>-0.6011800038502386</v>
+        <v>-0.5344447519348066</v>
       </c>
       <c r="K24" s="4" t="n">
-        <v>-0.6417320553643293</v>
+        <v>-0.5750256865568275</v>
       </c>
       <c r="L24" s="4" t="n">
-        <v>-0.553852242498138</v>
+        <v>-0.4862261389576972</v>
       </c>
       <c r="M24" s="4" t="n">
-        <v>-0.2969105518398933</v>
+        <v>-0.2532005550641401</v>
       </c>
       <c r="N24" s="4" t="n">
-        <v>-0.7987751468244255</v>
+        <v>-0.7781543081223035</v>
       </c>
       <c r="O24" s="4" t="n">
-        <v>-1.078019612853666</v>
+        <v>-1.080635209611167</v>
       </c>
       <c r="P24" s="4" t="n">
-        <v>-1.27546526801666</v>
+        <v>-1.301714086057757</v>
       </c>
       <c r="Q24" s="4" t="n">
-        <v>-1.088097266350474</v>
+        <v>-1.114987011508603</v>
       </c>
       <c r="R24" s="4" t="n">
-        <v>-0.8801017775552751</v>
+        <v>-0.9070686329413178</v>
       </c>
       <c r="S24" s="4" t="n">
-        <v>-1.031208233814986</v>
+        <v>-1.058010162549543</v>
       </c>
       <c r="T24" s="4" t="n">
-        <v>-0.988541598321703</v>
+        <v>-1.015483170544947</v>
       </c>
       <c r="U24" s="4" t="n">
-        <v>-1.036508375521585</v>
+        <v>-1.063287113781833</v>
       </c>
       <c r="V24" s="4" t="n">
-        <v>-0.9489596209311912</v>
+        <v>-0.9758122308743538</v>
       </c>
       <c r="W24" s="4" t="n">
-        <v>-1.055875594488477</v>
+        <v>-1.082831688803864</v>
       </c>
       <c r="X24" s="4" t="n">
-        <v>-0.8188977326817977</v>
+        <v>-0.846299950707504</v>
       </c>
       <c r="Y24" s="4" t="n">
-        <v>-0.3959479549241038</v>
+        <v>-0.4239348717517046</v>
       </c>
       <c r="Z24" s="4" t="n">
-        <v>0.006576835540492709</v>
+        <v>-0.02212983607314811</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>X &lt; 0.007397</t>
+          <t>X &lt; 0.007398</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>2585</v>
+        <v>2589</v>
       </c>
       <c r="C25" s="4" t="n">
-        <v>0.6511381098201383</v>
+        <v>0.6393832128636205</v>
       </c>
       <c r="D25" s="4" t="n">
-        <v>0.5291646180664102</v>
+        <v>0.5174636458219126</v>
       </c>
       <c r="E25" s="4" t="n">
-        <v>0.1108333196357023</v>
+        <v>0.09922680484223889</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>0.08961407339137395</v>
+        <v>0.09938303511727753</v>
       </c>
       <c r="G25" s="4" t="n">
-        <v>-0.6219427451070914</v>
+        <v>-0.5992578872510848</v>
       </c>
       <c r="H25" s="4" t="n">
-        <v>-0.4732544691530052</v>
+        <v>-0.429267420551561</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>-0.2842121748892197</v>
+        <v>-0.2178201237392727</v>
       </c>
       <c r="J25" s="4" t="n">
-        <v>-0.5627668204077807</v>
+        <v>-0.4960315684923486</v>
       </c>
       <c r="K25" s="4" t="n">
-        <v>-0.6366797665432884</v>
+        <v>-0.5699733977357866</v>
       </c>
       <c r="L25" s="4" t="n">
-        <v>-0.7948937844693162</v>
+        <v>-0.7272676809288754</v>
       </c>
       <c r="M25" s="4" t="n">
-        <v>-0.7679056712382959</v>
+        <v>-0.7225423981359427</v>
       </c>
       <c r="N25" s="4" t="n">
-        <v>-0.8709955812381693</v>
+        <v>-0.8473864533730904</v>
       </c>
       <c r="O25" s="4" t="n">
-        <v>-0.9718895828346632</v>
+        <v>-0.9701637568586747</v>
       </c>
       <c r="P25" s="4" t="n">
-        <v>-1.324929641551087</v>
+        <v>-1.345147981516114</v>
       </c>
       <c r="Q25" s="4" t="n">
-        <v>-1.22898413077445</v>
+        <v>-1.24961122035436</v>
       </c>
       <c r="R25" s="4" t="n">
-        <v>-0.9968607700203478</v>
+        <v>-1.017636900386229</v>
       </c>
       <c r="S25" s="4" t="n">
-        <v>-1.069788480728576</v>
+        <v>-1.090517034255335</v>
       </c>
       <c r="T25" s="4" t="n">
-        <v>-0.9591781511419839</v>
+        <v>-0.9801311110736535</v>
       </c>
       <c r="U25" s="4" t="n">
-        <v>-1.067835301411932</v>
+        <v>-1.088554177451016</v>
       </c>
       <c r="V25" s="4" t="n">
-        <v>-0.9740730011587502</v>
+        <v>-0.9948807511111823</v>
       </c>
       <c r="W25" s="4" t="n">
-        <v>-1.031028847946956</v>
+        <v>-1.051967491273011</v>
       </c>
       <c r="X25" s="4" t="n">
-        <v>-0.8522923026769078</v>
+        <v>-0.8735501194917177</v>
       </c>
       <c r="Y25" s="4" t="n">
-        <v>-0.4386378387616858</v>
+        <v>-0.4604458473071631</v>
       </c>
       <c r="Z25" s="4" t="n">
-        <v>-0.2595382718563002</v>
+        <v>-0.2816665944705008</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>X &lt; 0.008996</t>
+          <t>X &lt; 0.008997</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>2720</v>
+        <v>2724</v>
       </c>
       <c r="C26" s="4" t="n">
-        <v>0.6387440913252291</v>
+        <v>0.6292258792687662</v>
       </c>
       <c r="D26" s="4" t="n">
-        <v>0.7987469552904329</v>
+        <v>0.7888886840561184</v>
       </c>
       <c r="E26" s="4" t="n">
-        <v>0.3666573338801129</v>
+        <v>0.3569925395524578</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>0.4575458056174639</v>
+        <v>0.4682148575230798</v>
       </c>
       <c r="G26" s="4" t="n">
-        <v>-0.3832177614109753</v>
+        <v>-0.3585862832121478</v>
       </c>
       <c r="H26" s="4" t="n">
-        <v>-0.04974736932591384</v>
+        <v>-0.004854539100286104</v>
       </c>
       <c r="I26" s="4" t="n">
-        <v>-0.1276610507581424</v>
+        <v>-0.06126899960819543</v>
       </c>
       <c r="J26" s="4" t="n">
-        <v>-0.4793685858158341</v>
+        <v>-0.412633333900402</v>
       </c>
       <c r="K26" s="4" t="n">
-        <v>-0.5475818551019032</v>
+        <v>-0.4808754862944014</v>
       </c>
       <c r="L26" s="4" t="n">
-        <v>-0.626464815249534</v>
+        <v>-0.5588387117090932</v>
       </c>
       <c r="M26" s="4" t="n">
-        <v>-0.6603755184314011</v>
+        <v>-0.6139670724732866</v>
       </c>
       <c r="N26" s="4" t="n">
-        <v>-0.8087264126795617</v>
+        <v>-0.7829871416125798</v>
       </c>
       <c r="O26" s="4" t="n">
-        <v>-0.8503466519588372</v>
+        <v>-0.8454323101512173</v>
       </c>
       <c r="P26" s="4" t="n">
-        <v>-1.050310233983694</v>
+        <v>-1.066511186597808</v>
       </c>
       <c r="Q26" s="4" t="n">
-        <v>-1.211467596720183</v>
+        <v>-1.227640422924267</v>
       </c>
       <c r="R26" s="4" t="n">
-        <v>-1.03469102132857</v>
+        <v>-1.050956120502242</v>
       </c>
       <c r="S26" s="4" t="n">
-        <v>-1.073990289798367</v>
+        <v>-1.090249038933692</v>
       </c>
       <c r="T26" s="4" t="n">
-        <v>-0.9740583745463809</v>
+        <v>-0.9905060925469016</v>
       </c>
       <c r="U26" s="4" t="n">
-        <v>-1.066630951583733</v>
+        <v>-1.082889556357671</v>
       </c>
       <c r="V26" s="4" t="n">
-        <v>-0.9315345080763606</v>
+        <v>-0.9479463586062025</v>
       </c>
       <c r="W26" s="4" t="n">
-        <v>-0.9758574049582904</v>
+        <v>-0.9923781990104459</v>
       </c>
       <c r="X26" s="4" t="n">
-        <v>-1.177109175147542</v>
+        <v>-1.193368736505917</v>
       </c>
       <c r="Y26" s="4" t="n">
-        <v>-0.8807180416350988</v>
+        <v>-0.8973414585146955</v>
       </c>
       <c r="Z26" s="4" t="n">
-        <v>-0.6776745786033729</v>
+        <v>-0.6946302853143322</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>X &lt; 0.01059</t>
+          <t>X &lt; 0.0106</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>2857</v>
+        <v>2861</v>
       </c>
       <c r="C27" s="4" t="n">
-        <v>0.79544381164051</v>
+        <v>0.7877739355433704</v>
       </c>
       <c r="D27" s="4" t="n">
-        <v>0.6879890921309695</v>
+        <v>0.6803872070507424</v>
       </c>
       <c r="E27" s="4" t="n">
-        <v>0.5551794341752014</v>
+        <v>0.5474275987979311</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>0.4876271296236325</v>
+        <v>0.4798007944315543</v>
       </c>
       <c r="G27" s="4" t="n">
-        <v>-0.03206605566956</v>
+        <v>-0.04499614845495614</v>
       </c>
       <c r="H27" s="4" t="n">
-        <v>0.2595917652787207</v>
+        <v>0.2659844396272319</v>
       </c>
       <c r="I27" s="4" t="n">
-        <v>0.1136848808735849</v>
+        <v>0.1402388207234182</v>
       </c>
       <c r="J27" s="4" t="n">
-        <v>-0.1648697646449762</v>
+        <v>-0.1180605039839264</v>
       </c>
       <c r="K27" s="4" t="n">
-        <v>-0.2626779768776402</v>
+        <v>-0.1959716080701384</v>
       </c>
       <c r="L27" s="4" t="n">
-        <v>-0.4443852093120029</v>
+        <v>-0.376759105771562</v>
       </c>
       <c r="M27" s="4" t="n">
-        <v>-0.498360349589106</v>
+        <v>-0.4510101567479126</v>
       </c>
       <c r="N27" s="4" t="n">
-        <v>-0.7923193920056946</v>
+        <v>-0.7645906295097404</v>
       </c>
       <c r="O27" s="4" t="n">
-        <v>-0.9205285145244346</v>
+        <v>-0.9124827555786794</v>
       </c>
       <c r="P27" s="4" t="n">
-        <v>-1.016899858752602</v>
+        <v>-1.029068424083789</v>
       </c>
       <c r="Q27" s="4" t="n">
-        <v>-1.20184005843187</v>
+        <v>-1.213909675612086</v>
       </c>
       <c r="R27" s="4" t="n">
-        <v>-1.17957850450351</v>
+        <v>-1.191551274332731</v>
       </c>
       <c r="S27" s="4" t="n">
-        <v>-1.398043877652505</v>
+        <v>-1.409750787288111</v>
       </c>
       <c r="T27" s="4" t="n">
-        <v>-1.238173944231605</v>
+        <v>-1.250136010356101</v>
       </c>
       <c r="U27" s="4" t="n">
-        <v>-1.24618076277627</v>
+        <v>-1.258090296284486</v>
       </c>
       <c r="V27" s="4" t="n">
-        <v>-1.143612373296051</v>
+        <v>-1.15563035956837</v>
       </c>
       <c r="W27" s="4" t="n">
-        <v>-1.141976632774174</v>
+        <v>-1.154129709357015</v>
       </c>
       <c r="X27" s="4" t="n">
-        <v>-1.197373373000133</v>
+        <v>-1.209474750724823</v>
       </c>
       <c r="Y27" s="4" t="n">
-        <v>-1.076973020341782</v>
+        <v>-1.08918779680382</v>
       </c>
       <c r="Z27" s="4" t="n">
-        <v>-1.062384990594559</v>
+        <v>-1.074645898597637</v>
       </c>
     </row>
     <row r="28">
@@ -7632,79 +7632,79 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>2977</v>
+        <v>2981</v>
       </c>
       <c r="C28" s="4" t="n">
-        <v>0.3952581806401341</v>
+        <v>0.3897991224108068</v>
       </c>
       <c r="D28" s="4" t="n">
-        <v>0.4785242340927027</v>
+        <v>0.4728932491645708</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>0.1918570881489146</v>
+        <v>0.1863570391872358</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>0.1644213223589759</v>
+        <v>0.1588314959032004</v>
       </c>
       <c r="G28" s="4" t="n">
-        <v>-0.1152348313958669</v>
+        <v>-0.1248290805546191</v>
       </c>
       <c r="H28" s="4" t="n">
-        <v>0.1910119151395904</v>
+        <v>0.18103518975105</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>0.03864441536659768</v>
+        <v>0.02873151802906904</v>
       </c>
       <c r="J28" s="4" t="n">
-        <v>-0.1730653103658781</v>
+        <v>-0.1636448344139438</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>-0.3655064645945743</v>
+        <v>-0.3368664245229738</v>
       </c>
       <c r="L28" s="4" t="n">
-        <v>-0.5519178385476735</v>
+        <v>-0.5227633141281558</v>
       </c>
       <c r="M28" s="4" t="n">
-        <v>-0.5258620101766596</v>
+        <v>-0.4968539906242029</v>
       </c>
       <c r="N28" s="4" t="n">
-        <v>-0.7857774543957206</v>
+        <v>-0.7756033940721991</v>
       </c>
       <c r="O28" s="4" t="n">
-        <v>-0.887061312382535</v>
+        <v>-0.8960916641368755</v>
       </c>
       <c r="P28" s="4" t="n">
-        <v>-0.9549642230032731</v>
+        <v>-0.9639479494589338</v>
       </c>
       <c r="Q28" s="4" t="n">
-        <v>-1.058463360755951</v>
+        <v>-1.067428373245313</v>
       </c>
       <c r="R28" s="4" t="n">
-        <v>-1.11362921179213</v>
+        <v>-1.122423634133234</v>
       </c>
       <c r="S28" s="4" t="n">
-        <v>-1.328679521009249</v>
+        <v>-1.337215177624905</v>
       </c>
       <c r="T28" s="4" t="n">
-        <v>-1.212964142595162</v>
+        <v>-1.221678781034626</v>
       </c>
       <c r="U28" s="4" t="n">
-        <v>-1.34608135430588</v>
+        <v>-1.354586202511683</v>
       </c>
       <c r="V28" s="4" t="n">
-        <v>-1.374329084199935</v>
+        <v>-1.382769545901432</v>
       </c>
       <c r="W28" s="4" t="n">
-        <v>-1.294039335172457</v>
+        <v>-1.302687380062594</v>
       </c>
       <c r="X28" s="4" t="n">
-        <v>-1.283178626775502</v>
+        <v>-1.29186033563613</v>
       </c>
       <c r="Y28" s="4" t="n">
-        <v>-1.223745644028142</v>
+        <v>-1.232465351721032</v>
       </c>
       <c r="Z28" s="4" t="n">
-        <v>-1.179265204776584</v>
+        <v>-1.188063733865881</v>
       </c>
     </row>
     <row r="29">
@@ -7714,79 +7714,79 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>3071</v>
+        <v>3075</v>
       </c>
       <c r="C29" s="4" t="n">
-        <v>0.3834278991311919</v>
+        <v>0.3791722601553786</v>
       </c>
       <c r="D29" s="4" t="n">
-        <v>0.09807694765144959</v>
+        <v>0.09414353007868215</v>
       </c>
       <c r="E29" s="4" t="n">
-        <v>-0.127095087489991</v>
+        <v>-0.1309289058854688</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>-0.07864830285240743</v>
+        <v>-0.08264093629946956</v>
       </c>
       <c r="G29" s="4" t="n">
-        <v>-0.3933890680011487</v>
+        <v>-0.4003117980986204</v>
       </c>
       <c r="H29" s="4" t="n">
-        <v>-0.0908958696916784</v>
+        <v>-0.0981897013755173</v>
       </c>
       <c r="I29" s="4" t="n">
-        <v>-0.2300561384480133</v>
+        <v>-0.2372761298257799</v>
       </c>
       <c r="J29" s="4" t="n">
-        <v>-0.4577735494029511</v>
+        <v>-0.4647399714006184</v>
       </c>
       <c r="K29" s="4" t="n">
-        <v>-0.6106839263764314</v>
+        <v>-0.5990828829064512</v>
       </c>
       <c r="L29" s="4" t="n">
-        <v>-0.6529990400126806</v>
+        <v>-0.6412067806623298</v>
       </c>
       <c r="M29" s="4" t="n">
-        <v>-0.5869823030682326</v>
+        <v>-0.5753052845616935</v>
       </c>
       <c r="N29" s="4" t="n">
-        <v>-0.7501945022217456</v>
+        <v>-0.7383036689031641</v>
       </c>
       <c r="O29" s="4" t="n">
-        <v>-0.7853349172932056</v>
+        <v>-0.79212030478066</v>
       </c>
       <c r="P29" s="4" t="n">
-        <v>-0.7929726348739408</v>
+        <v>-0.799781760996197</v>
       </c>
       <c r="Q29" s="4" t="n">
-        <v>-0.8809031446826694</v>
+        <v>-0.8876895985141502</v>
       </c>
       <c r="R29" s="4" t="n">
-        <v>-0.8836822484379567</v>
+        <v>-0.8903910987920085</v>
       </c>
       <c r="S29" s="4" t="n">
-        <v>-1.031208233814986</v>
+        <v>-1.037747786103381</v>
       </c>
       <c r="T29" s="4" t="n">
-        <v>-0.9546375467875379</v>
+        <v>-0.9612947975128208</v>
       </c>
       <c r="U29" s="4" t="n">
-        <v>-1.239547046595725</v>
+        <v>-1.245810182818055</v>
       </c>
       <c r="V29" s="4" t="n">
-        <v>-1.326219512195124</v>
+        <v>-1.332349642987488</v>
       </c>
       <c r="W29" s="4" t="n">
-        <v>-1.199918040748116</v>
+        <v>-1.20628847892732</v>
       </c>
       <c r="X29" s="4" t="n">
-        <v>-1.159140820969881</v>
+        <v>-1.165578712254323</v>
       </c>
       <c r="Y29" s="4" t="n">
-        <v>-1.125630298158434</v>
+        <v>-1.132079769916373</v>
       </c>
       <c r="Z29" s="4" t="n">
-        <v>-1.215054623424948</v>
+        <v>-1.221402249069214</v>
       </c>
     </row>
     <row r="30">
@@ -7796,79 +7796,79 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>3138</v>
+        <v>3142</v>
       </c>
       <c r="C30" s="4" t="n">
-        <v>0.1379633775456242</v>
+        <v>0.1348242925711887</v>
       </c>
       <c r="D30" s="4" t="n">
-        <v>-0.1801829963444916</v>
+        <v>-0.1829564023001069</v>
       </c>
       <c r="E30" s="4" t="n">
-        <v>-0.5265535731485613</v>
+        <v>-0.5290397360261707</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>-0.5579775247801777</v>
+        <v>-0.5604995735508993</v>
       </c>
       <c r="G30" s="4" t="n">
-        <v>-0.7155802799743611</v>
+        <v>-0.7205336090824375</v>
       </c>
       <c r="H30" s="4" t="n">
-        <v>-0.4156740699451618</v>
+        <v>-0.4209908869585774</v>
       </c>
       <c r="I30" s="4" t="n">
-        <v>-0.5368998781323882</v>
+        <v>-0.54214677870592</v>
       </c>
       <c r="J30" s="4" t="n">
-        <v>-0.638987541366987</v>
+        <v>-0.6441374434805596</v>
       </c>
       <c r="K30" s="4" t="n">
-        <v>-0.6111875153212409</v>
+        <v>-0.6163716920530717</v>
       </c>
       <c r="L30" s="4" t="n">
-        <v>-0.7959557899653689</v>
+        <v>-0.8009896106366554</v>
       </c>
       <c r="M30" s="4" t="n">
-        <v>-0.6938184586789689</v>
+        <v>-0.6989565864529155</v>
       </c>
       <c r="N30" s="4" t="n">
-        <v>-0.954767454767449</v>
+        <v>-0.9596070699069799</v>
       </c>
       <c r="O30" s="4" t="n">
-        <v>-0.8861260587183608</v>
+        <v>-0.8911731670260679</v>
       </c>
       <c r="P30" s="4" t="n">
-        <v>-0.8983444530471516</v>
+        <v>-0.9034025229934102</v>
       </c>
       <c r="Q30" s="4" t="n">
-        <v>-0.903136234122627</v>
+        <v>-0.9082603435599808</v>
       </c>
       <c r="R30" s="4" t="n">
-        <v>-0.8931902933175806</v>
+        <v>-0.8982683982683923</v>
       </c>
       <c r="S30" s="4" t="n">
-        <v>-0.9768401402312108</v>
+        <v>-0.9818294131209271</v>
       </c>
       <c r="T30" s="4" t="n">
-        <v>-0.9359277728016124</v>
+        <v>-0.9409834000763126</v>
       </c>
       <c r="U30" s="4" t="n">
-        <v>-1.146517228646204</v>
+        <v>-1.151286022516963</v>
       </c>
       <c r="V30" s="4" t="n">
-        <v>-1.25915022278803</v>
+        <v>-1.263759577645232</v>
       </c>
       <c r="W30" s="4" t="n">
-        <v>-1.24261938384673</v>
+        <v>-1.247309892497761</v>
       </c>
       <c r="X30" s="4" t="n">
-        <v>-1.108805146169225</v>
+        <v>-1.113677179003844</v>
       </c>
       <c r="Y30" s="4" t="n">
-        <v>-1.133843503000747</v>
+        <v>-1.138658262713342</v>
       </c>
       <c r="Z30" s="4" t="n">
-        <v>-1.191115136470877</v>
+        <v>-1.195868308179207</v>
       </c>
     </row>
     <row r="31">
@@ -7878,79 +7878,79 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>3203</v>
+        <v>3207</v>
       </c>
       <c r="C31" s="4" t="n">
-        <v>0.04565540764039611</v>
+        <v>0.04336341288382073</v>
       </c>
       <c r="D31" s="4" t="n">
-        <v>-0.2418550599300104</v>
+        <v>-0.2438183992391956</v>
       </c>
       <c r="E31" s="4" t="n">
-        <v>-0.4862182281537173</v>
+        <v>-0.4879924031919529</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>-0.5313913802682819</v>
+        <v>-0.5331665495148812</v>
       </c>
       <c r="G31" s="4" t="n">
-        <v>-0.6311020717735758</v>
+        <v>-0.6347371118232488</v>
       </c>
       <c r="H31" s="4" t="n">
-        <v>-0.4886760621784845</v>
+        <v>-0.4924755302712995</v>
       </c>
       <c r="I31" s="4" t="n">
-        <v>-0.5609669706898046</v>
+        <v>-0.5647396776429119</v>
       </c>
       <c r="J31" s="4" t="n">
-        <v>-0.6666254388144424</v>
+        <v>-0.6702912929597602</v>
       </c>
       <c r="K31" s="4" t="n">
-        <v>-0.6074817506692227</v>
+        <v>-0.6112202221243805</v>
       </c>
       <c r="L31" s="4" t="n">
-        <v>-0.8041510691689737</v>
+        <v>-0.8077084302964437</v>
       </c>
       <c r="M31" s="4" t="n">
-        <v>-0.605251850273838</v>
+        <v>-0.6090372038304324</v>
       </c>
       <c r="N31" s="4" t="n">
-        <v>-0.8043317491217934</v>
+        <v>-0.8078941210890918</v>
       </c>
       <c r="O31" s="4" t="n">
-        <v>-0.7597734844476918</v>
+        <v>-0.7634819786445064</v>
       </c>
       <c r="P31" s="4" t="n">
-        <v>-0.8073070498040522</v>
+        <v>-0.8109763416503242</v>
       </c>
       <c r="Q31" s="4" t="n">
-        <v>-0.76304155421834</v>
+        <v>-0.7668202100479249</v>
       </c>
       <c r="R31" s="4" t="n">
-        <v>-0.7723505147670906</v>
+        <v>-0.7760733305056746</v>
       </c>
       <c r="S31" s="4" t="n">
-        <v>-0.8881368134849978</v>
+        <v>-0.8917286057410294</v>
       </c>
       <c r="T31" s="4" t="n">
-        <v>-0.8501520006214278</v>
+        <v>-0.8538018381955865</v>
       </c>
       <c r="U31" s="4" t="n">
-        <v>-0.9585525237999803</v>
+        <v>-0.9620528442661893</v>
       </c>
       <c r="V31" s="4" t="n">
-        <v>-1.096234798877461</v>
+        <v>-1.099551316270976</v>
       </c>
       <c r="W31" s="4" t="n">
-        <v>-1.059809891218784</v>
+        <v>-1.063217058597331</v>
       </c>
       <c r="X31" s="4" t="n">
-        <v>-1.023796650287991</v>
+        <v>-1.027257146921684</v>
       </c>
       <c r="Y31" s="4" t="n">
-        <v>-0.9490931570847678</v>
+        <v>-0.9526275551995909</v>
       </c>
       <c r="Z31" s="4" t="n">
-        <v>-0.9442445222224052</v>
+        <v>-0.9477934512412958</v>
       </c>
     </row>
     <row r="32">
@@ -7960,79 +7960,79 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>3246</v>
+        <v>3250</v>
       </c>
       <c r="C32" s="4" t="n">
-        <v>-0.07975003836016015</v>
+        <v>-0.08142151001002418</v>
       </c>
       <c r="D32" s="4" t="n">
-        <v>-0.1537277649483642</v>
+        <v>-0.1553305132487779</v>
       </c>
       <c r="E32" s="4" t="n">
-        <v>-0.4750151377717415</v>
+        <v>-0.4763149265724778</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>-0.5596063743431259</v>
+        <v>-0.5608477447815119</v>
       </c>
       <c r="G32" s="4" t="n">
-        <v>-0.5403116312436396</v>
+        <v>-0.543146094589261</v>
       </c>
       <c r="H32" s="4" t="n">
-        <v>-0.4279056736132532</v>
+        <v>-0.4308680231313602</v>
       </c>
       <c r="I32" s="4" t="n">
-        <v>-0.4174702456929964</v>
+        <v>-0.4204951419027623</v>
       </c>
       <c r="J32" s="4" t="n">
-        <v>-0.556019896804429</v>
+        <v>-0.5588943163531184</v>
       </c>
       <c r="K32" s="4" t="n">
-        <v>-0.4664092912266113</v>
+        <v>-0.4693928351799244</v>
       </c>
       <c r="L32" s="4" t="n">
-        <v>-0.6399734163239472</v>
+        <v>-0.642794203196118</v>
       </c>
       <c r="M32" s="4" t="n">
-        <v>-0.4093439244228847</v>
+        <v>-0.4124323190218391</v>
       </c>
       <c r="N32" s="4" t="n">
-        <v>-0.609419739253994</v>
+        <v>-0.6122821155022535</v>
       </c>
       <c r="O32" s="4" t="n">
-        <v>-0.580235811628107</v>
+        <v>-0.5832057838501612</v>
       </c>
       <c r="P32" s="4" t="n">
-        <v>-0.6607223443958148</v>
+        <v>-0.6636093057158376</v>
       </c>
       <c r="Q32" s="4" t="n">
-        <v>-0.5949793910169845</v>
+        <v>-0.5979899978074954</v>
       </c>
       <c r="R32" s="4" t="n">
-        <v>-0.5962502662551898</v>
+        <v>-0.5992242870695819</v>
       </c>
       <c r="S32" s="4" t="n">
-        <v>-0.7122244277935792</v>
+        <v>-0.7150663633523706</v>
       </c>
       <c r="T32" s="4" t="n">
-        <v>-0.7375765526481928</v>
+        <v>-0.740395842436655</v>
       </c>
       <c r="U32" s="4" t="n">
-        <v>-0.7801305381611954</v>
+        <v>-0.7828860102164654</v>
       </c>
       <c r="V32" s="4" t="n">
-        <v>-0.8826923076923094</v>
+        <v>-0.8853119650242931</v>
       </c>
       <c r="W32" s="4" t="n">
-        <v>-0.9462090270342713</v>
+        <v>-0.9487863820974312</v>
       </c>
       <c r="X32" s="4" t="n">
-        <v>-0.9424313267095243</v>
+        <v>-0.9450199580804934</v>
       </c>
       <c r="Y32" s="4" t="n">
-        <v>-0.8650532270158351</v>
+        <v>-0.8677217790371117</v>
       </c>
       <c r="Z32" s="4" t="n">
-        <v>-0.7996346380430452</v>
+        <v>-0.8023903666427046</v>
       </c>
     </row>
     <row r="33">
@@ -8042,79 +8042,79 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>3280</v>
+        <v>3284</v>
       </c>
       <c r="C33" s="4" t="n">
-        <v>-0.05619830553887084</v>
+        <v>-0.05753897917131212</v>
       </c>
       <c r="D33" s="4" t="n">
-        <v>-0.1328583982873042</v>
+        <v>-0.1341236093014402</v>
       </c>
       <c r="E33" s="4" t="n">
-        <v>-0.3444836007793484</v>
+        <v>-0.3455642921289552</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>-0.3749119097956282</v>
+        <v>-0.3759916533790033</v>
       </c>
       <c r="G33" s="4" t="n">
-        <v>-0.4807734260146148</v>
+        <v>-0.4829747976408143</v>
       </c>
       <c r="H33" s="4" t="n">
-        <v>-0.3372573008620847</v>
+        <v>-0.3396247797278207</v>
       </c>
       <c r="I33" s="4" t="n">
-        <v>-0.4258639125737318</v>
+        <v>-0.4281636494748895</v>
       </c>
       <c r="J33" s="4" t="n">
-        <v>-0.5051807249341635</v>
+        <v>-0.5073995771670141</v>
       </c>
       <c r="K33" s="4" t="n">
-        <v>-0.385701947947247</v>
+        <v>-0.3880651137069435</v>
       </c>
       <c r="L33" s="4" t="n">
-        <v>-0.5654374502059625</v>
+        <v>-0.5676223818902741</v>
       </c>
       <c r="M33" s="4" t="n">
-        <v>-0.4254361549877359</v>
+        <v>-0.4277788793984811</v>
       </c>
       <c r="N33" s="4" t="n">
-        <v>-0.5048262794313843</v>
+        <v>-0.5070880002712599</v>
       </c>
       <c r="O33" s="4" t="n">
-        <v>-0.5179153270434256</v>
+        <v>-0.5202183185232769</v>
       </c>
       <c r="P33" s="4" t="n">
-        <v>-0.5694435829042845</v>
+        <v>-0.571696513913686</v>
       </c>
       <c r="Q33" s="4" t="n">
-        <v>-0.5415685662176557</v>
+        <v>-0.5438895399849315</v>
       </c>
       <c r="R33" s="4" t="n">
-        <v>-0.5062431329795771</v>
+        <v>-0.5085791082145903</v>
       </c>
       <c r="S33" s="4" t="n">
-        <v>-0.561531580181331</v>
+        <v>-0.5638085764404721</v>
       </c>
       <c r="T33" s="4" t="n">
-        <v>-0.5876617850890682</v>
+        <v>-0.5899137770609784</v>
       </c>
       <c r="U33" s="4" t="n">
-        <v>-0.6579342065793341</v>
+        <v>-0.6600915536211645</v>
       </c>
       <c r="V33" s="4" t="n">
-        <v>-0.7270097442143708</v>
+        <v>-0.7290752838368419</v>
       </c>
       <c r="W33" s="4" t="n">
-        <v>-0.7649868847823029</v>
+        <v>-0.7670347032979308</v>
       </c>
       <c r="X33" s="4" t="n">
-        <v>-0.7924491879799902</v>
+        <v>-0.7944688481871651</v>
       </c>
       <c r="Y33" s="4" t="n">
-        <v>-0.7739368357993968</v>
+        <v>-0.7759668477596691</v>
       </c>
       <c r="Z33" s="4" t="n">
-        <v>-0.6489801740122729</v>
+        <v>-0.651167655127658</v>
       </c>
     </row>
     <row r="34">
@@ -8124,79 +8124,79 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>3312</v>
+        <v>3316</v>
       </c>
       <c r="C34" s="4" t="n">
-        <v>-0.09091300994870011</v>
+        <v>-0.09188035691803975</v>
       </c>
       <c r="D34" s="4" t="n">
-        <v>-0.1400707656260778</v>
+        <v>-0.1409923959040071</v>
       </c>
       <c r="E34" s="4" t="n">
-        <v>-0.3034828330261163</v>
+        <v>-0.3042632784633597</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>-0.3704737709037076</v>
+        <v>-0.3712012968022762</v>
       </c>
       <c r="G34" s="4" t="n">
-        <v>-0.478826018573578</v>
+        <v>-0.4803784573005316</v>
       </c>
       <c r="H34" s="4" t="n">
-        <v>-0.3949499237457346</v>
+        <v>-0.3965970315524388</v>
       </c>
       <c r="I34" s="4" t="n">
-        <v>-0.4901513078436324</v>
+        <v>-0.4917143850392094</v>
       </c>
       <c r="J34" s="4" t="n">
-        <v>-0.6014512626488795</v>
+        <v>-0.6028923197185847</v>
       </c>
       <c r="K34" s="4" t="n">
-        <v>-0.5428655055960121</v>
+        <v>-0.5443764109724114</v>
       </c>
       <c r="L34" s="4" t="n">
-        <v>-0.698298049535417</v>
+        <v>-0.6996525321132694</v>
       </c>
       <c r="M34" s="4" t="n">
-        <v>-0.5570436431889618</v>
+        <v>-0.5585585380867073</v>
       </c>
       <c r="N34" s="4" t="n">
-        <v>-0.6684801359891566</v>
+        <v>-0.6698727276797669</v>
       </c>
       <c r="O34" s="4" t="n">
-        <v>-0.6321344930578903</v>
+        <v>-0.6336143476098073</v>
       </c>
       <c r="P34" s="4" t="n">
-        <v>-0.6552306998313213</v>
+        <v>-0.6566922476974071</v>
       </c>
       <c r="Q34" s="4" t="n">
-        <v>-0.6641107530935315</v>
+        <v>-0.6655876510384573</v>
       </c>
       <c r="R34" s="4" t="n">
-        <v>-0.6535476796333484</v>
+        <v>-0.6550158625970965</v>
       </c>
       <c r="S34" s="4" t="n">
-        <v>-0.6192516352560062</v>
+        <v>-0.6207672815164571</v>
       </c>
       <c r="T34" s="4" t="n">
-        <v>-0.6461597252791904</v>
+        <v>-0.6476480675696692</v>
       </c>
       <c r="U34" s="4" t="n">
-        <v>-0.6533913988763871</v>
+        <v>-0.6548639414653081</v>
       </c>
       <c r="V34" s="4" t="n">
-        <v>-0.6898371531966276</v>
+        <v>-0.6912597882779679</v>
       </c>
       <c r="W34" s="4" t="n">
-        <v>-0.672348221969294</v>
+        <v>-0.6738136519862863</v>
       </c>
       <c r="X34" s="4" t="n">
-        <v>-0.7304258327757509</v>
+        <v>-0.7318252402382015</v>
       </c>
       <c r="Y34" s="4" t="n">
-        <v>-0.709419537518535</v>
+        <v>-0.7108349159054512</v>
       </c>
       <c r="Z34" s="4" t="n">
-        <v>-0.6769641495042009</v>
+        <v>-0.6784226576327725</v>
       </c>
     </row>
     <row r="35">
@@ -8206,79 +8206,79 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>3332</v>
+        <v>3336</v>
       </c>
       <c r="C35" s="4" t="n">
-        <v>-0.05266089904439042</v>
+        <v>-0.05346991783804356</v>
       </c>
       <c r="D35" s="4" t="n">
-        <v>-0.1035127820528388</v>
+        <v>-0.1042719165465229</v>
       </c>
       <c r="E35" s="4" t="n">
-        <v>-0.2745267611588602</v>
+        <v>-0.2751264281943619</v>
       </c>
       <c r="F35" s="4" t="n">
-        <v>-0.3155353277460122</v>
+        <v>-0.3161083032590852</v>
       </c>
       <c r="G35" s="4" t="n">
-        <v>-0.4254045590935718</v>
+        <v>-0.4266199416254395</v>
       </c>
       <c r="H35" s="4" t="n">
-        <v>-0.3707466159603428</v>
+        <v>-0.3720223400506626</v>
       </c>
       <c r="I35" s="4" t="n">
-        <v>-0.4102684215725247</v>
+        <v>-0.4115214567096857</v>
       </c>
       <c r="J35" s="4" t="n">
-        <v>-0.4926750702033331</v>
+        <v>-0.4938391519120771</v>
       </c>
       <c r="K35" s="4" t="n">
-        <v>-0.4939138179751197</v>
+        <v>-0.4950760099127933</v>
       </c>
       <c r="L35" s="4" t="n">
-        <v>-0.6231416714330535</v>
+        <v>-0.6241740685751012</v>
       </c>
       <c r="M35" s="4" t="n">
-        <v>-0.481068953100511</v>
+        <v>-0.4822634751379056</v>
       </c>
       <c r="N35" s="4" t="n">
-        <v>-0.5934854619065106</v>
+        <v>-0.5945550868379357</v>
       </c>
       <c r="O35" s="4" t="n">
-        <v>-0.593975518213739</v>
+        <v>-0.595079823379173</v>
       </c>
       <c r="P35" s="4" t="n">
-        <v>-0.6780911903104325</v>
+        <v>-0.679102578518453</v>
       </c>
       <c r="Q35" s="4" t="n">
-        <v>-0.6908694429758171</v>
+        <v>-0.6918865822229208</v>
       </c>
       <c r="R35" s="4" t="n">
-        <v>-0.6768143992062505</v>
+        <v>-0.6778309409888408</v>
       </c>
       <c r="S35" s="4" t="n">
-        <v>-0.6435339467696366</v>
+        <v>-0.6445952613259536</v>
       </c>
       <c r="T35" s="4" t="n">
-        <v>-0.670917108342536</v>
+        <v>-0.6719497237212408</v>
       </c>
       <c r="U35" s="4" t="n">
-        <v>-0.6768175444966644</v>
+        <v>-0.6778372996700668</v>
       </c>
       <c r="V35" s="4" t="n">
-        <v>-0.7119304556354891</v>
+        <v>-0.7129032483457891</v>
       </c>
       <c r="W35" s="4" t="n">
-        <v>-0.6978106039004999</v>
+        <v>-0.6988178456705327</v>
       </c>
       <c r="X35" s="4" t="n">
-        <v>-0.7560030951144654</v>
+        <v>-0.7569437813331064</v>
       </c>
       <c r="Y35" s="4" t="n">
-        <v>-0.7334817082994434</v>
+        <v>-0.7344417491124631</v>
       </c>
       <c r="Z35" s="4" t="n">
-        <v>-0.7016841824449074</v>
+        <v>-0.7026855151392866</v>
       </c>
     </row>
   </sheetData>

--- a/workspaces/nasdaq_hourly_24hrs/treasury/tnx_ma_ratio_20.xlsx
+++ b/workspaces/nasdaq_hourly_24hrs/treasury/tnx_ma_ratio_20.xlsx
@@ -618,2379 +618,2379 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>X ≈ -0.02218</t>
+          <t>X ≈ -0.02165</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>-3.615960962337972</v>
+        <v>-0.5974106262807695</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>-3.949943212867538</v>
+        <v>5.00263275777197</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>0.8306814201895136</v>
+        <v>9.603255960055755</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>-6.090554643001397</v>
+        <v>9.017633432898933</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>-12.64112056627233</v>
+        <v>2.896511629202941</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>-18.67586029428402</v>
+        <v>-2.798230935516656</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>-19.44942855103064</v>
+        <v>2.262286476387338</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>-7.291670576513198</v>
+        <v>-3.894638610580628</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>-13.47423996419435</v>
+        <v>-3.767914323020463</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>-14.24767324933735</v>
+        <v>7.154187014048588</v>
       </c>
       <c r="M6" s="4" t="n">
-        <v>-1.527454587259349</v>
+        <v>-4.291592863037707</v>
       </c>
       <c r="N6" s="4" t="n">
-        <v>-14.26079219099792</v>
+        <v>-16.29122354956156</v>
       </c>
       <c r="O6" s="4" t="n">
-        <v>-15.38437616111161</v>
+        <v>-17.40716843523569</v>
       </c>
       <c r="P6" s="4" t="n">
-        <v>-9.378118390504696</v>
+        <v>-17.65989756321779</v>
       </c>
       <c r="Q6" s="4" t="n">
-        <v>-10.03712956851162</v>
+        <v>-18.34534651277293</v>
       </c>
       <c r="R6" s="4" t="n">
-        <v>-9.447124969330019</v>
+        <v>-17.79091017332094</v>
       </c>
       <c r="S6" s="4" t="n">
-        <v>-22.05707975961501</v>
+        <v>-29.64003239960631</v>
       </c>
       <c r="T6" s="4" t="n">
-        <v>-9.690857748665536</v>
+        <v>-18.03799686995327</v>
       </c>
       <c r="U6" s="4" t="n">
-        <v>3.002930018205753</v>
+        <v>-0.208517686814865</v>
       </c>
       <c r="V6" s="4" t="n">
-        <v>3.19030117313811</v>
+        <v>-5.869957342721051</v>
       </c>
       <c r="W6" s="4" t="n">
-        <v>2.649198020584485</v>
+        <v>-12.31577802523732</v>
       </c>
       <c r="X6" s="4" t="n">
-        <v>2.574226415431404</v>
+        <v>-12.39469938844834</v>
       </c>
       <c r="Y6" s="4" t="n">
-        <v>2.84944795053498</v>
+        <v>-12.15488109322268</v>
       </c>
       <c r="Z6" s="4" t="n">
-        <v>2.774532710278955</v>
+        <v>-12.32070676922552</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>X ≈ -0.02058</t>
+          <t>X ≈ -0.02007</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>-1.776630970591576</v>
+        <v>-7.06508705854062</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>8.927324149752934</v>
+        <v>-0.2152787270263588</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>-3.539670391358591</v>
+        <v>-12.10874774836616</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>-0.5680692023262921</v>
+        <v>-9.150778432704861</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>-4.584821464740095</v>
+        <v>-12.97909837936669</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>-8.084306995080681</v>
+        <v>-19.9318867238406</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>-1.485333105525633</v>
+        <v>-20.72921371891401</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>-16.50571789459047</v>
+        <v>-24.5928069358984</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>-16.46907581909801</v>
+        <v>-24.4723145931788</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>-13.55539715889715</v>
+        <v>-21.71588269835545</v>
       </c>
       <c r="M7" s="4" t="n">
-        <v>-20.66479600397564</v>
+        <v>-25.00843381625795</v>
       </c>
       <c r="N7" s="4" t="n">
-        <v>-17.25846290808551</v>
+        <v>-21.73290867317544</v>
       </c>
       <c r="O7" s="4" t="n">
-        <v>-18.38295965439533</v>
+        <v>-19.29088703612006</v>
       </c>
       <c r="P7" s="4" t="n">
-        <v>-18.60898257033779</v>
+        <v>-19.54424353150284</v>
       </c>
       <c r="Q7" s="4" t="n">
-        <v>-15.57719177582113</v>
+        <v>-16.66854533521629</v>
       </c>
       <c r="R7" s="4" t="n">
-        <v>-14.98892256049297</v>
+        <v>-16.11369739311235</v>
       </c>
       <c r="S7" s="4" t="n">
-        <v>-15.12675959826029</v>
+        <v>-16.22213536418285</v>
       </c>
       <c r="T7" s="4" t="n">
-        <v>-15.23607986772546</v>
+        <v>-16.35991389177218</v>
       </c>
       <c r="U7" s="4" t="n">
-        <v>-11.3272221740006</v>
+        <v>-12.58479557814047</v>
       </c>
       <c r="V7" s="4" t="n">
-        <v>-18.54261115099277</v>
+        <v>-23.07598778389144</v>
       </c>
       <c r="W7" s="4" t="n">
-        <v>-22.79062181536202</v>
+        <v>-23.64990583719044</v>
       </c>
       <c r="X7" s="4" t="n">
-        <v>-26.57475837311694</v>
+        <v>-23.73229517617893</v>
       </c>
       <c r="Y7" s="4" t="n">
-        <v>-22.60579687902953</v>
+        <v>-23.49594772665799</v>
       </c>
       <c r="Z7" s="4" t="n">
-        <v>-18.9847265489772</v>
+        <v>-20.093816012923</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>X ≈ -0.01898</t>
+          <t>X ≈ -0.01849</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>6.314767112448735</v>
+        <v>11.99867975769181</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>9.956478028830702</v>
+        <v>17.96648665146699</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>16.48018318889687</v>
+        <v>13.62094057597167</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>-0.1262811852932515</v>
+        <v>13.03651396820118</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>-8.414001482012637</v>
+        <v>3.445075395945722</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>-12.2090525549478</v>
+        <v>3.601772748327313</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>-16.96028547341049</v>
+        <v>-0.2973651678060207</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>-17.24159680969895</v>
+        <v>-9.929957415883464</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>-21.18697965788824</v>
+        <v>-12.91594122371027</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>-25.94585166638187</v>
+        <v>-16.82434261293649</v>
       </c>
       <c r="M8" s="4" t="n">
-        <v>-21.69643847343924</v>
+        <v>-4.107248680345123</v>
       </c>
       <c r="N8" s="4" t="n">
-        <v>-21.98086868510991</v>
+        <v>1.843084322132384</v>
       </c>
       <c r="O8" s="4" t="n">
-        <v>-11.14708297003283</v>
+        <v>10.07618977945923</v>
       </c>
       <c r="P8" s="4" t="n">
-        <v>-3.395382034041724</v>
+        <v>12.94716815525292</v>
       </c>
       <c r="Q8" s="4" t="n">
-        <v>-8.041713339915319</v>
+        <v>9.154367521675489</v>
       </c>
       <c r="R8" s="4" t="n">
-        <v>-3.46100903371368</v>
+        <v>9.716944284273609</v>
       </c>
       <c r="S8" s="4" t="n">
-        <v>-3.595388337532469</v>
+        <v>6.497923391659079</v>
       </c>
       <c r="T8" s="4" t="n">
-        <v>-7.693927167219762</v>
+        <v>3.247664290465792</v>
       </c>
       <c r="U8" s="4" t="n">
-        <v>-11.47487084694864</v>
+        <v>0.3423039633057812</v>
       </c>
       <c r="V8" s="4" t="n">
-        <v>-15.28698087070352</v>
+        <v>-2.564749963361876</v>
       </c>
       <c r="W8" s="4" t="n">
-        <v>-15.83371737647918</v>
+        <v>-6.254691198429441</v>
       </c>
       <c r="X8" s="4" t="n">
-        <v>-11.91680742361215</v>
+        <v>-3.208819774672911</v>
       </c>
       <c r="Y8" s="4" t="n">
-        <v>-19.64363211266975</v>
+        <v>-6.090404343038024</v>
       </c>
       <c r="Z8" s="4" t="n">
-        <v>-23.72546728972053</v>
+        <v>-9.379530298637995</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>X ≈ -0.01738</t>
+          <t>X ≈ -0.01691</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>-11.25296343496465</v>
+        <v>-11.94856655358875</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>-0.1299942940045256</v>
+        <v>0.9214069389529698</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>-7.290218655739316</v>
+        <v>-5.947489295076799</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>-0.3556166395393419</v>
+        <v>-10.28809121051324</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>-0.689249743650187</v>
+        <v>-4.937710938195913</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>5.233372521890153</v>
+        <v>-4.783600675683317</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>-1.271899559835575</v>
+        <v>-5.576134072338903</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>0.3651260713496214</v>
+        <v>-0.2478473938544781</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>-7.249660617105022</v>
+        <v>-9.510356189099241</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>3.467229290544218</v>
+        <v>-4.669913647386252</v>
       </c>
       <c r="M9" s="4" t="n">
-        <v>7.571937024705413</v>
+        <v>-6.279638150086164</v>
       </c>
       <c r="N9" s="4" t="n">
-        <v>11.12829421157882</v>
+        <v>-4.677637965465294</v>
       </c>
       <c r="O9" s="4" t="n">
-        <v>15.76178252843881</v>
+        <v>-0.1492677936985771</v>
       </c>
       <c r="P9" s="4" t="n">
-        <v>9.794626290592774</v>
+        <v>-2.277921215143685</v>
       </c>
       <c r="Q9" s="4" t="n">
-        <v>12.97692453539225</v>
+        <v>-1.077179211525255</v>
       </c>
       <c r="R9" s="4" t="n">
-        <v>7.818831981362791</v>
+        <v>-2.399859702216048</v>
       </c>
       <c r="S9" s="4" t="n">
-        <v>5.769041219137677</v>
+        <v>-2.504122715578816</v>
       </c>
       <c r="T9" s="4" t="n">
-        <v>9.505102154535223</v>
+        <v>4.89541873013566</v>
       </c>
       <c r="U9" s="4" t="n">
-        <v>7.803272832156786</v>
+        <v>6.994750044386919</v>
       </c>
       <c r="V9" s="4" t="n">
-        <v>4.15082981935182</v>
+        <v>3.442058755073774</v>
       </c>
       <c r="W9" s="4" t="n">
-        <v>1.688746861281963</v>
+        <v>6.646224798582978</v>
       </c>
       <c r="X9" s="4" t="n">
-        <v>-0.3084670873393875</v>
+        <v>4.687292441007223</v>
       </c>
       <c r="Y9" s="4" t="n">
-        <v>-0.03420123041784962</v>
+        <v>4.932178777210446</v>
       </c>
       <c r="Z9" s="4" t="n">
-        <v>-2.033159597411938</v>
+        <v>4.771413097589566</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>X ≈ -0.01578</t>
+          <t>X ≈ -0.01533</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>59</v>
+        <v>70</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>-7.820133880655717</v>
+        <v>-6.352579662359538</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>-8.157513805085252</v>
+        <v>-5.18192809846019</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>-7.903798172403889</v>
+        <v>-9.266229160511415</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>-5.246344875992911</v>
+        <v>-7.017867752412307</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>-5.581442482731127</v>
+        <v>-5.874304877218847</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>-8.768670748535087</v>
+        <v>-8.561558772590061</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>-4.481256130103468</v>
+        <v>-9.355182656618538</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>-14.87710732574375</v>
+        <v>-16.76787268214689</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>-13.15260638397154</v>
+        <v>-10.95721703413044</v>
       </c>
       <c r="L10" s="4" t="n">
-        <v>-7.1770715703516</v>
+        <v>-6.064485300571064</v>
       </c>
       <c r="M10" s="4" t="n">
-        <v>-5.21868108358634</v>
+        <v>-1.527244416186988</v>
       </c>
       <c r="N10" s="4" t="n">
-        <v>-2.121342401151537</v>
+        <v>-0.3805518959775895</v>
       </c>
       <c r="O10" s="4" t="n">
-        <v>-3.241675927052434</v>
+        <v>-1.492232345555863</v>
       </c>
       <c r="P10" s="4" t="n">
-        <v>4.984810208455499</v>
+        <v>6.804167659662234</v>
       </c>
       <c r="Q10" s="4" t="n">
-        <v>4.330168600410339</v>
+        <v>6.12619042113861</v>
       </c>
       <c r="R10" s="4" t="n">
-        <v>6.615210843760266</v>
+        <v>5.262956642353828</v>
       </c>
       <c r="S10" s="4" t="n">
-        <v>1.41061838058345</v>
+        <v>2.310270619130044</v>
       </c>
       <c r="T10" s="4" t="n">
-        <v>4.6896593365759</v>
+        <v>3.603757093211847</v>
       </c>
       <c r="U10" s="4" t="n">
-        <v>3.214296012333342</v>
+        <v>2.392479212882947</v>
       </c>
       <c r="V10" s="4" t="n">
-        <v>-3.369152725695187</v>
+        <v>-1.672903394298373</v>
       </c>
       <c r="W10" s="4" t="n">
-        <v>-3.912239855167286</v>
+        <v>-5.094869990366689</v>
       </c>
       <c r="X10" s="4" t="n">
-        <v>-7.376991747418543</v>
+        <v>-8.027134603001265</v>
       </c>
       <c r="Y10" s="4" t="n">
-        <v>-5.41059297409452</v>
+        <v>-6.358102343071394</v>
       </c>
       <c r="Z10" s="4" t="n">
-        <v>-5.488179154126406</v>
+        <v>-5.093816012923</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>X ≈ -0.01418</t>
+          <t>X ≈ -0.01375</t>
         </is>
       </c>
       <c r="B11" t="n">
         <v>87</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>1.522333989012111</v>
+        <v>-6.366485008684172</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>-3.377135235959976</v>
+        <v>-10.03862881636176</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>-1.380574866615071</v>
+        <v>-1.010738020778717</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>-6.657760648706557</v>
+        <v>-3.883192605967722</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>-1.281505745389879</v>
+        <v>-5.301250994610889</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>-3.381981680350194</v>
+        <v>1.709233865440858</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>-1.864575930498944</v>
+        <v>4.348312713744484</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>4.720434771279855</v>
+        <v>12.05200326404335</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>9.339396854752536</v>
+        <v>13.32770069469166</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>7.427655504960271</v>
+        <v>12.53863165970559</v>
       </c>
       <c r="M11" s="4" t="n">
-        <v>8.847092117233693</v>
+        <v>11.66860358349804</v>
       </c>
       <c r="N11" s="4" t="n">
-        <v>5.136861955390771</v>
+        <v>9.106380839573475</v>
       </c>
       <c r="O11" s="4" t="n">
-        <v>5.16433979058052</v>
+        <v>7.997940067230594</v>
       </c>
       <c r="P11" s="4" t="n">
-        <v>7.236600109106845</v>
+        <v>8.898124484776737</v>
       </c>
       <c r="Q11" s="4" t="n">
-        <v>5.436790395957537</v>
+        <v>8.221039448826524</v>
       </c>
       <c r="R11" s="4" t="n">
-        <v>4.885042258836862</v>
+        <v>8.783553196523911</v>
       </c>
       <c r="S11" s="4" t="n">
-        <v>4.753733385739636</v>
+        <v>7.53627160059677</v>
       </c>
       <c r="T11" s="4" t="n">
-        <v>1.208810760954115</v>
+        <v>5.111184723443174</v>
       </c>
       <c r="U11" s="4" t="n">
-        <v>3.719761155887213</v>
+        <v>7.621908065054669</v>
       </c>
       <c r="V11" s="4" t="n">
-        <v>3.907760788596761</v>
+        <v>11.28245433491168</v>
       </c>
       <c r="W11" s="4" t="n">
-        <v>3.367015973844275</v>
+        <v>10.71918956505796</v>
       </c>
       <c r="X11" s="4" t="n">
-        <v>3.292301160100386</v>
+        <v>12.94470975761974</v>
       </c>
       <c r="Y11" s="4" t="n">
-        <v>3.567668591244647</v>
+        <v>12.04324418822436</v>
       </c>
       <c r="Z11" s="4" t="n">
-        <v>5.791774089590724</v>
+        <v>10.73541223009835</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>X ≈ -0.01259</t>
+          <t>X ≈ -0.01217</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>-2.107406661709021</v>
+        <v>0.3795841119712549</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>1.568573629114461</v>
+        <v>4.026758512683799</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>4.153907724451074</v>
+        <v>4.730220483607461</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>6.457651466434811</v>
+        <v>9.013534659290229</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>13.1512804159641</v>
+        <v>16.53564646216867</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>11.33331355226224</v>
+        <v>7.925304541974377</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>9.564927419426247</v>
+        <v>7.136913761489183</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>13.31084050940109</v>
+        <v>7.811435855334835</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>13.35681471902659</v>
+        <v>8.917424268249725</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>12.59111406428654</v>
+        <v>7.151525856553391</v>
       </c>
       <c r="M12" s="4" t="n">
-        <v>10.85621010712135</v>
+        <v>6.448442813870315</v>
       </c>
       <c r="N12" s="4" t="n">
-        <v>13.60021759077324</v>
+        <v>8.127806306015415</v>
       </c>
       <c r="O12" s="4" t="n">
-        <v>15.50454889620516</v>
+        <v>10.92654900847059</v>
       </c>
       <c r="P12" s="4" t="n">
-        <v>13.27537004431227</v>
+        <v>11.65918592231396</v>
       </c>
       <c r="Q12" s="4" t="n">
-        <v>12.624024911306</v>
+        <v>10.9833489292562</v>
       </c>
       <c r="R12" s="4" t="n">
-        <v>8.184291289345467</v>
+        <v>7.635829295309122</v>
       </c>
       <c r="S12" s="4" t="n">
-        <v>8.054253197346767</v>
+        <v>9.491443453717189</v>
       </c>
       <c r="T12" s="4" t="n">
-        <v>7.952277223238283</v>
+        <v>10.34006895885315</v>
       </c>
       <c r="U12" s="4" t="n">
-        <v>9.178672268612097</v>
+        <v>8.599906622608103</v>
       </c>
       <c r="V12" s="4" t="n">
-        <v>9.368578967586913</v>
+        <v>8.816994970215134</v>
       </c>
       <c r="W12" s="4" t="n">
-        <v>8.829782999464094</v>
+        <v>7.273763627346668</v>
       </c>
       <c r="X12" s="4" t="n">
-        <v>11.78524089460847</v>
+        <v>9.160402550851877</v>
       </c>
       <c r="Y12" s="4" t="n">
-        <v>15.09280525995</v>
+        <v>9.406977254169682</v>
       </c>
       <c r="Z12" s="4" t="n">
-        <v>10.98160341735109</v>
+        <v>6.306744211166638</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>X ≈ -0.01099</t>
+          <t>X ≈ -0.01059</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="C13" s="4" t="n">
-        <v>3.987427970357693</v>
+        <v>6.585115401949075</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>6.335872920808434</v>
+        <v>6.340705637718266</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>7.593668239783433</v>
+        <v>7.733795231486141</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>9.572288966875078</v>
+        <v>5.390684815584734</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>8.344988924563026</v>
+        <v>6.875022021045474</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>5.848234097116396</v>
+        <v>6.154414968708487</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>12.24769147136745</v>
+        <v>13.28341534775744</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>10.18364467231268</v>
+        <v>13.86509996383009</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>10.22885890975796</v>
+        <v>12.23707663975127</v>
       </c>
       <c r="L13" s="4" t="n">
-        <v>10.35910946421774</v>
+        <v>12.32937850771729</v>
       </c>
       <c r="M13" s="4" t="n">
-        <v>12.42895976904861</v>
+        <v>17.00917504270419</v>
       </c>
       <c r="N13" s="4" t="n">
-        <v>12.15532149814652</v>
+        <v>15.8580142377581</v>
       </c>
       <c r="O13" s="4" t="n">
-        <v>12.83514969045103</v>
+        <v>14.75232379349116</v>
       </c>
       <c r="P13" s="4" t="n">
-        <v>13.5168511119203</v>
+        <v>12.74561651513999</v>
       </c>
       <c r="Q13" s="4" t="n">
-        <v>10.17186337378924</v>
+        <v>11.18845448872583</v>
       </c>
       <c r="R13" s="4" t="n">
-        <v>13.46405540002367</v>
+        <v>14.40004128598579</v>
       </c>
       <c r="S13" s="4" t="n">
-        <v>16.93094813113717</v>
+        <v>17.83310029876854</v>
       </c>
       <c r="T13" s="4" t="n">
-        <v>15.0342495942304</v>
+        <v>15.94018042868611</v>
       </c>
       <c r="U13" s="4" t="n">
-        <v>13.45615056900728</v>
+        <v>14.39297615977405</v>
       </c>
       <c r="V13" s="4" t="n">
-        <v>11.8484899187647</v>
+        <v>11.0774009222278</v>
       </c>
       <c r="W13" s="4" t="n">
-        <v>10.41087832938575</v>
+        <v>12.28272547335368</v>
       </c>
       <c r="X13" s="4" t="n">
-        <v>7.637962664937028</v>
+        <v>8.674431500792146</v>
       </c>
       <c r="Y13" s="4" t="n">
-        <v>7.915038126342495</v>
+        <v>10.69034977020747</v>
       </c>
       <c r="Z13" s="4" t="n">
-        <v>5.139397575145033</v>
+        <v>7.87710686950431</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>X ≈ -0.009389</t>
+          <t>X ≈ -0.009012</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>150</v>
+        <v>169</v>
       </c>
       <c r="C14" s="4" t="n">
-        <v>6.968308161588872</v>
+        <v>8.516616106222919</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>8.618939066249176</v>
+        <v>5.925417936768319</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>7.856532097830645</v>
+        <v>5.857584141501782</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>9.798413194754687</v>
+        <v>9.384056956985319</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>10.79077311449065</v>
+        <v>10.28646111246569</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>10.31933267953607</v>
+        <v>10.44695805468483</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>6.242171841029744</v>
+        <v>7.894760775919565</v>
       </c>
       <c r="J14" s="4" t="n">
-        <v>5.968676988435398</v>
+        <v>5.830255983975029</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>4.68670754165165</v>
+        <v>4.783943157320728</v>
       </c>
       <c r="L14" s="4" t="n">
-        <v>6.571831196287789</v>
+        <v>8.114028524213353</v>
       </c>
       <c r="M14" s="4" t="n">
-        <v>7.509998650660684</v>
+        <v>7.209239855254538</v>
       </c>
       <c r="N14" s="4" t="n">
-        <v>7.235043349809047</v>
+        <v>6.936558268672812</v>
       </c>
       <c r="O14" s="4" t="n">
-        <v>4.126744760172251</v>
+        <v>6.4178299267112</v>
       </c>
       <c r="P14" s="4" t="n">
-        <v>4.572051822419375</v>
+        <v>7.35163085855519</v>
       </c>
       <c r="Q14" s="4" t="n">
-        <v>6.576893138398084</v>
+        <v>9.034481597089247</v>
       </c>
       <c r="R14" s="4" t="n">
-        <v>6.507840045275202</v>
+        <v>9.007837356457102</v>
       </c>
       <c r="S14" s="4" t="n">
-        <v>10.36727928132449</v>
+        <v>11.85886070761662</v>
       </c>
       <c r="T14" s="4" t="n">
-        <v>8.271359312116047</v>
+        <v>9.959532664355336</v>
       </c>
       <c r="U14" s="4" t="n">
-        <v>8.490003847433677</v>
+        <v>11.35883359243701</v>
       </c>
       <c r="V14" s="4" t="n">
-        <v>9.346045292615329</v>
+        <v>12.759382730287</v>
       </c>
       <c r="W14" s="4" t="n">
-        <v>12.13762477964405</v>
+        <v>12.78874889928925</v>
       </c>
       <c r="X14" s="4" t="n">
-        <v>10.73424744497159</v>
+        <v>11.5359839467712</v>
       </c>
       <c r="Y14" s="4" t="n">
-        <v>12.34555692097858</v>
+        <v>14.14994516836079</v>
       </c>
       <c r="Z14" s="4" t="n">
-        <v>10.27453271028038</v>
+        <v>11.03467088479467</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>X ≈ -0.00779</t>
+          <t>X ≈ -0.007432</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="C15" s="4" t="n">
-        <v>4.38206874871814</v>
+        <v>1.467586840884373</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>-3.414801805210971</v>
+        <v>-1.399552208460896</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>-1.642733042619518</v>
+        <v>-0.5446062377924221</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>-2.885258620231966</v>
+        <v>-1.133099596018639</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>-5.35641244905576</v>
+        <v>-6.136140887226546</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>-3.569685064040208</v>
+        <v>-5.456341166961344</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>-4.337560962900739</v>
+        <v>-9.402295187913467</v>
       </c>
       <c r="J15" s="4" t="n">
-        <v>0.1936324789802129</v>
+        <v>-2.873035383636747</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>0.236151752787741</v>
+        <v>-1.167292283457321</v>
       </c>
       <c r="L15" s="4" t="n">
-        <v>0.5357602329850764</v>
+        <v>0.6699898027935802</v>
       </c>
       <c r="M15" s="4" t="n">
-        <v>-1.33155891176493</v>
+        <v>-1.691355416297938</v>
       </c>
       <c r="N15" s="4" t="n">
-        <v>-3.214769134156796</v>
+        <v>-1.967024368949431</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>-1.122089499046474</v>
+        <v>-0.9706574979926756</v>
       </c>
       <c r="P15" s="4" t="n">
-        <v>1.334636825644822</v>
+        <v>0.889253716904804</v>
       </c>
       <c r="Q15" s="4" t="n">
-        <v>3.35914059130814</v>
+        <v>2.319700193005026</v>
       </c>
       <c r="R15" s="4" t="n">
-        <v>4.489740861680382</v>
+        <v>5.51780898898491</v>
       </c>
       <c r="S15" s="4" t="n">
-        <v>4.358563599173301</v>
+        <v>4.888973103694333</v>
       </c>
       <c r="T15" s="4" t="n">
-        <v>3.720350904208239</v>
+        <v>4.759004982069328</v>
       </c>
       <c r="U15" s="4" t="n">
-        <v>3.40099022171465</v>
+        <v>3.919272201983951</v>
       </c>
       <c r="V15" s="4" t="n">
-        <v>2.516175479600925</v>
+        <v>2.550904644012732</v>
       </c>
       <c r="W15" s="4" t="n">
-        <v>2.512777627588854</v>
+        <v>4.099779711361464</v>
       </c>
       <c r="X15" s="4" t="n">
-        <v>3.513056840576226</v>
+        <v>5.612894794668698</v>
       </c>
       <c r="Y15" s="4" t="n">
-        <v>4.864010059644372</v>
+        <v>5.859065868728003</v>
       </c>
       <c r="Z15" s="4" t="n">
-        <v>4.253027333936409</v>
+        <v>7.287136368029373</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>X ≈ -0.006191</t>
+          <t>X ≈ -0.005852</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>171</v>
+        <v>152</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>-0.7331267348505506</v>
+        <v>-4.16395747848108</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>0.671775548818303</v>
+        <v>-1.801884606726482</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>-0.7622603155831129</v>
+        <v>-1.089534597368889</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>3.747099895347262</v>
+        <v>2.888672163077196</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>1.672401811192223</v>
+        <v>2.615969664431063</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>2.440901099572713</v>
+        <v>0.8148258540321081</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>1.090292433503194</v>
+        <v>3.292557228041204</v>
       </c>
       <c r="J16" s="4" t="n">
-        <v>-0.9303241146533026</v>
+        <v>0.3753008532519644</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>1.436592956500597</v>
+        <v>2.464979430899518</v>
       </c>
       <c r="L16" s="4" t="n">
-        <v>4.73562008618778</v>
+        <v>3.634206028392818</v>
       </c>
       <c r="M16" s="4" t="n">
-        <v>4.430671982080149</v>
+        <v>3.252502117301034</v>
       </c>
       <c r="N16" s="4" t="n">
-        <v>4.154031348701892</v>
+        <v>2.32451043119579</v>
       </c>
       <c r="O16" s="4" t="n">
-        <v>5.361004731001891</v>
+        <v>3.834727631640511</v>
       </c>
       <c r="P16" s="4" t="n">
-        <v>5.143204320503472</v>
+        <v>2.277846628192833</v>
       </c>
       <c r="Q16" s="4" t="n">
-        <v>5.652095406086922</v>
+        <v>3.566159341371936</v>
       </c>
       <c r="R16" s="4" t="n">
-        <v>2.170023107712076</v>
+        <v>-1.773928511435521</v>
       </c>
       <c r="S16" s="4" t="n">
-        <v>3.787318269342862</v>
+        <v>0.09008498547353128</v>
       </c>
       <c r="T16" s="4" t="n">
-        <v>6.601431364710848</v>
+        <v>4.552025681607695</v>
       </c>
       <c r="U16" s="4" t="n">
-        <v>2.735613609767562</v>
+        <v>1.486254209728479</v>
       </c>
       <c r="V16" s="4" t="n">
-        <v>6.428421326437913</v>
+        <v>6.299515703613451</v>
       </c>
       <c r="W16" s="4" t="n">
-        <v>7.975788046659723</v>
+        <v>7.050382254246685</v>
       </c>
       <c r="X16" s="4" t="n">
-        <v>6.735563828407017</v>
+        <v>4.349604541495346</v>
       </c>
       <c r="Y16" s="4" t="n">
-        <v>5.844163630138567</v>
+        <v>2.622762060937703</v>
       </c>
       <c r="Z16" s="4" t="n">
-        <v>4.017222768759908</v>
+        <v>-0.1690039828478191</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>X ≈ -0.004593</t>
+          <t>X ≈ -0.004272</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>172</v>
+        <v>197</v>
       </c>
       <c r="C17" s="4" t="n">
-        <v>-6.487467972602943</v>
+        <v>-3.256031307128836</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>1.238768167204505</v>
+        <v>3.532382978292233</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>2.695008683500099</v>
+        <v>3.799639366039564</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>0.2568467555059044</v>
+        <v>3.211689427271367</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>-5.84242405554982</v>
+        <v>-2.595271256787754</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>-7.966629873846919</v>
+        <v>-1.935599742308248</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>-5.272079596473183</v>
+        <v>-2.725498794648416</v>
       </c>
       <c r="J17" s="4" t="n">
-        <v>-2.086361970767868</v>
+        <v>-0.00708691476305745</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>-1.468016372984358</v>
+        <v>2.640970510059084</v>
       </c>
       <c r="L17" s="4" t="n">
-        <v>-0.5060892386049787</v>
+        <v>2.856665405149734</v>
       </c>
       <c r="M17" s="4" t="n">
-        <v>-1.389857290572365</v>
+        <v>3.633747440916792</v>
       </c>
       <c r="N17" s="4" t="n">
-        <v>0.06861842528399364</v>
+        <v>3.866021248883044</v>
       </c>
       <c r="O17" s="4" t="n">
-        <v>1.84377795387045</v>
+        <v>7.303001098560948</v>
       </c>
       <c r="P17" s="4" t="n">
-        <v>-4.166352138317365</v>
+        <v>3.521722578589987</v>
       </c>
       <c r="Q17" s="4" t="n">
-        <v>-3.664477377156281</v>
+        <v>2.844630831496779</v>
       </c>
       <c r="R17" s="4" t="n">
-        <v>-1.33315706557952</v>
+        <v>4.417966152573747</v>
       </c>
       <c r="S17" s="4" t="n">
-        <v>-2.626181595130006</v>
+        <v>4.316630410586463</v>
       </c>
       <c r="T17" s="4" t="n">
-        <v>0.1695374233275615</v>
+        <v>4.18638868036011</v>
       </c>
       <c r="U17" s="4" t="n">
-        <v>2.127454702128432</v>
+        <v>6.429536365680036</v>
       </c>
       <c r="V17" s="4" t="n">
-        <v>1.735415187456198</v>
+        <v>4.620621659613192</v>
       </c>
       <c r="W17" s="4" t="n">
-        <v>2.354645510460919</v>
+        <v>5.577882126989792</v>
       </c>
       <c r="X17" s="4" t="n">
-        <v>1.119459032640357</v>
+        <v>4.999378912202467</v>
       </c>
       <c r="Y17" s="4" t="n">
-        <v>2.557381518180804</v>
+        <v>5.753503909432489</v>
       </c>
       <c r="Z17" s="4" t="n">
-        <v>1.321044338187349</v>
+        <v>6.102703203900667</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>X ≈ -0.002994</t>
+          <t>X ≈ -0.002693</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>221</v>
+        <v>217</v>
       </c>
       <c r="C18" s="4" t="n">
-        <v>1.09760340781343</v>
+        <v>0.8265091601630701</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>3.444992774782506</v>
+        <v>2.853276342580919</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>4.261800510766122</v>
+        <v>0.7017528832924995</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>4.451928379294081</v>
+        <v>2.849837124136563</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>2.780739662558794</v>
+        <v>1.670530773775184</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>3.417941743757147</v>
+        <v>3.198160199344322</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>2.653777005194868</v>
+        <v>3.782434506425901</v>
       </c>
       <c r="J18" s="4" t="n">
-        <v>0.5805574836546512</v>
+        <v>2.107598058473997</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>1.071358425476511</v>
+        <v>0.4052604441843073</v>
       </c>
       <c r="L18" s="4" t="n">
-        <v>-0.5989966622721994</v>
+        <v>-2.218934808661849</v>
       </c>
       <c r="M18" s="4" t="n">
-        <v>1.472832969649161</v>
+        <v>-1.033767835441751</v>
       </c>
       <c r="N18" s="4" t="n">
-        <v>-0.6029322670626627</v>
+        <v>-2.224088005624331</v>
       </c>
       <c r="O18" s="4" t="n">
-        <v>-1.722060780483048</v>
+        <v>-4.252921599353108</v>
       </c>
       <c r="P18" s="4" t="n">
-        <v>-1.04081187433281</v>
+        <v>-4.50080974916505</v>
       </c>
       <c r="Q18" s="4" t="n">
-        <v>-1.245317217960171</v>
+        <v>-4.722256803459942</v>
       </c>
       <c r="R18" s="4" t="n">
-        <v>-1.103073476394364</v>
+        <v>-4.623476844539944</v>
       </c>
       <c r="S18" s="4" t="n">
-        <v>-2.138218182024801</v>
+        <v>-6.106430653822393</v>
       </c>
       <c r="T18" s="4" t="n">
-        <v>-3.597126048535877</v>
+        <v>-7.619693949376213</v>
       </c>
       <c r="U18" s="4" t="n">
-        <v>-2.479058360844633</v>
+        <v>-6.948593068424188</v>
       </c>
       <c r="V18" s="4" t="n">
-        <v>-4.09962385720317</v>
+        <v>-7.196537266377675</v>
       </c>
       <c r="W18" s="4" t="n">
-        <v>-3.738015895160288</v>
+        <v>-6.84523205990191</v>
       </c>
       <c r="X18" s="4" t="n">
-        <v>-2.909956356986008</v>
+        <v>-6.001441632730241</v>
       </c>
       <c r="Y18" s="4" t="n">
-        <v>-3.992928535580695</v>
+        <v>-5.299146961884979</v>
       </c>
       <c r="Z18" s="4" t="n">
-        <v>0.9080168731762015</v>
+        <v>-1.775843662692381</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>X ≈ -0.001395</t>
+          <t>X ≈ -0.001113</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>213</v>
+        <v>201</v>
       </c>
       <c r="C19" s="4" t="n">
-        <v>-2.473337660517785</v>
+        <v>-0.1116556465523999</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>-0.9528423601530207</v>
+        <v>0.6299014761577695</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>-4.713082447380756</v>
+        <v>0.8468227402731614</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>-0.7781244817122825</v>
+        <v>2.225981511272401</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>-2.043974999406352</v>
+        <v>1.454491198621625</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>-0.9264532308274198</v>
+        <v>0.1340928138161885</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>-1.699382891062605</v>
+        <v>-0.6654987952148161</v>
       </c>
       <c r="J19" s="4" t="n">
-        <v>0.8178954033028063</v>
+        <v>0.510920957451205</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>0.8609797469944951</v>
+        <v>0.641212251568092</v>
       </c>
       <c r="L19" s="4" t="n">
-        <v>-0.3777747247265069</v>
+        <v>1.820414530750419</v>
       </c>
       <c r="M19" s="4" t="n">
-        <v>-1.501325623790088</v>
+        <v>0.1204041739228359</v>
       </c>
       <c r="N19" s="4" t="n">
-        <v>-2.71565925387555</v>
+        <v>-1.644139310286008</v>
       </c>
       <c r="O19" s="4" t="n">
-        <v>-2.440709587745381</v>
+        <v>-2.765643252836291</v>
       </c>
       <c r="P19" s="4" t="n">
-        <v>-2.662763907111255</v>
+        <v>-2.026320071976144</v>
       </c>
       <c r="Q19" s="4" t="n">
-        <v>-6.131764087495824</v>
+        <v>-5.195388768884087</v>
       </c>
       <c r="R19" s="4" t="n">
-        <v>-6.472262883277985</v>
+        <v>-5.620974440669677</v>
       </c>
       <c r="S19" s="4" t="n">
-        <v>-5.673284836137142</v>
+        <v>-5.727244813911611</v>
       </c>
       <c r="T19" s="4" t="n">
-        <v>-7.383923972554726</v>
+        <v>-7.849166530095673</v>
       </c>
       <c r="U19" s="4" t="n">
-        <v>-5.495134255124036</v>
+        <v>-6.640178926725589</v>
       </c>
       <c r="V19" s="4" t="n">
-        <v>-3.903904260248595</v>
+        <v>-6.424783832841136</v>
       </c>
       <c r="W19" s="4" t="n">
-        <v>-5.383283927085323</v>
+        <v>-6.006143384895836</v>
       </c>
       <c r="X19" s="4" t="n">
-        <v>-3.115640037959217</v>
+        <v>-3.312532717795314</v>
       </c>
       <c r="Y19" s="4" t="n">
-        <v>-2.372820658669546</v>
+        <v>-2.78199721536123</v>
       </c>
       <c r="Z19" s="4" t="n">
-        <v>-0.5705377122546693</v>
+        <v>-0.6730626369458506</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>X ≈ 0.0002037</t>
+          <t>X ≈ 0.0004671</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>186</v>
+        <v>198</v>
       </c>
       <c r="C20" s="4" t="n">
-        <v>3.024034024505994</v>
+        <v>2.984440255995494</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>-2.099161031999841</v>
+        <v>-1.263450216813254</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>-1.933334177900626</v>
+        <v>-0.005255907070953469</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>0.01343249460005325</v>
+        <v>1.898456581685622</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>3.944173539618134</v>
+        <v>5.135141376813117</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>2.002225645337973</v>
+        <v>6.796323350530109</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>1.234839880688078</v>
+        <v>5.513282003450023</v>
       </c>
       <c r="J20" s="4" t="n">
-        <v>-3.310662724088651</v>
+        <v>2.20648159391866</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>-3.270668872814653</v>
+        <v>1.83404907189729</v>
       </c>
       <c r="L20" s="4" t="n">
-        <v>-5.112789619476494</v>
+        <v>-2.468643533426757</v>
       </c>
       <c r="M20" s="4" t="n">
-        <v>-3.77168173227998</v>
+        <v>-1.195159132864653</v>
       </c>
       <c r="N20" s="4" t="n">
-        <v>-6.191097931175165</v>
+        <v>-3.475743056964404</v>
       </c>
       <c r="O20" s="4" t="n">
-        <v>-9.993709381299212</v>
+        <v>-6.095360514728739</v>
       </c>
       <c r="P20" s="4" t="n">
-        <v>-9.148772287200813</v>
+        <v>-6.345278051000506</v>
       </c>
       <c r="Q20" s="4" t="n">
-        <v>-8.205610702558353</v>
+        <v>-3.504436314060143</v>
       </c>
       <c r="R20" s="4" t="n">
-        <v>-7.077511896461736</v>
+        <v>-2.44263858599507</v>
       </c>
       <c r="S20" s="4" t="n">
-        <v>-8.288393578179246</v>
+        <v>-5.065602716566005</v>
       </c>
       <c r="T20" s="4" t="n">
-        <v>-8.394218825929052</v>
+        <v>-5.200112911883735</v>
       </c>
       <c r="U20" s="4" t="n">
-        <v>-9.249564638257453</v>
+        <v>-4.988521290051295</v>
       </c>
       <c r="V20" s="4" t="n">
-        <v>-7.145494315695466</v>
+        <v>-4.271418022476645</v>
       </c>
       <c r="W20" s="4" t="n">
-        <v>-7.15056047061826</v>
+        <v>-4.840408722216431</v>
       </c>
       <c r="X20" s="4" t="n">
-        <v>-5.081678287189384</v>
+        <v>-3.400419729020143</v>
       </c>
       <c r="Y20" s="4" t="n">
-        <v>-3.73501107561038</v>
+        <v>-2.65173473869126</v>
       </c>
       <c r="Z20" s="4" t="n">
-        <v>-3.27385438649388</v>
+        <v>-0.2886212077281911</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>X ≈ 0.001803</t>
+          <t>X ≈ 0.002047</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>196</v>
+        <v>190</v>
       </c>
       <c r="C21" s="4" t="n">
-        <v>2.115328903206148</v>
+        <v>1.690056761469194</v>
       </c>
       <c r="D21" s="4" t="n">
-        <v>1.287354294425434</v>
+        <v>0.9172846394570797</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>0.3301036295005773</v>
+        <v>-2.915170259826965</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>-1.385919372113541</v>
+        <v>-5.074867647991638</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>-5.508436894595846</v>
+        <v>-8.98458542452034</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>-0.995568724913511</v>
+        <v>-5.191760640500988</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>2.783452340201137</v>
+        <v>-1.290851398236313</v>
       </c>
       <c r="J21" s="4" t="n">
-        <v>-0.0286306287671465</v>
+        <v>-5.24218904387736</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>-0.4914275462380076</v>
+        <v>-6.161508710018971</v>
       </c>
       <c r="L21" s="4" t="n">
-        <v>-4.313491248950896</v>
+        <v>-8.521346479252458</v>
       </c>
       <c r="M21" s="4" t="n">
-        <v>-5.050687179431314</v>
+        <v>-8.257510043044277</v>
       </c>
       <c r="N21" s="4" t="n">
-        <v>-5.850684751154034</v>
+        <v>-8.009076446666562</v>
       </c>
       <c r="O21" s="4" t="n">
-        <v>-9.533653796272567</v>
+        <v>-10.16926941319522</v>
       </c>
       <c r="P21" s="4" t="n">
-        <v>-10.27098310621095</v>
+        <v>-10.94627410477613</v>
       </c>
       <c r="Q21" s="4" t="n">
-        <v>-5.551695401256914</v>
+        <v>-9.012147759772645</v>
       </c>
       <c r="R21" s="4" t="n">
-        <v>-4.147725907857186</v>
+        <v>-8.458919422456383</v>
       </c>
       <c r="S21" s="4" t="n">
-        <v>-4.494393645034421</v>
+        <v>-8.042049157655796</v>
       </c>
       <c r="T21" s="4" t="n">
-        <v>-3.071277628409938</v>
+        <v>-5.553513125385464</v>
       </c>
       <c r="U21" s="4" t="n">
-        <v>-1.838337551577105</v>
+        <v>-5.868545061027106</v>
       </c>
       <c r="V21" s="4" t="n">
-        <v>-3.179588678324166</v>
+        <v>-6.709350779760946</v>
       </c>
       <c r="W21" s="4" t="n">
-        <v>-4.230238545435917</v>
+        <v>-8.333231688723487</v>
       </c>
       <c r="X21" s="4" t="n">
-        <v>-4.308234762927377</v>
+        <v>-7.882078421205144</v>
       </c>
       <c r="Y21" s="4" t="n">
-        <v>-4.036343280101448</v>
+        <v>-7.638443935926766</v>
       </c>
       <c r="Z21" s="4" t="n">
-        <v>-0.03158973869921056</v>
+        <v>-4.116372403900435</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>X ≈ 0.003402</t>
+          <t>X ≈ 0.003626</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>203</v>
+        <v>208</v>
       </c>
       <c r="C22" s="4" t="n">
-        <v>0.6789197442905959</v>
+        <v>0.2870641802320364</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>-2.317827876377969</v>
+        <v>-2.333782091099259</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>-5.001212404815362</v>
+        <v>-4.033216033904182</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>-10.34010546563325</v>
+        <v>-8.897357840676435</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>-8.248343979433365</v>
+        <v>-6.789540309897134</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>-9.522454951655355</v>
+        <v>-9.494798092054488</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>-9.540924712992201</v>
+        <v>-9.816057863131007</v>
       </c>
       <c r="J22" s="4" t="n">
-        <v>-9.342292651493253</v>
+        <v>-8.217828233572334</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>-9.796230983802957</v>
+        <v>-5.717494306816661</v>
       </c>
       <c r="L22" s="4" t="n">
-        <v>-8.131939607025153</v>
+        <v>-5.079383353031197</v>
       </c>
       <c r="M22" s="4" t="n">
-        <v>-10.80509536693331</v>
+        <v>-7.198348789533071</v>
       </c>
       <c r="N22" s="4" t="n">
-        <v>-12.58177199474877</v>
+        <v>-8.902605622914933</v>
       </c>
       <c r="O22" s="4" t="n">
-        <v>-11.27601003321506</v>
+        <v>-9.060933578662649</v>
       </c>
       <c r="P22" s="4" t="n">
-        <v>-14.9575350975595</v>
+        <v>-11.22603800770914</v>
       </c>
       <c r="Q22" s="4" t="n">
-        <v>-14.63477786796009</v>
+        <v>-10.95875723404668</v>
       </c>
       <c r="R22" s="4" t="n">
-        <v>-14.02850778985077</v>
+        <v>-10.41004792537539</v>
       </c>
       <c r="S22" s="4" t="n">
-        <v>-15.64565887376459</v>
+        <v>-11.95855096665867</v>
       </c>
       <c r="T22" s="4" t="n">
-        <v>-13.78221680168045</v>
+        <v>-12.10165087414411</v>
       </c>
       <c r="U22" s="4" t="n">
-        <v>-17.98902008845986</v>
+        <v>-15.25762608053913</v>
       </c>
       <c r="V22" s="4" t="n">
-        <v>-15.82849006796562</v>
+        <v>-13.13455414284634</v>
       </c>
       <c r="W22" s="4" t="n">
-        <v>-16.37967853132524</v>
+        <v>-14.19355557536322</v>
       </c>
       <c r="X22" s="4" t="n">
-        <v>-15.17976648535045</v>
+        <v>-14.26871809731851</v>
       </c>
       <c r="Y22" s="4" t="n">
-        <v>-14.61144507479451</v>
+        <v>-12.10200668896321</v>
       </c>
       <c r="Z22" s="4" t="n">
-        <v>-13.91265940794623</v>
+        <v>-13.22568414479113</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>X ≈ 0.005</t>
+          <t>X ≈ 0.005206</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>184</v>
+        <v>167</v>
       </c>
       <c r="C23" s="4" t="n">
-        <v>2.315294014156144</v>
+        <v>1.1920765409278</v>
       </c>
       <c r="D23" s="4" t="n">
-        <v>3.057317488577937</v>
+        <v>4.470790076284658</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>2.17532829112168</v>
+        <v>5.013602580957311</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>-2.852121873968443</v>
+        <v>0.895365502351126</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>-2.098953649475824</v>
+        <v>0.6323892036345455</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>-2.45464304825817</v>
+        <v>0.1962683364022269</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>-4.302784083706591</v>
+        <v>-2.958589525298684</v>
       </c>
       <c r="J23" s="4" t="n">
-        <v>-2.959892069530611</v>
+        <v>-1.488126280020488</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>-4.003416769386291</v>
+        <v>-4.324583258825868</v>
       </c>
       <c r="L23" s="4" t="n">
-        <v>-3.695103828565799</v>
+        <v>-1.564534055399037</v>
       </c>
       <c r="M23" s="4" t="n">
-        <v>0.3677870587636036</v>
+        <v>1.672199396874582</v>
       </c>
       <c r="N23" s="4" t="n">
-        <v>1.719879946568511</v>
+        <v>1.994904242115403</v>
       </c>
       <c r="O23" s="4" t="n">
-        <v>-0.487157019784668</v>
+        <v>-0.3063589031717342</v>
       </c>
       <c r="P23" s="4" t="n">
-        <v>0.3766681015927134</v>
+        <v>-0.5560615826590052</v>
       </c>
       <c r="Q23" s="4" t="n">
-        <v>-0.2814751959877881</v>
+        <v>-0.04947719676565754</v>
       </c>
       <c r="R23" s="4" t="n">
-        <v>0.3129117259552032</v>
+        <v>1.108273085101871</v>
       </c>
       <c r="S23" s="4" t="n">
-        <v>1.809429371586369</v>
+        <v>2.19634231566819</v>
       </c>
       <c r="T23" s="4" t="n">
-        <v>0.6176321460260468</v>
+        <v>2.064093974092572</v>
       </c>
       <c r="U23" s="4" t="n">
-        <v>0.8335235269504437</v>
+        <v>2.278829589404246</v>
       </c>
       <c r="V23" s="4" t="n">
-        <v>-0.6100654456902248</v>
+        <v>0.4639574783987257</v>
       </c>
       <c r="W23" s="4" t="n">
-        <v>-1.152611613656319</v>
+        <v>0.4943762532871645</v>
       </c>
       <c r="X23" s="4" t="n">
-        <v>-1.228457575065299</v>
+        <v>-0.1795886638776949</v>
       </c>
       <c r="Y23" s="4" t="n">
-        <v>-3.127895906061568</v>
+        <v>-2.929966154647225</v>
       </c>
       <c r="Z23" s="4" t="n">
-        <v>-2.660249898415209</v>
+        <v>-3.092105148936753</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>X ≈ 0.006599</t>
+          <t>X ≈ 0.006786</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="C24" s="4" t="n">
-        <v>4.947052886042648</v>
+        <v>7.811008908491381</v>
       </c>
       <c r="D24" s="4" t="n">
-        <v>-1.513241526435799</v>
+        <v>-0.506700933458049</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>-0.4806749470644576</v>
+        <v>0.6076353061633597</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>3.100968657681996</v>
+        <v>1.806193359520655</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>-1.506968458057564</v>
+        <v>-3.308792737976525</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>-0.09938894533383547</v>
+        <v>-1.943353301425567</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>2.806908836767988</v>
+        <v>3.277094468606052</v>
       </c>
       <c r="J24" s="4" t="n">
-        <v>0.08487561676384558</v>
+        <v>-0.6588221911526873</v>
       </c>
       <c r="K24" s="4" t="n">
-        <v>-0.4873087284622386</v>
+        <v>-0.5309147453556022</v>
       </c>
       <c r="L24" s="4" t="n">
-        <v>-4.33014308923444</v>
+        <v>-5.58116883326749</v>
       </c>
       <c r="M24" s="4" t="n">
-        <v>-7.755132329582537</v>
+        <v>-8.330193723013572</v>
       </c>
       <c r="N24" s="4" t="n">
-        <v>-1.881498692351059</v>
+        <v>-1.979108217210189</v>
       </c>
       <c r="O24" s="4" t="n">
-        <v>0.6931578622482277</v>
+        <v>-0.1065578768105979</v>
       </c>
       <c r="P24" s="4" t="n">
-        <v>-1.998533186651926</v>
+        <v>-2.209581668138284</v>
       </c>
       <c r="Q24" s="4" t="n">
-        <v>-3.27396043484984</v>
+        <v>-3.135037738022227</v>
       </c>
       <c r="R24" s="4" t="n">
-        <v>-2.679573512906849</v>
+        <v>-2.789303784035035</v>
       </c>
       <c r="S24" s="4" t="n">
-        <v>-1.578922748649681</v>
+        <v>-1.689095152449489</v>
       </c>
       <c r="T24" s="4" t="n">
-        <v>-0.4491955512362935</v>
+        <v>-0.841364858950719</v>
       </c>
       <c r="U24" s="4" t="n">
-        <v>-1.467872071546637</v>
+        <v>-1.47667655846427</v>
       </c>
       <c r="V24" s="4" t="n">
-        <v>-1.281026261578575</v>
+        <v>-1.869334342387248</v>
       </c>
       <c r="W24" s="4" t="n">
-        <v>-0.589004528309971</v>
+        <v>0.3702342933046907</v>
       </c>
       <c r="X24" s="4" t="n">
-        <v>-1.282134440336499</v>
+        <v>-1.53419652133352</v>
       </c>
       <c r="Y24" s="4" t="n">
-        <v>-1.007659727854367</v>
+        <v>-1.290562036055142</v>
       </c>
       <c r="Z24" s="4" t="n">
-        <v>-4.169911734164145</v>
+        <v>-4.50148151814944</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>X ≈ 0.008197</t>
+          <t>X ≈ 0.008366</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="C25" s="4" t="n">
-        <v>0.4022838343515573</v>
+        <v>-3.928610772190289</v>
       </c>
       <c r="D25" s="4" t="n">
-        <v>5.93808515035613</v>
+        <v>2.599095814975968</v>
       </c>
       <c r="E25" s="4" t="n">
-        <v>5.260467952496725</v>
+        <v>1.705439575288828</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>7.486511769795484</v>
+        <v>6.390276735783779</v>
       </c>
       <c r="G25" s="4" t="n">
-        <v>4.243866216730488</v>
+        <v>3.827029885573509</v>
       </c>
       <c r="H25" s="4" t="n">
-        <v>8.089435515533907</v>
+        <v>8.949022030156961</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>2.919498285296676</v>
+        <v>1.022206164387995</v>
       </c>
       <c r="J25" s="4" t="n">
-        <v>1.187601088764026</v>
+        <v>-0.7922386223450459</v>
       </c>
       <c r="K25" s="4" t="n">
-        <v>1.231372990789886</v>
+        <v>-2.939202407334975</v>
       </c>
       <c r="L25" s="4" t="n">
-        <v>2.675844738345717</v>
+        <v>-0.7071709464838918</v>
       </c>
       <c r="M25" s="4" t="n">
-        <v>1.47559497614882</v>
+        <v>-2.716520526795428</v>
       </c>
       <c r="N25" s="4" t="n">
-        <v>0.4605126674155144</v>
+        <v>-4.524044749761181</v>
       </c>
       <c r="O25" s="4" t="n">
-        <v>1.556731176623551</v>
+        <v>-1.84617575214876</v>
       </c>
       <c r="P25" s="4" t="n">
-        <v>4.297763109644308</v>
+        <v>0.1791713448973411</v>
       </c>
       <c r="Q25" s="4" t="n">
-        <v>-0.8048246323807078</v>
+        <v>-5.085973473719719</v>
       </c>
       <c r="R25" s="4" t="n">
-        <v>-1.691919191919197</v>
+        <v>-6.040981873905508</v>
       </c>
       <c r="S25" s="4" t="n">
-        <v>-1.08509558815593</v>
+        <v>-4.152751272264631</v>
       </c>
       <c r="T25" s="4" t="n">
-        <v>-1.189936291977112</v>
+        <v>-4.285635377426189</v>
       </c>
       <c r="U25" s="4" t="n">
-        <v>-0.9740449110527365</v>
+        <v>-2.544455593028545</v>
       </c>
       <c r="V25" s="4" t="n">
-        <v>-0.04645836034401896</v>
+        <v>-1.566510369343618</v>
       </c>
       <c r="W25" s="4" t="n">
-        <v>0.1517362124306985</v>
+        <v>-2.897313649350295</v>
       </c>
       <c r="X25" s="4" t="n">
-        <v>-7.331517156385765</v>
+        <v>-9.079346400313227</v>
       </c>
       <c r="Y25" s="4" t="n">
-        <v>-9.279264666125982</v>
+        <v>-10.36242947228676</v>
       </c>
       <c r="Z25" s="4" t="n">
-        <v>-8.614356178608517</v>
+        <v>-9.76120968795022</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>X ≈ 0.009798</t>
+          <t>X ≈ 0.009948</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="C26" s="4" t="n">
-        <v>3.951248312303115</v>
+        <v>4.865543300861887</v>
       </c>
       <c r="D26" s="4" t="n">
-        <v>-1.443367844594007</v>
+        <v>1.696194404796898</v>
       </c>
       <c r="E26" s="4" t="n">
-        <v>4.335050594451573</v>
+        <v>5.555252080276844</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>0.7282008976472625</v>
+        <v>0.9597753940369884</v>
       </c>
       <c r="G26" s="4" t="n">
-        <v>6.159174288595807</v>
+        <v>6.233434489716963</v>
       </c>
       <c r="H26" s="4" t="n">
-        <v>5.631428010030803</v>
+        <v>4.905328396368503</v>
       </c>
       <c r="I26" s="4" t="n">
-        <v>4.130748533993291</v>
+        <v>4.858395445665785</v>
       </c>
       <c r="J26" s="4" t="n">
-        <v>5.708043575527235</v>
+        <v>6.047745695322789</v>
       </c>
       <c r="K26" s="4" t="n">
-        <v>5.446311201950053</v>
+        <v>5.455269465033318</v>
       </c>
       <c r="L26" s="4" t="n">
-        <v>3.240874920588503</v>
+        <v>3.940195280817797</v>
       </c>
       <c r="M26" s="4" t="n">
-        <v>2.792657094615976</v>
+        <v>4.21761091632694</v>
       </c>
       <c r="N26" s="4" t="n">
-        <v>-0.3888028909633121</v>
+        <v>1.735702285986534</v>
       </c>
       <c r="O26" s="4" t="n">
-        <v>-2.24229341693529</v>
+        <v>-1.596807769660131</v>
       </c>
       <c r="P26" s="4" t="n">
-        <v>-0.2818530028185222</v>
+        <v>1.850888182197806</v>
       </c>
       <c r="Q26" s="4" t="n">
-        <v>-0.9399963003990806</v>
+        <v>1.168733800312793</v>
       </c>
       <c r="R26" s="4" t="n">
-        <v>-3.995244414952445</v>
+        <v>-2.71440662531203</v>
       </c>
       <c r="S26" s="4" t="n">
-        <v>-7.77879658842626</v>
+        <v>-7.262731481481488</v>
       </c>
       <c r="T26" s="4" t="n">
-        <v>-6.423783277648909</v>
+        <v>-5.173393364420861</v>
       </c>
       <c r="U26" s="4" t="n">
-        <v>-4.748037882126042</v>
+        <v>-4.218190396534389</v>
       </c>
       <c r="V26" s="4" t="n">
-        <v>-5.291119079457289</v>
+        <v>-4.003603951475363</v>
       </c>
       <c r="W26" s="4" t="n">
-        <v>-4.373811232824821</v>
+        <v>-3.830307712115399</v>
       </c>
       <c r="X26" s="4" t="n">
-        <v>-1.529949165036832</v>
+        <v>-0.9425072711076368</v>
       </c>
       <c r="Y26" s="4" t="n">
-        <v>-4.905109489051092</v>
+        <v>-4.402576489533004</v>
       </c>
       <c r="Z26" s="4" t="n">
-        <v>-8.630576778770717</v>
+        <v>-8.268419187526177</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>X ≈ 0.01139</t>
+          <t>X ≈ 0.01153</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="C27" s="4" t="n">
-        <v>-9.00450446739179</v>
+        <v>-6.755862505106421</v>
       </c>
       <c r="D27" s="4" t="n">
-        <v>-4.373787025253094</v>
+        <v>-7.805501249147291</v>
       </c>
       <c r="E27" s="4" t="n">
-        <v>-8.340518115810774</v>
+        <v>-9.848136600088509</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>-7.41301616323441</v>
+        <v>-8.831947077987884</v>
       </c>
       <c r="G27" s="4" t="n">
-        <v>-2.005372136863436</v>
+        <v>-1.875045947288861</v>
       </c>
       <c r="H27" s="4" t="n">
-        <v>-1.781634013740124</v>
+        <v>-2.53086748350632</v>
       </c>
       <c r="I27" s="4" t="n">
-        <v>-2.583000247251249</v>
+        <v>-3.316926261860502</v>
       </c>
       <c r="J27" s="4" t="n">
-        <v>-1.235464494795536</v>
+        <v>-3.161884531889747</v>
       </c>
       <c r="K27" s="4" t="n">
-        <v>-3.689594611084132</v>
+        <v>-5.441913669933015</v>
       </c>
       <c r="L27" s="4" t="n">
-        <v>-4.011912051836504</v>
+        <v>-5.430576088476478</v>
       </c>
       <c r="M27" s="4" t="n">
-        <v>-1.593548960448821</v>
+        <v>-4.365088502805371</v>
       </c>
       <c r="N27" s="4" t="n">
-        <v>-1.058352670939144</v>
+        <v>-2.218080214438444</v>
       </c>
       <c r="O27" s="4" t="n">
-        <v>-0.5396017787748875</v>
+        <v>-1.718175031011306</v>
       </c>
       <c r="P27" s="4" t="n">
-        <v>0.5940594059405981</v>
+        <v>-1.979283452851881</v>
       </c>
       <c r="Q27" s="4" t="n">
-        <v>2.43591610836004</v>
+        <v>-0.2224134444930712</v>
       </c>
       <c r="R27" s="4" t="n">
-        <v>0.5303030303029814</v>
+        <v>-1.28712568583601</v>
       </c>
       <c r="S27" s="4" t="n">
-        <v>0.396385893325558</v>
+        <v>-1.391006097560975</v>
       </c>
       <c r="T27" s="4" t="n">
-        <v>-0.5417881438289598</v>
+        <v>-3.149906462885177</v>
       </c>
       <c r="U27" s="4" t="n">
-        <v>-3.659230096237962</v>
+        <v>-6.187476756064569</v>
       </c>
       <c r="V27" s="4" t="n">
-        <v>-6.805717619603271</v>
+        <v>-9.224922831330829</v>
       </c>
       <c r="W27" s="4" t="n">
-        <v>-4.848263787569252</v>
+        <v>-6.54033481238632</v>
       </c>
       <c r="X27" s="4" t="n">
-        <v>-3.257443082311738</v>
+        <v>-5.80248920426034</v>
       </c>
       <c r="Y27" s="4" t="n">
-        <v>-4.649635036496342</v>
+        <v>-6.37186284906327</v>
       </c>
       <c r="Z27" s="4" t="n">
-        <v>-3.892133956386246</v>
+        <v>-5.720993713271383</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>X ≈ 0.01299</t>
+          <t>X ≈ 0.0131</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="C28" s="4" t="n">
-        <v>0.07308870520378008</v>
+        <v>-3.010011024357098</v>
       </c>
       <c r="D28" s="4" t="n">
-        <v>-11.92312033640957</v>
+        <v>-12.89135642704439</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>-10.20421924834666</v>
+        <v>-10.92092228068095</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>-7.740667424217314</v>
+        <v>-7.228220899751008</v>
       </c>
       <c r="G28" s="4" t="n">
-        <v>-9.154878884433451</v>
+        <v>-10.70683176880502</v>
       </c>
       <c r="H28" s="4" t="n">
-        <v>-8.950107510628612</v>
+        <v>-9.488871616118914</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>-8.675684544723467</v>
+        <v>-9.205056423182469</v>
       </c>
       <c r="J28" s="4" t="n">
-        <v>-10.02697542083316</v>
+        <v>-8.430028446217165</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>-8.933775032810786</v>
+        <v>-5.530176235851513</v>
       </c>
       <c r="L28" s="4" t="n">
-        <v>-4.419636377976751</v>
+        <v>-3.104678753570752</v>
       </c>
       <c r="M28" s="4" t="n">
-        <v>-3.081399898311915</v>
+        <v>-0.696591933141093</v>
       </c>
       <c r="N28" s="4" t="n">
-        <v>0.4584142378276113</v>
+        <v>0.1076888249914489</v>
       </c>
       <c r="O28" s="4" t="n">
-        <v>2.517265941961625</v>
+        <v>2.237167680001527</v>
       </c>
       <c r="P28" s="4" t="n">
-        <v>4.423846639983154</v>
+        <v>4.153625702326636</v>
       </c>
       <c r="Q28" s="4" t="n">
-        <v>4.829533129636637</v>
+        <v>5.645384363919838</v>
       </c>
       <c r="R28" s="4" t="n">
-        <v>6.487749838813727</v>
+        <v>7.293644904478725</v>
       </c>
       <c r="S28" s="4" t="n">
-        <v>8.48149227630428</v>
+        <v>9.363677536231883</v>
       </c>
       <c r="T28" s="4" t="n">
-        <v>7.312821785249028</v>
+        <v>8.143836909331156</v>
       </c>
       <c r="U28" s="4" t="n">
-        <v>2.209564230003203</v>
+        <v>2.923516527781267</v>
       </c>
       <c r="V28" s="4" t="n">
-        <v>0.2687504655031105</v>
+        <v>0.9641899293620284</v>
       </c>
       <c r="W28" s="4" t="n">
-        <v>1.853863872005199</v>
+        <v>2.570658471459517</v>
       </c>
       <c r="X28" s="4" t="n">
-        <v>2.841847697830104</v>
+        <v>4.669408992982433</v>
       </c>
       <c r="Y28" s="4" t="n">
-        <v>2.052492623078088</v>
+        <v>2.739130434782609</v>
       </c>
       <c r="Z28" s="4" t="n">
-        <v>-2.278658779081354</v>
+        <v>-1.770834646463435</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>X ≈ 0.01459</t>
+          <t>X ≈ 0.01468</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="C29" s="4" t="n">
-        <v>-11.08324238781535</v>
+        <v>-11.27217651992184</v>
       </c>
       <c r="D29" s="4" t="n">
-        <v>-12.94662990898612</v>
+        <v>-13.21630363089749</v>
       </c>
       <c r="E29" s="4" t="n">
-        <v>-18.91186183622425</v>
+        <v>-19.31771153107736</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>-22.60989048253263</v>
+        <v>-24.56201200654527</v>
       </c>
       <c r="G29" s="4" t="n">
-        <v>-15.53259532582437</v>
+        <v>-17.24970437056319</v>
       </c>
       <c r="H29" s="4" t="n">
-        <v>-15.30053737799185</v>
+        <v>-16.91566574490285</v>
       </c>
       <c r="I29" s="4" t="n">
-        <v>-14.61151298166392</v>
+        <v>-16.27818501135717</v>
       </c>
       <c r="J29" s="4" t="n">
-        <v>-8.955648582073891</v>
+        <v>-10.49864443232764</v>
       </c>
       <c r="K29" s="4" t="n">
-        <v>-1.469511537689016</v>
+        <v>-2.65887623279859</v>
       </c>
       <c r="L29" s="4" t="n">
-        <v>-8.230613172150896</v>
+        <v>-7.245890281110988</v>
       </c>
       <c r="M29" s="4" t="n">
-        <v>-6.450488688035563</v>
+        <v>-4.436858956932369</v>
       </c>
       <c r="N29" s="4" t="n">
-        <v>-11.23390508882319</v>
+        <v>-8.457689974215121</v>
       </c>
       <c r="O29" s="4" t="n">
-        <v>-5.453518434030677</v>
+        <v>-2.359275266650364</v>
       </c>
       <c r="P29" s="4" t="n">
-        <v>-5.674597310477267</v>
+        <v>-2.639852558542934</v>
       </c>
       <c r="Q29" s="4" t="n">
-        <v>-1.855128667759409</v>
+        <v>-0.1970069404279897</v>
       </c>
       <c r="R29" s="4" t="n">
-        <v>-1.260741745816325</v>
+        <v>0.3642970783916297</v>
       </c>
       <c r="S29" s="4" t="n">
-        <v>1.590415744071869</v>
+        <v>3.385416666666664</v>
       </c>
       <c r="T29" s="4" t="n">
-        <v>-0.006962273182196554</v>
+        <v>1.690032561505063</v>
       </c>
       <c r="U29" s="4" t="n">
-        <v>3.194003734607769</v>
+        <v>5.029494788650837</v>
       </c>
       <c r="V29" s="4" t="n">
-        <v>1.888312231142997</v>
+        <v>3.681581233709778</v>
       </c>
       <c r="W29" s="4" t="n">
-        <v>-3.131845877121584</v>
+        <v>-1.573363267670914</v>
       </c>
       <c r="X29" s="4" t="n">
-        <v>1.269920101767866</v>
+        <v>3.038974210373802</v>
       </c>
       <c r="Y29" s="4" t="n">
-        <v>-1.440679812615706</v>
+        <v>0.1576086956521792</v>
       </c>
       <c r="Z29" s="4" t="n">
-        <v>-0.02397475240623237</v>
+        <v>1.557969701362673</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>X ≈ 0.01619</t>
+          <t>X ≈ 0.01626</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C30" s="4" t="n">
-        <v>-4.410077882662733</v>
+        <v>-2.796617012635217</v>
       </c>
       <c r="D30" s="4" t="n">
-        <v>-3.206393142550994</v>
+        <v>-1.579419522639363</v>
       </c>
       <c r="E30" s="4" t="n">
-        <v>1.50943396226419</v>
+        <v>4.666464677574091</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>0.7964799428214064</v>
+        <v>1.032193406362467</v>
       </c>
       <c r="G30" s="4" t="n">
-        <v>3.537612547197213</v>
+        <v>5.267391685416484</v>
       </c>
       <c r="H30" s="4" t="n">
-        <v>-3.967728959013144</v>
+        <v>-3.608753588992585</v>
       </c>
       <c r="I30" s="4" t="n">
-        <v>-1.662754565980414</v>
+        <v>-1.40823069722348</v>
       </c>
       <c r="J30" s="4" t="n">
-        <v>-1.940966010733447</v>
+        <v>-0.2211317096813232</v>
       </c>
       <c r="K30" s="4" t="n">
-        <v>-0.361017290357168</v>
+        <v>1.427731736204528</v>
       </c>
       <c r="L30" s="4" t="n">
-        <v>-1.133932966393743</v>
+        <v>-0.9239524215176687</v>
       </c>
       <c r="M30" s="4" t="n">
-        <v>3.755511291152843</v>
+        <v>5.432020737893474</v>
       </c>
       <c r="N30" s="4" t="n">
-        <v>6.553684964627877</v>
+        <v>8.133694624273403</v>
       </c>
       <c r="O30" s="4" t="n">
-        <v>5.430522897771759</v>
+        <v>7.013019485772453</v>
       </c>
       <c r="P30" s="4" t="n">
-        <v>3.670982482863671</v>
+        <v>6.261662592972222</v>
       </c>
       <c r="Q30" s="4" t="n">
-        <v>6.089762262206285</v>
+        <v>8.609811241390183</v>
       </c>
       <c r="R30" s="4" t="n">
-        <v>5.145687645687644</v>
+        <v>7.65596374505833</v>
       </c>
       <c r="S30" s="4" t="n">
-        <v>3.473308970248631</v>
+        <v>6.036931818181863</v>
       </c>
       <c r="T30" s="4" t="n">
-        <v>3.368468266427449</v>
+        <v>5.904047713020219</v>
       </c>
       <c r="U30" s="4" t="n">
-        <v>8.199744262736353</v>
+        <v>10.66396448562054</v>
       </c>
       <c r="V30" s="4" t="n">
-        <v>6.848128534242832</v>
+        <v>9.363399415527994</v>
       </c>
       <c r="W30" s="4" t="n">
-        <v>7.844043904738349</v>
+        <v>10.31110642929879</v>
       </c>
       <c r="X30" s="4" t="n">
-        <v>3.152813327944628</v>
+        <v>5.690489361888957</v>
       </c>
       <c r="Y30" s="4" t="n">
-        <v>8.042672655811302</v>
+        <v>10.47957839262188</v>
       </c>
       <c r="Z30" s="4" t="n">
-        <v>11.04376347951111</v>
+        <v>13.34774242863549</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>X ≈ 0.01779</t>
+          <t>X ≈ 0.01784</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="C31" s="4" t="n">
-        <v>-9.45480060180406</v>
+        <v>-7.201163313476414</v>
       </c>
       <c r="D31" s="4" t="n">
-        <v>6.489492367287951</v>
+        <v>7.187076192283094</v>
       </c>
       <c r="E31" s="4" t="n">
-        <v>0.40031052755932</v>
+        <v>-3.823715470584098</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>-2.638224887232262</v>
+        <v>0.4619311110954882</v>
       </c>
       <c r="G31" s="4" t="n">
-        <v>6.328310221615816</v>
+        <v>5.064421751483955</v>
       </c>
       <c r="H31" s="4" t="n">
-        <v>4.189695012364353</v>
+        <v>5.221355357482004</v>
       </c>
       <c r="I31" s="4" t="n">
-        <v>10.39449051452052</v>
+        <v>11.74334651598103</v>
       </c>
       <c r="J31" s="4" t="n">
-        <v>7.79069767441861</v>
+        <v>6.560377292084567</v>
       </c>
       <c r="K31" s="4" t="n">
-        <v>10.15776625168215</v>
+        <v>9.127330592012619</v>
       </c>
       <c r="L31" s="4" t="n">
-        <v>11.71043197099456</v>
+        <v>10.77030348703711</v>
       </c>
       <c r="M31" s="4" t="n">
-        <v>14.31007300850525</v>
+        <v>11.04253850164152</v>
       </c>
       <c r="N31" s="4" t="n">
-        <v>14.03132360505732</v>
+        <v>10.76595654717015</v>
       </c>
       <c r="O31" s="4" t="n">
-        <v>12.90816153820121</v>
+        <v>9.651064429719376</v>
       </c>
       <c r="P31" s="4" t="n">
-        <v>10.36150126640565</v>
+        <v>6.963805978042394</v>
       </c>
       <c r="Q31" s="4" t="n">
-        <v>12.02893936417396</v>
+        <v>8.720675986401311</v>
       </c>
       <c r="R31" s="4" t="n">
-        <v>12.62332628611689</v>
+        <v>9.281980005220944</v>
       </c>
       <c r="S31" s="4" t="n">
-        <v>12.48940914913945</v>
+        <v>9.178099593495865</v>
       </c>
       <c r="T31" s="4" t="n">
-        <v>7.733405654620725</v>
+        <v>4.167166707846526</v>
       </c>
       <c r="U31" s="4" t="n">
-        <v>12.60045982624272</v>
+        <v>9.259677715480109</v>
       </c>
       <c r="V31" s="4" t="n">
-        <v>15.11288703155958</v>
+        <v>11.91328855078299</v>
       </c>
       <c r="W31" s="4" t="n">
-        <v>7.593596677547048</v>
+        <v>4.028770878670549</v>
       </c>
       <c r="X31" s="4" t="n">
-        <v>5.192169320789112</v>
+        <v>1.514583966471363</v>
       </c>
       <c r="Y31" s="4" t="n">
-        <v>5.466644033271166</v>
+        <v>1.758218451749741</v>
       </c>
       <c r="Z31" s="4" t="n">
-        <v>10.04197457074553</v>
+        <v>6.474128237948115</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>X ≈ 0.01939</t>
+          <t>X ≈ 0.01942</t>
         </is>
       </c>
       <c r="B32" t="n">
         <v>34</v>
       </c>
       <c r="C32" s="4" t="n">
-        <v>2.241505827744525</v>
+        <v>2.339726213065852</v>
       </c>
       <c r="D32" s="4" t="n">
-        <v>1.906729029394668</v>
+        <v>5.034995847950221</v>
       </c>
       <c r="E32" s="4" t="n">
-        <v>12.2334158627166</v>
+        <v>15.5450076284116</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>17.40281478445037</v>
+        <v>17.89378190019161</v>
       </c>
       <c r="G32" s="4" t="n">
-        <v>5.302318429550155</v>
+        <v>8.794694348327567</v>
       </c>
       <c r="H32" s="4" t="n">
-        <v>8.430461086235724</v>
+        <v>11.89280442491393</v>
       </c>
       <c r="I32" s="4" t="n">
-        <v>-1.16501700941933</v>
+        <v>2.274193000916419</v>
       </c>
       <c r="J32" s="4" t="n">
-        <v>4.439124487004108</v>
+        <v>7.851625498684314</v>
       </c>
       <c r="K32" s="4" t="n">
-        <v>7.421788139507086</v>
+        <v>10.9207308789567</v>
       </c>
       <c r="L32" s="4" t="n">
-        <v>6.648872463470553</v>
+        <v>10.12467938373736</v>
       </c>
       <c r="M32" s="4" t="n">
-        <v>-1.900597306132227</v>
+        <v>1.573384986576954</v>
       </c>
       <c r="N32" s="4" t="n">
-        <v>9.585359172772684</v>
+        <v>13.0615089144586</v>
       </c>
       <c r="O32" s="4" t="n">
-        <v>5.521020635328362</v>
+        <v>9.005440326419624</v>
       </c>
       <c r="P32" s="4" t="n">
-        <v>8.241118229469976</v>
+        <v>11.69838273557475</v>
       </c>
       <c r="Q32" s="4" t="n">
-        <v>4.641798461301128</v>
+        <v>8.075051883101388</v>
       </c>
       <c r="R32" s="4" t="n">
-        <v>8.17736185383248</v>
+        <v>11.57753237250935</v>
       </c>
       <c r="S32" s="4" t="n">
-        <v>13.9257976580314</v>
+        <v>17.35600490196078</v>
       </c>
       <c r="T32" s="4" t="n">
-        <v>13.82095695421026</v>
+        <v>17.22312079679918</v>
       </c>
       <c r="U32" s="4" t="n">
-        <v>11.09567186454635</v>
+        <v>14.49640655335668</v>
       </c>
       <c r="V32" s="4" t="n">
-        <v>14.22369414510261</v>
+        <v>17.65216946900394</v>
       </c>
       <c r="W32" s="4" t="n">
-        <v>16.62232444772481</v>
+        <v>20.02590143821143</v>
       </c>
       <c r="X32" s="4" t="n">
-        <v>13.60530201572744</v>
+        <v>17.00956244566792</v>
       </c>
       <c r="Y32" s="4" t="n">
-        <v>7.997423787033071</v>
+        <v>11.37084398976983</v>
       </c>
       <c r="Z32" s="4" t="n">
-        <v>13.8039444749863</v>
+        <v>17.09105793665675</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>X ≈ 0.02099</t>
+          <t>X ≈ 0.021</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C33" s="4" t="n">
-        <v>-3.640847113431988</v>
+        <v>-5.155529953917068</v>
       </c>
       <c r="D33" s="4" t="n">
-        <v>-0.85062391178176</v>
+        <v>-2.175630338007998</v>
       </c>
       <c r="E33" s="4" t="n">
-        <v>3.96135703918727</v>
+        <v>3.021288463326215</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>0.1234030197444866</v>
+        <v>-0.7969201870949192</v>
       </c>
       <c r="G33" s="4" t="n">
-        <v>-0.2123874528027869</v>
+        <v>-1.072478327194254</v>
       </c>
       <c r="H33" s="4" t="n">
-        <v>-6.275421266705365</v>
+        <v>-7.367157624421971</v>
       </c>
       <c r="I33" s="4" t="n">
-        <v>-7.047369950595716</v>
+        <v>-8.162239636654647</v>
       </c>
       <c r="J33" s="4" t="n">
-        <v>-10.45058139534883</v>
+        <v>-11.69296653167617</v>
       </c>
       <c r="K33" s="4" t="n">
-        <v>-16.65909421343417</v>
+        <v>-18.01665052521796</v>
       </c>
       <c r="L33" s="4" t="n">
-        <v>-14.30700988947062</v>
+        <v>-15.5868955688244</v>
       </c>
       <c r="M33" s="4" t="n">
-        <v>-14.0329502473087</v>
+        <v>-15.31466055422001</v>
       </c>
       <c r="N33" s="4" t="n">
-        <v>-17.43669965075669</v>
+        <v>-18.81704896030426</v>
       </c>
       <c r="O33" s="4" t="n">
-        <v>-12.30986171761285</v>
+        <v>-13.48032817452927</v>
       </c>
       <c r="P33" s="4" t="n">
-        <v>-9.405940594059359</v>
+        <v>-10.50275578434938</v>
       </c>
       <c r="Q33" s="4" t="n">
-        <v>-13.18908389163987</v>
+        <v>-14.4107166178473</v>
       </c>
       <c r="R33" s="4" t="n">
-        <v>-15.71969696969697</v>
+        <v>-17.07521905064063</v>
       </c>
       <c r="S33" s="4" t="n">
-        <v>-6.478614106674442</v>
+        <v>-7.50168010752693</v>
       </c>
       <c r="T33" s="4" t="n">
-        <v>-6.583454810495624</v>
+        <v>-7.634564212688488</v>
       </c>
       <c r="U33" s="4" t="n">
-        <v>-0.1175634295712982</v>
+        <v>-0.9684890823168573</v>
       </c>
       <c r="V33" s="4" t="n">
-        <v>3.194282380396771</v>
+        <v>2.471903814355031</v>
       </c>
       <c r="W33" s="4" t="n">
-        <v>8.901736212430741</v>
+        <v>8.356072216200104</v>
       </c>
       <c r="X33" s="4" t="n">
-        <v>5.700890251021598</v>
+        <v>5.055103242631823</v>
       </c>
       <c r="Y33" s="4" t="n">
-        <v>5.975364963503651</v>
+        <v>5.298737727910243</v>
       </c>
       <c r="Z33" s="4" t="n">
-        <v>-3.475467289719582</v>
+        <v>-4.540820621217833</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>X ≈ 0.02259</t>
+          <t>X ≈ 0.02258</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C34" s="4" t="n">
-        <v>6.359152886567998</v>
+        <v>4.352110113994669</v>
       </c>
       <c r="D34" s="4" t="n">
-        <v>6.024376088218183</v>
+        <v>4.106203278290799</v>
       </c>
       <c r="E34" s="4" t="n">
-        <v>4.586357039187227</v>
+        <v>2.851509176399219</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>8.873403019744487</v>
+        <v>7.522264872327831</v>
       </c>
       <c r="G34" s="4" t="n">
-        <v>8.537612547197213</v>
+        <v>7.246706732228496</v>
       </c>
       <c r="H34" s="4" t="n">
-        <v>3.724578733294592</v>
+        <v>7.40364033822658</v>
       </c>
       <c r="I34" s="4" t="n">
-        <v>12.95263004940424</v>
+        <v>17.13487411546754</v>
       </c>
       <c r="J34" s="4" t="n">
-        <v>17.67441860465117</v>
+        <v>22.09311156679577</v>
       </c>
       <c r="K34" s="4" t="n">
-        <v>7.71590578656587</v>
+        <v>11.69472468700619</v>
       </c>
       <c r="L34" s="4" t="n">
-        <v>11.94299011052938</v>
+        <v>16.16183108652369</v>
       </c>
       <c r="M34" s="4" t="n">
-        <v>12.2170497526913</v>
+        <v>16.43406610112802</v>
       </c>
       <c r="N34" s="4" t="n">
-        <v>11.93830034924335</v>
+        <v>16.15748414665681</v>
       </c>
       <c r="O34" s="4" t="n">
-        <v>5.815138282387259</v>
+        <v>9.779434134469206</v>
       </c>
       <c r="P34" s="4" t="n">
-        <v>-4.405940594059395</v>
+        <v>-0.9951157164376667</v>
       </c>
       <c r="Q34" s="4" t="n">
-        <v>-5.064083891640031</v>
+        <v>-1.677270098322801</v>
       </c>
       <c r="R34" s="4" t="n">
-        <v>-4.469696969696962</v>
+        <v>-1.11596607950306</v>
       </c>
       <c r="S34" s="4" t="n">
-        <v>-4.603614106674371</v>
+        <v>-1.21984649122799</v>
       </c>
       <c r="T34" s="4" t="n">
-        <v>-4.708454810495617</v>
+        <v>-1.352730596389669</v>
       </c>
       <c r="U34" s="4" t="n">
-        <v>-4.492563429571291</v>
+        <v>-1.138268369243896</v>
       </c>
       <c r="V34" s="4" t="n">
-        <v>-4.305717619603342</v>
+        <v>-0.9236819241849901</v>
       </c>
       <c r="W34" s="4" t="n">
-        <v>-4.848263787569373</v>
+        <v>-1.491126425565724</v>
       </c>
       <c r="X34" s="4" t="n">
-        <v>-4.924109748978331</v>
+        <v>-1.566288947520853</v>
       </c>
       <c r="Y34" s="4" t="n">
-        <v>-4.649635036496342</v>
+        <v>-1.322654462242554</v>
       </c>
       <c r="Z34" s="4" t="n">
-        <v>-4.725467289719695</v>
+        <v>-1.484793456532095</v>
       </c>
     </row>
   </sheetData>
@@ -3180,2297 +3180,2297 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>X &gt; -0.02298</t>
+          <t>X &gt; -0.02244</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3336</v>
+        <v>3360</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>-0.02369915272937106</v>
+        <v>-0.01025900715286809</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>-0.07449228581394607</v>
+        <v>0.084914100289609</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>-0.06660691672578878</v>
+        <v>0.1475442952522457</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>-0.107526658443831</v>
+        <v>0.2223583011662029</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>-0.1881698671097922</v>
+        <v>0.1113038568838718</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>-0.3123920478622324</v>
+        <v>-0.04081449334613296</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>-0.3220493421853803</v>
+        <v>-0.07909655298623619</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>-0.2551756674252132</v>
+        <v>-0.04146064572605468</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>-0.2264994655976622</v>
+        <v>0.0736720554272452</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>-0.1764128745452496</v>
+        <v>0.1539691079257466</v>
       </c>
       <c r="M6" s="4" t="n">
-        <v>-0.1239475599393316</v>
+        <v>0.1764787589213483</v>
       </c>
       <c r="N6" s="4" t="n">
-        <v>-0.1763949912584906</v>
+        <v>0.1541751624524537</v>
       </c>
       <c r="O6" s="4" t="n">
-        <v>-0.146917289766975</v>
+        <v>0.2133206900749798</v>
       </c>
       <c r="P6" s="4" t="n">
-        <v>-0.1411468104371636</v>
+        <v>0.2199397263235383</v>
       </c>
       <c r="Q6" s="4" t="n">
-        <v>-0.09397925785820149</v>
+        <v>0.2973905068857547</v>
       </c>
       <c r="R6" s="4" t="n">
-        <v>-0.07974481658692412</v>
+        <v>0.3123374584391811</v>
       </c>
       <c r="S6" s="4" t="n">
-        <v>0.01349627322385771</v>
+        <v>0.3448761261261239</v>
       </c>
       <c r="T6" s="4" t="n">
-        <v>0.04618313085686054</v>
+        <v>0.3484921574646549</v>
       </c>
       <c r="U6" s="4" t="n">
-        <v>0.01057934205396549</v>
+        <v>0.4320765122763959</v>
       </c>
       <c r="V6" s="4" t="n">
-        <v>-0.1141008531362004</v>
+        <v>0.2184421136146923</v>
       </c>
       <c r="W6" s="4" t="n">
-        <v>-0.1597342877190471</v>
+        <v>0.2335241840091342</v>
       </c>
       <c r="X6" s="4" t="n">
-        <v>-0.1877406656950029</v>
+        <v>0.1463507719442916</v>
       </c>
       <c r="Y6" s="4" t="n">
-        <v>-0.1950350964304306</v>
+        <v>0.1696958720877646</v>
       </c>
       <c r="Z6" s="4" t="n">
-        <v>-0.1930931890002014</v>
+        <v>0.0847554156484307</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>X &gt; -0.02138</t>
+          <t>X &gt; -0.02086</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>3320</v>
+        <v>3343</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>-0.006387047622816056</v>
+        <v>-0.007273192757061508</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>-0.05581541387633848</v>
+        <v>0.05990625787944026</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>-0.07093119786754443</v>
+        <v>0.09945961134508252</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>-0.0786927886387403</v>
+        <v>0.1776321039662463</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>-0.1281556468728624</v>
+        <v>0.09714037135307763</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>-0.2238934057107969</v>
+        <v>-0.02679233375388179</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>-0.2298692014198522</v>
+        <v>-0.09100307751490533</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>-0.2212648485862445</v>
+        <v>-0.02186626181863005</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>-0.1626549330743075</v>
+        <v>0.09320749318781907</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>-0.1085995715342065</v>
+        <v>0.1183712304491991</v>
       </c>
       <c r="M7" s="4" t="n">
-        <v>-0.1171836706510376</v>
+        <v>0.1992000324999665</v>
       </c>
       <c r="N7" s="4" t="n">
-        <v>-0.1085183782476946</v>
+        <v>0.2378041717567427</v>
       </c>
       <c r="O7" s="4" t="n">
-        <v>-0.0734837530376069</v>
+        <v>0.3029253311549382</v>
       </c>
       <c r="P7" s="4" t="n">
-        <v>-0.09663128475008875</v>
+        <v>0.3108632183732567</v>
       </c>
       <c r="Q7" s="4" t="n">
-        <v>-0.04606046118036033</v>
+        <v>0.3921935368989793</v>
       </c>
       <c r="R7" s="4" t="n">
-        <v>-0.03460081585081554</v>
+        <v>0.404397048549832</v>
       </c>
       <c r="S7" s="4" t="n">
-        <v>0.1198604950688704</v>
+        <v>0.4973569651741272</v>
       </c>
       <c r="T7" s="4" t="n">
-        <v>0.09310862907143047</v>
+        <v>0.4419921016663011</v>
       </c>
       <c r="U7" s="4" t="n">
-        <v>-0.003841625060019283</v>
+        <v>0.4353340956998295</v>
       </c>
       <c r="V7" s="4" t="n">
-        <v>-0.1300256821784842</v>
+        <v>0.2494031637964724</v>
       </c>
       <c r="W7" s="4" t="n">
-        <v>-0.1732713108916002</v>
+        <v>0.2973405577923245</v>
       </c>
       <c r="X7" s="4" t="n">
-        <v>-0.2010513504233202</v>
+        <v>0.2101251819732113</v>
       </c>
       <c r="Y7" s="4" t="n">
-        <v>-0.2097073038856863</v>
+        <v>0.232369461202417</v>
       </c>
       <c r="Z7" s="4" t="n">
-        <v>-0.2073950005629897</v>
+        <v>0.1478403265496766</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>X &gt; -0.01978</t>
+          <t>X &gt; -0.01928</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3293</v>
+        <v>3315</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>0.008127554843063933</v>
+        <v>0.05234031802481098</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>-0.1294700656279346</v>
+        <v>0.06223059561016697</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>-0.04249027523643178</v>
+        <v>0.2025756916081036</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>-0.07468028843540964</v>
+        <v>0.2564241084992176</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>-0.09161450594288567</v>
+        <v>0.20758824013744</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>-0.1594442204958</v>
+        <v>0.1413351603403683</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>-0.2195753886622285</v>
+        <v>0.08331665037624703</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>-0.08774519105750755</v>
+        <v>0.185671095307832</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>-0.02895515660220127</v>
+        <v>0.3006990824542726</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>0.001653551714746015</v>
+        <v>0.3027932847498178</v>
       </c>
       <c r="M8" s="4" t="n">
-        <v>0.05129052704096893</v>
+        <v>0.4121151901968574</v>
       </c>
       <c r="N8" s="4" t="n">
-        <v>0.03209762609655797</v>
+        <v>0.4233788202207194</v>
       </c>
       <c r="O8" s="4" t="n">
-        <v>0.07663949304094331</v>
+        <v>0.4684235954939098</v>
       </c>
       <c r="P8" s="4" t="n">
-        <v>0.0551553792981565</v>
+        <v>0.4785684940886483</v>
       </c>
       <c r="Q8" s="4" t="n">
-        <v>0.08128255293907927</v>
+        <v>0.5362963086694847</v>
       </c>
       <c r="R8" s="4" t="n">
-        <v>0.08801281521669324</v>
+        <v>0.5439163982833364</v>
       </c>
       <c r="S8" s="4" t="n">
-        <v>0.2448707418104092</v>
+        <v>0.6385774132048923</v>
       </c>
       <c r="T8" s="4" t="n">
-        <v>0.2187958715292311</v>
+        <v>0.5839086530437569</v>
       </c>
       <c r="U8" s="4" t="n">
-        <v>0.0890011550254286</v>
+        <v>0.545308041662885</v>
       </c>
       <c r="V8" s="4" t="n">
-        <v>0.0209429809426851</v>
+        <v>0.4464200405793548</v>
       </c>
       <c r="W8" s="4" t="n">
-        <v>0.01217310563458085</v>
+        <v>0.4996099089415011</v>
       </c>
       <c r="X8" s="4" t="n">
-        <v>0.01519222370748707</v>
+        <v>0.412353770217031</v>
       </c>
       <c r="Y8" s="4" t="n">
-        <v>-0.02607705228262347</v>
+        <v>0.4327896365448183</v>
       </c>
       <c r="Z8" s="4" t="n">
-        <v>-0.05343570757568727</v>
+        <v>0.3188105761741795</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>X &gt; -0.01818</t>
+          <t>X &gt; -0.0177</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3268</v>
+        <v>3283</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>-0.040117851809363</v>
+        <v>-0.06410283216383306</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>-0.2066269512954548</v>
+        <v>-0.1122854548885925</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>-0.1688877160575331</v>
+        <v>0.07178444083148605</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>-0.07428554473239757</v>
+        <v>0.1318542408444969</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>-0.02794875490196347</v>
+        <v>0.1760318621338257</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>-0.0672654541673694</v>
+        <v>0.1076056437958712</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>-0.0915099810371629</v>
+        <v>0.08702722551539921</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>0.04348072401778325</v>
+        <v>0.2842699720541404</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>0.1329024359719</v>
+        <v>0.4295240869615071</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>0.2001503786585701</v>
+        <v>0.4697346032773666</v>
       </c>
       <c r="M9" s="4" t="n">
-        <v>0.2176593229442716</v>
+        <v>0.4561662544238914</v>
       </c>
       <c r="N9" s="4" t="n">
-        <v>0.2004954711945288</v>
+        <v>0.4095406916611282</v>
       </c>
       <c r="O9" s="4" t="n">
-        <v>0.1625002829971294</v>
+        <v>0.3747749455131242</v>
       </c>
       <c r="P9" s="4" t="n">
-        <v>0.08155177933900859</v>
+        <v>0.3570347782320411</v>
       </c>
       <c r="Q9" s="4" t="n">
-        <v>0.1434229743960458</v>
+        <v>0.4522943961455255</v>
       </c>
       <c r="R9" s="4" t="n">
-        <v>0.1151626151626175</v>
+        <v>0.4545052218131289</v>
       </c>
       <c r="S9" s="4" t="n">
-        <v>0.2742484887454069</v>
+        <v>0.5814652988855116</v>
       </c>
       <c r="T9" s="4" t="n">
-        <v>0.2793277185208751</v>
+        <v>0.5579445408300785</v>
       </c>
       <c r="U9" s="4" t="n">
-        <v>0.1774640681372261</v>
+        <v>0.5472867594537618</v>
       </c>
       <c r="V9" s="4" t="n">
-        <v>0.1380476615703259</v>
+        <v>0.4757704640110063</v>
       </c>
       <c r="W9" s="4" t="n">
-        <v>0.1333931980620022</v>
+        <v>0.5654453141915354</v>
       </c>
       <c r="X9" s="4" t="n">
-        <v>0.1064712907769447</v>
+        <v>0.4476500094605527</v>
       </c>
       <c r="Y9" s="4" t="n">
-        <v>0.1239960433445759</v>
+        <v>0.4963723984536372</v>
       </c>
       <c r="Z9" s="4" t="n">
-        <v>0.127653885310977</v>
+        <v>0.4133420741924496</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>X &gt; -0.01658</t>
+          <t>X &gt; -0.01612</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>3216</v>
+        <v>3230</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>0.1411843777690223</v>
+        <v>0.1309053960824613</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>-0.2078660365501577</v>
+        <v>-0.129246970948536</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>-0.05374181777909826</v>
+        <v>0.1705527095631041</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>-0.06973665887108638</v>
+        <v>0.3028316739472672</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>-0.01725607722319467</v>
+        <v>0.2599415737181872</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>-0.1529722871135775</v>
+        <v>0.187863827985467</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>-0.07242407988744048</v>
+        <v>0.1799521632201291</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>0.03827999078978195</v>
+        <v>0.2930013096371624</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>0.2522722365813479</v>
+        <v>0.5926242896337115</v>
       </c>
       <c r="L10" s="4" t="n">
-        <v>0.1473244758544539</v>
+        <v>0.5540693888145753</v>
       </c>
       <c r="M10" s="4" t="n">
-        <v>0.09874687254265524</v>
+        <v>0.5666918375319483</v>
       </c>
       <c r="N10" s="4" t="n">
-        <v>0.02380220797935806</v>
+        <v>0.4930145210195462</v>
       </c>
       <c r="O10" s="4" t="n">
-        <v>-0.08972691748886064</v>
+        <v>0.3833737892215581</v>
       </c>
       <c r="P10" s="4" t="n">
-        <v>-0.07550042046982242</v>
+        <v>0.4002708982471859</v>
       </c>
       <c r="Q10" s="4" t="n">
-        <v>-0.0640838916399602</v>
+        <v>0.4773910219060582</v>
       </c>
       <c r="R10" s="4" t="n">
-        <v>-0.009399202947584229</v>
+        <v>0.5013415502879042</v>
       </c>
       <c r="S10" s="4" t="n">
-        <v>0.1854023376320981</v>
+        <v>0.6320956904541148</v>
       </c>
       <c r="T10" s="4" t="n">
-        <v>0.130154748784328</v>
+        <v>0.4867723637300259</v>
       </c>
       <c r="U10" s="4" t="n">
-        <v>0.05416119011203335</v>
+        <v>0.4414924702582539</v>
       </c>
       <c r="V10" s="4" t="n">
-        <v>0.0731643679743641</v>
+        <v>0.4270976220833518</v>
       </c>
       <c r="W10" s="4" t="n">
-        <v>0.1082444448009952</v>
+        <v>0.465667818008022</v>
       </c>
       <c r="X10" s="4" t="n">
-        <v>0.1131804934081728</v>
+        <v>0.3780831212648934</v>
       </c>
       <c r="Y10" s="4" t="n">
-        <v>0.126553959462619</v>
+        <v>0.4235867210313202</v>
       </c>
       <c r="Z10" s="4" t="n">
-        <v>0.1625924117729127</v>
+        <v>0.3418319304648847</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>X &gt; -0.01498</t>
+          <t>X &gt; -0.01454</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>3157</v>
+        <v>3160</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>0.2899704966309287</v>
+        <v>0.2745269005416162</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>-0.05929802313755772</v>
+        <v>-0.01732049027580729</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>0.09296496870264548</v>
+        <v>0.3795953459255159</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>0.02700704870262172</v>
+        <v>0.464999066303335</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>0.08673093510653729</v>
+        <v>0.3958267799098252</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>0.00804330022372568</v>
+        <v>0.3816801514159422</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>0.009970944174241936</v>
+        <v>0.3911735041659199</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>0.3170281224576499</v>
+        <v>0.6709320626197197</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>0.5027910324675133</v>
+        <v>0.8484752050335516</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>0.2842073921440118</v>
+        <v>0.7006829420604603</v>
       </c>
       <c r="M11" s="4" t="n">
-        <v>0.1981223078963481</v>
+        <v>0.6130765013801565</v>
       </c>
       <c r="N11" s="4" t="n">
-        <v>0.06389201853961168</v>
+        <v>0.5123656758264445</v>
       </c>
       <c r="O11" s="4" t="n">
-        <v>-0.03082131357240314</v>
+        <v>0.4249220263843441</v>
       </c>
       <c r="P11" s="4" t="n">
-        <v>-0.1700706856287084</v>
+        <v>0.2584124256841918</v>
       </c>
       <c r="Q11" s="4" t="n">
-        <v>-0.1462064437561992</v>
+        <v>0.3522593896445798</v>
       </c>
       <c r="R11" s="4" t="n">
-        <v>-0.1332040787017092</v>
+        <v>0.3958627349573334</v>
       </c>
       <c r="S11" s="4" t="n">
-        <v>0.1625047302408547</v>
+        <v>0.5949209293758528</v>
       </c>
       <c r="T11" s="4" t="n">
-        <v>0.04494386165107045</v>
+        <v>0.4177252336465642</v>
       </c>
       <c r="U11" s="4" t="n">
-        <v>-0.004897395415703443</v>
+        <v>0.3982744095039195</v>
       </c>
       <c r="V11" s="4" t="n">
-        <v>0.1374965531268799</v>
+        <v>0.4736166319399118</v>
       </c>
       <c r="W11" s="4" t="n">
-        <v>0.1833817820509509</v>
+        <v>0.5888442884467011</v>
       </c>
       <c r="X11" s="4" t="n">
-        <v>0.2531615394039903</v>
+        <v>0.5642746531315481</v>
       </c>
       <c r="Y11" s="4" t="n">
-        <v>0.2300356411477296</v>
+        <v>0.5738140104259912</v>
       </c>
       <c r="Z11" s="4" t="n">
-        <v>0.2681975819940234</v>
+        <v>0.4622418532614461</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>X &gt; -0.01339</t>
+          <t>X &gt; -0.01296</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>3070</v>
+        <v>3073</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>0.2550468406579114</v>
+        <v>0.4625412305457317</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>0.03472537670463538</v>
+        <v>0.2663937382856929</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>0.1347232637100291</v>
+        <v>0.4189572082435333</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>0.2164450909419031</v>
+        <v>0.5881011409820118</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>0.1255050690489483</v>
+        <v>0.5571172993967366</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>0.1041124120510659</v>
+        <v>0.3440956499124681</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>0.06309328231645139</v>
+        <v>0.2791425535530578</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>0.1922410285008027</v>
+        <v>0.3487214558758609</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>0.2523725612822361</v>
+        <v>0.4951746461008284</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>0.08177091467983644</v>
+        <v>0.3655376317984533</v>
       </c>
       <c r="M12" s="4" t="n">
-        <v>-0.04697879093503587</v>
+        <v>0.3000824056612359</v>
       </c>
       <c r="N12" s="4" t="n">
-        <v>-0.07986967022457492</v>
+        <v>0.2690596819292779</v>
       </c>
       <c r="O12" s="4" t="n">
-        <v>-0.1780457487715239</v>
+        <v>0.2105215807111875</v>
       </c>
       <c r="P12" s="4" t="n">
-        <v>-0.3799665680853792</v>
+        <v>0.01381270256636924</v>
       </c>
       <c r="Q12" s="4" t="n">
-        <v>-0.3044216636438577</v>
+        <v>0.1294855968854378</v>
       </c>
       <c r="R12" s="4" t="n">
-        <v>-0.2754149683974205</v>
+        <v>0.1583980196445083</v>
       </c>
       <c r="S12" s="4" t="n">
-        <v>0.03239499309805893</v>
+        <v>0.3984036796536827</v>
       </c>
       <c r="T12" s="4" t="n">
-        <v>0.0119613143418249</v>
+        <v>0.2848482484163952</v>
       </c>
       <c r="U12" s="4" t="n">
-        <v>-0.110449608433079</v>
+        <v>0.1937654189302407</v>
       </c>
       <c r="V12" s="4" t="n">
-        <v>0.03065193147024559</v>
+        <v>0.1676065830760862</v>
       </c>
       <c r="W12" s="4" t="n">
-        <v>0.09316152971022973</v>
+        <v>0.3020431042406528</v>
       </c>
       <c r="X12" s="4" t="n">
-        <v>0.1670360843549332</v>
+        <v>0.2137709583412857</v>
       </c>
       <c r="Y12" s="4" t="n">
-        <v>0.1354512546140398</v>
+        <v>0.2491018641622631</v>
       </c>
       <c r="Z12" s="4" t="n">
-        <v>0.1116662607689705</v>
+        <v>0.1713971338391218</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>X &gt; -0.01179</t>
+          <t>X &gt; -0.01138</t>
         </is>
       </c>
       <c r="B13" t="n">
         <v>2971</v>
       </c>
       <c r="C13" s="4" t="n">
-        <v>0.33376878503163</v>
+        <v>0.4653893039535362</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>-0.01638568926257022</v>
+        <v>0.1372933656877038</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>0.0007955418610308129</v>
+        <v>0.2709434572886025</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>0.008474902058090095</v>
+        <v>0.2988402123830838</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>-0.3085412989566336</v>
+        <v>0.008544436857960136</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>-0.2700683058489375</v>
+        <v>0.08381853547614071</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>-0.2535279157898742</v>
+        <v>0.04370241110624562</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>-0.2448984358577064</v>
+        <v>0.09251247952285269</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>-0.1842951511434379</v>
+        <v>0.2060230266261769</v>
       </c>
       <c r="L13" s="4" t="n">
-        <v>-0.3350668408943989</v>
+        <v>0.1325619337422523</v>
       </c>
       <c r="M13" s="4" t="n">
-        <v>-0.410296091812711</v>
+        <v>0.08899766596505998</v>
       </c>
       <c r="N13" s="4" t="n">
-        <v>-0.5357190942699361</v>
+        <v>-0.0007458231722949904</v>
       </c>
       <c r="O13" s="4" t="n">
-        <v>-0.7006229516839042</v>
+        <v>-0.1573797311809173</v>
       </c>
       <c r="P13" s="4" t="n">
-        <v>-0.8349912482023072</v>
+        <v>-0.38599479269255</v>
       </c>
       <c r="Q13" s="4" t="n">
-        <v>-0.7352248312372751</v>
+        <v>-0.2431478800253046</v>
       </c>
       <c r="R13" s="4" t="n">
-        <v>-0.5573102627483308</v>
+        <v>-0.09831621465968965</v>
       </c>
       <c r="S13" s="4" t="n">
-        <v>-0.2349102786019088</v>
+        <v>0.08622257667337863</v>
       </c>
       <c r="T13" s="4" t="n">
-        <v>-0.2526267957156492</v>
+        <v>-0.06036632999644809</v>
       </c>
       <c r="U13" s="4" t="n">
-        <v>-0.4199827844100099</v>
+        <v>-0.09483316833841116</v>
       </c>
       <c r="V13" s="4" t="n">
-        <v>-0.2805075355696616</v>
+        <v>-0.1293431360380808</v>
       </c>
       <c r="W13" s="4" t="n">
-        <v>-0.197961164838965</v>
+        <v>0.06269086817306402</v>
       </c>
       <c r="X13" s="4" t="n">
-        <v>-0.2201070580937738</v>
+        <v>-0.09338367728176422</v>
       </c>
       <c r="Y13" s="4" t="n">
-        <v>-0.3629593971962137</v>
+        <v>-0.06530516706653344</v>
       </c>
       <c r="Z13" s="4" t="n">
-        <v>-0.2505430217963678</v>
+        <v>-0.0392408338106307</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>X &gt; -0.01019</t>
+          <t>X &gt; -0.009801</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>2860</v>
+        <v>2858</v>
       </c>
       <c r="C14" s="4" t="n">
-        <v>0.1919659285382096</v>
+        <v>0.2234267255513274</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>-0.262924397555544</v>
+        <v>-0.107978008258911</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>-0.2938928740373541</v>
+        <v>-0.02412381020067045</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>-0.3627080913666205</v>
+        <v>0.09751815494368543</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>-0.6443950943449863</v>
+        <v>-0.2629433052740211</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>-0.5075268956143759</v>
+        <v>-0.1562015474333194</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>-0.7387151017949236</v>
+        <v>-0.4797711934569406</v>
       </c>
       <c r="J14" s="4" t="n">
-        <v>-0.649642591454537</v>
+        <v>-0.452029992739817</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>-0.5884420395210839</v>
+        <v>-0.2696624381334871</v>
       </c>
       <c r="L14" s="4" t="n">
-        <v>-0.7501205366522541</v>
+        <v>-0.3496774899313664</v>
       </c>
       <c r="M14" s="4" t="n">
-        <v>-0.9086028752237638</v>
+        <v>-0.5799946515897147</v>
       </c>
       <c r="N14" s="4" t="n">
-        <v>-1.02827346691268</v>
+        <v>-0.6277716758263026</v>
       </c>
       <c r="O14" s="4" t="n">
-        <v>-1.225962379403136</v>
+        <v>-0.7468816550045574</v>
       </c>
       <c r="P14" s="4" t="n">
-        <v>-1.392003311829434</v>
+        <v>-0.9051942600771028</v>
       </c>
       <c r="Q14" s="4" t="n">
-        <v>-1.15854189094285</v>
+        <v>-0.695132158425892</v>
       </c>
       <c r="R14" s="4" t="n">
-        <v>-1.101496132876889</v>
+        <v>-0.6715542823899057</v>
       </c>
       <c r="S14" s="4" t="n">
-        <v>-0.9011376504484261</v>
+        <v>-0.6154559336823695</v>
       </c>
       <c r="T14" s="4" t="n">
-        <v>-0.8459286416191389</v>
+        <v>-0.6929981647519199</v>
       </c>
       <c r="U14" s="4" t="n">
-        <v>-0.9585320159587312</v>
+        <v>-0.6676541809614633</v>
       </c>
       <c r="V14" s="4" t="n">
-        <v>-0.7512483458602546</v>
+        <v>-0.5724369354026848</v>
       </c>
       <c r="W14" s="4" t="n">
-        <v>-0.6097028375169131</v>
+        <v>-0.4204665532353999</v>
       </c>
       <c r="X14" s="4" t="n">
-        <v>-0.5250880858057982</v>
+        <v>-0.4400467686471714</v>
       </c>
       <c r="Y14" s="4" t="n">
-        <v>-0.6842383220608355</v>
+        <v>-0.4905637422631699</v>
       </c>
       <c r="Z14" s="4" t="n">
-        <v>-0.4597330239853505</v>
+        <v>-0.3522384861810224</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>X &gt; -0.008589</t>
+          <t>X &gt; -0.008222</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>2710</v>
+        <v>2689</v>
       </c>
       <c r="C15" s="4" t="n">
-        <v>-0.1831083648040845</v>
+        <v>-0.2977889699984999</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>-0.7545404564377165</v>
+        <v>-0.4871687537812619</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>-0.7450234075355837</v>
+        <v>-0.3937811712411019</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>-0.9251317787903091</v>
+        <v>-0.486128203384709</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>-1.277337984132942</v>
+        <v>-0.9259590533580706</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>-1.106799565825646</v>
+        <v>-0.8225957358892515</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>-1.125111058039835</v>
+        <v>-1.006099160293921</v>
       </c>
       <c r="J15" s="4" t="n">
-        <v>-1.015970243477959</v>
+        <v>-0.8468631389149053</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>-0.8804244886634862</v>
+        <v>-0.5872746901348833</v>
       </c>
       <c r="L15" s="4" t="n">
-        <v>-1.155394617811297</v>
+        <v>-0.8816099244387843</v>
       </c>
       <c r="M15" s="4" t="n">
-        <v>-1.374577129424004</v>
+        <v>-1.069537467378723</v>
       </c>
       <c r="N15" s="4" t="n">
-        <v>-1.485652626509818</v>
+        <v>-1.103179545153317</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>-1.522237682331657</v>
+        <v>-1.197174052665382</v>
       </c>
       <c r="P15" s="4" t="n">
-        <v>-1.722117064647641</v>
+        <v>-1.424124511117967</v>
       </c>
       <c r="Q15" s="4" t="n">
-        <v>-1.58670250142297</v>
+        <v>-1.306625176158157</v>
       </c>
       <c r="R15" s="4" t="n">
-        <v>-1.522677102147306</v>
+        <v>-1.279890908260164</v>
       </c>
       <c r="S15" s="4" t="n">
-        <v>-1.524850764753204</v>
+        <v>-1.399449802176065</v>
       </c>
       <c r="T15" s="4" t="n">
-        <v>-1.350575576327728</v>
+        <v>-1.362495267808484</v>
       </c>
       <c r="U15" s="4" t="n">
-        <v>-1.481513705814393</v>
+        <v>-1.423502612982418</v>
       </c>
       <c r="V15" s="4" t="n">
-        <v>-1.310139137657806</v>
+        <v>-1.410323705020218</v>
       </c>
       <c r="W15" s="4" t="n">
-        <v>-1.315274476843165</v>
+        <v>-1.25064781447626</v>
       </c>
       <c r="X15" s="4" t="n">
-        <v>-1.148298539538871</v>
+        <v>-1.192724043063585</v>
       </c>
       <c r="Y15" s="4" t="n">
-        <v>-1.405444700826848</v>
+        <v>-1.410699854533689</v>
       </c>
       <c r="Z15" s="4" t="n">
-        <v>-1.05388057385246</v>
+        <v>-1.067890283761862</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>X &gt; -0.006991</t>
+          <t>X &gt; -0.006642</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>2524</v>
+        <v>2500</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>-0.5195279143742511</v>
+        <v>-0.4312513813012444</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>-0.5584990099750229</v>
+        <v>-0.4181925646074873</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>-0.6788688940151317</v>
+        <v>-0.3823787962098137</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>-0.7806850305699768</v>
+        <v>-0.4372171661015685</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>-0.9767405790316559</v>
+        <v>-0.5320693067176165</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>-0.9253032493962081</v>
+        <v>-0.4722845813001868</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>-0.8883774279668799</v>
+        <v>-0.3713467406058868</v>
       </c>
       <c r="J16" s="4" t="n">
-        <v>-1.105108954403953</v>
+        <v>-0.6936845172139385</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>-0.9627078408464982</v>
+        <v>-0.5434253600797092</v>
       </c>
       <c r="L16" s="4" t="n">
-        <v>-1.280020133757461</v>
+        <v>-0.9989108638175423</v>
       </c>
       <c r="M16" s="4" t="n">
-        <v>-1.377747251644529</v>
+        <v>-1.022528030440441</v>
       </c>
       <c r="N16" s="4" t="n">
-        <v>-1.358229619210952</v>
+        <v>-1.037872876474339</v>
       </c>
       <c r="O16" s="4" t="n">
-        <v>-1.551725622938257</v>
+        <v>-1.214298704198633</v>
       </c>
       <c r="P16" s="4" t="n">
-        <v>-1.947377058147801</v>
+        <v>-1.599015905156477</v>
       </c>
       <c r="Q16" s="4" t="n">
-        <v>-1.951174298272413</v>
+        <v>-1.580775374066889</v>
       </c>
       <c r="R16" s="4" t="n">
-        <v>-1.965747522619559</v>
+        <v>-1.793797020491894</v>
       </c>
       <c r="S16" s="4" t="n">
-        <v>-1.958414580795342</v>
+        <v>-1.874854573859864</v>
       </c>
       <c r="T16" s="4" t="n">
-        <v>-1.724265087175468</v>
+        <v>-1.825280686699244</v>
       </c>
       <c r="U16" s="4" t="n">
-        <v>-1.841317877969871</v>
+        <v>-1.827416388993875</v>
       </c>
       <c r="V16" s="4" t="n">
-        <v>-1.59211002466656</v>
+        <v>-1.709792568207114</v>
       </c>
       <c r="W16" s="4" t="n">
-        <v>-1.597373403714933</v>
+        <v>-1.655140135429598</v>
       </c>
       <c r="X16" s="4" t="n">
-        <v>-1.491805710973658</v>
+        <v>-1.70722882719614</v>
       </c>
       <c r="Y16" s="4" t="n">
-        <v>-1.867456818674569</v>
+        <v>-1.960294143212273</v>
       </c>
       <c r="Z16" s="4" t="n">
-        <v>-1.444960158182383</v>
+        <v>-1.699530298637285</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>X &gt; -0.005392</t>
+          <t>X &gt; -0.005062</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>2353</v>
+        <v>2348</v>
       </c>
       <c r="C17" s="4" t="n">
-        <v>-0.5040050081688037</v>
+        <v>-0.1896111228807413</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>-0.647906978336124</v>
+        <v>-0.3286179520001227</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>-0.6728085739606868</v>
+        <v>-0.3366003968162161</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>-1.109733573847421</v>
+        <v>-0.6525217564061663</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>-1.169262189200929</v>
+        <v>-0.7358605859401806</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>-1.1699360346379</v>
+        <v>-0.5556068922757049</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>-1.032173665243292</v>
+        <v>-0.6085330281843895</v>
       </c>
       <c r="J17" s="4" t="n">
-        <v>-1.117811125078561</v>
+        <v>-0.7628862958812306</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>-1.137072667173044</v>
+        <v>-0.7381772886269147</v>
       </c>
       <c r="L17" s="4" t="n">
-        <v>-1.717195857348891</v>
+        <v>-1.298840066379725</v>
       </c>
       <c r="M17" s="4" t="n">
-        <v>-1.7998635665476</v>
+        <v>-1.299276149033581</v>
       </c>
       <c r="N17" s="4" t="n">
-        <v>-1.758823170215244</v>
+        <v>-1.255539938981087</v>
       </c>
       <c r="O17" s="4" t="n">
-        <v>-2.054095742157877</v>
+        <v>-1.541152197830471</v>
       </c>
       <c r="P17" s="4" t="n">
-        <v>-2.462672177463297</v>
+        <v>-1.849988266770247</v>
       </c>
       <c r="Q17" s="4" t="n">
-        <v>-2.503728110191425</v>
+        <v>-1.913967059223062</v>
       </c>
       <c r="R17" s="4" t="n">
-        <v>-2.266307139188491</v>
+        <v>-1.795083227211052</v>
       </c>
       <c r="S17" s="4" t="n">
-        <v>-2.375975276661727</v>
+        <v>-2.002056794055207</v>
       </c>
       <c r="T17" s="4" t="n">
-        <v>-2.329319950444727</v>
+        <v>-2.238121644102421</v>
       </c>
       <c r="U17" s="4" t="n">
-        <v>-2.173938058336674</v>
+        <v>-2.041929988229739</v>
       </c>
       <c r="V17" s="4" t="n">
-        <v>-2.174987568669486</v>
+        <v>-2.22828271186841</v>
       </c>
       <c r="W17" s="4" t="n">
-        <v>-2.293085519318026</v>
+        <v>-2.218700358270652</v>
       </c>
       <c r="X17" s="4" t="n">
-        <v>-2.089714844519804</v>
+        <v>-2.099323661966622</v>
       </c>
       <c r="Y17" s="4" t="n">
-        <v>-2.427884824091926</v>
+        <v>-2.256982619801207</v>
       </c>
       <c r="Z17" s="4" t="n">
-        <v>-1.841914378542405</v>
+        <v>-1.798610366780387</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>X &gt; -0.003793</t>
+          <t>X &gt; -0.003482</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>2181</v>
+        <v>2151</v>
       </c>
       <c r="C18" s="4" t="n">
-        <v>-0.0321317253248381</v>
+        <v>0.09122791770357708</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>-0.7966956647336403</v>
+        <v>-0.6822289158623249</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>-0.9384044328709251</v>
+        <v>-0.7154191942511758</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>-1.217506071164607</v>
+        <v>-1.006426732317124</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>-0.8007230598969244</v>
+        <v>-0.565565884797941</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>-0.6339290010093137</v>
+        <v>-0.4292198204689086</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>-0.6978023584246102</v>
+        <v>-0.4146500639847659</v>
       </c>
       <c r="J18" s="4" t="n">
-        <v>-1.041428389884359</v>
+        <v>-0.8321064158627678</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>-1.110973484504747</v>
+        <v>-1.047657584461945</v>
       </c>
       <c r="L18" s="4" t="n">
-        <v>-1.812707245897236</v>
+        <v>-1.679423319699708</v>
       </c>
       <c r="M18" s="4" t="n">
-        <v>-1.832197853327848</v>
+        <v>-1.751068639605506</v>
       </c>
       <c r="N18" s="4" t="n">
-        <v>-1.902940526669106</v>
+        <v>-1.724599703745966</v>
       </c>
       <c r="O18" s="4" t="n">
-        <v>-2.361493392647041</v>
+        <v>-2.351146711725924</v>
       </c>
       <c r="P18" s="4" t="n">
-        <v>-2.328315023283146</v>
+        <v>-2.34195806525279</v>
       </c>
       <c r="Q18" s="4" t="n">
-        <v>-2.412188048789339</v>
+        <v>-2.349784718205768</v>
       </c>
       <c r="R18" s="4" t="n">
-        <v>-2.339898066589107</v>
+        <v>-2.36410727547586</v>
       </c>
       <c r="S18" s="4" t="n">
-        <v>-2.356243279056706</v>
+        <v>-2.580755715168372</v>
       </c>
       <c r="T18" s="4" t="n">
-        <v>-2.526387106927459</v>
+        <v>-2.826512408360493</v>
       </c>
       <c r="U18" s="4" t="n">
-        <v>-2.51315839524635</v>
+        <v>-2.817791853278656</v>
       </c>
       <c r="V18" s="4" t="n">
-        <v>-2.48337329725895</v>
+        <v>-2.855541736127762</v>
       </c>
       <c r="W18" s="4" t="n">
-        <v>-2.659619098924615</v>
+        <v>-2.932752775563209</v>
       </c>
       <c r="X18" s="4" t="n">
-        <v>-2.342799625295399</v>
+        <v>-2.74946053184636</v>
       </c>
       <c r="Y18" s="4" t="n">
-        <v>-2.821037419631089</v>
+        <v>-2.990625505091316</v>
       </c>
       <c r="Z18" s="4" t="n">
-        <v>-2.091354497422515</v>
+        <v>-2.522254612909713</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>X &gt; -0.002194</t>
+          <t>X &gt; -0.001903</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>1960</v>
+        <v>1934</v>
       </c>
       <c r="C19" s="4" t="n">
-        <v>-0.1595151255409419</v>
+        <v>0.008727385328342052</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>-1.274967677556639</v>
+        <v>-1.078922111871726</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>-1.524754071923887</v>
+        <v>-0.8744297117418469</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>-1.856763731139793</v>
+        <v>-1.439109905455929</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>-1.204551254622807</v>
+        <v>-0.816461942145601</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>-1.09079810029165</v>
+        <v>-0.8362216117302737</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>-1.075710031567418</v>
+        <v>-0.8855742376037483</v>
       </c>
       <c r="J19" s="4" t="n">
-        <v>-1.224315572564024</v>
+        <v>-1.161949161949167</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>-1.35704254170161</v>
+        <v>-1.21067889377747</v>
       </c>
       <c r="L19" s="4" t="n">
-        <v>-1.949559306601898</v>
+        <v>-1.618888680038495</v>
       </c>
       <c r="M19" s="4" t="n">
-        <v>-2.204856941020665</v>
+        <v>-1.831551718459458</v>
       </c>
       <c r="N19" s="4" t="n">
-        <v>-2.049523090634935</v>
+        <v>-1.668555773287004</v>
       </c>
       <c r="O19" s="4" t="n">
-        <v>-2.433592682079819</v>
+        <v>-2.137762455978717</v>
       </c>
       <c r="P19" s="4" t="n">
-        <v>-2.473487572220911</v>
+        <v>-2.099729101752814</v>
       </c>
       <c r="Q19" s="4" t="n">
-        <v>-2.543758688387932</v>
+        <v>-2.083586971308073</v>
       </c>
       <c r="R19" s="4" t="n">
-        <v>-2.47935634946311</v>
+        <v>-2.110599934996586</v>
       </c>
       <c r="S19" s="4" t="n">
-        <v>-2.380826721120009</v>
+        <v>-2.185165507470373</v>
       </c>
       <c r="T19" s="4" t="n">
-        <v>-2.405655828307324</v>
+        <v>-2.288704551896998</v>
       </c>
       <c r="U19" s="4" t="n">
-        <v>-2.517003348104907</v>
+        <v>-2.354304850338337</v>
       </c>
       <c r="V19" s="4" t="n">
-        <v>-2.301132800448912</v>
+        <v>-2.368470365877386</v>
       </c>
       <c r="W19" s="4" t="n">
-        <v>-2.538024358124567</v>
+        <v>-2.493762080267715</v>
       </c>
       <c r="X19" s="4" t="n">
-        <v>-2.278849810140478</v>
+        <v>-2.384579508634467</v>
       </c>
       <c r="Y19" s="4" t="n">
-        <v>-2.688900717271466</v>
+        <v>-2.731603190652727</v>
       </c>
       <c r="Z19" s="4" t="n">
-        <v>-2.429548922372682</v>
+        <v>-2.606003928420122</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>X &gt; -0.0005956</t>
+          <t>X &gt; -0.0003229</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>1747</v>
+        <v>1733</v>
       </c>
       <c r="C20" s="4" t="n">
-        <v>0.1225937467830818</v>
+        <v>0.0226898720034896</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>-1.314242258327653</v>
+        <v>-1.277118038700308</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>-1.136022564212205</v>
+        <v>-1.074067185980176</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>-1.988274984790657</v>
+        <v>-1.864201293085699</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>-1.102205944010962</v>
+        <v>-1.079855814790847</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>-1.110835568635032</v>
+        <v>-0.9487624077688466</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>-0.9996697802380083</v>
+        <v>-0.9110994331722253</v>
       </c>
       <c r="J20" s="4" t="n">
-        <v>-1.473308668076115</v>
+        <v>-1.355975067315278</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>-1.627471132137941</v>
+        <v>-1.425468345718883</v>
       </c>
       <c r="L20" s="4" t="n">
-        <v>-2.141196465124771</v>
+        <v>-2.01779228382879</v>
       </c>
       <c r="M20" s="4" t="n">
-        <v>-2.290633798816948</v>
+        <v>-2.057947064315691</v>
       </c>
       <c r="N20" s="4" t="n">
-        <v>-1.968305573307951</v>
+        <v>-1.671387688499472</v>
       </c>
       <c r="O20" s="4" t="n">
-        <v>-2.432724965476062</v>
+        <v>-2.064938428183922</v>
       </c>
       <c r="P20" s="4" t="n">
-        <v>-2.450410377411735</v>
+        <v>-2.108243363140637</v>
       </c>
       <c r="Q20" s="4" t="n">
-        <v>-2.106297240185313</v>
+        <v>-1.722668240025456</v>
       </c>
       <c r="R20" s="4" t="n">
-        <v>-1.992528019925288</v>
+        <v>-1.703453209295326</v>
       </c>
       <c r="S20" s="4" t="n">
-        <v>-1.979399372236983</v>
+        <v>-1.77434153713299</v>
       </c>
       <c r="T20" s="4" t="n">
-        <v>-1.798688962408818</v>
+        <v>-1.643780802550239</v>
       </c>
       <c r="U20" s="4" t="n">
-        <v>-2.153899808783173</v>
+        <v>-1.857212704144551</v>
       </c>
       <c r="V20" s="4" t="n">
-        <v>-2.105717619603276</v>
+        <v>-1.898003541376688</v>
       </c>
       <c r="W20" s="4" t="n">
-        <v>-2.191120930426436</v>
+        <v>-2.086382598311424</v>
       </c>
       <c r="X20" s="4" t="n">
-        <v>-2.176825586599904</v>
+        <v>-2.276951929268435</v>
       </c>
       <c r="Y20" s="4" t="n">
-        <v>-2.727438240157674</v>
+        <v>-2.725758298000443</v>
       </c>
       <c r="Z20" s="4" t="n">
-        <v>-2.656205698420258</v>
+        <v>-2.830193887789044</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>X &gt; 0.001003</t>
+          <t>X &gt; 0.001257</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>1561</v>
+        <v>1535</v>
       </c>
       <c r="C21" s="4" t="n">
-        <v>-0.2231255944446318</v>
+        <v>-0.3593469853453186</v>
       </c>
       <c r="D21" s="4" t="n">
-        <v>-1.220715742054104</v>
+        <v>-1.278881054161964</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>-1.041019386668289</v>
+        <v>-1.211933396549576</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>-2.226787214878222</v>
+        <v>-2.349547390287469</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>-1.703504204071827</v>
+        <v>-1.881529719636177</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>-1.48177047305461</v>
+        <v>-1.947802785712291</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>-1.265921411840992</v>
+        <v>-1.739781859524804</v>
       </c>
       <c r="J21" s="4" t="n">
-        <v>-1.254379869601848</v>
+        <v>-1.815497164334381</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>-1.431676910635147</v>
+        <v>-1.845914240629632</v>
       </c>
       <c r="L21" s="4" t="n">
-        <v>-1.787118100800988</v>
+        <v>-1.95963687834319</v>
       </c>
       <c r="M21" s="4" t="n">
-        <v>-2.114160438391501</v>
+        <v>-2.169238276320442</v>
       </c>
       <c r="N21" s="4" t="n">
-        <v>-1.465141333357082</v>
+        <v>-1.438643478104652</v>
       </c>
       <c r="O21" s="4" t="n">
-        <v>-1.531800493123015</v>
+        <v>-1.545053364251757</v>
       </c>
       <c r="P21" s="4" t="n">
-        <v>-1.652271162023666</v>
+        <v>-1.561707292654482</v>
       </c>
       <c r="Q21" s="4" t="n">
-        <v>-1.379537276058862</v>
+        <v>-1.492837569889382</v>
       </c>
       <c r="R21" s="4" t="n">
-        <v>-1.386629877045216</v>
+        <v>-1.608105519010927</v>
       </c>
       <c r="S21" s="4" t="n">
-        <v>-1.227655027390554</v>
+        <v>-1.349801007147498</v>
       </c>
       <c r="T21" s="4" t="n">
-        <v>-1.012802636582578</v>
+        <v>-1.185048712877254</v>
       </c>
       <c r="U21" s="4" t="n">
-        <v>-1.308420207064906</v>
+        <v>-1.453304495669272</v>
       </c>
       <c r="V21" s="4" t="n">
-        <v>-1.505206110651869</v>
+        <v>-1.591856266290179</v>
       </c>
       <c r="W21" s="4" t="n">
-        <v>-1.600181946137084</v>
+        <v>-1.731140140635077</v>
       </c>
       <c r="X21" s="4" t="n">
-        <v>-1.830699640213204</v>
+        <v>-2.132035561613165</v>
       </c>
       <c r="Y21" s="4" t="n">
-        <v>-2.607381515369589</v>
+        <v>-2.735306613794073</v>
       </c>
       <c r="Z21" s="4" t="n">
-        <v>-2.582610146862486</v>
+        <v>-3.158031927301778</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>X &gt; 0.002602</t>
+          <t>X &gt; 0.002837</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>1365</v>
+        <v>1345</v>
       </c>
       <c r="C22" s="4" t="n">
-        <v>-0.5589036761585859</v>
+        <v>-0.6488538343377002</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>-1.58084887549731</v>
+        <v>-1.589120074078402</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>-1.237898588989971</v>
+        <v>-0.971327445603329</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>-2.34752721281366</v>
+        <v>-1.964557911503995</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>-1.15715489466325</v>
+        <v>-0.8781240810280053</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>-1.551584057403076</v>
+        <v>-1.489548516262587</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>-1.847369950595755</v>
+        <v>-1.803199545506075</v>
       </c>
       <c r="J22" s="4" t="n">
-        <v>-1.430384888798621</v>
+        <v>-1.331429166480717</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>-1.566687075779356</v>
+        <v>-1.236276360195454</v>
       </c>
       <c r="L22" s="4" t="n">
-        <v>-1.424356828246133</v>
+        <v>-1.032703923567901</v>
       </c>
       <c r="M22" s="4" t="n">
-        <v>-1.692505316601178</v>
+        <v>-1.309185015593663</v>
       </c>
       <c r="N22" s="4" t="n">
-        <v>-0.8354222784939225</v>
+        <v>-0.5104782260401421</v>
       </c>
       <c r="O22" s="4" t="n">
-        <v>-0.3828164290810321</v>
+        <v>-0.3267626212783412</v>
       </c>
       <c r="P22" s="4" t="n">
-        <v>-0.4147125238839635</v>
+        <v>-0.2360064046967807</v>
       </c>
       <c r="Q22" s="4" t="n">
-        <v>-0.7804581606458143</v>
+        <v>-0.430630182470928</v>
       </c>
       <c r="R22" s="4" t="n">
-        <v>-0.9901648059542794</v>
+        <v>-0.6403325512379539</v>
       </c>
       <c r="S22" s="4" t="n">
-        <v>-0.7585848669083646</v>
+        <v>-0.4044276624660199</v>
       </c>
       <c r="T22" s="4" t="n">
-        <v>-0.7172267403201857</v>
+        <v>-0.5679422159430061</v>
       </c>
       <c r="U22" s="4" t="n">
-        <v>-1.232329511442643</v>
+        <v>-0.829590215061117</v>
       </c>
       <c r="V22" s="4" t="n">
-        <v>-1.264781947088657</v>
+        <v>-0.8689388257255359</v>
       </c>
       <c r="W22" s="4" t="n">
-        <v>-1.222532793417251</v>
+        <v>-0.7985026728753795</v>
       </c>
       <c r="X22" s="4" t="n">
-        <v>-1.474951007208098</v>
+        <v>-1.319761849105753</v>
       </c>
       <c r="Y22" s="4" t="n">
-        <v>-2.402197261972191</v>
+        <v>-2.042670114756739</v>
       </c>
       <c r="Z22" s="4" t="n">
-        <v>-2.948910513162851</v>
+        <v>-3.022652975217213</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>X &gt; 0.004201</t>
+          <t>X &gt; 0.004416</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>1162</v>
+        <v>1137</v>
       </c>
       <c r="C23" s="4" t="n">
-        <v>-0.7751499363575434</v>
+        <v>-0.8200683875747359</v>
       </c>
       <c r="D23" s="4" t="n">
-        <v>-1.452099531969978</v>
+        <v>-1.452893425406167</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>-0.5804521994783016</v>
+        <v>-0.4111930336714167</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>-0.9512334216584222</v>
+        <v>-0.6962884433704204</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>0.08166729484477742</v>
+        <v>0.2032959502866589</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>-0.1590825156361149</v>
+        <v>-0.02508773194885805</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>-0.503315202948194</v>
+        <v>-0.3373468365650112</v>
       </c>
       <c r="J23" s="4" t="n">
-        <v>-0.04818413507485531</v>
+        <v>-0.07164815860468821</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>-0.1289956701607764</v>
+        <v>-0.4164933057563971</v>
       </c>
       <c r="L23" s="4" t="n">
-        <v>-0.2525501982184792</v>
+        <v>-0.2924142829976617</v>
       </c>
       <c r="M23" s="4" t="n">
-        <v>-0.1005468138323025</v>
+        <v>-0.2318357939758968</v>
       </c>
       <c r="N23" s="4" t="n">
-        <v>1.216650864707226</v>
+        <v>1.024757040934311</v>
       </c>
       <c r="O23" s="4" t="n">
-        <v>1.520211369231554</v>
+        <v>1.271045258348693</v>
       </c>
       <c r="P23" s="4" t="n">
-        <v>2.125901058264184</v>
+        <v>1.774483105792733</v>
       </c>
       <c r="Q23" s="4" t="n">
-        <v>1.63987480027054</v>
+        <v>1.495359638749619</v>
       </c>
       <c r="R23" s="4" t="n">
-        <v>1.287618004485473</v>
+        <v>1.146915292051922</v>
       </c>
       <c r="S23" s="4" t="n">
-        <v>1.842169025855675</v>
+        <v>1.709255404615831</v>
       </c>
       <c r="T23" s="4" t="n">
-        <v>1.565211282447578</v>
+        <v>1.542006245715591</v>
       </c>
       <c r="U23" s="4" t="n">
-        <v>1.695044143578443</v>
+        <v>1.809839389177618</v>
       </c>
       <c r="V23" s="4" t="n">
-        <v>1.279480314992256</v>
+        <v>1.374902850581528</v>
       </c>
       <c r="W23" s="4" t="n">
-        <v>1.4254023053739</v>
+        <v>1.651955553789065</v>
       </c>
       <c r="X23" s="4" t="n">
-        <v>0.919263744997501</v>
+        <v>1.049088546345658</v>
       </c>
       <c r="Y23" s="4" t="n">
-        <v>-0.2692563790092635</v>
+        <v>-0.2024396772589938</v>
       </c>
       <c r="Z23" s="4" t="n">
-        <v>-1.033556790580214</v>
+        <v>-1.156135399780645</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>X &gt; 0.005799</t>
+          <t>X &gt; 0.005996</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>978</v>
+        <v>970</v>
       </c>
       <c r="C24" s="4" t="n">
-        <v>-1.356583154041104</v>
+        <v>-1.166489215471564</v>
       </c>
       <c r="D24" s="4" t="n">
-        <v>-2.300497008228476</v>
+        <v>-2.472744090130256</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>-1.098922148630038</v>
+        <v>-1.345152691035331</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>-0.5936020563976427</v>
+        <v>-0.9703154628915485</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>0.4919272680093982</v>
+        <v>0.1294211324422321</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>0.272802083548406</v>
+        <v>-0.06319748804641989</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>0.2115132981352019</v>
+        <v>0.11393927582521</v>
       </c>
       <c r="J24" s="4" t="n">
-        <v>0.4996218566836887</v>
+        <v>0.1722197241545373</v>
       </c>
       <c r="K24" s="4" t="n">
-        <v>0.5999342707978101</v>
+        <v>0.2563427995658785</v>
       </c>
       <c r="L24" s="4" t="n">
-        <v>0.3951286034010622</v>
+        <v>-0.0733998479553577</v>
       </c>
       <c r="M24" s="4" t="n">
-        <v>-0.1886587080630306</v>
+        <v>-0.5596439144625265</v>
       </c>
       <c r="N24" s="4" t="n">
-        <v>1.121973818631062</v>
+        <v>0.8577316980505572</v>
       </c>
       <c r="O24" s="4" t="n">
-        <v>1.897875769619056</v>
+        <v>1.542618964507369</v>
       </c>
       <c r="P24" s="4" t="n">
-        <v>2.455000101237125</v>
+        <v>2.175721211948861</v>
       </c>
       <c r="Q24" s="4" t="n">
-        <v>2.001355781161678</v>
+        <v>1.761326392905339</v>
       </c>
       <c r="R24" s="4" t="n">
-        <v>1.470998326826546</v>
+        <v>1.1535681256196</v>
       </c>
       <c r="S24" s="4" t="n">
-        <v>1.848328633611864</v>
+        <v>1.625396111682079</v>
       </c>
       <c r="T24" s="4" t="n">
-        <v>1.743487929790682</v>
+        <v>1.452121038871311</v>
       </c>
       <c r="U24" s="4" t="n">
-        <v>1.857129821962445</v>
+        <v>1.729095715530342</v>
       </c>
       <c r="V24" s="4" t="n">
-        <v>1.634977676920244</v>
+        <v>1.531735713627427</v>
       </c>
       <c r="W24" s="4" t="n">
-        <v>1.91042741897467</v>
+        <v>1.851250134390945</v>
       </c>
       <c r="X24" s="4" t="n">
-        <v>1.323334013802778</v>
+        <v>1.260623694909881</v>
       </c>
       <c r="Y24" s="4" t="n">
-        <v>0.2685653725016053</v>
+        <v>0.2671447781264078</v>
       </c>
       <c r="Z24" s="4" t="n">
-        <v>-0.7275122794946824</v>
+        <v>-0.8228292677094444</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>X &gt; 0.007398</t>
+          <t>X &gt; 0.007576</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>816</v>
+        <v>806</v>
       </c>
       <c r="C25" s="4" t="n">
-        <v>-2.608040309057728</v>
+        <v>-2.99317617866005</v>
       </c>
       <c r="D25" s="4" t="n">
-        <v>-2.456790375937317</v>
+        <v>-2.872782648063556</v>
       </c>
       <c r="E25" s="4" t="n">
-        <v>-1.221662401882028</v>
+        <v>-1.742494169373529</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>-1.327083006986982</v>
+        <v>-1.535262667451846</v>
       </c>
       <c r="G25" s="4" t="n">
-        <v>0.8887668606844557</v>
+        <v>0.8290080738177608</v>
       </c>
       <c r="H25" s="4" t="n">
-        <v>0.3466929495764859</v>
+        <v>0.3193652332863195</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>-0.3037490514463101</v>
+        <v>-0.5296803911922225</v>
       </c>
       <c r="J25" s="4" t="n">
-        <v>0.581961183726591</v>
+        <v>0.3413151014626976</v>
       </c>
       <c r="K25" s="4" t="n">
-        <v>0.8157839838862131</v>
+        <v>0.4165291982843868</v>
       </c>
       <c r="L25" s="4" t="n">
-        <v>1.333234012968404</v>
+        <v>1.047287637889788</v>
       </c>
       <c r="M25" s="4" t="n">
-        <v>1.313508849150402</v>
+        <v>1.021460513083845</v>
       </c>
       <c r="N25" s="4" t="n">
-        <v>1.718251449487809</v>
+        <v>1.434954708103618</v>
       </c>
       <c r="O25" s="4" t="n">
-        <v>2.137047707111797</v>
+        <v>1.878183483088193</v>
       </c>
       <c r="P25" s="4" t="n">
-        <v>3.339157445156282</v>
+        <v>3.068016090775522</v>
       </c>
       <c r="Q25" s="4" t="n">
-        <v>3.048661206399252</v>
+        <v>2.757608920786382</v>
       </c>
       <c r="R25" s="4" t="n">
-        <v>2.295008912655973</v>
+        <v>1.955839829321036</v>
       </c>
       <c r="S25" s="4" t="n">
-        <v>2.528738834502029</v>
+        <v>2.299808726220014</v>
       </c>
       <c r="T25" s="4" t="n">
-        <v>2.178800091465163</v>
+        <v>1.918785663242041</v>
       </c>
       <c r="U25" s="4" t="n">
-        <v>2.517240491997335</v>
+        <v>2.381386848204187</v>
       </c>
       <c r="V25" s="4" t="n">
-        <v>2.213890223533987</v>
+        <v>2.223764856538601</v>
       </c>
       <c r="W25" s="4" t="n">
-        <v>2.406638173215015</v>
+        <v>2.152598270790627</v>
       </c>
       <c r="X25" s="4" t="n">
-        <v>1.84059613337454</v>
+        <v>1.829296791018962</v>
       </c>
       <c r="Y25" s="4" t="n">
-        <v>0.5219335909546317</v>
+        <v>0.5840975293990738</v>
       </c>
       <c r="Z25" s="4" t="n">
-        <v>-0.04409474070001806</v>
+        <v>-0.07431938052313569</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>X &gt; 0.008997</t>
+          <t>X &gt; 0.009156</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>681</v>
+        <v>675</v>
       </c>
       <c r="C26" s="4" t="n">
-        <v>-3.20480060180406</v>
+        <v>-2.811632576063815</v>
       </c>
       <c r="D26" s="4" t="n">
-        <v>-4.120972748991086</v>
+        <v>-3.934732394223822</v>
       </c>
       <c r="E26" s="4" t="n">
-        <v>-2.506666216626719</v>
+        <v>-2.411648718337631</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>-3.074271398860162</v>
+        <v>-3.073404388672401</v>
       </c>
       <c r="G26" s="4" t="n">
-        <v>0.2236590588251204</v>
+        <v>0.2471697666473887</v>
       </c>
       <c r="H26" s="4" t="n">
-        <v>-1.188211964379832</v>
+        <v>-1.355427419143389</v>
       </c>
       <c r="I26" s="4" t="n">
-        <v>-0.9427187878050631</v>
+        <v>-0.8308613375344649</v>
       </c>
       <c r="J26" s="4" t="n">
-        <v>0.4619004096002257</v>
+        <v>0.5613084908239045</v>
       </c>
       <c r="K26" s="4" t="n">
-        <v>0.7333984979361361</v>
+        <v>1.067789702486067</v>
       </c>
       <c r="L26" s="4" t="n">
-        <v>1.067077701770259</v>
+        <v>1.387782563153422</v>
       </c>
       <c r="M26" s="4" t="n">
-        <v>1.281377238071421</v>
+        <v>1.746905722304867</v>
       </c>
       <c r="N26" s="4" t="n">
-        <v>1.967582926110069</v>
+        <v>2.591442010296632</v>
       </c>
       <c r="O26" s="4" t="n">
-        <v>2.252088429014755</v>
+        <v>2.600985053186037</v>
       </c>
       <c r="P26" s="4" t="n">
-        <v>3.14912548523575</v>
+        <v>3.628665959975585</v>
       </c>
       <c r="Q26" s="4" t="n">
-        <v>3.812568090738893</v>
+        <v>4.279844911423858</v>
       </c>
       <c r="R26" s="4" t="n">
-        <v>3.085369109598183</v>
+        <v>3.507815596910191</v>
       </c>
       <c r="S26" s="4" t="n">
-        <v>3.245137728861536</v>
+        <v>3.552083333333336</v>
       </c>
       <c r="T26" s="4" t="n">
-        <v>2.846611268799528</v>
+        <v>3.12290293187543</v>
       </c>
       <c r="U26" s="4" t="n">
-        <v>3.209345527844263</v>
+        <v>3.337365159021203</v>
       </c>
       <c r="V26" s="4" t="n">
-        <v>2.661976947210242</v>
+        <v>2.959359011487599</v>
       </c>
       <c r="W26" s="4" t="n">
-        <v>2.85364516984626</v>
+        <v>3.132655250847606</v>
       </c>
       <c r="X26" s="4" t="n">
-        <v>3.658856477159624</v>
+        <v>3.946381617781213</v>
       </c>
       <c r="Y26" s="4" t="n">
-        <v>2.464902408437574</v>
+        <v>2.70853462157811</v>
       </c>
       <c r="Z26" s="4" t="n">
-        <v>1.654855764612243</v>
+        <v>1.805654886547906</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>X &gt; 0.0106</t>
+          <t>X &gt; 0.01074</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>544</v>
+        <v>540</v>
       </c>
       <c r="C27" s="4" t="n">
-        <v>-5.0069673320112</v>
+        <v>-4.73092654529524</v>
       </c>
       <c r="D27" s="4" t="n">
-        <v>-4.795296042929323</v>
+        <v>-5.342464093979004</v>
       </c>
       <c r="E27" s="4" t="n">
-        <v>-4.229672104710772</v>
+        <v>-4.403373917991246</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>-4.031879311767355</v>
+        <v>-4.081699334349736</v>
       </c>
       <c r="G27" s="4" t="n">
-        <v>-1.271130622201696</v>
+        <v>-1.249396414120007</v>
       </c>
       <c r="H27" s="4" t="n">
-        <v>-2.905658060876625</v>
+        <v>-2.920616373021367</v>
       </c>
       <c r="I27" s="4" t="n">
-        <v>-2.220411844949133</v>
+        <v>-2.253175533334527</v>
       </c>
       <c r="J27" s="4" t="n">
-        <v>-0.8592790274071191</v>
+        <v>-0.8103008103008165</v>
       </c>
       <c r="K27" s="4" t="n">
-        <v>-0.4534931205379564</v>
+        <v>-0.02908023815073335</v>
       </c>
       <c r="L27" s="4" t="n">
-        <v>0.5196324462958088</v>
+        <v>0.7496793837373232</v>
       </c>
       <c r="M27" s="4" t="n">
-        <v>0.9007791859636924</v>
+        <v>1.129229423799345</v>
       </c>
       <c r="N27" s="4" t="n">
-        <v>2.561010971953927</v>
+        <v>2.805376941374163</v>
       </c>
       <c r="O27" s="4" t="n">
-        <v>3.38394562183673</v>
+        <v>3.650433258897571</v>
       </c>
       <c r="P27" s="4" t="n">
-        <v>4.013177052999417</v>
+        <v>4.073110404420028</v>
       </c>
       <c r="Q27" s="4" t="n">
-        <v>5.00944552012475</v>
+        <v>5.057622689201629</v>
       </c>
       <c r="R27" s="4" t="n">
-        <v>4.868538324420683</v>
+        <v>5.063371152465749</v>
       </c>
       <c r="S27" s="4" t="n">
-        <v>6.021385893325558</v>
+        <v>6.255787037037031</v>
       </c>
       <c r="T27" s="4" t="n">
-        <v>5.181251071857318</v>
+        <v>5.196977005949506</v>
       </c>
       <c r="U27" s="4" t="n">
-        <v>5.213318923369876</v>
+        <v>5.226254047910103</v>
       </c>
       <c r="V27" s="4" t="n">
-        <v>4.664870615690845</v>
+        <v>4.70009975222834</v>
       </c>
       <c r="W27" s="4" t="n">
-        <v>4.673795035960119</v>
+        <v>4.873395991588353</v>
       </c>
       <c r="X27" s="4" t="n">
-        <v>4.96559613337454</v>
+        <v>5.168603840003421</v>
       </c>
       <c r="Y27" s="4" t="n">
-        <v>4.320953198797767</v>
+        <v>4.486312399355889</v>
       </c>
       <c r="Z27" s="4" t="n">
-        <v>4.245120945574492</v>
+        <v>4.324173405066425</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>X &gt; 0.01219</t>
+          <t>X &gt; 0.01232</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>424</v>
+        <v>417</v>
       </c>
       <c r="C28" s="4" t="n">
-        <v>-3.875588897469527</v>
+        <v>-4.133643276573956</v>
       </c>
       <c r="D28" s="4" t="n">
-        <v>-4.914591047932021</v>
+        <v>-4.615956731663168</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>-3.066225120437188</v>
+        <v>-2.797364781545291</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>-3.074953787767249</v>
+        <v>-2.680547122197488</v>
       </c>
       <c r="G28" s="4" t="n">
-        <v>-1.063326419938939</v>
+        <v>-1.064852307214075</v>
       </c>
       <c r="H28" s="4" t="n">
-        <v>-3.223778074217144</v>
+        <v>-3.035578275684081</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>-2.117792485807023</v>
+        <v>-1.939407332834058</v>
       </c>
       <c r="J28" s="4" t="n">
-        <v>-0.7528114422971939</v>
+        <v>-0.116668201774587</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>0.4623846598053092</v>
+        <v>1.567510917986489</v>
       </c>
       <c r="L28" s="4" t="n">
-        <v>1.802145040106844</v>
+        <v>2.572632436692473</v>
       </c>
       <c r="M28" s="4" t="n">
-        <v>1.606721114193654</v>
+        <v>2.749855574812244</v>
       </c>
       <c r="N28" s="4" t="n">
-        <v>3.585359172772719</v>
+        <v>4.287116102441182</v>
       </c>
       <c r="O28" s="4" t="n">
-        <v>4.494383565406061</v>
+        <v>5.233979589014574</v>
       </c>
       <c r="P28" s="4" t="n">
-        <v>4.980851858770791</v>
+        <v>5.858348880305989</v>
       </c>
       <c r="Q28" s="4" t="n">
-        <v>5.737802900812873</v>
+        <v>6.615043419284241</v>
       </c>
       <c r="R28" s="4" t="n">
-        <v>6.096340766152096</v>
+        <v>6.93653928462669</v>
       </c>
       <c r="S28" s="4" t="n">
-        <v>7.613367025401033</v>
+        <v>8.511315947242203</v>
       </c>
       <c r="T28" s="4" t="n">
-        <v>6.80097915176853</v>
+        <v>7.659007381648948</v>
       </c>
       <c r="U28" s="4" t="n">
-        <v>7.724417702504176</v>
+        <v>8.592894069226375</v>
       </c>
       <c r="V28" s="4" t="n">
-        <v>7.911263512472203</v>
+        <v>8.807480514285359</v>
       </c>
       <c r="W28" s="4" t="n">
-        <v>7.368717344506173</v>
+        <v>8.240036012904625</v>
       </c>
       <c r="X28" s="4" t="n">
-        <v>7.292871383097072</v>
+        <v>8.404681644426553</v>
       </c>
       <c r="Y28" s="4" t="n">
-        <v>6.859798925767805</v>
+        <v>7.689083515796064</v>
       </c>
       <c r="Z28" s="4" t="n">
-        <v>6.548117615940747</v>
+        <v>7.287136368029373</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>X &gt; 0.01379</t>
+          <t>X &gt; 0.01389</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>330</v>
+        <v>325</v>
       </c>
       <c r="C29" s="4" t="n">
-        <v>-5.000363729746169</v>
+        <v>-4.451717637201504</v>
       </c>
       <c r="D29" s="4" t="n">
-        <v>-2.918222099092965</v>
+        <v>-2.273382048662953</v>
       </c>
       <c r="E29" s="4" t="n">
-        <v>-1.032978308244793</v>
+        <v>-0.4977731202515088</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>-1.745932327687534</v>
+        <v>-1.393205622090022</v>
       </c>
       <c r="G29" s="4" t="n">
-        <v>1.241540039644342</v>
+        <v>1.664569571143971</v>
       </c>
       <c r="H29" s="4" t="n">
-        <v>-1.592641810512056</v>
+        <v>-1.208799853160983</v>
       </c>
       <c r="I29" s="4" t="n">
-        <v>-0.24978686902476</v>
+        <v>0.1173302558184233</v>
       </c>
       <c r="J29" s="4" t="n">
-        <v>1.888920115225176</v>
+        <v>2.236652236652233</v>
       </c>
       <c r="K29" s="4" t="n">
-        <v>3.138866511641396</v>
+        <v>3.576702358457553</v>
       </c>
       <c r="L29" s="4" t="n">
-        <v>3.574410050106415</v>
+        <v>4.179748219782375</v>
       </c>
       <c r="M29" s="4" t="n">
-        <v>2.942125281392215</v>
+        <v>3.725465330909806</v>
       </c>
       <c r="N29" s="4" t="n">
-        <v>4.476064699696479</v>
+        <v>5.470215516365407</v>
       </c>
       <c r="O29" s="4" t="n">
-        <v>5.057562524811438</v>
+        <v>6.082307883258274</v>
       </c>
       <c r="P29" s="4" t="n">
-        <v>5.139513951395145</v>
+        <v>6.340916672226292</v>
       </c>
       <c r="Q29" s="4" t="n">
-        <v>5.996522168966102</v>
+        <v>6.889531521110477</v>
       </c>
       <c r="R29" s="4" t="n">
-        <v>5.984848484848484</v>
+        <v>6.835450924545512</v>
       </c>
       <c r="S29" s="4" t="n">
-        <v>7.366082863022527</v>
+        <v>8.270032051282051</v>
       </c>
       <c r="T29" s="4" t="n">
-        <v>6.65518155314075</v>
+        <v>7.521763330735837</v>
       </c>
       <c r="U29" s="4" t="n">
-        <v>9.295315358307484</v>
+        <v>10.19776401942006</v>
       </c>
       <c r="V29" s="4" t="n">
-        <v>10.08822177433612</v>
+        <v>11.02773507986366</v>
       </c>
       <c r="W29" s="4" t="n">
-        <v>8.93961500030948</v>
+        <v>9.844905963098313</v>
       </c>
       <c r="X29" s="4" t="n">
-        <v>8.560738735870082</v>
+        <v>9.462051133450721</v>
       </c>
       <c r="Y29" s="4" t="n">
-        <v>8.229152842291541</v>
+        <v>9.090301003344486</v>
       </c>
       <c r="Z29" s="4" t="n">
-        <v>9.062411498159157</v>
+        <v>9.851238932131942</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>X &gt; 0.01539</t>
+          <t>X &gt; 0.01547</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="C30" s="4" t="n">
-        <v>-3.450733044990905</v>
+        <v>-2.779267949484641</v>
       </c>
       <c r="D30" s="4" t="n">
-        <v>-0.3634566114015527</v>
+        <v>0.40993971862828</v>
       </c>
       <c r="E30" s="4" t="n">
-        <v>3.521718255917271</v>
+        <v>4.117077677805405</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>3.569220510238786</v>
+        <v>4.288034257623139</v>
       </c>
       <c r="G30" s="4" t="n">
-        <v>5.514798858984285</v>
+        <v>6.30255245340166</v>
       </c>
       <c r="H30" s="4" t="n">
-        <v>1.899483676260367</v>
+        <v>2.642692166269974</v>
       </c>
       <c r="I30" s="4" t="n">
-        <v>3.408903813662789</v>
+        <v>4.137686489915112</v>
       </c>
       <c r="J30" s="4" t="n">
-        <v>4.651604916438238</v>
+        <v>5.359483603758406</v>
       </c>
       <c r="K30" s="4" t="n">
-        <v>4.312863961470818</v>
+        <v>5.105733124129543</v>
       </c>
       <c r="L30" s="4" t="n">
-        <v>6.581773380491356</v>
+        <v>6.981437354101047</v>
       </c>
       <c r="M30" s="4" t="n">
-        <v>5.334920475124761</v>
+        <v>5.726954811453467</v>
       </c>
       <c r="N30" s="4" t="n">
-        <v>8.478224303615931</v>
+        <v>8.885487360798962</v>
       </c>
       <c r="O30" s="4" t="n">
-        <v>7.735290373641938</v>
+        <v>8.152274632661168</v>
       </c>
       <c r="P30" s="4" t="n">
-        <v>7.894439634077472</v>
+        <v>8.543097633027948</v>
       </c>
       <c r="Q30" s="4" t="n">
-        <v>7.99675261026119</v>
+        <v>8.627226776047102</v>
       </c>
       <c r="R30" s="4" t="n">
-        <v>7.830683258439905</v>
+        <v>8.422247269962554</v>
       </c>
       <c r="S30" s="4" t="n">
-        <v>8.837450532108818</v>
+        <v>9.467792145593869</v>
       </c>
       <c r="T30" s="4" t="n">
-        <v>8.352381691405526</v>
+        <v>8.951766277980155</v>
       </c>
       <c r="U30" s="4" t="n">
-        <v>10.84964189362262</v>
+        <v>11.46507907983857</v>
       </c>
       <c r="V30" s="4" t="n">
-        <v>12.17717211423704</v>
+        <v>12.82909081225388</v>
       </c>
       <c r="W30" s="4" t="n">
-        <v>12.01485408315313</v>
+        <v>12.64478807332526</v>
       </c>
       <c r="X30" s="4" t="n">
-        <v>10.41809557421552</v>
+        <v>11.03705850156154</v>
       </c>
       <c r="Y30" s="4" t="n">
-        <v>10.69257028669757</v>
+        <v>11.28069298683992</v>
       </c>
       <c r="Z30" s="4" t="n">
-        <v>11.37719430723855</v>
+        <v>11.88483751745468</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>X &gt; 0.01699</t>
+          <t>X &gt; 0.01705</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>198</v>
+        <v>195</v>
       </c>
       <c r="C31" s="4" t="n">
-        <v>-3.135796608381462</v>
+        <v>-2.773395958879831</v>
       </c>
       <c r="D31" s="4" t="n">
-        <v>0.5698306336727583</v>
+        <v>1.083261307980408</v>
       </c>
       <c r="E31" s="4" t="n">
-        <v>4.182316635146819</v>
+        <v>3.93113130865293</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>4.479463625805096</v>
+        <v>5.390011161126758</v>
       </c>
       <c r="G31" s="4" t="n">
-        <v>6.163875173459843</v>
+        <v>6.652914559488956</v>
       </c>
       <c r="H31" s="4" t="n">
-        <v>3.825588834304689</v>
+        <v>4.758566114204989</v>
       </c>
       <c r="I31" s="4" t="n">
-        <v>5.073842170616366</v>
+        <v>6.014766153254321</v>
       </c>
       <c r="J31" s="4" t="n">
-        <v>6.815832746065311</v>
+        <v>7.248307248307242</v>
       </c>
       <c r="K31" s="4" t="n">
-        <v>5.847218917878998</v>
+        <v>6.350595132350321</v>
       </c>
       <c r="L31" s="4" t="n">
-        <v>9.114707282246556</v>
+        <v>9.657107739695078</v>
       </c>
       <c r="M31" s="4" t="n">
-        <v>5.853413389054936</v>
+        <v>5.826778651735317</v>
       </c>
       <c r="N31" s="4" t="n">
-        <v>9.110017520960483</v>
+        <v>9.139940287007605</v>
       </c>
       <c r="O31" s="4" t="n">
-        <v>8.49190595915487</v>
+        <v>8.537868682377344</v>
       </c>
       <c r="P31" s="4" t="n">
-        <v>9.280928092809276</v>
+        <v>9.31527564658527</v>
       </c>
       <c r="Q31" s="4" t="n">
-        <v>8.622784795228718</v>
+        <v>8.633121264700215</v>
       </c>
       <c r="R31" s="4" t="n">
-        <v>8.712121212121204</v>
+        <v>8.681604770699366</v>
       </c>
       <c r="S31" s="4" t="n">
-        <v>10.59840609534575</v>
+        <v>10.6290064102564</v>
       </c>
       <c r="T31" s="4" t="n">
-        <v>9.988514886474078</v>
+        <v>9.98330179227429</v>
       </c>
       <c r="U31" s="4" t="n">
-        <v>11.71955778254992</v>
+        <v>11.73622555788161</v>
       </c>
       <c r="V31" s="4" t="n">
-        <v>13.92660561271997</v>
+        <v>14.00209405422264</v>
       </c>
       <c r="W31" s="4" t="n">
-        <v>13.38405944475394</v>
+        <v>13.4346495528419</v>
       </c>
       <c r="X31" s="4" t="n">
-        <v>12.80316297829433</v>
+        <v>12.84666651806611</v>
       </c>
       <c r="Y31" s="4" t="n">
-        <v>11.56248617562487</v>
+        <v>11.55183946488295</v>
       </c>
       <c r="Z31" s="4" t="n">
-        <v>11.48665392240159</v>
+        <v>11.38970047059349</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>X &gt; 0.01859</t>
+          <t>X &gt; 0.01863</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="C32" s="4" t="n">
-        <v>-1.382782597302935</v>
+        <v>-1.594574780058657</v>
       </c>
       <c r="D32" s="4" t="n">
-        <v>-1.072398105330166</v>
+        <v>-0.5417803170612245</v>
       </c>
       <c r="E32" s="4" t="n">
-        <v>5.231518329509804</v>
+        <v>5.995733373254986</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>6.454048181034814</v>
+        <v>6.702032473148066</v>
       </c>
       <c r="G32" s="4" t="n">
-        <v>6.11825770848754</v>
+        <v>7.075824982399382</v>
       </c>
       <c r="H32" s="4" t="n">
-        <v>3.724578733294592</v>
+        <v>4.635355990994874</v>
       </c>
       <c r="I32" s="4" t="n">
-        <v>3.597791339726818</v>
+        <v>4.489624628112793</v>
       </c>
       <c r="J32" s="4" t="n">
-        <v>6.545386346586646</v>
+        <v>7.431457431457432</v>
       </c>
       <c r="K32" s="4" t="n">
-        <v>4.651389657533613</v>
+        <v>5.611334393089585</v>
       </c>
       <c r="L32" s="4" t="n">
-        <v>8.394603013755187</v>
+        <v>9.360737443324794</v>
       </c>
       <c r="M32" s="4" t="n">
-        <v>3.507372333336463</v>
+        <v>4.438167263123937</v>
       </c>
       <c r="N32" s="4" t="n">
-        <v>7.744751962146537</v>
+        <v>8.70703985410718</v>
       </c>
       <c r="O32" s="4" t="n">
-        <v>7.266751185612996</v>
+        <v>8.241498386007059</v>
       </c>
       <c r="P32" s="4" t="n">
-        <v>8.98115618013415</v>
+        <v>9.941316272625905</v>
       </c>
       <c r="Q32" s="4" t="n">
-        <v>7.677851592231001</v>
+        <v>8.609811241390183</v>
       </c>
       <c r="R32" s="4" t="n">
-        <v>7.62707722385143</v>
+        <v>8.521764610859208</v>
       </c>
       <c r="S32" s="4" t="n">
-        <v>10.07380524816426</v>
+        <v>11.01528679653679</v>
       </c>
       <c r="T32" s="4" t="n">
-        <v>10.61412583466567</v>
+        <v>11.53175334072584</v>
       </c>
       <c r="U32" s="4" t="n">
-        <v>11.47517850591257</v>
+        <v>12.39556621722227</v>
       </c>
       <c r="V32" s="4" t="n">
-        <v>13.59750818684834</v>
+        <v>14.55820461033319</v>
       </c>
       <c r="W32" s="4" t="n">
-        <v>14.99044588985006</v>
+        <v>15.93881205700441</v>
       </c>
       <c r="X32" s="4" t="n">
-        <v>14.91459992844096</v>
+        <v>15.86364953504913</v>
       </c>
       <c r="Y32" s="4" t="n">
-        <v>13.25359076995527</v>
+        <v>14.15923207227555</v>
       </c>
       <c r="Z32" s="4" t="n">
-        <v>11.88743593608684</v>
+        <v>12.69839177928478</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>X &gt; 0.02019</t>
+          <t>X &gt; 0.02021</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="C33" s="4" t="n">
-        <v>-2.401177691944369</v>
+        <v>-2.709293394777269</v>
       </c>
       <c r="D33" s="4" t="n">
-        <v>-1.909508209302437</v>
+        <v>-2.121866897147797</v>
       </c>
       <c r="E33" s="4" t="n">
-        <v>3.264042989600455</v>
+        <v>3.290105667627287</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>3.377535251149446</v>
+        <v>3.531036802152393</v>
       </c>
       <c r="G33" s="4" t="n">
-        <v>6.347529902569114</v>
+        <v>6.588811995386394</v>
       </c>
       <c r="H33" s="4" t="n">
-        <v>2.40226468370782</v>
+        <v>2.579078934717813</v>
       </c>
       <c r="I33" s="4" t="n">
-        <v>4.936101123784411</v>
+        <v>5.11733025581843</v>
       </c>
       <c r="J33" s="4" t="n">
-        <v>7.137228522006538</v>
+        <v>7.312409812409811</v>
       </c>
       <c r="K33" s="4" t="n">
-        <v>3.872930579954293</v>
+        <v>4.107005388760577</v>
       </c>
       <c r="L33" s="4" t="n">
-        <v>8.885138870859961</v>
+        <v>9.144287226874567</v>
       </c>
       <c r="M33" s="4" t="n">
-        <v>5.026967108063204</v>
+        <v>5.249855574812244</v>
       </c>
       <c r="N33" s="4" t="n">
-        <v>7.227556547590424</v>
+        <v>7.473273620340947</v>
       </c>
       <c r="O33" s="4" t="n">
-        <v>7.75728704271777</v>
+        <v>8.025048169556833</v>
       </c>
       <c r="P33" s="4" t="n">
-        <v>9.189100728254658</v>
+        <v>9.443480774790395</v>
       </c>
       <c r="Q33" s="4" t="n">
-        <v>8.5309574306741</v>
+        <v>8.761326392905339</v>
       </c>
       <c r="R33" s="4" t="n">
-        <v>7.472451790633613</v>
+        <v>7.65596374505833</v>
       </c>
       <c r="S33" s="4" t="n">
-        <v>8.991427215639618</v>
+        <v>9.218749999999993</v>
       </c>
       <c r="T33" s="4" t="n">
-        <v>9.713032792810168</v>
+        <v>9.919199228171735</v>
       </c>
       <c r="U33" s="4" t="n">
-        <v>11.58181673571796</v>
+        <v>11.80032812198418</v>
       </c>
       <c r="V33" s="4" t="n">
-        <v>13.42155510766946</v>
+        <v>13.68158123370982</v>
       </c>
       <c r="W33" s="4" t="n">
-        <v>14.5319015016869</v>
+        <v>14.78080339899576</v>
       </c>
       <c r="X33" s="4" t="n">
-        <v>15.28250182126954</v>
+        <v>15.5389742103738</v>
       </c>
       <c r="Y33" s="4" t="n">
-        <v>14.73053025275985</v>
+        <v>14.94927536231885</v>
       </c>
       <c r="Z33" s="4" t="n">
-        <v>11.34891287556963</v>
+        <v>11.45380303469606</v>
       </c>
     </row>
     <row r="34">
@@ -5483,158 +5483,158 @@
         <v>89</v>
       </c>
       <c r="C34" s="4" t="n">
-        <v>-1.955453855004997</v>
+        <v>-1.857233469683628</v>
       </c>
       <c r="D34" s="4" t="n">
-        <v>-2.290230653354811</v>
+        <v>-2.103140305387498</v>
       </c>
       <c r="E34" s="4" t="n">
-        <v>3.013323331322056</v>
+        <v>3.38373862642878</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>4.547560323115277</v>
+        <v>5.038527438856519</v>
       </c>
       <c r="G34" s="4" t="n">
-        <v>8.706151873039914</v>
+        <v>9.257351321229095</v>
       </c>
       <c r="H34" s="4" t="n">
-        <v>5.522331542283354</v>
+        <v>6.043498410373239</v>
       </c>
       <c r="I34" s="4" t="n">
-        <v>9.244764880864913</v>
+        <v>9.742798420612431</v>
       </c>
       <c r="J34" s="4" t="n">
-        <v>13.46093545858375</v>
+        <v>13.93225999967572</v>
       </c>
       <c r="K34" s="4" t="n">
-        <v>11.2552316292625</v>
+        <v>11.81299789812388</v>
       </c>
       <c r="L34" s="4" t="n">
-        <v>17.22388898693387</v>
+        <v>17.7585194366124</v>
       </c>
       <c r="M34" s="4" t="n">
-        <v>11.87997110100591</v>
+        <v>12.41277692312686</v>
       </c>
       <c r="N34" s="4" t="n">
-        <v>16.09560372002983</v>
+        <v>16.63057699112747</v>
       </c>
       <c r="O34" s="4" t="n">
-        <v>14.97244165317371</v>
+        <v>15.5156848736767</v>
       </c>
       <c r="P34" s="4" t="n">
-        <v>15.87495828234509</v>
+        <v>16.39104631786156</v>
       </c>
       <c r="Q34" s="4" t="n">
-        <v>16.3404104903825</v>
+        <v>16.83248744159447</v>
       </c>
       <c r="R34" s="4" t="n">
-        <v>15.81120190670752</v>
+        <v>16.27019595479616</v>
       </c>
       <c r="S34" s="4" t="n">
-        <v>14.55368926411208</v>
+        <v>15.04272003745319</v>
       </c>
       <c r="T34" s="4" t="n">
-        <v>15.57244406590887</v>
+        <v>16.03343143790956</v>
       </c>
       <c r="U34" s="4" t="n">
-        <v>15.78833544683319</v>
+        <v>16.24789366505533</v>
       </c>
       <c r="V34" s="4" t="n">
-        <v>17.09877676241919</v>
+        <v>17.58607561573228</v>
       </c>
       <c r="W34" s="4" t="n">
-        <v>16.55623059445316</v>
+        <v>17.01863111435155</v>
       </c>
       <c r="X34" s="4" t="n">
-        <v>18.72757564428003</v>
+        <v>19.19065960363223</v>
       </c>
       <c r="Y34" s="4" t="n">
-        <v>17.8784548511441</v>
+        <v>18.31069858329263</v>
       </c>
       <c r="Z34" s="4" t="n">
-        <v>16.67902709230284</v>
+        <v>17.02496408338518</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>X &gt; 0.02339</t>
+          <t>X &gt; 0.02337</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C35" s="4" t="n">
-        <v>-4.365484794591382</v>
+        <v>-3.542626728110598</v>
       </c>
       <c r="D35" s="4" t="n">
-        <v>-4.700261592941196</v>
+        <v>-3.788533563814468</v>
       </c>
       <c r="E35" s="4" t="n">
-        <v>2.557371531940852</v>
+        <v>3.528200905722528</v>
       </c>
       <c r="F35" s="4" t="n">
-        <v>3.293692874816948</v>
+        <v>4.364370135485728</v>
       </c>
       <c r="G35" s="4" t="n">
-        <v>8.755003851545041</v>
+        <v>9.803097709672102</v>
       </c>
       <c r="H35" s="4" t="n">
-        <v>6.043419313004733</v>
+        <v>5.674317029955908</v>
       </c>
       <c r="I35" s="4" t="n">
-        <v>8.17002135375207</v>
+        <v>7.736377874866051</v>
       </c>
       <c r="J35" s="4" t="n">
-        <v>12.23963599595551</v>
+        <v>11.71717171717171</v>
       </c>
       <c r="K35" s="4" t="n">
-        <v>12.28112317787021</v>
+        <v>11.84510062685582</v>
       </c>
       <c r="L35" s="4" t="n">
-        <v>18.75458431342793</v>
+        <v>18.19190627449362</v>
       </c>
       <c r="M35" s="4" t="n">
-        <v>11.78226714399565</v>
+        <v>11.32128414624081</v>
       </c>
       <c r="N35" s="4" t="n">
-        <v>17.30061918982302</v>
+        <v>16.75898790605524</v>
       </c>
       <c r="O35" s="4" t="n">
-        <v>17.62673248528574</v>
+        <v>17.07266721717588</v>
       </c>
       <c r="P35" s="4" t="n">
-        <v>21.75347969579568</v>
+        <v>21.11014744145707</v>
       </c>
       <c r="Q35" s="4" t="n">
-        <v>22.54461176053395</v>
+        <v>21.85656448814344</v>
       </c>
       <c r="R35" s="4" t="n">
-        <v>21.68972332015811</v>
+        <v>20.98929707839167</v>
       </c>
       <c r="S35" s="4" t="n">
-        <v>20.10653082086179</v>
+        <v>19.45684523809523</v>
       </c>
       <c r="T35" s="4" t="n">
-        <v>21.45096547935945</v>
+        <v>20.75253256150506</v>
       </c>
       <c r="U35" s="4" t="n">
-        <v>21.66685686028378</v>
+        <v>20.96699478865084</v>
       </c>
       <c r="V35" s="4" t="n">
-        <v>23.30297803257064</v>
+        <v>22.61015266228125</v>
       </c>
       <c r="W35" s="4" t="n">
-        <v>22.76043186460461</v>
+        <v>22.04270816090052</v>
       </c>
       <c r="X35" s="4" t="n">
-        <v>25.58313662783319</v>
+        <v>24.82468849608809</v>
       </c>
       <c r="Y35" s="4" t="n">
-        <v>24.4083359779964</v>
+        <v>23.63975155279504</v>
       </c>
       <c r="Z35" s="4" t="n">
-        <v>22.88322836245428</v>
+        <v>22.04904112993415</v>
       </c>
     </row>
   </sheetData>
@@ -5824,2297 +5824,2297 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>X &lt; -0.02298</t>
+          <t>X &lt; -0.02244</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>-5.814760156910225</v>
+        <v>-4.971198156682028</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>-6.149536955260039</v>
+        <v>-8.074247849528753</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>-7.587556004291031</v>
+        <v>-10.75751337999176</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>-6.851234661414928</v>
+        <v>-12.77848700737142</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>-2.839199047005678</v>
+        <v>-7.339759433185037</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>3.144868588367054</v>
+        <v>-1.468540112901238</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>3.822195266795553</v>
+        <v>-0.8350506965625257</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>0.6454330974047906</v>
+        <v>-2.568542568542576</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>-0.7623550829993491</v>
+        <v>-5.297756516001328</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>-2.984546121354676</v>
+        <v>-8.95095086836352</v>
       </c>
       <c r="M6" s="4" t="n">
-        <v>-5.609037203830439</v>
+        <v>-8.678715853759186</v>
       </c>
       <c r="N6" s="4" t="n">
-        <v>-2.989235882640749</v>
+        <v>-6.098154951087629</v>
       </c>
       <c r="O6" s="4" t="n">
-        <v>-4.112397949496867</v>
+        <v>-7.213047068538401</v>
       </c>
       <c r="P6" s="4" t="n">
-        <v>-4.333476825943457</v>
+        <v>-6.032709701400073</v>
       </c>
       <c r="Q6" s="4" t="n">
-        <v>-6.440895485842852</v>
+        <v>-8.143435511856566</v>
       </c>
       <c r="R6" s="4" t="n">
-        <v>-7.295783926218711</v>
+        <v>-9.010702921608328</v>
       </c>
       <c r="S6" s="4" t="n">
-        <v>-11.7775271501527</v>
+        <v>-13.40029761904762</v>
       </c>
       <c r="T6" s="4" t="n">
-        <v>-13.33164321629273</v>
+        <v>-14.96175315278065</v>
       </c>
       <c r="U6" s="4" t="n">
-        <v>-11.66647647304956</v>
+        <v>-14.74729092563488</v>
       </c>
       <c r="V6" s="4" t="n">
-        <v>-5.682529213806163</v>
+        <v>-7.389847337718756</v>
       </c>
       <c r="W6" s="4" t="n">
-        <v>-3.32652465713452</v>
+        <v>-5.100148981956629</v>
       </c>
       <c r="X6" s="4" t="n">
-        <v>-1.953095256224778</v>
+        <v>-3.746740075340483</v>
       </c>
       <c r="Y6" s="4" t="n">
-        <v>-1.678620543742724</v>
+        <v>-2.074534161490682</v>
       </c>
       <c r="Z6" s="4" t="n">
-        <v>-1.754452796966</v>
+        <v>-0.8081017272087081</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>X &lt; -0.02138</t>
+          <t>X &lt; -0.02086</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>-5.405552995784909</v>
+        <v>-4.117339371788759</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>-5.740329794134723</v>
+        <v>-5.512671494848952</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>-6.001878254930418</v>
+        <v>-6.767365596740532</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>-6.714832274373158</v>
+        <v>-8.509193082905078</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>-4.697681570449838</v>
+        <v>-5.336475360935438</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>-0.9813036196465816</v>
+        <v>-1.731265892868393</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>-0.5767817153016424</v>
+        <v>-0.2274973303884735</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>-0.8549931600547183</v>
+        <v>-2.831268348509731</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>-3.166447154610601</v>
+        <v>-5.002190013538268</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>-5.115833418882382</v>
+        <v>-5.798241508757606</v>
       </c>
       <c r="M7" s="4" t="n">
-        <v>-4.841773776720458</v>
+        <v>-7.824857068865917</v>
       </c>
       <c r="N7" s="4" t="n">
-        <v>-5.120523180168455</v>
+        <v>-8.101439023337214</v>
       </c>
       <c r="O7" s="4" t="n">
-        <v>-6.243685247024573</v>
+        <v>-9.216331140787986</v>
       </c>
       <c r="P7" s="4" t="n">
-        <v>-5.288293535235873</v>
+        <v>-8.315139914864766</v>
       </c>
       <c r="Q7" s="4" t="n">
-        <v>-7.122907421051721</v>
+        <v>-10.14671958410615</v>
       </c>
       <c r="R7" s="4" t="n">
-        <v>-7.70499108734402</v>
+        <v>-10.73484085264281</v>
       </c>
       <c r="S7" s="4" t="n">
-        <v>-13.72126116549797</v>
+        <v>-16.58584770114943</v>
       </c>
       <c r="T7" s="4" t="n">
-        <v>-12.64963128108386</v>
+        <v>-15.5693065189547</v>
       </c>
       <c r="U7" s="4" t="n">
-        <v>-8.904328135453653</v>
+        <v>-11.90656842973997</v>
       </c>
       <c r="V7" s="4" t="n">
-        <v>-4.011599972544445</v>
+        <v>-7.094280835255695</v>
       </c>
       <c r="W7" s="4" t="n">
-        <v>-2.201204964039896</v>
+        <v>-6.512300049280107</v>
       </c>
       <c r="X7" s="4" t="n">
-        <v>-1.100580337213692</v>
+        <v>-5.438037283879069</v>
       </c>
       <c r="Y7" s="4" t="n">
-        <v>-0.826105624731639</v>
+        <v>-4.044977511244376</v>
       </c>
       <c r="Z7" s="4" t="n">
-        <v>-0.9019378779549143</v>
+        <v>-3.057691218177517</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>X &lt; -0.01978</t>
+          <t>X &lt; -0.01928</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>-4.533704256289113</v>
+        <v>-4.846974554197551</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>-2.18990962606749</v>
+        <v>-4.223316172510117</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>-5.413642960812773</v>
+        <v>-8.086705926575611</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>-5.233739837398375</v>
+        <v>-8.679108125383834</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>-4.676673167088495</v>
+        <v>-7.21553583070056</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>-2.703992695276838</v>
+        <v>-6.189037007311171</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>-0.7973699505957583</v>
+        <v>-5.24498858476128</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>-4.647009966777404</v>
+        <v>-8.158604680343814</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>-6.391237070576992</v>
+        <v>-9.769806205442315</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>-7.164152746613482</v>
+        <v>-9.696292483270348</v>
       </c>
       <c r="M8" s="4" t="n">
-        <v>-8.675807390165843</v>
+        <v>-12.03275312083993</v>
       </c>
       <c r="N8" s="4" t="n">
-        <v>-8.061699650756694</v>
+        <v>-11.43976985791992</v>
       </c>
       <c r="O8" s="4" t="n">
-        <v>-9.184861717612812</v>
+        <v>-11.68509675797939</v>
       </c>
       <c r="P8" s="4" t="n">
-        <v>-8.513083451202263</v>
+        <v>-11.06376560202119</v>
       </c>
       <c r="Q8" s="4" t="n">
-        <v>-9.171226748782821</v>
+        <v>-11.74591998390625</v>
       </c>
       <c r="R8" s="4" t="n">
-        <v>-9.469696969696969</v>
+        <v>-12.05418118247789</v>
       </c>
       <c r="S8" s="4" t="n">
-        <v>-14.06789982096016</v>
+        <v>-16.50588768115942</v>
       </c>
       <c r="T8" s="4" t="n">
-        <v>-13.27988338192419</v>
+        <v>-15.76920656892972</v>
       </c>
       <c r="U8" s="4" t="n">
-        <v>-9.492563429571298</v>
+        <v>-12.07648347221873</v>
       </c>
       <c r="V8" s="4" t="n">
-        <v>-7.52000333388898</v>
+        <v>-10.99233180976844</v>
       </c>
       <c r="W8" s="4" t="n">
-        <v>-7.169692358997871</v>
+        <v>-10.69021109375787</v>
       </c>
       <c r="X8" s="4" t="n">
-        <v>-7.245538320406972</v>
+        <v>-9.895808398321847</v>
       </c>
       <c r="Y8" s="4" t="n">
-        <v>-6.07820646506778</v>
+        <v>-8.782608695652172</v>
       </c>
       <c r="Z8" s="4" t="n">
-        <v>-5.261181575433916</v>
+        <v>-7.205617255159027</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>X &lt; -0.01818</t>
+          <t>X &lt; -0.0177</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>137</v>
+        <v>147</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>-2.545956602483059</v>
+        <v>-1.161674347158211</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>0.03897462836420118</v>
+        <v>0.6332351436685286</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>-1.39904442066679</v>
+        <v>-3.342547393597201</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>-4.301779462007332</v>
+        <v>-3.934949592405424</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>-5.367496941853879</v>
+        <v>-4.890779841348298</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>-4.450603748457226</v>
+        <v>-4.053574126506675</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>-3.762698417749043</v>
+        <v>-4.168384029895854</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>-6.960617891699194</v>
+        <v>-8.554937126365708</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>-9.108911731682305</v>
+        <v>-10.46782454321221</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>-10.61175441501807</v>
+        <v>-11.26387603843155</v>
       </c>
       <c r="M9" s="4" t="n">
-        <v>-11.06762178015541</v>
+        <v>-10.31136891498367</v>
       </c>
       <c r="N9" s="4" t="n">
-        <v>-10.61644417630414</v>
+        <v>-8.547134542924361</v>
       </c>
       <c r="O9" s="4" t="n">
-        <v>-9.549825221262445</v>
+        <v>-6.940938225000977</v>
       </c>
       <c r="P9" s="4" t="n">
-        <v>-7.58112307581122</v>
+        <v>-5.828628068747015</v>
       </c>
       <c r="Q9" s="4" t="n">
-        <v>-8.969193380691053</v>
+        <v>-7.191054559475603</v>
       </c>
       <c r="R9" s="4" t="n">
-        <v>-8.374806458748061</v>
+        <v>-7.31002264949948</v>
       </c>
       <c r="S9" s="4" t="n">
-        <v>-12.15835863222189</v>
+        <v>-11.49553571428572</v>
       </c>
       <c r="T9" s="4" t="n">
-        <v>-12.26319933604307</v>
+        <v>-11.62841981944732</v>
       </c>
       <c r="U9" s="4" t="n">
-        <v>-9.857526933220932</v>
+        <v>-9.373141265770933</v>
       </c>
       <c r="V9" s="4" t="n">
-        <v>-8.940754115953631</v>
+        <v>-9.158554820711949</v>
       </c>
       <c r="W9" s="4" t="n">
-        <v>-8.753373276620394</v>
+        <v>-9.725999322092683</v>
       </c>
       <c r="X9" s="4" t="n">
-        <v>-8.099292230730221</v>
+        <v>-8.44061762636089</v>
       </c>
       <c r="Y9" s="4" t="n">
-        <v>-8.554744525547441</v>
+        <v>-8.196983141082512</v>
       </c>
       <c r="Z9" s="4" t="n">
-        <v>-8.630576778770717</v>
+        <v>-7.678850026528437</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>X &lt; -0.01658</t>
+          <t>X &lt; -0.01612</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>189</v>
+        <v>200</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>-4.96359843618329</v>
+        <v>-4.042626728110598</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>-0.00736994352781295</v>
+        <v>0.711466436185539</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>-3.032690579860386</v>
+        <v>-4.043227665706048</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>-3.216544070202609</v>
+        <v>-5.635629864514272</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>-4.0814350718504</v>
+        <v>-4.911188004613606</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>-1.778066769350907</v>
+        <v>-4.254254398615522</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>-3.07911598234179</v>
+        <v>-4.549336410848241</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>-4.944629014396448</v>
+        <v>-6.35425685425686</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>-8.606845536185453</v>
+        <v>-10.22632794457275</v>
       </c>
       <c r="L10" s="4" t="n">
-        <v>-6.734258566719298</v>
+        <v>-9.52237943979209</v>
       </c>
       <c r="M10" s="4" t="n">
-        <v>-5.93109839545685</v>
+        <v>-9.250144425187756</v>
       </c>
       <c r="N10" s="4" t="n">
-        <v>-4.62254621160325</v>
+        <v>-7.526726379659053</v>
       </c>
       <c r="O10" s="4" t="n">
-        <v>-2.571105103856198</v>
+        <v>-5.141618497109825</v>
       </c>
       <c r="P10" s="4" t="n">
-        <v>-2.792183980302788</v>
+        <v>-4.889852558542934</v>
       </c>
       <c r="Q10" s="4" t="n">
-        <v>-2.921226748782821</v>
+        <v>-5.57200694042799</v>
       </c>
       <c r="R10" s="4" t="n">
-        <v>-3.914141414141412</v>
+        <v>-6.010702921608328</v>
       </c>
       <c r="S10" s="4" t="n">
-        <v>-7.222661725722055</v>
+        <v>-9.114583333333336</v>
       </c>
       <c r="T10" s="4" t="n">
-        <v>-6.269301371342181</v>
+        <v>-7.247467438494937</v>
       </c>
       <c r="U10" s="4" t="n">
-        <v>-4.995208932216798</v>
+        <v>-5.033005211349163</v>
       </c>
       <c r="V10" s="4" t="n">
-        <v>-5.337463651349303</v>
+        <v>-5.818418766290179</v>
       </c>
       <c r="W10" s="4" t="n">
-        <v>-5.880009819315333</v>
+        <v>-5.385863267670914</v>
       </c>
       <c r="X10" s="4" t="n">
-        <v>-5.955855780724434</v>
+        <v>-4.961025789626191</v>
       </c>
       <c r="Y10" s="4" t="n">
-        <v>-6.210481597342906</v>
+        <v>-4.717391304347814</v>
       </c>
       <c r="Z10" s="4" t="n">
-        <v>-6.81541437966672</v>
+        <v>-4.379530298637277</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>X &lt; -0.01498</t>
+          <t>X &lt; -0.01454</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>248</v>
+        <v>270</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>-5.656976145690031</v>
+        <v>-4.653737839221712</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>-1.959494879523717</v>
+        <v>-0.8255706008514991</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>-4.203965541457933</v>
+        <v>-5.413598036076422</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>-3.707242141545841</v>
+        <v>-6.006000234884645</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>-4.446258420544723</v>
+        <v>-5.170447263872866</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>-3.452840621544119</v>
+        <v>-5.383884028245156</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>-3.418337692531246</v>
+        <v>-5.808595670107501</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>-7.325581395348834</v>
+        <v>-9.076479076479082</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>-9.703449052143803</v>
+        <v>-10.43003164827645</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>-6.847332470115781</v>
+        <v>-8.633490550903204</v>
       </c>
       <c r="M11" s="4" t="n">
-        <v>-5.766821215050633</v>
+        <v>-7.250144425187756</v>
       </c>
       <c r="N11" s="4" t="n">
-        <v>-4.029441586240566</v>
+        <v>-5.674874527807205</v>
       </c>
       <c r="O11" s="4" t="n">
-        <v>-2.733248814386997</v>
+        <v>-4.197174052665382</v>
       </c>
       <c r="P11" s="4" t="n">
-        <v>-0.93819865857553</v>
+        <v>-1.852815521505896</v>
       </c>
       <c r="Q11" s="4" t="n">
-        <v>-1.193116149704473</v>
+        <v>-2.534969903390952</v>
       </c>
       <c r="R11" s="4" t="n">
-        <v>-1.405180840664705</v>
+        <v>-3.084776995682404</v>
       </c>
       <c r="S11" s="4" t="n">
-        <v>-5.168130235706705</v>
+        <v>-6.151620370370367</v>
       </c>
       <c r="T11" s="4" t="n">
-        <v>-3.660067713721439</v>
+        <v>-4.43265262368012</v>
       </c>
       <c r="U11" s="4" t="n">
-        <v>-3.040950526345483</v>
+        <v>-3.107079285423239</v>
       </c>
       <c r="V11" s="4" t="n">
-        <v>-4.870233748635535</v>
+        <v>-4.744344692216103</v>
       </c>
       <c r="W11" s="4" t="n">
-        <v>-5.412779916601565</v>
+        <v>-5.311789193596837</v>
       </c>
       <c r="X11" s="4" t="n">
-        <v>-6.29507749091389</v>
+        <v>-5.757322085922489</v>
       </c>
       <c r="Y11" s="4" t="n">
-        <v>-6.020602778431837</v>
+        <v>-5.143317230273745</v>
       </c>
       <c r="Z11" s="4" t="n">
-        <v>-6.499660838106728</v>
+        <v>-4.564715483822468</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>X &lt; -0.01339</t>
+          <t>X &lt; -0.01296</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>335</v>
+        <v>357</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>-3.790100844775253</v>
+        <v>-5.083242974609199</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>-2.333832867005661</v>
+        <v>-3.088253451769653</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>-3.47334445335008</v>
+        <v>-4.342947553661233</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>-4.484805935479393</v>
+        <v>-5.495573842105308</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>-3.626566557280398</v>
+        <v>-5.210907892568791</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>-3.439600371183019</v>
+        <v>-3.653414062481062</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>-3.017519204327101</v>
+        <v>-3.328047895442076</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>-4.191253037139873</v>
+        <v>-3.913080383668621</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>-4.746780780598314</v>
+        <v>-4.625487608438291</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>-3.13163675514226</v>
+        <v>-3.460754789932146</v>
       </c>
       <c r="M12" s="4" t="n">
-        <v>-1.962054724920641</v>
+        <v>-2.62829568569196</v>
       </c>
       <c r="N12" s="4" t="n">
-        <v>-1.643789202995492</v>
+        <v>-2.064541505709471</v>
       </c>
       <c r="O12" s="4" t="n">
-        <v>-0.6773990310456455</v>
+        <v>-1.21864930943476</v>
       </c>
       <c r="P12" s="4" t="n">
-        <v>1.191074331313736</v>
+        <v>0.7740129876755546</v>
       </c>
       <c r="Q12" s="4" t="n">
-        <v>0.5329310337331776</v>
+        <v>0.09185860579049887</v>
       </c>
       <c r="R12" s="4" t="n">
-        <v>0.2317955676164587</v>
+        <v>-0.1871735098436176</v>
       </c>
       <c r="S12" s="4" t="n">
-        <v>-2.58868873354011</v>
+        <v>-2.812062324929975</v>
       </c>
       <c r="T12" s="4" t="n">
-        <v>-2.395021974674727</v>
+        <v>-2.104610295637798</v>
       </c>
       <c r="U12" s="4" t="n">
-        <v>-1.283608205690697</v>
+        <v>-0.4895878444023793</v>
       </c>
       <c r="V12" s="4" t="n">
-        <v>-2.589299709155512</v>
+        <v>-0.8352254889792476</v>
       </c>
       <c r="W12" s="4" t="n">
-        <v>-3.131845877121542</v>
+        <v>-1.402669990359982</v>
       </c>
       <c r="X12" s="4" t="n">
-        <v>-3.804706763903773</v>
+        <v>-1.197720467497341</v>
       </c>
       <c r="Y12" s="4" t="n">
-        <v>-3.53023205142172</v>
+        <v>-0.9540859822189631</v>
       </c>
       <c r="Z12" s="4" t="n">
-        <v>-3.307556841958423</v>
+        <v>-0.8361129316905007</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>X &lt; -0.01179</t>
+          <t>X &lt; -0.01138</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>434</v>
+        <v>459</v>
       </c>
       <c r="C13" s="4" t="n">
-        <v>-3.41043236688818</v>
+        <v>-3.869424113731512</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>-1.441061699800223</v>
+        <v>-1.500951864468057</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>-1.727007016112317</v>
+        <v>-2.319916118865095</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>-1.979131542467492</v>
+        <v>-2.25872354643149</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>0.2196401969668003</v>
+        <v>-0.3556324490580494</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>-0.05422311002337921</v>
+        <v>-1.070158538049071</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>-0.1349275542823918</v>
+        <v>-0.9937808552926839</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>-0.1827242524916954</v>
+        <v>-1.298701298701303</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>-0.6020665636645433</v>
+        <v>-1.606502236511751</v>
       </c>
       <c r="L13" s="4" t="n">
-        <v>0.4683357326491944</v>
+        <v>-1.095364189247427</v>
       </c>
       <c r="M13" s="4" t="n">
-        <v>0.9728101213548896</v>
+        <v>-0.6052642508958215</v>
       </c>
       <c r="N13" s="4" t="n">
-        <v>1.84613445062579</v>
+        <v>0.207478413369266</v>
       </c>
       <c r="O13" s="4" t="n">
-        <v>3.027119849207459</v>
+        <v>1.489100457138541</v>
       </c>
       <c r="P13" s="4" t="n">
-        <v>3.958114705479765</v>
+        <v>3.201650709430922</v>
       </c>
       <c r="Q13" s="4" t="n">
-        <v>3.299971407899207</v>
+        <v>2.519496327545866</v>
       </c>
       <c r="R13" s="4" t="n">
-        <v>2.051040357491964</v>
+        <v>1.555745880134594</v>
       </c>
       <c r="S13" s="4" t="n">
-        <v>-0.1566094983795097</v>
+        <v>-0.07318899782134736</v>
       </c>
       <c r="T13" s="4" t="n">
-        <v>-0.03103545565691235</v>
+        <v>0.6653865920061577</v>
       </c>
       <c r="U13" s="4" t="n">
-        <v>1.106514911442524</v>
+        <v>1.533443590393759</v>
       </c>
       <c r="V13" s="4" t="n">
-        <v>0.141286988691661</v>
+        <v>1.312300187958186</v>
       </c>
       <c r="W13" s="4" t="n">
-        <v>-0.4012591792743692</v>
+        <v>0.5269907628301809</v>
       </c>
       <c r="X13" s="4" t="n">
-        <v>-0.2466903941396907</v>
+        <v>1.105423012116724</v>
       </c>
       <c r="Y13" s="4" t="n">
-        <v>0.7190285579737008</v>
+        <v>1.349057497395101</v>
       </c>
       <c r="Z13" s="4" t="n">
-        <v>-0.04804793488091263</v>
+        <v>0.7511886556110809</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>X &lt; -0.01019</t>
+          <t>X &lt; -0.009801</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>545</v>
+        <v>572</v>
       </c>
       <c r="C14" s="4" t="n">
-        <v>-1.89772784737692</v>
+        <v>-1.794374979858851</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>0.1528164551906954</v>
+        <v>0.05762028233937855</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>0.182687314416583</v>
+        <v>-0.3229479454263284</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>0.3871644876344007</v>
+        <v>-0.7405249694093783</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>1.886236400408222</v>
+        <v>1.08181898839338</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>1.15577139384505</v>
+        <v>0.3646267202655906</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>2.402171333807914</v>
+        <v>1.842271980760152</v>
       </c>
       <c r="J14" s="4" t="n">
-        <v>1.940473650522726</v>
+        <v>1.712176712176699</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>1.614988355373207</v>
+        <v>1.140804922560115</v>
       </c>
       <c r="L14" s="4" t="n">
-        <v>2.493448826125714</v>
+        <v>1.568529651117004</v>
       </c>
       <c r="M14" s="4" t="n">
-        <v>3.317967183883958</v>
+        <v>2.889715714672377</v>
       </c>
       <c r="N14" s="4" t="n">
-        <v>3.95664897309652</v>
+        <v>3.312434459501794</v>
       </c>
       <c r="O14" s="4" t="n">
-        <v>5.035321768625728</v>
+        <v>4.120619265127935</v>
       </c>
       <c r="P14" s="4" t="n">
-        <v>5.915160323371794</v>
+        <v>5.096161427471053</v>
       </c>
       <c r="Q14" s="4" t="n">
-        <v>4.7065583101949</v>
+        <v>4.239181870760824</v>
       </c>
       <c r="R14" s="4" t="n">
-        <v>4.383514039477348</v>
+        <v>4.101185190279786</v>
       </c>
       <c r="S14" s="4" t="n">
-        <v>3.332165709839316</v>
+        <v>3.472829254079251</v>
       </c>
       <c r="T14" s="4" t="n">
-        <v>3.043838767486029</v>
+        <v>3.689595498568004</v>
       </c>
       <c r="U14" s="4" t="n">
-        <v>3.626702625474579</v>
+        <v>4.07888290053895</v>
       </c>
       <c r="V14" s="4" t="n">
-        <v>2.529144765717831</v>
+        <v>3.244518296646881</v>
       </c>
       <c r="W14" s="4" t="n">
-        <v>1.803112359219689</v>
+        <v>2.851898970091327</v>
       </c>
       <c r="X14" s="4" t="n">
-        <v>1.360293920746372</v>
+        <v>2.601911273310861</v>
       </c>
       <c r="Y14" s="4" t="n">
-        <v>2.185227348824753</v>
+        <v>3.195196108239593</v>
       </c>
       <c r="Z14" s="4" t="n">
-        <v>1.008477664408815</v>
+        <v>2.158931239824255</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>X &lt; -0.008589</t>
+          <t>X &lt; -0.008222</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>695</v>
+        <v>741</v>
       </c>
       <c r="C15" s="4" t="n">
-        <v>0.0282176347694687</v>
+        <v>0.5734326511066783</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>1.995599109800956</v>
+        <v>1.407147947656519</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>1.852544089546932</v>
+        <v>1.097123211486931</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>2.434554098881172</v>
+        <v>1.584343144932419</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>3.825382331369873</v>
+        <v>3.198123736277083</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>3.149039164949272</v>
+        <v>2.68029350961659</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>3.240399833576902</v>
+        <v>3.234739162701018</v>
       </c>
       <c r="J15" s="4" t="n">
-        <v>2.818303496737499</v>
+        <v>2.659913186228962</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>2.284251110306883</v>
+        <v>1.978125496722797</v>
       </c>
       <c r="L15" s="4" t="n">
-        <v>3.381839031392687</v>
+        <v>3.071412732947444</v>
       </c>
       <c r="M15" s="4" t="n">
-        <v>4.231438241899944</v>
+        <v>3.883458813678644</v>
       </c>
       <c r="N15" s="4" t="n">
-        <v>4.672113298883595</v>
+        <v>4.146687925334206</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>4.843915260804458</v>
+        <v>4.651229006263989</v>
       </c>
       <c r="P15" s="4" t="n">
-        <v>5.630030628962174</v>
+        <v>5.617569843616302</v>
       </c>
       <c r="Q15" s="4" t="n">
-        <v>5.11577222346795</v>
+        <v>5.340273761326394</v>
       </c>
       <c r="R15" s="4" t="n">
-        <v>4.846849792892968</v>
+        <v>5.226813947487486</v>
       </c>
       <c r="S15" s="4" t="n">
-        <v>4.856817548001814</v>
+        <v>5.3928390688259</v>
       </c>
       <c r="T15" s="4" t="n">
-        <v>4.176437275835312</v>
+        <v>5.125002197132588</v>
       </c>
       <c r="U15" s="4" t="n">
-        <v>4.680098440932305</v>
+        <v>5.744322723873509</v>
       </c>
       <c r="V15" s="4" t="n">
-        <v>4.003634898382337</v>
+        <v>5.419098102805634</v>
       </c>
       <c r="W15" s="4" t="n">
-        <v>4.036628298761634</v>
+        <v>5.121559134488322</v>
       </c>
       <c r="X15" s="4" t="n">
-        <v>3.385242769007206</v>
+        <v>4.641538312937904</v>
       </c>
       <c r="Y15" s="4" t="n">
-        <v>4.379141941920921</v>
+        <v>5.694889397406563</v>
       </c>
       <c r="Z15" s="4" t="n">
-        <v>3.008345659920664</v>
+        <v>4.183222737799966</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>X &lt; -0.006991</t>
+          <t>X &lt; -0.006642</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>881</v>
+        <v>930</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>0.9562016947405638</v>
+        <v>0.7584485407066026</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>0.8484396523498816</v>
+        <v>0.8351223501640277</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>1.113031273012432</v>
+        <v>0.7632239471971829</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>1.308136277406241</v>
+        <v>1.031036802152393</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>1.880404828695518</v>
+        <v>1.29311307065521</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>1.726848880854178</v>
+        <v>1.019939149771574</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>1.635944464841245</v>
+        <v>0.6549646644205751</v>
       </c>
       <c r="J16" s="4" t="n">
-        <v>2.265792043924719</v>
+        <v>1.532839919936684</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>1.853249713921151</v>
+        <v>1.338188184459511</v>
       </c>
       <c r="L16" s="4" t="n">
-        <v>2.782944707578189</v>
+        <v>2.585147441928342</v>
       </c>
       <c r="M16" s="4" t="n">
-        <v>3.057004349740112</v>
+        <v>2.749855574812244</v>
       </c>
       <c r="N16" s="4" t="n">
-        <v>3.005269702251255</v>
+        <v>2.90338114722266</v>
       </c>
       <c r="O16" s="4" t="n">
-        <v>3.584718305088664</v>
+        <v>3.508919137298776</v>
       </c>
       <c r="P16" s="4" t="n">
-        <v>4.725727964396896</v>
+        <v>4.658534538231258</v>
       </c>
       <c r="Q16" s="4" t="n">
-        <v>4.748628934693748</v>
+        <v>4.729068328389225</v>
       </c>
       <c r="R16" s="4" t="n">
-        <v>4.775478966738902</v>
+        <v>5.290372347208887</v>
       </c>
       <c r="S16" s="4" t="n">
-        <v>4.755069207740988</v>
+        <v>5.294018817204297</v>
       </c>
       <c r="T16" s="4" t="n">
-        <v>4.082691614021975</v>
+        <v>5.053607830322278</v>
       </c>
       <c r="U16" s="4" t="n">
-        <v>4.41209037292586</v>
+        <v>5.375596939188469</v>
       </c>
       <c r="V16" s="4" t="n">
-        <v>3.690877159057337</v>
+        <v>4.837495212204445</v>
       </c>
       <c r="W16" s="4" t="n">
-        <v>3.715867880989151</v>
+        <v>4.915212001146301</v>
       </c>
       <c r="X16" s="4" t="n">
-        <v>3.413007163620918</v>
+        <v>4.840049479191016</v>
       </c>
       <c r="Y16" s="4" t="n">
-        <v>4.482033521959949</v>
+        <v>5.728845254791956</v>
       </c>
       <c r="Z16" s="4" t="n">
-        <v>3.271127488940984</v>
+        <v>4.814018088459498</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>X &lt; -0.005392</t>
+          <t>X &lt; -0.005062</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>1052</v>
+        <v>1082</v>
       </c>
       <c r="C17" s="4" t="n">
-        <v>0.6801405408890204</v>
+        <v>0.06180950109457939</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>0.8201975507063466</v>
+        <v>0.4628527578121506</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>0.806679926176777</v>
+        <v>0.5020588407634534</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>1.708160854502317</v>
+        <v>1.295978268572604</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>1.847204190122184</v>
+        <v>1.482527337345729</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>1.844236852952719</v>
+        <v>0.9925108509223648</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>1.547121977229509</v>
+        <v>1.029221814660076</v>
       </c>
       <c r="J17" s="4" t="n">
-        <v>1.743744340643573</v>
+        <v>1.371251463672905</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>1.785231522558277</v>
+        <v>1.499180373357014</v>
       </c>
       <c r="L17" s="4" t="n">
-        <v>3.101584602457201</v>
+        <v>2.736400597176484</v>
       </c>
       <c r="M17" s="4" t="n">
-        <v>3.280677482985702</v>
+        <v>2.823792728231844</v>
       </c>
       <c r="N17" s="4" t="n">
-        <v>3.191861602804558</v>
+        <v>2.824475099084012</v>
       </c>
       <c r="O17" s="4" t="n">
-        <v>3.873068006983587</v>
+        <v>3.558011817123074</v>
       </c>
       <c r="P17" s="4" t="n">
-        <v>4.79159027013813</v>
+        <v>4.326413615209376</v>
       </c>
       <c r="Q17" s="4" t="n">
-        <v>4.893181065624994</v>
+        <v>4.568473651069233</v>
       </c>
       <c r="R17" s="4" t="n">
-        <v>4.347966847966845</v>
+        <v>4.29798469391848</v>
       </c>
       <c r="S17" s="4" t="n">
-        <v>4.59391675752309</v>
+        <v>4.563790049291427</v>
       </c>
       <c r="T17" s="4" t="n">
-        <v>4.489076053701908</v>
+        <v>4.985434594776791</v>
       </c>
       <c r="U17" s="4" t="n">
-        <v>4.135166864825656</v>
+        <v>4.830211054824588</v>
       </c>
       <c r="V17" s="4" t="n">
-        <v>4.132079151526838</v>
+        <v>5.044797499883572</v>
       </c>
       <c r="W17" s="4" t="n">
-        <v>4.410291345510551</v>
+        <v>5.216724532698763</v>
       </c>
       <c r="X17" s="4" t="n">
-        <v>3.954217247219319</v>
+        <v>4.771876243645529</v>
       </c>
       <c r="Y17" s="4" t="n">
-        <v>4.703977130804034</v>
+        <v>5.292775054247365</v>
       </c>
       <c r="Z17" s="4" t="n">
-        <v>3.392403432713834</v>
+        <v>4.114000200438504</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>X &lt; -0.003793</t>
+          <t>X &lt; -0.003482</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>1224</v>
+        <v>1279</v>
       </c>
       <c r="C18" s="4" t="n">
-        <v>-0.3347246644523807</v>
+        <v>-0.4542764544593112</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>0.8815189453610799</v>
+        <v>0.9417244502590307</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>1.076152957554577</v>
+        <v>1.016193757280661</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>1.506056080968982</v>
+        <v>1.596582801631151</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>0.7621023431155791</v>
+        <v>0.8519081642683375</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>0.4592726108456162</v>
+        <v>0.5397252730029294</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>0.5852831106287368</v>
+        <v>0.4483180066654455</v>
       </c>
       <c r="J18" s="4" t="n">
-        <v>1.205030849549125</v>
+        <v>1.159816640661049</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>1.328150684525056</v>
+        <v>1.67867596473139</v>
       </c>
       <c r="L18" s="4" t="n">
-        <v>2.596051335019169</v>
+        <v>2.759090458566007</v>
       </c>
       <c r="M18" s="4" t="n">
-        <v>2.625213017997424</v>
+        <v>2.953139390293089</v>
       </c>
       <c r="N18" s="4" t="n">
-        <v>2.75462687985555</v>
+        <v>2.98930176733078</v>
       </c>
       <c r="O18" s="4" t="n">
-        <v>3.590648486468815</v>
+        <v>4.141806053320195</v>
       </c>
       <c r="P18" s="4" t="n">
-        <v>3.532834916144679</v>
+        <v>4.206316323396088</v>
       </c>
       <c r="Q18" s="4" t="n">
-        <v>3.691018149176365</v>
+        <v>4.306022770283505</v>
       </c>
       <c r="R18" s="4" t="n">
-        <v>3.55071119356834</v>
+        <v>4.320024208962437</v>
       </c>
       <c r="S18" s="4" t="n">
-        <v>3.580059362713314</v>
+        <v>4.528888128746409</v>
       </c>
       <c r="T18" s="4" t="n">
-        <v>3.883381924198247</v>
+        <v>4.865120520848293</v>
       </c>
       <c r="U18" s="4" t="n">
-        <v>3.854375345938912</v>
+        <v>5.079582747994067</v>
       </c>
       <c r="V18" s="4" t="n">
-        <v>3.796323196723264</v>
+        <v>4.981424861544063</v>
       </c>
       <c r="W18" s="4" t="n">
-        <v>4.122324447724814</v>
+        <v>5.274027271813068</v>
       </c>
       <c r="X18" s="4" t="n">
-        <v>3.556282407884339</v>
+        <v>4.807934335471536</v>
       </c>
       <c r="Y18" s="4" t="n">
-        <v>4.402652545202997</v>
+        <v>5.364313152258909</v>
       </c>
       <c r="Z18" s="4" t="n">
-        <v>3.101330095901289</v>
+        <v>4.420313329196958</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>X &lt; -0.002194</t>
+          <t>X &lt; -0.001903</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>1445</v>
+        <v>1496</v>
       </c>
       <c r="C19" s="4" t="n">
-        <v>-0.1138761590751187</v>
+        <v>-0.2672256585918831</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>1.280254373142149</v>
+        <v>1.224835420142753</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>1.571142654678233</v>
+        <v>0.9728151150426143</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>1.964689326798435</v>
+        <v>1.784156231742415</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>1.075648508469683</v>
+        <v>0.9738387333543059</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>0.9168332284536476</v>
+        <v>0.9302375799941061</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>0.9056037700128243</v>
+        <v>0.9372946051945377</v>
       </c>
       <c r="J19" s="4" t="n">
-        <v>1.11148637781853</v>
+        <v>1.300823359646884</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>1.291286146178599</v>
+        <v>1.495597189117092</v>
       </c>
       <c r="L19" s="4" t="n">
-        <v>2.108965214263819</v>
+        <v>2.036444089619671</v>
       </c>
       <c r="M19" s="4" t="n">
-        <v>2.452181149648425</v>
+        <v>2.375524024010112</v>
       </c>
       <c r="N19" s="4" t="n">
-        <v>2.242588039423111</v>
+        <v>2.232631909110992</v>
       </c>
       <c r="O19" s="4" t="n">
-        <v>2.779177009911393</v>
+        <v>2.922552625884826</v>
       </c>
       <c r="P19" s="4" t="n">
-        <v>2.834723306355535</v>
+        <v>2.9416982435961</v>
       </c>
       <c r="Q19" s="4" t="n">
-        <v>2.93729923422449</v>
+        <v>2.994837979358103</v>
       </c>
       <c r="R19" s="4" t="n">
-        <v>2.840123223940651</v>
+        <v>3.021382639889005</v>
       </c>
       <c r="S19" s="4" t="n">
-        <v>2.706206086963178</v>
+        <v>2.984347147950082</v>
       </c>
       <c r="T19" s="4" t="n">
-        <v>2.739677969587362</v>
+        <v>3.051997802146779</v>
       </c>
       <c r="U19" s="4" t="n">
-        <v>2.886413057289005</v>
+        <v>3.333304949078645</v>
       </c>
       <c r="V19" s="4" t="n">
-        <v>2.58916481469825</v>
+        <v>3.213666795207153</v>
       </c>
       <c r="W19" s="4" t="n">
-        <v>2.919902302396089</v>
+        <v>3.515206251045669</v>
       </c>
       <c r="X19" s="4" t="n">
-        <v>2.567239731990462</v>
+        <v>3.239508969732086</v>
       </c>
       <c r="Y19" s="4" t="n">
-        <v>3.118531053469042</v>
+        <v>3.817368053940953</v>
       </c>
       <c r="Z19" s="4" t="n">
-        <v>2.76588219124924</v>
+        <v>3.521539220079298</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>X &lt; -0.0005956</t>
+          <t>X &lt; -0.0003229</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>1658</v>
+        <v>1697</v>
       </c>
       <c r="C20" s="4" t="n">
-        <v>-0.4198958792356962</v>
+        <v>-0.2485090810517718</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>0.9912635054367627</v>
+        <v>1.152642906773771</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>0.7573383757314716</v>
+        <v>0.9567723342939587</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>1.609706451412151</v>
+        <v>1.834958370779844</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>0.6718690192020347</v>
+        <v>1.029988465974633</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>0.6782211174005539</v>
+        <v>0.8339808955021297</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>0.5685240891393377</v>
+        <v>0.744781236210585</v>
       </c>
       <c r="J20" s="4" t="n">
-        <v>1.072973691947979</v>
+        <v>1.204566675154901</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>1.234870265795251</v>
+        <v>1.391319114250777</v>
       </c>
       <c r="L20" s="4" t="n">
-        <v>1.786457901017037</v>
+        <v>2.007032324913794</v>
       </c>
       <c r="M20" s="4" t="n">
-        <v>1.940108151246385</v>
+        <v>2.102796751282831</v>
       </c>
       <c r="N20" s="4" t="n">
-        <v>1.601154051832111</v>
+        <v>1.767391267399766</v>
       </c>
       <c r="O20" s="4" t="n">
-        <v>2.103518776065698</v>
+        <v>2.240734444066639</v>
       </c>
       <c r="P20" s="4" t="n">
-        <v>2.123258683484245</v>
+        <v>2.345441559104124</v>
       </c>
       <c r="Q20" s="4" t="n">
-        <v>1.766138865735115</v>
+        <v>2.016228353689655</v>
       </c>
       <c r="R20" s="4" t="n">
-        <v>1.638069436082681</v>
+        <v>1.989297078391672</v>
       </c>
       <c r="S20" s="4" t="n">
-        <v>1.624561691037783</v>
+        <v>1.944240196078432</v>
       </c>
       <c r="T20" s="4" t="n">
-        <v>1.436123502757397</v>
+        <v>1.752532561505063</v>
       </c>
       <c r="U20" s="4" t="n">
-        <v>1.809425720519123</v>
+        <v>2.143465376886134</v>
       </c>
       <c r="V20" s="4" t="n">
-        <v>1.755162428618547</v>
+        <v>2.063934174886285</v>
       </c>
       <c r="W20" s="4" t="n">
-        <v>1.852580603263029</v>
+        <v>2.378842614682029</v>
       </c>
       <c r="X20" s="4" t="n">
-        <v>1.837048272734499</v>
+        <v>2.457749960815235</v>
       </c>
       <c r="Y20" s="4" t="n">
-        <v>2.413091139619453</v>
+        <v>3.032314231576798</v>
       </c>
       <c r="Z20" s="4" t="n">
-        <v>2.337258886396178</v>
+        <v>3.02471248274162</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>X &lt; 0.001003</t>
+          <t>X &lt; 0.001257</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>1844</v>
+        <v>1895</v>
       </c>
       <c r="C21" s="4" t="n">
-        <v>-0.06941854200339748</v>
+        <v>0.09277896208961067</v>
       </c>
       <c r="D21" s="4" t="n">
-        <v>0.6780557418978717</v>
+        <v>0.900612906153917</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>0.4846254374556267</v>
+        <v>0.8577207009957348</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>1.449160595502065</v>
+        <v>1.845929671839784</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>1.005145014729678</v>
+        <v>1.46499745376363</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>0.8133233220391816</v>
+        <v>1.463869942796492</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>0.6366127333869258</v>
+        <v>1.248345359436271</v>
       </c>
       <c r="J21" s="4" t="n">
-        <v>0.6289640591966261</v>
+        <v>1.312234188946512</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>0.778676349336429</v>
+        <v>1.44016309863062</v>
       </c>
       <c r="L21" s="4" t="n">
-        <v>1.088011755551022</v>
+        <v>1.53979126621423</v>
       </c>
       <c r="M21" s="4" t="n">
-        <v>1.362071397712945</v>
+        <v>1.759339241830162</v>
       </c>
       <c r="N21" s="4" t="n">
-        <v>0.8127592237021872</v>
+        <v>1.219322092416817</v>
       </c>
       <c r="O21" s="4" t="n">
-        <v>0.8800733473222522</v>
+        <v>1.36891891068786</v>
       </c>
       <c r="P21" s="4" t="n">
-        <v>0.9836697955509948</v>
+        <v>1.436807083185194</v>
       </c>
       <c r="Q21" s="4" t="n">
-        <v>0.7584269308708613</v>
+        <v>1.439584208149462</v>
       </c>
       <c r="R21" s="4" t="n">
-        <v>0.7575757575757578</v>
+        <v>1.526704876073445</v>
       </c>
       <c r="S21" s="4" t="n">
-        <v>0.6236586205982846</v>
+        <v>1.212076308394792</v>
       </c>
       <c r="T21" s="4" t="n">
-        <v>0.4431423741280938</v>
+        <v>1.026505164244789</v>
       </c>
       <c r="U21" s="4" t="n">
-        <v>0.6916185855966361</v>
+        <v>1.399028508355784</v>
       </c>
       <c r="V21" s="4" t="n">
-        <v>0.8568840064129972</v>
+        <v>1.402866797461137</v>
       </c>
       <c r="W21" s="4" t="n">
-        <v>0.9434932623222352</v>
+        <v>1.625727880906538</v>
       </c>
       <c r="X21" s="4" t="n">
-        <v>1.138796975533531</v>
+        <v>1.846301569361678</v>
       </c>
       <c r="Y21" s="4" t="n">
-        <v>1.792881232484127</v>
+        <v>2.438726839112093</v>
       </c>
       <c r="Z21" s="4" t="n">
-        <v>1.771278914184926</v>
+        <v>2.678517194766407</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>X &lt; 0.002602</t>
+          <t>X &lt; 0.002837</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>2040</v>
+        <v>2085</v>
       </c>
       <c r="C22" s="4" t="n">
-        <v>0.1414857318584168</v>
+        <v>0.2408981761039684</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>0.7339905342894752</v>
+        <v>0.9049530262238434</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>0.4672745599290522</v>
+        <v>0.5123278898495087</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>1.169645089046583</v>
+        <v>1.213029139317143</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>0.3735500471972131</v>
+        <v>0.5064365164591891</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>0.6371336917704085</v>
+        <v>0.8549410036833294</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>0.8422245779826412</v>
+        <v>1.017713397580877</v>
       </c>
       <c r="J22" s="4" t="n">
-        <v>0.5640131332295653</v>
+        <v>0.712792954172258</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>0.6543522936494099</v>
+        <v>0.7449364232433382</v>
       </c>
       <c r="L22" s="4" t="n">
-        <v>0.5653643166847289</v>
+        <v>0.6193830123151898</v>
       </c>
       <c r="M22" s="4" t="n">
-        <v>0.7417200018363985</v>
+        <v>0.8437253066130097</v>
       </c>
       <c r="N22" s="4" t="n">
-        <v>0.1698587273576209</v>
+        <v>0.3755724709156567</v>
       </c>
       <c r="O22" s="4" t="n">
-        <v>-0.1228197049113007</v>
+        <v>0.3143202002081864</v>
       </c>
       <c r="P22" s="4" t="n">
-        <v>-0.09963868883223626</v>
+        <v>0.3055497403076401</v>
       </c>
       <c r="Q22" s="4" t="n">
-        <v>0.1509698718009034</v>
+        <v>0.4854643239398229</v>
       </c>
       <c r="R22" s="4" t="n">
-        <v>0.2858042527969218</v>
+        <v>0.6157338600008657</v>
       </c>
       <c r="S22" s="4" t="n">
-        <v>0.1321980263979654</v>
+        <v>0.3681752873563227</v>
       </c>
       <c r="T22" s="4" t="n">
-        <v>0.1055442105518551</v>
+        <v>0.4268620634207778</v>
       </c>
       <c r="U22" s="4" t="n">
-        <v>0.4486706546598427</v>
+        <v>0.7371097311795793</v>
       </c>
       <c r="V22" s="4" t="n">
-        <v>0.4689026645711607</v>
+        <v>0.6643398543994792</v>
       </c>
       <c r="W22" s="4" t="n">
-        <v>0.4458538594895174</v>
+        <v>0.7195007170034202</v>
       </c>
       <c r="X22" s="4" t="n">
-        <v>0.6151059372961001</v>
+        <v>0.9606320925012568</v>
       </c>
       <c r="Y22" s="4" t="n">
-        <v>1.232717904680115</v>
+        <v>1.520863729209225</v>
       </c>
       <c r="Z22" s="4" t="n">
-        <v>1.598062122045086</v>
+        <v>2.059318622226023</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>X &lt; 0.004201</t>
+          <t>X &lt; 0.004416</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>2243</v>
+        <v>2293</v>
       </c>
       <c r="C23" s="4" t="n">
-        <v>0.1882808192816299</v>
+        <v>0.2465718781611841</v>
       </c>
       <c r="D23" s="4" t="n">
-        <v>0.453074051017154</v>
+        <v>0.6104211400182891</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>-0.03039085624919124</v>
+        <v>0.09614515659360023</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>0.1234030197444866</v>
+        <v>0.2877150832209168</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>-0.4091723751974641</v>
+        <v>-0.1620590847529826</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>-0.2860690040612184</v>
+        <v>-0.09223349269217351</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>-0.1010761201474679</v>
+        <v>0.0273186414165707</v>
       </c>
       <c r="J23" s="4" t="n">
-        <v>-0.3349023008082241</v>
+        <v>-0.1033857741174842</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>-0.2934151188935203</v>
+        <v>0.1552051564725474</v>
       </c>
       <c r="L23" s="4" t="n">
-        <v>-0.2230107771759009</v>
+        <v>0.09957177972010101</v>
       </c>
       <c r="M23" s="4" t="n">
-        <v>-0.3040332477525496</v>
+        <v>0.1104827525125955</v>
       </c>
       <c r="N23" s="4" t="n">
-        <v>-0.9822500280314372</v>
+        <v>-0.4709772507391889</v>
       </c>
       <c r="O23" s="4" t="n">
-        <v>-1.128936284856486</v>
+        <v>-0.5405732009425819</v>
       </c>
       <c r="P23" s="4" t="n">
-        <v>-1.438785689487716</v>
+        <v>-0.745253255407043</v>
       </c>
       <c r="Q23" s="4" t="n">
-        <v>-1.183089220236759</v>
+        <v>-0.556327497919284</v>
       </c>
       <c r="R23" s="4" t="n">
-        <v>-1.006791594308254</v>
+        <v>-0.3870095418173847</v>
       </c>
       <c r="S23" s="4" t="n">
-        <v>-1.292502995563325</v>
+        <v>-0.7522139953542464</v>
       </c>
       <c r="T23" s="4" t="n">
-        <v>-1.149095095066542</v>
+        <v>-0.710882072641283</v>
       </c>
       <c r="U23" s="4" t="n">
-        <v>-1.218542077258135</v>
+        <v>-0.7141898803387079</v>
       </c>
       <c r="V23" s="4" t="n">
-        <v>-1.005762123386091</v>
+        <v>-0.5867114492170131</v>
       </c>
       <c r="W23" s="4" t="n">
-        <v>-1.077115078753636</v>
+        <v>-0.6315078669740473</v>
       </c>
       <c r="X23" s="4" t="n">
-        <v>-0.8149783458603608</v>
+        <v>-0.4196314541142101</v>
       </c>
       <c r="Y23" s="4" t="n">
-        <v>-0.20221970672808</v>
+        <v>0.2856601341874949</v>
       </c>
       <c r="Z23" s="4" t="n">
-        <v>0.1942830446539858</v>
+        <v>0.6728028893260856</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>X &lt; 0.005799</t>
+          <t>X &lt; 0.005996</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>2427</v>
+        <v>2460</v>
       </c>
       <c r="C24" s="4" t="n">
-        <v>0.350147565241798</v>
+        <v>0.312892752408878</v>
       </c>
       <c r="D24" s="4" t="n">
-        <v>0.651730715572846</v>
+        <v>0.8786742283933293</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>0.1373607262007468</v>
+        <v>0.4356684381900564</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>-0.1020068163210865</v>
+        <v>0.330279226394822</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>-0.5378282072103318</v>
+        <v>-0.1076165760421759</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>-0.4509749992730789</v>
+        <v>-0.07243621679734247</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>-0.4203695402551801</v>
+        <v>-0.1775831640949974</v>
       </c>
       <c r="J24" s="4" t="n">
-        <v>-0.5344447519348066</v>
+        <v>-0.198412698412703</v>
       </c>
       <c r="K24" s="4" t="n">
-        <v>-0.5750256865568275</v>
+        <v>-0.1516526198974262</v>
       </c>
       <c r="L24" s="4" t="n">
-        <v>-0.4862261389576972</v>
+        <v>-0.01426255667521303</v>
       </c>
       <c r="M24" s="4" t="n">
-        <v>-0.2532005550641401</v>
+        <v>0.2173880423447088</v>
       </c>
       <c r="N24" s="4" t="n">
-        <v>-0.7781543081223035</v>
+        <v>-0.3027004056330824</v>
       </c>
       <c r="O24" s="4" t="n">
-        <v>-1.080635209611167</v>
+        <v>-0.5247353802267014</v>
       </c>
       <c r="P24" s="4" t="n">
-        <v>-1.301714086057757</v>
+        <v>-0.7323850260753986</v>
       </c>
       <c r="Q24" s="4" t="n">
-        <v>-1.114987011508603</v>
+        <v>-0.5216822651033155</v>
       </c>
       <c r="R24" s="4" t="n">
-        <v>-0.9070686329413178</v>
+        <v>-0.2850535709589721</v>
       </c>
       <c r="S24" s="4" t="n">
-        <v>-1.058010162549543</v>
+        <v>-0.5512716450216431</v>
       </c>
       <c r="T24" s="4" t="n">
-        <v>-1.015483170544947</v>
+        <v>-0.5218180878455811</v>
       </c>
       <c r="U24" s="4" t="n">
-        <v>-1.063287113781833</v>
+        <v>-0.5102779386218899</v>
       </c>
       <c r="V24" s="4" t="n">
-        <v>-0.9758122308743538</v>
+        <v>-0.5155361028715788</v>
       </c>
       <c r="W24" s="4" t="n">
-        <v>-1.082831688803864</v>
+        <v>-0.5551689923968581</v>
       </c>
       <c r="X24" s="4" t="n">
-        <v>-0.846299950707504</v>
+        <v>-0.4033491040047608</v>
       </c>
       <c r="Y24" s="4" t="n">
-        <v>-0.4239348717517046</v>
+        <v>0.0674522551808252</v>
       </c>
       <c r="Z24" s="4" t="n">
-        <v>-0.02212983607314811</v>
+        <v>0.4172176688423974</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>X &lt; 0.007398</t>
+          <t>X &lt; 0.007576</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>2589</v>
+        <v>2624</v>
       </c>
       <c r="C25" s="4" t="n">
-        <v>0.6393832128636205</v>
+        <v>0.7853914951240242</v>
       </c>
       <c r="D25" s="4" t="n">
-        <v>0.5174636458219126</v>
+        <v>0.7879951107012886</v>
       </c>
       <c r="E25" s="4" t="n">
-        <v>0.09922680484223889</v>
+        <v>0.4448087946053789</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>0.09938303511727753</v>
+        <v>0.4220989619194597</v>
       </c>
       <c r="G25" s="4" t="n">
-        <v>-0.5992578872510848</v>
+        <v>-0.3092130710777141</v>
       </c>
       <c r="H25" s="4" t="n">
-        <v>-0.429267420551561</v>
+        <v>-0.1902589561544588</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>-0.2178201237392727</v>
+        <v>0.0401052906329582</v>
       </c>
       <c r="J25" s="4" t="n">
-        <v>-0.4960315684923486</v>
+        <v>-0.2268356617008465</v>
       </c>
       <c r="K25" s="4" t="n">
-        <v>-0.5699733977357866</v>
+        <v>-0.1748657341663744</v>
       </c>
       <c r="L25" s="4" t="n">
-        <v>-0.7272676809288754</v>
+        <v>-0.3632453721886009</v>
       </c>
       <c r="M25" s="4" t="n">
-        <v>-0.7225423981359427</v>
+        <v>-0.3188873040331757</v>
       </c>
       <c r="N25" s="4" t="n">
-        <v>-0.8473864533730904</v>
+        <v>-0.4055718031303783</v>
       </c>
       <c r="O25" s="4" t="n">
-        <v>-0.9701637568586747</v>
+        <v>-0.4950176615610218</v>
       </c>
       <c r="P25" s="4" t="n">
-        <v>-1.345147981516114</v>
+        <v>-0.8192107051437674</v>
       </c>
       <c r="Q25" s="4" t="n">
-        <v>-1.24961122035436</v>
+        <v>-0.681429432829205</v>
       </c>
       <c r="R25" s="4" t="n">
-        <v>-1.017636900386229</v>
+        <v>-0.4398173267774581</v>
       </c>
       <c r="S25" s="4" t="n">
-        <v>-1.090517034255335</v>
+        <v>-0.6197144621816832</v>
       </c>
       <c r="T25" s="4" t="n">
-        <v>-0.9801311110736535</v>
+        <v>-0.5402431038941771</v>
       </c>
       <c r="U25" s="4" t="n">
-        <v>-1.088554177451016</v>
+        <v>-0.5697111832015764</v>
       </c>
       <c r="V25" s="4" t="n">
-        <v>-0.9948807511111823</v>
+        <v>-0.5992406840983975</v>
       </c>
       <c r="W25" s="4" t="n">
-        <v>-1.051967491273011</v>
+        <v>-0.4973973369514653</v>
       </c>
       <c r="X25" s="4" t="n">
-        <v>-0.8735501194917177</v>
+        <v>-0.4739732382172051</v>
       </c>
       <c r="Y25" s="4" t="n">
-        <v>-0.4604458473071631</v>
+        <v>-0.0173913043478251</v>
       </c>
       <c r="Z25" s="4" t="n">
-        <v>-0.2816665944705008</v>
+        <v>0.1097989696553938</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>X &lt; 0.008997</t>
+          <t>X &lt; 0.009156</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>2724</v>
+        <v>2755</v>
       </c>
       <c r="C26" s="4" t="n">
-        <v>0.6292258792687662</v>
+        <v>0.5563259623913908</v>
       </c>
       <c r="D26" s="4" t="n">
-        <v>0.7888886840561184</v>
+        <v>0.8718710604629933</v>
       </c>
       <c r="E26" s="4" t="n">
-        <v>0.3569925395524578</v>
+        <v>0.5042967289451994</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>0.4682148575230798</v>
+        <v>0.7069794596635361</v>
       </c>
       <c r="G26" s="4" t="n">
-        <v>-0.3585862832121478</v>
+        <v>-0.1106820414766361</v>
       </c>
       <c r="H26" s="4" t="n">
-        <v>-0.004854539100286104</v>
+        <v>0.2471917329824507</v>
       </c>
       <c r="I26" s="4" t="n">
-        <v>-0.06126899960819543</v>
+        <v>0.08719161808485865</v>
       </c>
       <c r="J26" s="4" t="n">
-        <v>-0.412633333900402</v>
+        <v>-0.2538951906040623</v>
       </c>
       <c r="K26" s="4" t="n">
-        <v>-0.4808754862944014</v>
+        <v>-0.3067981073213915</v>
       </c>
       <c r="L26" s="4" t="n">
-        <v>-0.5588387117090932</v>
+        <v>-0.379522296934951</v>
       </c>
       <c r="M26" s="4" t="n">
-        <v>-0.6139670724732866</v>
+        <v>-0.4327845698532187</v>
       </c>
       <c r="N26" s="4" t="n">
-        <v>-0.7829871416125798</v>
+        <v>-0.6008674284836388</v>
       </c>
       <c r="O26" s="4" t="n">
-        <v>-0.8454323101512173</v>
+        <v>-0.5584358569651542</v>
       </c>
       <c r="P26" s="4" t="n">
-        <v>-1.066511186597808</v>
+        <v>-0.770503553117976</v>
       </c>
       <c r="Q26" s="4" t="n">
-        <v>-1.227640422924267</v>
+        <v>-0.8889389230618505</v>
       </c>
       <c r="R26" s="4" t="n">
-        <v>-1.050956120502242</v>
+        <v>-0.7045139965268916</v>
       </c>
       <c r="S26" s="4" t="n">
-        <v>-1.090249038933692</v>
+        <v>-0.7872842746801894</v>
       </c>
       <c r="T26" s="4" t="n">
-        <v>-0.9905060925469016</v>
+        <v>-0.7179491480204661</v>
       </c>
       <c r="U26" s="4" t="n">
-        <v>-1.082889556357671</v>
+        <v>-0.6634399939578586</v>
       </c>
       <c r="V26" s="4" t="n">
-        <v>-0.9479463586062025</v>
+        <v>-0.6451675883271548</v>
       </c>
       <c r="W26" s="4" t="n">
-        <v>-0.9923781990104459</v>
+        <v>-0.6113890109631583</v>
       </c>
       <c r="X26" s="4" t="n">
-        <v>-1.193368736505917</v>
+        <v>-0.8828611178815535</v>
       </c>
       <c r="Y26" s="4" t="n">
-        <v>-0.8973414585146955</v>
+        <v>-0.5091184451315627</v>
       </c>
       <c r="Z26" s="4" t="n">
-        <v>-0.6946302853143322</v>
+        <v>-0.3595665962779364</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>X &lt; 0.0106</t>
+          <t>X &lt; 0.01074</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>2861</v>
+        <v>2890</v>
       </c>
       <c r="C27" s="4" t="n">
-        <v>0.7877739355433704</v>
+        <v>0.7588185575053714</v>
       </c>
       <c r="D27" s="4" t="n">
-        <v>0.6803872070507424</v>
+        <v>0.9102616169084214</v>
       </c>
       <c r="E27" s="4" t="n">
-        <v>0.5474275987979311</v>
+        <v>0.7418963012361033</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>0.4798007944315543</v>
+        <v>0.7198644517103219</v>
       </c>
       <c r="G27" s="4" t="n">
-        <v>-0.04499614845495614</v>
+        <v>0.188053897522849</v>
       </c>
       <c r="H27" s="4" t="n">
-        <v>0.2659844396272319</v>
+        <v>0.4677380177926196</v>
       </c>
       <c r="I27" s="4" t="n">
-        <v>0.1402388207234182</v>
+        <v>0.3127325546690045</v>
       </c>
       <c r="J27" s="4" t="n">
-        <v>-0.1180605039839264</v>
+        <v>0.04229486988107567</v>
       </c>
       <c r="K27" s="4" t="n">
-        <v>-0.1959716080701384</v>
+        <v>-0.03667277215896547</v>
       </c>
       <c r="L27" s="4" t="n">
-        <v>-0.376759105771562</v>
+        <v>-0.1775518535852001</v>
       </c>
       <c r="M27" s="4" t="n">
-        <v>-0.4510101567479126</v>
+        <v>-0.2156616665670725</v>
       </c>
       <c r="N27" s="4" t="n">
-        <v>-0.7645906295097404</v>
+        <v>-0.4922436210383694</v>
       </c>
       <c r="O27" s="4" t="n">
-        <v>-0.9124827555786794</v>
+        <v>-0.6071357384891414</v>
       </c>
       <c r="P27" s="4" t="n">
-        <v>-1.029068424083789</v>
+        <v>-0.6484732481981013</v>
       </c>
       <c r="Q27" s="4" t="n">
-        <v>-1.213909675612086</v>
+        <v>-0.7931176682651753</v>
       </c>
       <c r="R27" s="4" t="n">
-        <v>-1.191551274332731</v>
+        <v>-0.7981425351348932</v>
       </c>
       <c r="S27" s="4" t="n">
-        <v>-1.409750787288111</v>
+        <v>-1.0890396674721</v>
       </c>
       <c r="T27" s="4" t="n">
-        <v>-1.250136010356101</v>
+        <v>-0.925644234075051</v>
       </c>
       <c r="U27" s="4" t="n">
-        <v>-1.258090296284486</v>
+        <v>-0.8292055567723011</v>
       </c>
       <c r="V27" s="4" t="n">
-        <v>-1.15563035956837</v>
+        <v>-0.8018327262072518</v>
       </c>
       <c r="W27" s="4" t="n">
-        <v>-1.154129709357015</v>
+        <v>-0.7615977992989826</v>
       </c>
       <c r="X27" s="4" t="n">
-        <v>-1.209474750724823</v>
+        <v>-0.8856454300134686</v>
       </c>
       <c r="Y27" s="4" t="n">
-        <v>-1.08918779680382</v>
+        <v>-0.6909298723173762</v>
       </c>
       <c r="Z27" s="4" t="n">
-        <v>-1.074645898597637</v>
+        <v>-0.7290112674954159</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>X &lt; 0.01219</t>
+          <t>X &lt; 0.01232</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>2981</v>
+        <v>3013</v>
       </c>
       <c r="C28" s="4" t="n">
-        <v>0.3897991224108068</v>
+        <v>0.450772611823389</v>
       </c>
       <c r="D28" s="4" t="n">
-        <v>0.4728932491645708</v>
+        <v>0.5528332239042442</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>0.1863570391872358</v>
+        <v>0.306838384492103</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>0.1588314959032004</v>
+        <v>0.3273698051256417</v>
       </c>
       <c r="G28" s="4" t="n">
-        <v>-0.1248290805546191</v>
+        <v>0.1033526431061489</v>
       </c>
       <c r="H28" s="4" t="n">
-        <v>0.18103518975105</v>
+        <v>0.3449191551034829</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>0.02873151802906904</v>
+        <v>0.1636265521147209</v>
       </c>
       <c r="J28" s="4" t="n">
-        <v>-0.1636448344139438</v>
+        <v>-0.08945367860354025</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>-0.3368664245229738</v>
+        <v>-0.2592422680924287</v>
       </c>
       <c r="L28" s="4" t="n">
-        <v>-0.5227633141281558</v>
+        <v>-0.3936993207050961</v>
       </c>
       <c r="M28" s="4" t="n">
-        <v>-0.4968539906242029</v>
+        <v>-0.3861020831434274</v>
       </c>
       <c r="N28" s="4" t="n">
-        <v>-0.7756033940721991</v>
+        <v>-0.563444871223723</v>
       </c>
       <c r="O28" s="4" t="n">
-        <v>-0.8960916641368755</v>
+        <v>-0.6528656026341437</v>
       </c>
       <c r="P28" s="4" t="n">
-        <v>-0.9639479494589338</v>
+        <v>-0.7026213312852363</v>
       </c>
       <c r="Q28" s="4" t="n">
-        <v>-1.067428373245313</v>
+        <v>-0.7698891376483701</v>
       </c>
       <c r="R28" s="4" t="n">
-        <v>-1.122423634133234</v>
+        <v>-0.8180514816877746</v>
       </c>
       <c r="S28" s="4" t="n">
-        <v>-1.337215177624905</v>
+        <v>-1.101338300220753</v>
       </c>
       <c r="T28" s="4" t="n">
-        <v>-1.221678781034626</v>
+        <v>-1.01626505359927</v>
       </c>
       <c r="U28" s="4" t="n">
-        <v>-1.354586202511683</v>
+        <v>-1.047584402866725</v>
       </c>
       <c r="V28" s="4" t="n">
-        <v>-1.382769545901432</v>
+        <v>-1.145233482896074</v>
       </c>
       <c r="W28" s="4" t="n">
-        <v>-1.302687380062594</v>
+        <v>-0.9972691032146841</v>
       </c>
       <c r="X28" s="4" t="n">
-        <v>-1.29186033563613</v>
+        <v>-1.086233086475282</v>
       </c>
       <c r="Y28" s="4" t="n">
-        <v>-1.232465351721032</v>
+        <v>-0.9227662214015737</v>
       </c>
       <c r="Z28" s="4" t="n">
-        <v>-1.188063733865881</v>
+        <v>-0.9327994655805227</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>X &lt; 0.01379</t>
+          <t>X &lt; 0.01389</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>3075</v>
+        <v>3105</v>
       </c>
       <c r="C29" s="4" t="n">
-        <v>0.3791722601553786</v>
+        <v>0.3478631854340719</v>
       </c>
       <c r="D29" s="4" t="n">
-        <v>0.09414353007868215</v>
+        <v>0.1512486270887976</v>
       </c>
       <c r="E29" s="4" t="n">
-        <v>-0.1309289058854688</v>
+        <v>-0.02880921008285497</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>-0.08264093629946956</v>
+        <v>0.1015496226652175</v>
       </c>
       <c r="G29" s="4" t="n">
-        <v>-0.4003117980986204</v>
+        <v>-0.2202614255818673</v>
       </c>
       <c r="H29" s="4" t="n">
-        <v>-0.0981897013755173</v>
+        <v>0.05074880856856367</v>
       </c>
       <c r="I29" s="4" t="n">
-        <v>-0.2372761298257799</v>
+        <v>-0.1168692950317549</v>
       </c>
       <c r="J29" s="4" t="n">
-        <v>-0.4647399714006184</v>
+        <v>-0.339494338210649</v>
       </c>
       <c r="K29" s="4" t="n">
-        <v>-0.5990828829064512</v>
+        <v>-0.4181417487461019</v>
       </c>
       <c r="L29" s="4" t="n">
-        <v>-0.6412067806623298</v>
+        <v>-0.4758304831307782</v>
       </c>
       <c r="M29" s="4" t="n">
-        <v>-0.5753052845616935</v>
+        <v>-0.3962118409180917</v>
       </c>
       <c r="N29" s="4" t="n">
-        <v>-0.7383036689031641</v>
+        <v>-0.544382880461626</v>
       </c>
       <c r="O29" s="4" t="n">
-        <v>-0.79212030478066</v>
+        <v>-0.5677822210263557</v>
       </c>
       <c r="P29" s="4" t="n">
-        <v>-0.799781760996197</v>
+        <v>-0.5591944526039327</v>
       </c>
       <c r="Q29" s="4" t="n">
-        <v>-0.8876895985141502</v>
+        <v>-0.5803563302802743</v>
       </c>
       <c r="R29" s="4" t="n">
-        <v>-0.8903910987920085</v>
+        <v>-0.5783225811007782</v>
       </c>
       <c r="S29" s="4" t="n">
-        <v>-1.037747786103381</v>
+        <v>-0.7919612253641901</v>
       </c>
       <c r="T29" s="4" t="n">
-        <v>-0.9612947975128208</v>
+        <v>-0.7453780781606412</v>
       </c>
       <c r="U29" s="4" t="n">
-        <v>-1.245810182818055</v>
+        <v>-0.930111320673916</v>
       </c>
       <c r="V29" s="4" t="n">
-        <v>-1.332349642987488</v>
+        <v>-1.082812462012285</v>
       </c>
       <c r="W29" s="4" t="n">
-        <v>-1.20628847892732</v>
+        <v>-0.8916547734624132</v>
       </c>
       <c r="X29" s="4" t="n">
-        <v>-1.165578712254323</v>
+        <v>-0.9158053197195315</v>
       </c>
       <c r="Y29" s="4" t="n">
-        <v>-1.132079769916373</v>
+        <v>-0.8143005123323661</v>
       </c>
       <c r="Z29" s="4" t="n">
-        <v>-1.221402249069214</v>
+        <v>-0.9576301376066922</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>X &lt; 0.01539</t>
+          <t>X &lt; 0.01547</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>3142</v>
+        <v>3169</v>
       </c>
       <c r="C30" s="4" t="n">
-        <v>0.1348242925711887</v>
+        <v>0.1082664088370677</v>
       </c>
       <c r="D30" s="4" t="n">
-        <v>-0.1829564023001069</v>
+        <v>-0.1208219650683873</v>
       </c>
       <c r="E30" s="4" t="n">
-        <v>-0.5290397360261707</v>
+        <v>-0.417953285022449</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>-0.5604995735508993</v>
+        <v>-0.3972358870989581</v>
       </c>
       <c r="G30" s="4" t="n">
-        <v>-0.7205336090824375</v>
+        <v>-0.5613292032329937</v>
       </c>
       <c r="H30" s="4" t="n">
-        <v>-0.4209908869585774</v>
+        <v>-0.2928608016287058</v>
       </c>
       <c r="I30" s="4" t="n">
-        <v>-0.54214677870592</v>
+        <v>-0.4425860183835653</v>
       </c>
       <c r="J30" s="4" t="n">
-        <v>-0.6441374434805596</v>
+        <v>-0.5414427839051044</v>
       </c>
       <c r="K30" s="4" t="n">
-        <v>-0.6163716920530717</v>
+        <v>-0.4586559370326952</v>
       </c>
       <c r="L30" s="4" t="n">
-        <v>-0.8009896106366554</v>
+        <v>-0.6084888049712305</v>
       </c>
       <c r="M30" s="4" t="n">
-        <v>-0.6989565864529155</v>
+        <v>-0.4755452425407896</v>
       </c>
       <c r="N30" s="4" t="n">
-        <v>-0.9596070699069799</v>
+        <v>-0.702827008589864</v>
       </c>
       <c r="O30" s="4" t="n">
-        <v>-0.8911731670260679</v>
+        <v>-0.604499906358015</v>
       </c>
       <c r="P30" s="4" t="n">
-        <v>-0.9034025229934102</v>
+        <v>-0.6010825050669979</v>
       </c>
       <c r="Q30" s="4" t="n">
-        <v>-0.9082603435599808</v>
+        <v>-0.5726362670485088</v>
       </c>
       <c r="R30" s="4" t="n">
-        <v>-0.8982683982683923</v>
+        <v>-0.5593337053665977</v>
       </c>
       <c r="S30" s="4" t="n">
-        <v>-0.9818294131209271</v>
+        <v>-0.7077823257766624</v>
       </c>
       <c r="T30" s="4" t="n">
-        <v>-0.9409834000763126</v>
+        <v>-0.6962863361327294</v>
       </c>
       <c r="U30" s="4" t="n">
-        <v>-1.151286022516963</v>
+        <v>-0.8099428294966131</v>
       </c>
       <c r="V30" s="4" t="n">
-        <v>-1.263759577645232</v>
+        <v>-0.9867137552596148</v>
       </c>
       <c r="W30" s="4" t="n">
-        <v>-1.247309892497761</v>
+        <v>-0.9054092954136621</v>
       </c>
       <c r="X30" s="4" t="n">
-        <v>-1.113677179003844</v>
+        <v>-0.835986369884786</v>
       </c>
       <c r="Y30" s="4" t="n">
-        <v>-1.138658262713342</v>
+        <v>-0.7946783705938785</v>
       </c>
       <c r="Z30" s="4" t="n">
-        <v>-1.195868308179207</v>
+        <v>-0.9068259755069619</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>X &lt; 0.01699</t>
+          <t>X &lt; 0.01705</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>3207</v>
+        <v>3235</v>
       </c>
       <c r="C31" s="4" t="n">
-        <v>0.04336341288382073</v>
+        <v>0.04853349288387676</v>
       </c>
       <c r="D31" s="4" t="n">
-        <v>-0.2438183992391956</v>
+        <v>-0.1502160937499895</v>
       </c>
       <c r="E31" s="4" t="n">
-        <v>-0.4879924031919529</v>
+        <v>-0.3134979359763221</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>-0.5331665495148812</v>
+        <v>-0.366812660213192</v>
       </c>
       <c r="G31" s="4" t="n">
-        <v>-0.6347371118232488</v>
+        <v>-0.4409974698871153</v>
       </c>
       <c r="H31" s="4" t="n">
-        <v>-0.4924755302712995</v>
+        <v>-0.359234417060037</v>
       </c>
       <c r="I31" s="4" t="n">
-        <v>-0.5647396776429119</v>
+        <v>-0.4607755252393915</v>
       </c>
       <c r="J31" s="4" t="n">
-        <v>-0.6702912929597602</v>
+        <v>-0.5331248948597533</v>
       </c>
       <c r="K31" s="4" t="n">
-        <v>-0.6112202221243805</v>
+        <v>-0.4186356368804454</v>
       </c>
       <c r="L31" s="4" t="n">
-        <v>-0.8077084302964437</v>
+        <v>-0.6125610341288095</v>
       </c>
       <c r="M31" s="4" t="n">
-        <v>-0.6090372038304324</v>
+        <v>-0.3535927010498199</v>
       </c>
       <c r="N31" s="4" t="n">
-        <v>-0.8078941210890918</v>
+        <v>-0.5202588711896894</v>
       </c>
       <c r="O31" s="4" t="n">
-        <v>-0.7634819786445064</v>
+        <v>-0.446917326438232</v>
       </c>
       <c r="P31" s="4" t="n">
-        <v>-0.8109763416503242</v>
+        <v>-0.4615012488356953</v>
       </c>
       <c r="Q31" s="4" t="n">
-        <v>-0.7668202100479249</v>
+        <v>-0.3858170514020927</v>
       </c>
       <c r="R31" s="4" t="n">
-        <v>-0.7760733305056746</v>
+        <v>-0.3921398627122414</v>
       </c>
       <c r="S31" s="4" t="n">
-        <v>-0.8917286057410294</v>
+        <v>-0.5704747583796035</v>
       </c>
       <c r="T31" s="4" t="n">
-        <v>-0.8538018381955865</v>
+        <v>-0.5618765714785781</v>
       </c>
       <c r="U31" s="4" t="n">
-        <v>-0.9620528442661893</v>
+        <v>-0.576215087892372</v>
       </c>
       <c r="V31" s="4" t="n">
-        <v>-1.099551316270976</v>
+        <v>-0.7758130237770615</v>
       </c>
       <c r="W31" s="4" t="n">
-        <v>-1.063217058597331</v>
+        <v>-0.6767835888568356</v>
       </c>
       <c r="X31" s="4" t="n">
-        <v>-1.027257146921684</v>
+        <v>-0.702916429107205</v>
       </c>
       <c r="Y31" s="4" t="n">
-        <v>-0.9526275551995909</v>
+        <v>-0.56473370237007</v>
       </c>
       <c r="Z31" s="4" t="n">
-        <v>-0.9477934512412958</v>
+        <v>-0.6160063419139448</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>X &lt; 0.01859</t>
+          <t>X &lt; 0.01863</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>3250</v>
+        <v>3276</v>
       </c>
       <c r="C32" s="4" t="n">
-        <v>-0.08142151001002418</v>
+        <v>-0.04156580055679626</v>
       </c>
       <c r="D32" s="4" t="n">
-        <v>-0.1553305132487779</v>
+        <v>-0.05900051348093172</v>
       </c>
       <c r="E32" s="4" t="n">
-        <v>-0.4763149265724778</v>
+        <v>-0.3571494127488108</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>-0.5608477447815119</v>
+        <v>-0.3565036509220363</v>
       </c>
       <c r="G32" s="4" t="n">
-        <v>-0.543146094589261</v>
+        <v>-0.3724930122008558</v>
       </c>
       <c r="H32" s="4" t="n">
-        <v>-0.4308680231313602</v>
+        <v>-0.2897735242985888</v>
       </c>
       <c r="I32" s="4" t="n">
-        <v>-0.4204951419027623</v>
+        <v>-0.3088262377538058</v>
       </c>
       <c r="J32" s="4" t="n">
-        <v>-0.5588943163531184</v>
+        <v>-0.4447793329931855</v>
       </c>
       <c r="K32" s="4" t="n">
-        <v>-0.4693928351799244</v>
+        <v>-0.2997098953475898</v>
       </c>
       <c r="L32" s="4" t="n">
-        <v>-0.642794203196118</v>
+        <v>-0.4707077072692911</v>
       </c>
       <c r="M32" s="4" t="n">
-        <v>-0.4124323190218391</v>
+        <v>-0.211530864835062</v>
       </c>
       <c r="N32" s="4" t="n">
-        <v>-0.6122821155022535</v>
+        <v>-0.3795244331870364</v>
       </c>
       <c r="O32" s="4" t="n">
-        <v>-0.5832057838501612</v>
+        <v>-0.320961362944935</v>
       </c>
       <c r="P32" s="4" t="n">
-        <v>-0.6636093057158376</v>
+        <v>-0.3688543844711205</v>
       </c>
       <c r="Q32" s="4" t="n">
-        <v>-0.5979899978074954</v>
+        <v>-0.2721591474295195</v>
       </c>
       <c r="R32" s="4" t="n">
-        <v>-0.5992242870695819</v>
+        <v>-0.2713606560784925</v>
       </c>
       <c r="S32" s="4" t="n">
-        <v>-0.7150663633523706</v>
+        <v>-0.4487289318712513</v>
       </c>
       <c r="T32" s="4" t="n">
-        <v>-0.740395842436655</v>
+        <v>-0.5027995530592264</v>
       </c>
       <c r="U32" s="4" t="n">
-        <v>-0.7828860102164654</v>
+        <v>-0.4533039007731148</v>
       </c>
       <c r="V32" s="4" t="n">
-        <v>-0.8853119650242931</v>
+        <v>-0.6171992540950555</v>
       </c>
       <c r="W32" s="4" t="n">
-        <v>-0.9487863820974312</v>
+        <v>-0.6179462197904684</v>
       </c>
       <c r="X32" s="4" t="n">
-        <v>-0.9450199580804934</v>
+        <v>-0.6751807621704344</v>
       </c>
       <c r="Y32" s="4" t="n">
-        <v>-0.8677217790371117</v>
+        <v>-0.535670217988347</v>
       </c>
       <c r="Z32" s="4" t="n">
-        <v>-0.8023903666427046</v>
+        <v>-0.5272714463784283</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>X &lt; 0.02019</t>
+          <t>X &lt; 0.02021</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>3284</v>
+        <v>3310</v>
       </c>
       <c r="C33" s="4" t="n">
-        <v>-0.05753897917131212</v>
+        <v>-0.01727419285707299</v>
       </c>
       <c r="D33" s="4" t="n">
-        <v>-0.1341236093014402</v>
+        <v>-0.00702095877245057</v>
       </c>
       <c r="E33" s="4" t="n">
-        <v>-0.3455642921289552</v>
+        <v>-0.1948337899930479</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>-0.3759916533790033</v>
+        <v>-0.1701643990488009</v>
       </c>
       <c r="G33" s="4" t="n">
-        <v>-0.4829747976408143</v>
+        <v>-0.2788659859893912</v>
       </c>
       <c r="H33" s="4" t="n">
-        <v>-0.3396247797278207</v>
+        <v>-0.1653120909232086</v>
       </c>
       <c r="I33" s="4" t="n">
-        <v>-0.4281636494748895</v>
+        <v>-0.2824292873135263</v>
       </c>
       <c r="J33" s="4" t="n">
-        <v>-0.5073995771670141</v>
+        <v>-0.3599694219056815</v>
       </c>
       <c r="K33" s="4" t="n">
-        <v>-0.3880651137069435</v>
+        <v>-0.1849745611141032</v>
       </c>
       <c r="L33" s="4" t="n">
-        <v>-0.5676223818902741</v>
+        <v>-0.3623313050147132</v>
       </c>
       <c r="M33" s="4" t="n">
-        <v>-0.4277788793984811</v>
+        <v>-0.1932681086063468</v>
       </c>
       <c r="N33" s="4" t="n">
-        <v>-0.5070880002712599</v>
+        <v>-0.2419581677385167</v>
       </c>
       <c r="O33" s="4" t="n">
-        <v>-0.5202183185232769</v>
+        <v>-0.2254787801571041</v>
       </c>
       <c r="P33" s="4" t="n">
-        <v>-0.571696513913686</v>
+        <v>-0.2452742452899201</v>
       </c>
       <c r="Q33" s="4" t="n">
-        <v>-0.5438895399849315</v>
+        <v>-0.1866499051764023</v>
       </c>
       <c r="R33" s="4" t="n">
-        <v>-0.5085791082145903</v>
+        <v>-0.149943427937437</v>
       </c>
       <c r="S33" s="4" t="n">
-        <v>-0.5638085764404721</v>
+        <v>-0.2662263842829873</v>
       </c>
       <c r="T33" s="4" t="n">
-        <v>-0.5899137770609784</v>
+        <v>-0.3210500681692494</v>
       </c>
       <c r="U33" s="4" t="n">
-        <v>-0.6600915536211645</v>
+        <v>-0.2999735371410139</v>
       </c>
       <c r="V33" s="4" t="n">
-        <v>-0.7290752838368419</v>
+        <v>-0.4297645719630836</v>
       </c>
       <c r="W33" s="4" t="n">
-        <v>-0.7670347032979308</v>
+        <v>-0.4060866301822372</v>
       </c>
       <c r="X33" s="4" t="n">
-        <v>-0.7944688481871651</v>
+        <v>-0.4936344852783705</v>
       </c>
       <c r="Y33" s="4" t="n">
-        <v>-0.7759668477596691</v>
+        <v>-0.4134045933843709</v>
       </c>
       <c r="Z33" s="4" t="n">
-        <v>-0.651167655127658</v>
+        <v>-0.3462976702384921</v>
       </c>
     </row>
     <row r="34">
@@ -8124,161 +8124,161 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>3316</v>
+        <v>3341</v>
       </c>
       <c r="C34" s="4" t="n">
-        <v>-0.09188035691803975</v>
+        <v>-0.06462434998931599</v>
       </c>
       <c r="D34" s="4" t="n">
-        <v>-0.1409923959040071</v>
+        <v>-0.02701111362119235</v>
       </c>
       <c r="E34" s="4" t="n">
-        <v>-0.3042632784633597</v>
+        <v>-0.1651788852182392</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>-0.3712012968022762</v>
+        <v>-0.1759452468409606</v>
       </c>
       <c r="G34" s="4" t="n">
-        <v>-0.4803784573005316</v>
+        <v>-0.2861880046136065</v>
       </c>
       <c r="H34" s="4" t="n">
-        <v>-0.3965970315524388</v>
+        <v>-0.2317774709584839</v>
       </c>
       <c r="I34" s="4" t="n">
-        <v>-0.4917143850392094</v>
+        <v>-0.3551732184718261</v>
       </c>
       <c r="J34" s="4" t="n">
-        <v>-0.6028923197185847</v>
+        <v>-0.4646232528270176</v>
       </c>
       <c r="K34" s="4" t="n">
-        <v>-0.5443764109724114</v>
+        <v>-0.3496890887920614</v>
       </c>
       <c r="L34" s="4" t="n">
-        <v>-0.6996525321132694</v>
+        <v>-0.5030053712376912</v>
       </c>
       <c r="M34" s="4" t="n">
-        <v>-0.5585585380867073</v>
+        <v>-0.3330305313296691</v>
       </c>
       <c r="N34" s="4" t="n">
-        <v>-0.6698727276797669</v>
+        <v>-0.41369327497668</v>
       </c>
       <c r="O34" s="4" t="n">
-        <v>-0.6336143476098073</v>
+        <v>-0.3480624111909734</v>
       </c>
       <c r="P34" s="4" t="n">
-        <v>-0.6566922476974071</v>
+        <v>-0.3401658978446349</v>
       </c>
       <c r="Q34" s="4" t="n">
-        <v>-0.6655876510384573</v>
+        <v>-0.3182755971444138</v>
       </c>
       <c r="R34" s="4" t="n">
-        <v>-0.6550158625970965</v>
+        <v>-0.306612148243147</v>
       </c>
       <c r="S34" s="4" t="n">
-        <v>-0.6207672815164571</v>
+        <v>-0.3332213261648747</v>
       </c>
       <c r="T34" s="4" t="n">
-        <v>-0.6476480675696692</v>
+        <v>-0.3887880240939765</v>
       </c>
       <c r="U34" s="4" t="n">
-        <v>-0.6548639414653081</v>
+        <v>-0.3061671958082144</v>
       </c>
       <c r="V34" s="4" t="n">
-        <v>-0.6912597882779679</v>
+        <v>-0.4028731758566977</v>
       </c>
       <c r="W34" s="4" t="n">
-        <v>-0.6738136519862863</v>
+        <v>-0.3248584829819166</v>
       </c>
       <c r="X34" s="4" t="n">
-        <v>-0.7318252402382015</v>
+        <v>-0.44218044113682</v>
       </c>
       <c r="Y34" s="4" t="n">
-        <v>-0.7108349159054512</v>
+        <v>-0.3604194312179629</v>
       </c>
       <c r="Z34" s="4" t="n">
-        <v>-0.6784226576327725</v>
+        <v>-0.3852172187210883</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>X &lt; 0.02339</t>
+          <t>X &lt; 0.02337</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>3336</v>
+        <v>3360</v>
       </c>
       <c r="C35" s="4" t="n">
-        <v>-0.05346991783804356</v>
+        <v>-0.03981856967134689</v>
       </c>
       <c r="D35" s="4" t="n">
-        <v>-0.1042719165465229</v>
+        <v>-0.003790808048641736</v>
       </c>
       <c r="E35" s="4" t="n">
-        <v>-0.2751264281943619</v>
+        <v>-0.1482261868536341</v>
       </c>
       <c r="F35" s="4" t="n">
-        <v>-0.3161083032590852</v>
+        <v>-0.1326712846326146</v>
       </c>
       <c r="G35" s="4" t="n">
-        <v>-0.4266199416254395</v>
+        <v>-0.2438307983395589</v>
       </c>
       <c r="H35" s="4" t="n">
-        <v>-0.3720223400506626</v>
+        <v>-0.1888310712028556</v>
       </c>
       <c r="I35" s="4" t="n">
-        <v>-0.4115214567096857</v>
+        <v>-0.2567690433623042</v>
       </c>
       <c r="J35" s="4" t="n">
-        <v>-0.4938391519120771</v>
+        <v>-0.3376691765317474</v>
       </c>
       <c r="K35" s="4" t="n">
-        <v>-0.4950760099127933</v>
+        <v>-0.2818835001283091</v>
       </c>
       <c r="L35" s="4" t="n">
-        <v>-0.6241740685751012</v>
+        <v>-0.4091607083161009</v>
       </c>
       <c r="M35" s="4" t="n">
-        <v>-0.4822634751379056</v>
+        <v>-0.238582017835256</v>
       </c>
       <c r="N35" s="4" t="n">
-        <v>-0.5945550868379357</v>
+        <v>-0.3203206857088716</v>
       </c>
       <c r="O35" s="4" t="n">
-        <v>-0.595079823379173</v>
+        <v>-0.290980704170039</v>
       </c>
       <c r="P35" s="4" t="n">
-        <v>-0.679102578518453</v>
+        <v>-0.3438584932610311</v>
       </c>
       <c r="Q35" s="4" t="n">
-        <v>-0.6918865822229208</v>
+        <v>-0.3259398582077466</v>
       </c>
       <c r="R35" s="4" t="n">
-        <v>-0.6778309409888408</v>
+        <v>-0.3111779809907489</v>
       </c>
       <c r="S35" s="4" t="n">
-        <v>-0.6445952613259536</v>
+        <v>-0.3382245569745663</v>
       </c>
       <c r="T35" s="4" t="n">
-        <v>-0.6719497237212408</v>
+        <v>-0.394229173491965</v>
       </c>
       <c r="U35" s="4" t="n">
-        <v>-0.6778372996700668</v>
+        <v>-0.3108655382436609</v>
       </c>
       <c r="V35" s="4" t="n">
-        <v>-0.7129032483457891</v>
+        <v>-0.4058147234839993</v>
       </c>
       <c r="W35" s="4" t="n">
-        <v>-0.6988178456705327</v>
+        <v>-0.3314475674033019</v>
       </c>
       <c r="X35" s="4" t="n">
-        <v>-0.7569437813331064</v>
+        <v>-0.4485332256761723</v>
       </c>
       <c r="Y35" s="4" t="n">
-        <v>-0.7344417491124631</v>
+        <v>-0.3658590222889018</v>
       </c>
       <c r="Z35" s="4" t="n">
-        <v>-0.7026855151392866</v>
+        <v>-0.3914350605420438</v>
       </c>
     </row>
   </sheetData>
